--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5047,7 +5047,7 @@
         <v>1.108</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.71</v>
+        <v>0.73</v>
       </c>
       <c r="R2" t="inlineStr">
         <is>
@@ -5093,7 +5093,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>2026-09-06 05:34:38</t>
+          <t>2026-09-06 05:41:38</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -4848,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AB2"/>
+  <dimension ref="A1:AF2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4969,25 +4969,45 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
+          <t>book_value</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>price_to_book</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>earnings_growth</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>shares_outstanding</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="Y1" t="inlineStr">
+      <c r="AC1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="Z1" t="inlineStr">
+      <c r="AD1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AA1" t="inlineStr">
+      <c r="AE1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AB1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5029,13 +5049,13 @@
         <v>3710545297408</v>
       </c>
       <c r="K2" t="n">
-        <v>28.408188</v>
+        <v>27.853958</v>
       </c>
       <c r="L2" t="n">
         <v>21.19773</v>
       </c>
       <c r="M2" t="n">
-        <v>17.59</v>
+        <v>17.94</v>
       </c>
       <c r="N2" t="n">
         <v>553.72</v>
@@ -5071,29 +5091,41 @@
       <c r="W2" t="n">
         <v>1.23</v>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="X2" t="n">
+        <v>59.565</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>8.389155000000001</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0.317</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>7425545491</v>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
         <is>
           <t>Software - Infrastructure</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>https://www.microsoft.com</t>
         </is>
       </c>
-      <c r="AA2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Microsoft Corporation, a technology company, develops and supports a portfolio of technology solutions for individuals and businesses worldwide. Its products include operating systems, server applications, business solution applications, software development tools, desktop and server management tools, and video games; and devices, such as PCs, tablets, gaming and entertainment consoles, other intelligent devices, and related accessories. The company's Productivity and Business Processes segment offers Microsoft 365 Commercial, Enterprise Mobility + Security, Power BI, Exchange, SharePoint, Microsoft Teams, Microsoft 365 Security and Compliance, Microsoft 365 Copilot, and Windows Commercial on-premises and Office licensed on-premises. This segment also provides Microsoft 365 Consumer products and cloud services; LinkedIn, including talent solutions, marketing solutions, subscriptions, and sales solutions; Dynamics 365, a set of cloud-based applications; and on-premises ERP and CRM applications. Its Intelligent Cloud segment offers server products and cloud services; cloud and AI consumption-based services, GitHub cloud services, health and life sciences cloud services, as well as virtual desktop offerings, and other cloud services; SQL Server, Windows Server, Visual Studio, System Center, and related client access licenses; and enterprise support services, industry solutions, Microsoft partner network, and learning experience. The company's More Personal Computing segment provides Windows OEM licensing and devices comprising Surface and PC accessories; XBOX hardware, and XBOX first- and third-party content and services; XBOX Game Pass and other subscriptions; XBOX Cloud Gaming, advertising, and other cloud services; and search advertising consisting of Bing, Copilot, Microsoft News, Microsoft Edge, and third-party affiliates. It sells its products through partners and retail networks. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2026-09-06 05:41:38</t>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>2026-09-06 16:09:41</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:09:41</t>
+          <t>2026-09-06 16:24:18</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:24:18</t>
+          <t>2026-09-06 16:34:12</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5125,7 +5125,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:34:12</t>
+          <t>2026-09-06 16:48:46</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5069,15 +5069,11 @@
       <c r="Q2" t="n">
         <v>0.73</v>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>N/A</t>
-        </is>
+      <c r="R2" t="n">
+        <v>0.40305</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.45111</v>
       </c>
       <c r="T2" t="n">
         <v>0.34039003</v>
@@ -5125,7 +5121,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>2026-09-06 16:48:46</t>
+          <t>2026-09-06 16:59:16</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -4848,7 +4848,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:AI2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4989,25 +4989,40 @@
       </c>
       <c r="AB1" t="inlineStr">
         <is>
+          <t>total_revenue</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>enterprise_value</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>ebitda</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
           <t>sector</t>
         </is>
       </c>
-      <c r="AC1" t="inlineStr">
+      <c r="AF1" t="inlineStr">
         <is>
           <t>industry</t>
         </is>
       </c>
-      <c r="AD1" t="inlineStr">
+      <c r="AG1" t="inlineStr">
         <is>
           <t>website</t>
         </is>
       </c>
-      <c r="AE1" t="inlineStr">
+      <c r="AH1" t="inlineStr">
         <is>
           <t>description</t>
         </is>
       </c>
-      <c r="AF1" t="inlineStr">
+      <c r="AI1" t="inlineStr">
         <is>
           <t>last_updated</t>
         </is>
@@ -5099,29 +5114,38 @@
       <c r="AA2" t="n">
         <v>7425545491</v>
       </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AB2" t="n">
+        <v>331839012864</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>3762515083264</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>194237005824</v>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>Technology</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>Software - Infrastructure</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AG2" t="inlineStr">
         <is>
           <t>https://www.microsoft.com</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AH2" t="inlineStr">
         <is>
           <t>Microsoft Corporation, a technology company, develops and supports a portfolio of technology solutions for individuals and businesses worldwide. Its products include operating systems, server applications, business solution applications, software development tools, desktop and server management tools, and video games; and devices, such as PCs, tablets, gaming and entertainment consoles, other intelligent devices, and related accessories. The company's Productivity and Business Processes segment offers Microsoft 365 Commercial, Enterprise Mobility + Security, Power BI, Exchange, SharePoint, Microsoft Teams, Microsoft 365 Security and Compliance, Microsoft 365 Copilot, and Windows Commercial on-premises and Office licensed on-premises. This segment also provides Microsoft 365 Consumer products and cloud services; LinkedIn, including talent solutions, marketing solutions, subscriptions, and sales solutions; Dynamics 365, a set of cloud-based applications; and on-premises ERP and CRM applications. Its Intelligent Cloud segment offers server products and cloud services; cloud and AI consumption-based services, GitHub cloud services, health and life sciences cloud services, as well as virtual desktop offerings, and other cloud services; SQL Server, Windows Server, Visual Studio, System Center, and related client access licenses; and enterprise support services, industry solutions, Microsoft partner network, and learning experience. The company's More Personal Computing segment provides Windows OEM licensing and devices comprising Surface and PC accessories; XBOX hardware, and XBOX first- and third-party content and services; XBOX Game Pass and other subscriptions; XBOX Cloud Gaming, advertising, and other cloud services; and search advertising consisting of Bing, Copilot, Microsoft News, Microsoft Edge, and third-party affiliates. It sells its products through partners and retail networks. The company was founded in 1975 and is headquartered in Redmond, Washington.</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>2026-09-06 16:59:16</t>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2026-09-06 22:20:21</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:20:21</t>
+          <t>2026-09-06 22:41:16</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -5145,7 +5145,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:41:16</t>
+          <t>2026-09-06 22:59:11</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H24"/>
+  <dimension ref="A1:H253"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>46239</v>
+        <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>495.4273384327132</v>
+        <v>504.9157608525771</v>
       </c>
       <c r="C2" t="n">
-        <v>497.3038108374591</v>
+        <v>507.7920894589463</v>
       </c>
       <c r="D2" t="n">
-        <v>484.7674131728324</v>
+        <v>488.3520284612672</v>
       </c>
       <c r="E2" t="n">
-        <v>486.5440673828125</v>
+        <v>490.9605712890625</v>
       </c>
       <c r="F2" t="n">
-        <v>33388900</v>
+        <v>31994800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>46240</v>
+        <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>487.6319998350186</v>
+        <v>494.0451377441344</v>
       </c>
       <c r="C3" t="n">
-        <v>500.6175637248969</v>
+        <v>497.1099483047291</v>
       </c>
       <c r="D3" t="n">
-        <v>487.6020574235835</v>
+        <v>490.990285532587</v>
       </c>
       <c r="E3" t="n">
-        <v>498.9207458496094</v>
+        <v>494.1344299316406</v>
       </c>
       <c r="F3" t="n">
-        <v>36441500</v>
+        <v>16771000</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>46241</v>
+        <v>45909</v>
       </c>
       <c r="B4" t="n">
-        <v>498.2719734340298</v>
+        <v>497.3380566961471</v>
       </c>
       <c r="C4" t="n">
-        <v>504.2307569931746</v>
+        <v>498.1513723235736</v>
       </c>
       <c r="D4" t="n">
-        <v>497.7928948509335</v>
+        <v>493.6385148559323</v>
       </c>
       <c r="E4" t="n">
-        <v>499.0505065917969</v>
+        <v>494.3427124023438</v>
       </c>
       <c r="F4" t="n">
-        <v>28846200</v>
+        <v>14410500</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>46244</v>
+        <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>502.4940586092805</v>
+        <v>498.8754600894228</v>
       </c>
       <c r="C5" t="n">
-        <v>512.7647021753171</v>
+        <v>499.1234199731124</v>
       </c>
       <c r="D5" t="n">
-        <v>501.326243590453</v>
+        <v>492.6665349159027</v>
       </c>
       <c r="E5" t="n">
-        <v>505.109130859375</v>
+        <v>496.2867431640625</v>
       </c>
       <c r="F5" t="n">
-        <v>31206100</v>
+        <v>21611800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>46245</v>
+        <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>503.3823542433026</v>
+        <v>498.1513800613702</v>
       </c>
       <c r="C6" t="n">
-        <v>504.3804752506704</v>
+        <v>499.0638857033828</v>
       </c>
       <c r="D6" t="n">
-        <v>498.6113370464939</v>
+        <v>493.8170463660224</v>
       </c>
       <c r="E6" t="n">
-        <v>502.8633422851562</v>
+        <v>496.9215087890625</v>
       </c>
       <c r="F6" t="n">
-        <v>23049800</v>
+        <v>18881600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>46246</v>
+        <v>45912</v>
       </c>
       <c r="B7" t="n">
-        <v>499.0505227551261</v>
+        <v>502.5154742767582</v>
       </c>
       <c r="C7" t="n">
-        <v>500.557695253814</v>
+        <v>508.367321245748</v>
       </c>
       <c r="D7" t="n">
-        <v>490.5964364344239</v>
+        <v>499.738335797131</v>
       </c>
       <c r="E7" t="n">
-        <v>491.5047302246094</v>
+        <v>505.7389526367188</v>
       </c>
       <c r="F7" t="n">
-        <v>29001500</v>
+        <v>23624900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>46247</v>
+        <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>492.3431478695614</v>
+        <v>504.6379958107742</v>
       </c>
       <c r="C8" t="n">
-        <v>500.3979918654044</v>
+        <v>511.2634457193681</v>
       </c>
       <c r="D8" t="n">
-        <v>492.0836571155829</v>
+        <v>502.8625947427051</v>
       </c>
       <c r="E8" t="n">
-        <v>495.9463806152344</v>
+        <v>511.1543579101562</v>
       </c>
       <c r="F8" t="n">
-        <v>23039000</v>
+        <v>17143800</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>46248</v>
+        <v>45916</v>
       </c>
       <c r="B9" t="n">
-        <v>495.427334377905</v>
+        <v>512.6619733694059</v>
       </c>
       <c r="C9" t="n">
-        <v>499.0705004655026</v>
+        <v>513.0090929577493</v>
       </c>
       <c r="D9" t="n">
-        <v>492.991947114923</v>
+        <v>504.449544036503</v>
       </c>
       <c r="E9" t="n">
-        <v>494.4691467285156</v>
+        <v>504.8859558105469</v>
       </c>
       <c r="F9" t="n">
-        <v>16217600</v>
+        <v>19711900</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>46251</v>
+        <v>45917</v>
       </c>
       <c r="B10" t="n">
-        <v>489.2190622628328</v>
+        <v>506.4530503919847</v>
       </c>
       <c r="C10" t="n">
-        <v>491.7343163235842</v>
+        <v>507.1175961354426</v>
       </c>
       <c r="D10" t="n">
-        <v>477.5110914717105</v>
+        <v>501.8013209933916</v>
       </c>
       <c r="E10" t="n">
-        <v>479.4474487304688</v>
+        <v>505.8579406738281</v>
       </c>
       <c r="F10" t="n">
-        <v>29635800</v>
+        <v>15816600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>46252</v>
+        <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>480.6352093836093</v>
+        <v>507.3159513893766</v>
       </c>
       <c r="C11" t="n">
-        <v>483.3600603013466</v>
+        <v>508.883074673213</v>
       </c>
       <c r="D11" t="n">
-        <v>476.2534434403709</v>
+        <v>503.5172196080818</v>
       </c>
       <c r="E11" t="n">
-        <v>480.7250366210938</v>
+        <v>504.30078125</v>
       </c>
       <c r="F11" t="n">
-        <v>24087600</v>
+        <v>18913700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>46253</v>
+        <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>479.1679704739861</v>
+        <v>506.3935778296786</v>
       </c>
       <c r="C12" t="n">
-        <v>488.3806080919379</v>
+        <v>515.0622454615835</v>
       </c>
       <c r="D12" t="n">
-        <v>478.4592826108848</v>
+        <v>506.1456179521661</v>
       </c>
       <c r="E12" t="n">
-        <v>483.3999938964844</v>
+        <v>513.7034301757812</v>
       </c>
       <c r="F12" t="n">
-        <v>19961900</v>
+        <v>52474100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,25 +755,25 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>46254</v>
+        <v>45922</v>
       </c>
       <c r="B13" t="n">
-        <v>483.2999877929688</v>
+        <v>511.382573172581</v>
       </c>
       <c r="C13" t="n">
-        <v>484.1600036621094</v>
+        <v>513.5149918534414</v>
       </c>
       <c r="D13" t="n">
-        <v>479.5</v>
+        <v>508.3574141571104</v>
       </c>
       <c r="E13" t="n">
-        <v>481.1499938964844</v>
+        <v>510.2518615722656</v>
       </c>
       <c r="F13" t="n">
-        <v>20020800</v>
+        <v>20009300</v>
       </c>
       <c r="G13" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>46255</v>
+        <v>45923</v>
       </c>
       <c r="B14" t="n">
-        <v>479.8800048828125</v>
+        <v>509.6071158201621</v>
       </c>
       <c r="C14" t="n">
-        <v>486.3599853515625</v>
+        <v>510.3907077578639</v>
       </c>
       <c r="D14" t="n">
-        <v>478.5299987792969</v>
+        <v>503.170087241692</v>
       </c>
       <c r="E14" t="n">
-        <v>483.239990234375</v>
+        <v>505.0744323730469</v>
       </c>
       <c r="F14" t="n">
-        <v>22510800</v>
+        <v>19799600</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>46258</v>
+        <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>483.2099914550781</v>
+        <v>506.2150114062044</v>
       </c>
       <c r="C15" t="n">
-        <v>490.6099853515625</v>
+        <v>508.297849987297</v>
       </c>
       <c r="D15" t="n">
-        <v>481.8599853515625</v>
+        <v>502.7832554652563</v>
       </c>
       <c r="E15" t="n">
-        <v>487.3099975585938</v>
+        <v>505.9868774414062</v>
       </c>
       <c r="F15" t="n">
-        <v>17230800</v>
+        <v>13533700</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>46259</v>
+        <v>45925</v>
       </c>
       <c r="B16" t="n">
-        <v>485.4400024414062</v>
+        <v>504.1519897302721</v>
       </c>
       <c r="C16" t="n">
-        <v>492.4400024414062</v>
+        <v>505.8480570147519</v>
       </c>
       <c r="D16" t="n">
-        <v>484.2999877929688</v>
+        <v>500.9186136455738</v>
       </c>
       <c r="E16" t="n">
-        <v>491.7099914550781</v>
+        <v>502.8923645019531</v>
       </c>
       <c r="F16" t="n">
-        <v>19519000</v>
+        <v>15786500</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>46260</v>
+        <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>487.8500061035156</v>
+        <v>505.8976246789574</v>
       </c>
       <c r="C17" t="n">
-        <v>497.3999938964844</v>
+        <v>509.7459665668783</v>
       </c>
       <c r="D17" t="n">
-        <v>487.3099975585938</v>
+        <v>502.4856945681329</v>
       </c>
       <c r="E17" t="n">
-        <v>496.3699951171875</v>
+        <v>507.2861938476562</v>
       </c>
       <c r="F17" t="n">
-        <v>20758900</v>
+        <v>16213100</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>46261</v>
+        <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>494.8800048828125</v>
+        <v>507.3258652143003</v>
       </c>
       <c r="C18" t="n">
-        <v>506.4800109863281</v>
+        <v>512.6321819161793</v>
       </c>
       <c r="D18" t="n">
-        <v>490.0799865722656</v>
+        <v>504.7272507672145</v>
       </c>
       <c r="E18" t="n">
-        <v>505.0599975585938</v>
+        <v>510.4005432128906</v>
       </c>
       <c r="F18" t="n">
-        <v>28688800</v>
+        <v>17617800</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>46262</v>
+        <v>45930</v>
       </c>
       <c r="B19" t="n">
-        <v>505.3299865722656</v>
+        <v>509.0516808953516</v>
       </c>
       <c r="C19" t="n">
-        <v>517.780029296875</v>
+        <v>513.9315141469417</v>
       </c>
       <c r="D19" t="n">
-        <v>504.8699951171875</v>
+        <v>505.5009089039439</v>
       </c>
       <c r="E19" t="n">
-        <v>513.530029296875</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="F19" t="n">
-        <v>29207300</v>
+        <v>19728200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>46265</v>
+        <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>510.3800048828125</v>
+        <v>510.5989067561486</v>
       </c>
       <c r="C20" t="n">
-        <v>512.1900024414062</v>
+        <v>516.2623314762835</v>
       </c>
       <c r="D20" t="n">
-        <v>506.3900146484375</v>
+        <v>507.5143007767599</v>
       </c>
       <c r="E20" t="n">
-        <v>507.2900085449219</v>
+        <v>515.4688720703125</v>
       </c>
       <c r="F20" t="n">
-        <v>27208900</v>
+        <v>22632300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>46266</v>
+        <v>45932</v>
       </c>
       <c r="B21" t="n">
-        <v>497.5199890136719</v>
+        <v>513.4157691025699</v>
       </c>
       <c r="C21" t="n">
-        <v>505.9700012207031</v>
+        <v>517.3434144406598</v>
       </c>
       <c r="D21" t="n">
-        <v>496.7799987792969</v>
+        <v>506.5125449836057</v>
       </c>
       <c r="E21" t="n">
-        <v>501.0199890136719</v>
+        <v>511.53125</v>
       </c>
       <c r="F21" t="n">
-        <v>21046900</v>
+        <v>21222900</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>46267</v>
+        <v>45933</v>
       </c>
       <c r="B22" t="n">
-        <v>499.8500061035156</v>
+        <v>512.8800919259904</v>
       </c>
       <c r="C22" t="n">
-        <v>500.2699890136719</v>
+        <v>516.2424417743944</v>
       </c>
       <c r="D22" t="n">
-        <v>493.8099975585938</v>
+        <v>510.7972535535121</v>
       </c>
       <c r="E22" t="n">
-        <v>496.8200073242188</v>
+        <v>513.1280517578125</v>
       </c>
       <c r="F22" t="n">
-        <v>15336100</v>
+        <v>15112300</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>46268</v>
+        <v>45936</v>
       </c>
       <c r="B23" t="n">
-        <v>501.6600036621094</v>
+        <v>514.377848960065</v>
       </c>
       <c r="C23" t="n">
-        <v>515.6500244140625</v>
+        <v>526.6965386672223</v>
       </c>
       <c r="D23" t="n">
-        <v>500.7999877929688</v>
+        <v>513.9712214168786</v>
       </c>
       <c r="E23" t="n">
-        <v>510.1199951171875</v>
+        <v>524.256591796875</v>
       </c>
       <c r="F23" t="n">
-        <v>24125900</v>
+        <v>21388600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,27 +1041,5981 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
+        <v>45937</v>
+      </c>
+      <c r="B24" t="n">
+        <v>523.9788663400786</v>
+      </c>
+      <c r="C24" t="n">
+        <v>525.4765536672338</v>
+      </c>
+      <c r="D24" t="n">
+        <v>517.1847899970462</v>
+      </c>
+      <c r="E24" t="n">
+        <v>519.7040405273438</v>
+      </c>
+      <c r="F24" t="n">
+        <v>14615200</v>
+      </c>
+      <c r="G24" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="1" t="n">
+        <v>45938</v>
+      </c>
+      <c r="B25" t="n">
+        <v>519.0097599169904</v>
+      </c>
+      <c r="C25" t="n">
+        <v>522.6497936321297</v>
+      </c>
+      <c r="D25" t="n">
+        <v>518.8213080060119</v>
+      </c>
+      <c r="E25" t="n">
+        <v>520.56689453125</v>
+      </c>
+      <c r="F25" t="n">
+        <v>13363400</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="1" t="n">
+        <v>45939</v>
+      </c>
+      <c r="B26" t="n">
+        <v>518.0773939158137</v>
+      </c>
+      <c r="C26" t="n">
+        <v>520.0511445409561</v>
+      </c>
+      <c r="D26" t="n">
+        <v>513.1777050939771</v>
+      </c>
+      <c r="E26" t="n">
+        <v>518.1369018554688</v>
+      </c>
+      <c r="F26" t="n">
+        <v>18343600</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="n">
+        <v>45940</v>
+      </c>
+      <c r="B27" t="n">
+        <v>515.3994727403434</v>
+      </c>
+      <c r="C27" t="n">
+        <v>519.3073226434543</v>
+      </c>
+      <c r="D27" t="n">
+        <v>505.4711500363669</v>
+      </c>
+      <c r="E27" t="n">
+        <v>506.790283203125</v>
+      </c>
+      <c r="F27" t="n">
+        <v>24133800</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="n">
+        <v>45943</v>
+      </c>
+      <c r="B28" t="n">
+        <v>512.1958293204747</v>
+      </c>
+      <c r="C28" t="n">
+        <v>512.1958293204747</v>
+      </c>
+      <c r="D28" t="n">
+        <v>507.5044476763347</v>
+      </c>
+      <c r="E28" t="n">
+        <v>509.8551025390625</v>
+      </c>
+      <c r="F28" t="n">
+        <v>14284200</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="n">
+        <v>45944</v>
+      </c>
+      <c r="B29" t="n">
+        <v>506.0661970064178</v>
+      </c>
+      <c r="C29" t="n">
+        <v>511.0750038311887</v>
+      </c>
+      <c r="D29" t="n">
+        <v>501.8707057043513</v>
+      </c>
+      <c r="E29" t="n">
+        <v>509.3789367675781</v>
+      </c>
+      <c r="F29" t="n">
+        <v>14684300</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="n">
+        <v>45945</v>
+      </c>
+      <c r="B30" t="n">
+        <v>510.7576863019565</v>
+      </c>
+      <c r="C30" t="n">
+        <v>512.9694689959882</v>
+      </c>
+      <c r="D30" t="n">
+        <v>505.838140631098</v>
+      </c>
+      <c r="E30" t="n">
+        <v>509.2401428222656</v>
+      </c>
+      <c r="F30" t="n">
+        <v>14694700</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="n">
+        <v>45946</v>
+      </c>
+      <c r="B31" t="n">
+        <v>508.3970522124076</v>
+      </c>
+      <c r="C31" t="n">
+        <v>512.6321652486282</v>
+      </c>
+      <c r="D31" t="n">
+        <v>503.983354813105</v>
+      </c>
+      <c r="E31" t="n">
+        <v>507.4349365234375</v>
+      </c>
+      <c r="F31" t="n">
+        <v>15559600</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="n">
+        <v>45947</v>
+      </c>
+      <c r="B32" t="n">
+        <v>504.8859867353243</v>
+      </c>
+      <c r="C32" t="n">
+        <v>511.2734052578957</v>
+      </c>
+      <c r="D32" t="n">
+        <v>503.1700935064365</v>
+      </c>
+      <c r="E32" t="n">
+        <v>509.3889465332031</v>
+      </c>
+      <c r="F32" t="n">
+        <v>19867800</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="n">
+        <v>45950</v>
+      </c>
+      <c r="B33" t="n">
+        <v>510.4104293345006</v>
+      </c>
+      <c r="C33" t="n">
+        <v>514.4670788802013</v>
+      </c>
+      <c r="D33" t="n">
+        <v>509.2400661752128</v>
+      </c>
+      <c r="E33" t="n">
+        <v>512.5726318359375</v>
+      </c>
+      <c r="F33" t="n">
+        <v>14665600</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45951</v>
+      </c>
+      <c r="B34" t="n">
+        <v>513.2769402267872</v>
+      </c>
+      <c r="C34" t="n">
+        <v>514.4572316509175</v>
+      </c>
+      <c r="D34" t="n">
+        <v>508.8533142722573</v>
+      </c>
+      <c r="E34" t="n">
+        <v>513.4356079101562</v>
+      </c>
+      <c r="F34" t="n">
+        <v>15586200</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45952</v>
+      </c>
+      <c r="B35" t="n">
+        <v>516.8971212574951</v>
+      </c>
+      <c r="C35" t="n">
+        <v>520.9437823737373</v>
+      </c>
+      <c r="D35" t="n">
+        <v>513.4851913413816</v>
+      </c>
+      <c r="E35" t="n">
+        <v>516.2920532226562</v>
+      </c>
+      <c r="F35" t="n">
+        <v>18962700</v>
+      </c>
+      <c r="G35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45953</v>
+      </c>
+      <c r="B36" t="n">
+        <v>518.1964698863214</v>
+      </c>
+      <c r="C36" t="n">
+        <v>519.6743010066873</v>
+      </c>
+      <c r="D36" t="n">
+        <v>514.3778516149157</v>
+      </c>
+      <c r="E36" t="n">
+        <v>516.3119506835938</v>
+      </c>
+      <c r="F36" t="n">
+        <v>14023500</v>
+      </c>
+      <c r="G36" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45954</v>
+      </c>
+      <c r="B37" t="n">
+        <v>518.5237205252405</v>
+      </c>
+      <c r="C37" t="n">
+        <v>521.0628270774097</v>
+      </c>
+      <c r="D37" t="n">
+        <v>516.4607380708425</v>
+      </c>
+      <c r="E37" t="n">
+        <v>519.3370361328125</v>
+      </c>
+      <c r="F37" t="n">
+        <v>15532400</v>
+      </c>
+      <c r="G37" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45957</v>
+      </c>
+      <c r="B38" t="n">
+        <v>527.4404441110845</v>
+      </c>
+      <c r="C38" t="n">
+        <v>530.2175826339089</v>
+      </c>
+      <c r="D38" t="n">
+        <v>524.6930292943027</v>
+      </c>
+      <c r="E38" t="n">
+        <v>527.1825561523438</v>
+      </c>
+      <c r="F38" t="n">
+        <v>18734700</v>
+      </c>
+      <c r="G38" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45958</v>
+      </c>
+      <c r="B39" t="n">
+        <v>545.5116410650497</v>
+      </c>
+      <c r="C39" t="n">
+        <v>549.2012543795508</v>
+      </c>
+      <c r="D39" t="n">
+        <v>536.3569832604931</v>
+      </c>
+      <c r="E39" t="n">
+        <v>537.6463623046875</v>
+      </c>
+      <c r="F39" t="n">
+        <v>29986700</v>
+      </c>
+      <c r="G39" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45959</v>
+      </c>
+      <c r="B40" t="n">
+        <v>540.4929039137475</v>
+      </c>
+      <c r="C40" t="n">
+        <v>541.8120671168963</v>
+      </c>
+      <c r="D40" t="n">
+        <v>532.3498815675878</v>
+      </c>
+      <c r="E40" t="n">
+        <v>537.1305541992188</v>
+      </c>
+      <c r="F40" t="n">
+        <v>36023000</v>
+      </c>
+      <c r="G40" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45960</v>
+      </c>
+      <c r="B41" t="n">
+        <v>526.150935240438</v>
+      </c>
+      <c r="C41" t="n">
+        <v>530.6042843733296</v>
+      </c>
+      <c r="D41" t="n">
+        <v>517.8591725476514</v>
+      </c>
+      <c r="E41" t="n">
+        <v>521.469482421875</v>
+      </c>
+      <c r="F41" t="n">
+        <v>41023100</v>
+      </c>
+      <c r="G41" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="B42" t="n">
+        <v>524.5640198650095</v>
+      </c>
+      <c r="C42" t="n">
+        <v>525.0004316167937</v>
+      </c>
+      <c r="D42" t="n">
+        <v>510.896444053691</v>
+      </c>
+      <c r="E42" t="n">
+        <v>513.5843505859375</v>
+      </c>
+      <c r="F42" t="n">
+        <v>34006400</v>
+      </c>
+      <c r="G42" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45964</v>
+      </c>
+      <c r="B43" t="n">
+        <v>515.5680119038287</v>
+      </c>
+      <c r="C43" t="n">
+        <v>520.6760087890081</v>
+      </c>
+      <c r="D43" t="n">
+        <v>510.3906395365282</v>
+      </c>
+      <c r="E43" t="n">
+        <v>512.8107299804688</v>
+      </c>
+      <c r="F43" t="n">
+        <v>22374700</v>
+      </c>
+      <c r="G43" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45965</v>
+      </c>
+      <c r="B44" t="n">
+        <v>507.5838081580189</v>
+      </c>
+      <c r="C44" t="n">
+        <v>511.342858187808</v>
+      </c>
+      <c r="D44" t="n">
+        <v>503.6957838776707</v>
+      </c>
+      <c r="E44" t="n">
+        <v>510.1328430175781</v>
+      </c>
+      <c r="F44" t="n">
+        <v>20958700</v>
+      </c>
+      <c r="G44" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45966</v>
+      </c>
+      <c r="B45" t="n">
+        <v>509.1111797792271</v>
+      </c>
+      <c r="C45" t="n">
+        <v>510.6287232020861</v>
+      </c>
+      <c r="D45" t="n">
+        <v>502.4460174356622</v>
+      </c>
+      <c r="E45" t="n">
+        <v>503.0213012695312</v>
+      </c>
+      <c r="F45" t="n">
+        <v>23024300</v>
+      </c>
+      <c r="G45" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45967</v>
+      </c>
+      <c r="B46" t="n">
+        <v>501.5335392553728</v>
+      </c>
+      <c r="C46" t="n">
+        <v>501.5732213085109</v>
+      </c>
+      <c r="D46" t="n">
+        <v>491.7639146320967</v>
+      </c>
+      <c r="E46" t="n">
+        <v>493.0433959960938</v>
+      </c>
+      <c r="F46" t="n">
+        <v>27406500</v>
+      </c>
+      <c r="G46" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45968</v>
+      </c>
+      <c r="B47" t="n">
+        <v>492.8946300074654</v>
+      </c>
+      <c r="C47" t="n">
+        <v>495.304792622274</v>
+      </c>
+      <c r="D47" t="n">
+        <v>489.2248119110569</v>
+      </c>
+      <c r="E47" t="n">
+        <v>492.7656860351562</v>
+      </c>
+      <c r="F47" t="n">
+        <v>24019800</v>
+      </c>
+      <c r="G47" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45971</v>
+      </c>
+      <c r="B48" t="n">
+        <v>495.9594034527451</v>
+      </c>
+      <c r="C48" t="n">
+        <v>502.7138276367279</v>
+      </c>
+      <c r="D48" t="n">
+        <v>494.7295019610679</v>
+      </c>
+      <c r="E48" t="n">
+        <v>501.8707580566406</v>
+      </c>
+      <c r="F48" t="n">
+        <v>26101500</v>
+      </c>
+      <c r="G48" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45972</v>
+      </c>
+      <c r="B49" t="n">
+        <v>500.6805581155917</v>
+      </c>
+      <c r="C49" t="n">
+        <v>505.4414057875519</v>
+      </c>
+      <c r="D49" t="n">
+        <v>498.2505695472254</v>
+      </c>
+      <c r="E49" t="n">
+        <v>504.5289001464844</v>
+      </c>
+      <c r="F49" t="n">
+        <v>17980000</v>
+      </c>
+      <c r="G49" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45973</v>
+      </c>
+      <c r="B50" t="n">
+        <v>505.203338237195</v>
+      </c>
+      <c r="C50" t="n">
+        <v>507.494515261433</v>
+      </c>
+      <c r="D50" t="n">
+        <v>495.0469117437556</v>
+      </c>
+      <c r="E50" t="n">
+        <v>506.9688415527344</v>
+      </c>
+      <c r="F50" t="n">
+        <v>26574900</v>
+      </c>
+      <c r="G50" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45974</v>
+      </c>
+      <c r="B51" t="n">
+        <v>506.1455939798088</v>
+      </c>
+      <c r="C51" t="n">
+        <v>509.3095642884979</v>
+      </c>
+      <c r="D51" t="n">
+        <v>497.1992129195551</v>
+      </c>
+      <c r="E51" t="n">
+        <v>499.1828918457031</v>
+      </c>
+      <c r="F51" t="n">
+        <v>25273100</v>
+      </c>
+      <c r="G51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45975</v>
+      </c>
+      <c r="B52" t="n">
+        <v>494.1641988801248</v>
+      </c>
+      <c r="C52" t="n">
+        <v>507.4250879884235</v>
+      </c>
+      <c r="D52" t="n">
+        <v>493.3806372096086</v>
+      </c>
+      <c r="E52" t="n">
+        <v>506.0166625976562</v>
+      </c>
+      <c r="F52" t="n">
+        <v>28505700</v>
+      </c>
+      <c r="G52" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45978</v>
+      </c>
+      <c r="B53" t="n">
+        <v>504.300789978241</v>
+      </c>
+      <c r="C53" t="n">
+        <v>507.9408238780629</v>
+      </c>
+      <c r="D53" t="n">
+        <v>500.7896697837805</v>
+      </c>
+      <c r="E53" t="n">
+        <v>503.3486022949219</v>
+      </c>
+      <c r="F53" t="n">
+        <v>19092800</v>
+      </c>
+      <c r="G53" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45979</v>
+      </c>
+      <c r="B54" t="n">
+        <v>491.3275301094218</v>
+      </c>
+      <c r="C54" t="n">
+        <v>498.8754444722887</v>
+      </c>
+      <c r="D54" t="n">
+        <v>482.8076324047851</v>
+      </c>
+      <c r="E54" t="n">
+        <v>489.7604370117188</v>
+      </c>
+      <c r="F54" t="n">
+        <v>33815100</v>
+      </c>
+      <c r="G54" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45980</v>
+      </c>
+      <c r="B55" t="n">
+        <v>486.1005289347495</v>
+      </c>
+      <c r="C55" t="n">
+        <v>491.1489881906385</v>
+      </c>
+      <c r="D55" t="n">
+        <v>478.8898366362471</v>
+      </c>
+      <c r="E55" t="n">
+        <v>483.1448364257812</v>
+      </c>
+      <c r="F55" t="n">
+        <v>23245300</v>
+      </c>
+      <c r="G55" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45981</v>
+      </c>
+      <c r="B56" t="n">
+        <v>489.6038543571071</v>
+      </c>
+      <c r="C56" t="n">
+        <v>490.4584485233347</v>
+      </c>
+      <c r="D56" t="n">
+        <v>472.5023579474745</v>
+      </c>
+      <c r="E56" t="n">
+        <v>475.4138793945312</v>
+      </c>
+      <c r="F56" t="n">
+        <v>26802500</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45982</v>
+      </c>
+      <c r="B57" t="n">
+        <v>475.4834610910571</v>
+      </c>
+      <c r="C57" t="n">
+        <v>475.9008266883901</v>
+      </c>
+      <c r="D57" t="n">
+        <v>465.31794169549</v>
+      </c>
+      <c r="E57" t="n">
+        <v>469.1436767578125</v>
+      </c>
+      <c r="F57" t="n">
+        <v>31769200</v>
+      </c>
+      <c r="G57" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45985</v>
+      </c>
+      <c r="B58" t="n">
+        <v>472.0055061050608</v>
+      </c>
+      <c r="C58" t="n">
+        <v>473.8935220644432</v>
+      </c>
+      <c r="D58" t="n">
+        <v>465.0694984877541</v>
+      </c>
+      <c r="E58" t="n">
+        <v>471.0118103027344</v>
+      </c>
+      <c r="F58" t="n">
+        <v>34421000</v>
+      </c>
+      <c r="G58" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45986</v>
+      </c>
+      <c r="B59" t="n">
+        <v>471.0813659766461</v>
+      </c>
+      <c r="C59" t="n">
+        <v>476.1293271988991</v>
+      </c>
+      <c r="D59" t="n">
+        <v>461.9592459889855</v>
+      </c>
+      <c r="E59" t="n">
+        <v>473.9829406738281</v>
+      </c>
+      <c r="F59" t="n">
+        <v>28019800</v>
+      </c>
+      <c r="G59" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45987</v>
+      </c>
+      <c r="B60" t="n">
+        <v>483.244191691805</v>
+      </c>
+      <c r="C60" t="n">
+        <v>485.2315832491155</v>
+      </c>
+      <c r="D60" t="n">
+        <v>478.1664208189674</v>
+      </c>
+      <c r="E60" t="n">
+        <v>482.4393005371094</v>
+      </c>
+      <c r="F60" t="n">
+        <v>25709100</v>
+      </c>
+      <c r="G60" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="B61" t="n">
+        <v>484.5260924315005</v>
+      </c>
+      <c r="C61" t="n">
+        <v>489.5243812398697</v>
+      </c>
+      <c r="D61" t="n">
+        <v>483.5820692635899</v>
+      </c>
+      <c r="E61" t="n">
+        <v>488.9082946777344</v>
+      </c>
+      <c r="F61" t="n">
+        <v>14386700</v>
+      </c>
+      <c r="G61" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45992</v>
+      </c>
+      <c r="B62" t="n">
+        <v>485.3608038657598</v>
+      </c>
+      <c r="C62" t="n">
+        <v>486.771834992007</v>
+      </c>
+      <c r="D62" t="n">
+        <v>481.5946880995925</v>
+      </c>
+      <c r="E62" t="n">
+        <v>483.6715087890625</v>
+      </c>
+      <c r="F62" t="n">
+        <v>23964000</v>
+      </c>
+      <c r="G62" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45993</v>
+      </c>
+      <c r="B63" t="n">
+        <v>483.6516286444489</v>
+      </c>
+      <c r="C63" t="n">
+        <v>490.3888850620814</v>
+      </c>
+      <c r="D63" t="n">
+        <v>483.2541563831954</v>
+      </c>
+      <c r="E63" t="n">
+        <v>486.9109497070312</v>
+      </c>
+      <c r="F63" t="n">
+        <v>19562700</v>
+      </c>
+      <c r="G63" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45994</v>
+      </c>
+      <c r="B64" t="n">
+        <v>473.3171775583083</v>
+      </c>
+      <c r="C64" t="n">
+        <v>481.1872310931236</v>
+      </c>
+      <c r="D64" t="n">
+        <v>472.2042431453193</v>
+      </c>
+      <c r="E64" t="n">
+        <v>474.7182922363281</v>
+      </c>
+      <c r="F64" t="n">
+        <v>34615100</v>
+      </c>
+      <c r="G64" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45995</v>
+      </c>
+      <c r="B65" t="n">
+        <v>476.7355071807625</v>
+      </c>
+      <c r="C65" t="n">
+        <v>478.2856702042714</v>
+      </c>
+      <c r="D65" t="n">
+        <v>473.4861025034468</v>
+      </c>
+      <c r="E65" t="n">
+        <v>477.8086853027344</v>
+      </c>
+      <c r="F65" t="n">
+        <v>22318200</v>
+      </c>
+      <c r="G65" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45996</v>
+      </c>
+      <c r="B66" t="n">
+        <v>479.4780643507397</v>
+      </c>
+      <c r="C66" t="n">
+        <v>480.3525214663767</v>
+      </c>
+      <c r="D66" t="n">
+        <v>475.8610275749173</v>
+      </c>
+      <c r="E66" t="n">
+        <v>480.1140441894531</v>
+      </c>
+      <c r="F66" t="n">
+        <v>22608700</v>
+      </c>
+      <c r="G66" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45999</v>
+      </c>
+      <c r="B67" t="n">
+        <v>481.8331998835391</v>
+      </c>
+      <c r="C67" t="n">
+        <v>489.1964595164875</v>
+      </c>
+      <c r="D67" t="n">
+        <v>481.3264052911177</v>
+      </c>
+      <c r="E67" t="n">
+        <v>487.9245300292969</v>
+      </c>
+      <c r="F67" t="n">
+        <v>21965900</v>
+      </c>
+      <c r="G67" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>46000</v>
+      </c>
+      <c r="B68" t="n">
+        <v>486.0166380400449</v>
+      </c>
+      <c r="C68" t="n">
+        <v>489.0175885389743</v>
+      </c>
+      <c r="D68" t="n">
+        <v>485.4204144751398</v>
+      </c>
+      <c r="E68" t="n">
+        <v>488.918212890625</v>
+      </c>
+      <c r="F68" t="n">
+        <v>14696100</v>
+      </c>
+      <c r="G68" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>46001</v>
+      </c>
+      <c r="B69" t="n">
+        <v>480.978577549523</v>
+      </c>
+      <c r="C69" t="n">
+        <v>481.1971918388435</v>
+      </c>
+      <c r="D69" t="n">
+        <v>472.084987996716</v>
+      </c>
+      <c r="E69" t="n">
+        <v>475.5430603027344</v>
+      </c>
+      <c r="F69" t="n">
+        <v>35756200</v>
+      </c>
+      <c r="G69" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>46002</v>
+      </c>
+      <c r="B70" t="n">
+        <v>473.6252433732215</v>
+      </c>
+      <c r="C70" t="n">
+        <v>482.9659780129214</v>
+      </c>
+      <c r="D70" t="n">
+        <v>472.8600781839672</v>
+      </c>
+      <c r="E70" t="n">
+        <v>480.422119140625</v>
+      </c>
+      <c r="F70" t="n">
+        <v>24669200</v>
+      </c>
+      <c r="G70" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>46003</v>
+      </c>
+      <c r="B71" t="n">
+        <v>476.7951512874317</v>
+      </c>
+      <c r="C71" t="n">
+        <v>479.4085762318817</v>
+      </c>
+      <c r="D71" t="n">
+        <v>473.3370788032073</v>
+      </c>
+      <c r="E71" t="n">
+        <v>475.5132751464844</v>
+      </c>
+      <c r="F71" t="n">
+        <v>21248100</v>
+      </c>
+      <c r="G71" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>46006</v>
+      </c>
+      <c r="B72" t="n">
+        <v>477.0733729131614</v>
+      </c>
+      <c r="C72" t="n">
+        <v>477.6894594742654</v>
+      </c>
+      <c r="D72" t="n">
+        <v>469.5411415575728</v>
+      </c>
+      <c r="E72" t="n">
+        <v>471.82666015625</v>
+      </c>
+      <c r="F72" t="n">
+        <v>23727700</v>
+      </c>
+      <c r="G72" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>46007</v>
+      </c>
+      <c r="B73" t="n">
+        <v>468.9349812365753</v>
+      </c>
+      <c r="C73" t="n">
+        <v>474.8772929441188</v>
+      </c>
+      <c r="D73" t="n">
+        <v>467.9114757916915</v>
+      </c>
+      <c r="E73" t="n">
+        <v>473.3867492675781</v>
+      </c>
+      <c r="F73" t="n">
+        <v>20705600</v>
+      </c>
+      <c r="G73" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>46008</v>
+      </c>
+      <c r="B74" t="n">
+        <v>473.903466892556</v>
+      </c>
+      <c r="C74" t="n">
+        <v>476.9739832708393</v>
+      </c>
+      <c r="D74" t="n">
+        <v>472.0055042784347</v>
+      </c>
+      <c r="E74" t="n">
+        <v>473.1184387207031</v>
+      </c>
+      <c r="F74" t="n">
+        <v>24527200</v>
+      </c>
+      <c r="G74" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>46009</v>
+      </c>
+      <c r="B75" t="n">
+        <v>475.1754171439269</v>
+      </c>
+      <c r="C75" t="n">
+        <v>486.5134903409316</v>
+      </c>
+      <c r="D75" t="n">
+        <v>474.8773205213831</v>
+      </c>
+      <c r="E75" t="n">
+        <v>480.9289245605469</v>
+      </c>
+      <c r="F75" t="n">
+        <v>28573500</v>
+      </c>
+      <c r="G75" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>46010</v>
+      </c>
+      <c r="B76" t="n">
+        <v>484.2875835443981</v>
+      </c>
+      <c r="C76" t="n">
+        <v>484.7745151206103</v>
+      </c>
+      <c r="D76" t="n">
+        <v>479.4482897203998</v>
+      </c>
+      <c r="E76" t="n">
+        <v>482.856689453125</v>
+      </c>
+      <c r="F76" t="n">
+        <v>70836100</v>
+      </c>
+      <c r="G76" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>46013</v>
+      </c>
+      <c r="B77" t="n">
+        <v>483.05539282771</v>
+      </c>
+      <c r="C77" t="n">
+        <v>485.6489546100234</v>
+      </c>
+      <c r="D77" t="n">
+        <v>479.6470235443271</v>
+      </c>
+      <c r="E77" t="n">
+        <v>481.8629760742188</v>
+      </c>
+      <c r="F77" t="n">
+        <v>16963000</v>
+      </c>
+      <c r="G77" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>46014</v>
+      </c>
+      <c r="B78" t="n">
+        <v>481.9226163967179</v>
+      </c>
+      <c r="C78" t="n">
+        <v>484.7546252629152</v>
+      </c>
+      <c r="D78" t="n">
+        <v>481.6841087754749</v>
+      </c>
+      <c r="E78" t="n">
+        <v>483.7808227539062</v>
+      </c>
+      <c r="F78" t="n">
+        <v>14683600</v>
+      </c>
+      <c r="G78" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>46015</v>
+      </c>
+      <c r="B79" t="n">
+        <v>482.6181758435609</v>
+      </c>
+      <c r="C79" t="n">
+        <v>486.0762481946253</v>
+      </c>
+      <c r="D79" t="n">
+        <v>481.7735283363114</v>
+      </c>
+      <c r="E79" t="n">
+        <v>484.9434204101562</v>
+      </c>
+      <c r="F79" t="n">
+        <v>5855900</v>
+      </c>
+      <c r="G79" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>46017</v>
+      </c>
+      <c r="B80" t="n">
+        <v>483.6417106195734</v>
+      </c>
+      <c r="C80" t="n">
+        <v>485.0428254417362</v>
+      </c>
+      <c r="D80" t="n">
+        <v>482.8964387136479</v>
+      </c>
+      <c r="E80" t="n">
+        <v>484.6354064941406</v>
+      </c>
+      <c r="F80" t="n">
+        <v>8842200</v>
+      </c>
+      <c r="G80" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>46020</v>
+      </c>
+      <c r="B81" t="n">
+        <v>481.8033366009864</v>
+      </c>
+      <c r="C81" t="n">
+        <v>485.2713556042012</v>
+      </c>
+      <c r="D81" t="n">
+        <v>481.1276307272214</v>
+      </c>
+      <c r="E81" t="n">
+        <v>484.0292358398438</v>
+      </c>
+      <c r="F81" t="n">
+        <v>10893400</v>
+      </c>
+      <c r="G81" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>46021</v>
+      </c>
+      <c r="B82" t="n">
+        <v>482.8666136001516</v>
+      </c>
+      <c r="C82" t="n">
+        <v>486.5929730105466</v>
+      </c>
+      <c r="D82" t="n">
+        <v>482.4393316658054</v>
+      </c>
+      <c r="E82" t="n">
+        <v>484.4068603515625</v>
+      </c>
+      <c r="F82" t="n">
+        <v>13944500</v>
+      </c>
+      <c r="G82" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B83" t="n">
+        <v>484.7645645601486</v>
+      </c>
+      <c r="C83" t="n">
+        <v>485.0626915008752</v>
+      </c>
+      <c r="D83" t="n">
+        <v>480.253177052155</v>
+      </c>
+      <c r="E83" t="n">
+        <v>480.5711669921875</v>
+      </c>
+      <c r="F83" t="n">
+        <v>15601600</v>
+      </c>
+      <c r="G83" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>46024</v>
+      </c>
+      <c r="B84" t="n">
+        <v>481.3363251826272</v>
+      </c>
+      <c r="C84" t="n">
+        <v>481.6046121327098</v>
+      </c>
+      <c r="D84" t="n">
+        <v>467.1960229709088</v>
+      </c>
+      <c r="E84" t="n">
+        <v>469.95849609375</v>
+      </c>
+      <c r="F84" t="n">
+        <v>25571600</v>
+      </c>
+      <c r="G84" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>46027</v>
+      </c>
+      <c r="B85" t="n">
+        <v>471.071443053882</v>
+      </c>
+      <c r="C85" t="n">
+        <v>473.0687813775576</v>
+      </c>
+      <c r="D85" t="n">
+        <v>466.5401924921144</v>
+      </c>
+      <c r="E85" t="n">
+        <v>469.8690795898438</v>
+      </c>
+      <c r="F85" t="n">
+        <v>25250300</v>
+      </c>
+      <c r="G85" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>46028</v>
+      </c>
+      <c r="B86" t="n">
+        <v>470.8130487247203</v>
+      </c>
+      <c r="C86" t="n">
+        <v>475.7219083069673</v>
+      </c>
+      <c r="D86" t="n">
+        <v>466.7885929433101</v>
+      </c>
+      <c r="E86" t="n">
+        <v>475.4933776855469</v>
+      </c>
+      <c r="F86" t="n">
+        <v>23037700</v>
+      </c>
+      <c r="G86" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>46029</v>
+      </c>
+      <c r="B87" t="n">
+        <v>476.7355161407656</v>
+      </c>
+      <c r="C87" t="n">
+        <v>486.6128550141313</v>
+      </c>
+      <c r="D87" t="n">
+        <v>474.936929133209</v>
+      </c>
+      <c r="E87" t="n">
+        <v>480.422119140625</v>
+      </c>
+      <c r="F87" t="n">
+        <v>25564200</v>
+      </c>
+      <c r="G87" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>46030</v>
+      </c>
+      <c r="B88" t="n">
+        <v>478.206189665966</v>
+      </c>
+      <c r="C88" t="n">
+        <v>479.6172511411785</v>
+      </c>
+      <c r="D88" t="n">
+        <v>472.8601010457309</v>
+      </c>
+      <c r="E88" t="n">
+        <v>475.0959167480469</v>
+      </c>
+      <c r="F88" t="n">
+        <v>18162600</v>
+      </c>
+      <c r="G88" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>46031</v>
+      </c>
+      <c r="B89" t="n">
+        <v>471.071451381159</v>
+      </c>
+      <c r="C89" t="n">
+        <v>476.7951491709672</v>
+      </c>
+      <c r="D89" t="n">
+        <v>469.2231916595613</v>
+      </c>
+      <c r="E89" t="n">
+        <v>476.258544921875</v>
+      </c>
+      <c r="F89" t="n">
+        <v>18491000</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>46034</v>
+      </c>
+      <c r="B90" t="n">
+        <v>473.6649886945649</v>
+      </c>
+      <c r="C90" t="n">
+        <v>477.9577314886077</v>
+      </c>
+      <c r="D90" t="n">
+        <v>472.681209234831</v>
+      </c>
+      <c r="E90" t="n">
+        <v>474.1717529296875</v>
+      </c>
+      <c r="F90" t="n">
+        <v>23519900</v>
+      </c>
+      <c r="G90" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>46035</v>
+      </c>
+      <c r="B91" t="n">
+        <v>471.6875193976834</v>
+      </c>
+      <c r="C91" t="n">
+        <v>472.7805908527595</v>
+      </c>
+      <c r="D91" t="n">
+        <v>463.0125743921384</v>
+      </c>
+      <c r="E91" t="n">
+        <v>467.7028198242188</v>
+      </c>
+      <c r="F91" t="n">
+        <v>28545800</v>
+      </c>
+      <c r="G91" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>46036</v>
+      </c>
+      <c r="B92" t="n">
+        <v>463.5193621312372</v>
+      </c>
+      <c r="C92" t="n">
+        <v>465.2484135478969</v>
+      </c>
+      <c r="D92" t="n">
+        <v>454.2879494306214</v>
+      </c>
+      <c r="E92" t="n">
+        <v>456.4840087890625</v>
+      </c>
+      <c r="F92" t="n">
+        <v>28184300</v>
+      </c>
+      <c r="G92" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>46037</v>
+      </c>
+      <c r="B93" t="n">
+        <v>461.1940901109254</v>
+      </c>
+      <c r="C93" t="n">
+        <v>461.3232754170305</v>
+      </c>
+      <c r="D93" t="n">
+        <v>453.0259094171898</v>
+      </c>
+      <c r="E93" t="n">
+        <v>453.7811279296875</v>
+      </c>
+      <c r="F93" t="n">
+        <v>23225800</v>
+      </c>
+      <c r="G93" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>46038</v>
+      </c>
+      <c r="B94" t="n">
+        <v>454.9437666153887</v>
+      </c>
+      <c r="C94" t="n">
+        <v>460.2699922453042</v>
+      </c>
+      <c r="D94" t="n">
+        <v>453.6023014516422</v>
+      </c>
+      <c r="E94" t="n">
+        <v>456.9609680175781</v>
+      </c>
+      <c r="F94" t="n">
+        <v>34246700</v>
+      </c>
+      <c r="G94" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>46042</v>
+      </c>
+      <c r="B95" t="n">
+        <v>448.3754180557273</v>
+      </c>
+      <c r="C95" t="n">
+        <v>453.9202272514996</v>
+      </c>
+      <c r="D95" t="n">
+        <v>446.4476457864541</v>
+      </c>
+      <c r="E95" t="n">
+        <v>451.6546020507812</v>
+      </c>
+      <c r="F95" t="n">
+        <v>26130000</v>
+      </c>
+      <c r="G95" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>46043</v>
+      </c>
+      <c r="B96" t="n">
+        <v>449.7467088388933</v>
+      </c>
+      <c r="C96" t="n">
+        <v>449.8361378186282</v>
+      </c>
+      <c r="D96" t="n">
+        <v>435.9144504613163</v>
+      </c>
+      <c r="E96" t="n">
+        <v>441.3102111816406</v>
+      </c>
+      <c r="F96" t="n">
+        <v>37980500</v>
+      </c>
+      <c r="G96" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>46044</v>
+      </c>
+      <c r="B97" t="n">
+        <v>444.7981003997206</v>
+      </c>
+      <c r="C97" t="n">
+        <v>449.9851935867555</v>
+      </c>
+      <c r="D97" t="n">
+        <v>441.8965257028684</v>
+      </c>
+      <c r="E97" t="n">
+        <v>448.2959289550781</v>
+      </c>
+      <c r="F97" t="n">
+        <v>25349400</v>
+      </c>
+      <c r="G97" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>46045</v>
+      </c>
+      <c r="B98" t="n">
+        <v>449.0213193023424</v>
+      </c>
+      <c r="C98" t="n">
+        <v>468.1301005814363</v>
+      </c>
+      <c r="D98" t="n">
+        <v>447.6897705604439</v>
+      </c>
+      <c r="E98" t="n">
+        <v>463.0125732421875</v>
+      </c>
+      <c r="F98" t="n">
+        <v>38000200</v>
+      </c>
+      <c r="G98" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>46048</v>
+      </c>
+      <c r="B99" t="n">
+        <v>462.3766075757791</v>
+      </c>
+      <c r="C99" t="n">
+        <v>471.2602507862521</v>
+      </c>
+      <c r="D99" t="n">
+        <v>459.0874767807031</v>
+      </c>
+      <c r="E99" t="n">
+        <v>467.3152770996094</v>
+      </c>
+      <c r="F99" t="n">
+        <v>29291200</v>
+      </c>
+      <c r="G99" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>46049</v>
+      </c>
+      <c r="B100" t="n">
+        <v>470.7137217228436</v>
+      </c>
+      <c r="C100" t="n">
+        <v>479.8258954035317</v>
+      </c>
+      <c r="D100" t="n">
+        <v>470.1771174893794</v>
+      </c>
+      <c r="E100" t="n">
+        <v>477.5503234863281</v>
+      </c>
+      <c r="F100" t="n">
+        <v>29213900</v>
+      </c>
+      <c r="G100" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>46050</v>
+      </c>
+      <c r="B101" t="n">
+        <v>480.1637149068934</v>
+      </c>
+      <c r="C101" t="n">
+        <v>480.6903724414303</v>
+      </c>
+      <c r="D101" t="n">
+        <v>474.9865685400099</v>
+      </c>
+      <c r="E101" t="n">
+        <v>478.5936889648438</v>
+      </c>
+      <c r="F101" t="n">
+        <v>36875400</v>
+      </c>
+      <c r="G101" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>46051</v>
+      </c>
+      <c r="B102" t="n">
+        <v>437.2162272399066</v>
+      </c>
+      <c r="C102" t="n">
+        <v>439.7104135269112</v>
+      </c>
+      <c r="D102" t="n">
+        <v>418.365815756604</v>
+      </c>
+      <c r="E102" t="n">
+        <v>430.7671508789062</v>
+      </c>
+      <c r="F102" t="n">
+        <v>128855300</v>
+      </c>
+      <c r="G102" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>46052</v>
+      </c>
+      <c r="B103" t="n">
+        <v>436.4013853645445</v>
+      </c>
+      <c r="C103" t="n">
+        <v>436.8286672682951</v>
+      </c>
+      <c r="D103" t="n">
+        <v>423.7615739365565</v>
+      </c>
+      <c r="E103" t="n">
+        <v>427.5773620605469</v>
+      </c>
+      <c r="F103" t="n">
+        <v>58566800</v>
+      </c>
+      <c r="G103" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>46055</v>
+      </c>
+      <c r="B104" t="n">
+        <v>427.5276741085398</v>
+      </c>
+      <c r="C104" t="n">
+        <v>428.0245220118177</v>
+      </c>
+      <c r="D104" t="n">
+        <v>419.588054318219</v>
+      </c>
+      <c r="E104" t="n">
+        <v>420.7009887695312</v>
+      </c>
+      <c r="F104" t="n">
+        <v>42219900</v>
+      </c>
+      <c r="G104" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>46056</v>
+      </c>
+      <c r="B105" t="n">
+        <v>419.3495781995532</v>
+      </c>
+      <c r="C105" t="n">
+        <v>419.3893041977899</v>
+      </c>
+      <c r="D105" t="n">
+        <v>405.9843574339844</v>
+      </c>
+      <c r="E105" t="n">
+        <v>408.6176452636719</v>
+      </c>
+      <c r="F105" t="n">
+        <v>61424100</v>
+      </c>
+      <c r="G105" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>46057</v>
+      </c>
+      <c r="B106" t="n">
+        <v>408.4089957411405</v>
+      </c>
+      <c r="C106" t="n">
+        <v>417.1535071208501</v>
+      </c>
+      <c r="D106" t="n">
+        <v>406.6600813351222</v>
+      </c>
+      <c r="E106" t="n">
+        <v>411.5788879394531</v>
+      </c>
+      <c r="F106" t="n">
+        <v>45012400</v>
+      </c>
+      <c r="G106" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>46058</v>
+      </c>
+      <c r="B107" t="n">
+        <v>404.8714440282318</v>
+      </c>
+      <c r="C107" t="n">
+        <v>405.7260079125925</v>
+      </c>
+      <c r="D107" t="n">
+        <v>389.8467674620769</v>
+      </c>
+      <c r="E107" t="n">
+        <v>391.1882629394531</v>
+      </c>
+      <c r="F107" t="n">
+        <v>66289200</v>
+      </c>
+      <c r="G107" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>46059</v>
+      </c>
+      <c r="B108" t="n">
+        <v>396.6535630940219</v>
+      </c>
+      <c r="C108" t="n">
+        <v>399.2570412200398</v>
+      </c>
+      <c r="D108" t="n">
+        <v>390.4429643868461</v>
+      </c>
+      <c r="E108" t="n">
+        <v>398.6111450195312</v>
+      </c>
+      <c r="F108" t="n">
+        <v>53515300</v>
+      </c>
+      <c r="G108" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>46062</v>
+      </c>
+      <c r="B109" t="n">
+        <v>402.2977759502542</v>
+      </c>
+      <c r="C109" t="n">
+        <v>412.2744908996196</v>
+      </c>
+      <c r="D109" t="n">
+        <v>398.3428555009064</v>
+      </c>
+      <c r="E109" t="n">
+        <v>410.9926147460938</v>
+      </c>
+      <c r="F109" t="n">
+        <v>45480500</v>
+      </c>
+      <c r="G109" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>46063</v>
+      </c>
+      <c r="B110" t="n">
+        <v>416.9746165751398</v>
+      </c>
+      <c r="C110" t="n">
+        <v>421.009018998737</v>
+      </c>
+      <c r="D110" t="n">
+        <v>410.0982587889407</v>
+      </c>
+      <c r="E110" t="n">
+        <v>410.6646423339844</v>
+      </c>
+      <c r="F110" t="n">
+        <v>44857900</v>
+      </c>
+      <c r="G110" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>46064</v>
+      </c>
+      <c r="B111" t="n">
+        <v>413.5563153661985</v>
+      </c>
+      <c r="C111" t="n">
+        <v>413.8345489802859</v>
+      </c>
+      <c r="D111" t="n">
+        <v>398.4819668946231</v>
+      </c>
+      <c r="E111" t="n">
+        <v>401.8207702636719</v>
+      </c>
+      <c r="F111" t="n">
+        <v>42491000</v>
+      </c>
+      <c r="G111" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>46065</v>
+      </c>
+      <c r="B112" t="n">
+        <v>402.4468146669985</v>
+      </c>
+      <c r="C112" t="n">
+        <v>403.6392618034954</v>
+      </c>
+      <c r="D112" t="n">
+        <v>395.5008904586587</v>
+      </c>
+      <c r="E112" t="n">
+        <v>399.3067321777344</v>
+      </c>
+      <c r="F112" t="n">
+        <v>40802400</v>
+      </c>
+      <c r="G112" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>46066</v>
+      </c>
+      <c r="B113" t="n">
+        <v>401.900281272875</v>
+      </c>
+      <c r="C113" t="n">
+        <v>402.9834060634867</v>
+      </c>
+      <c r="D113" t="n">
+        <v>395.5406038478973</v>
+      </c>
+      <c r="E113" t="n">
+        <v>398.7900085449219</v>
+      </c>
+      <c r="F113" t="n">
+        <v>34091600</v>
+      </c>
+      <c r="G113" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>46070</v>
+      </c>
+      <c r="B114" t="n">
+        <v>396.7032617740463</v>
+      </c>
+      <c r="C114" t="n">
+        <v>397.9950542597942</v>
+      </c>
+      <c r="D114" t="n">
+        <v>392.0428257724806</v>
+      </c>
+      <c r="E114" t="n">
+        <v>394.3581237792969</v>
+      </c>
+      <c r="F114" t="n">
+        <v>32078800</v>
+      </c>
+      <c r="G114" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>46071</v>
+      </c>
+      <c r="B115" t="n">
+        <v>395.6201070500213</v>
+      </c>
+      <c r="C115" t="n">
+        <v>400.0221720919145</v>
+      </c>
+      <c r="D115" t="n">
+        <v>393.8215201082963</v>
+      </c>
+      <c r="E115" t="n">
+        <v>397.0808410644531</v>
+      </c>
+      <c r="F115" t="n">
+        <v>23223400</v>
+      </c>
+      <c r="G115" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>46072</v>
+      </c>
+      <c r="B116" t="n">
+        <v>399.0727866126232</v>
+      </c>
+      <c r="C116" t="n">
+        <v>402.7976819572589</v>
+      </c>
+      <c r="D116" t="n">
+        <v>395.0690225854118</v>
+      </c>
+      <c r="E116" t="n">
+        <v>396.8517761230469</v>
+      </c>
+      <c r="F116" t="n">
+        <v>28234000</v>
+      </c>
+      <c r="G116" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H116" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>46073</v>
+      </c>
+      <c r="B117" t="n">
+        <v>394.5112344348997</v>
+      </c>
+      <c r="C117" t="n">
+        <v>398.5050592846536</v>
+      </c>
+      <c r="D117" t="n">
+        <v>393.5650869938952</v>
+      </c>
+      <c r="E117" t="n">
+        <v>395.6267395019531</v>
+      </c>
+      <c r="F117" t="n">
+        <v>34015200</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>46076</v>
+      </c>
+      <c r="B118" t="n">
+        <v>393.405742102137</v>
+      </c>
+      <c r="C118" t="n">
+        <v>393.7642745182822</v>
+      </c>
+      <c r="D118" t="n">
+        <v>381.5537777227514</v>
+      </c>
+      <c r="E118" t="n">
+        <v>382.9182434082031</v>
+      </c>
+      <c r="F118" t="n">
+        <v>43238300</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>46077</v>
+      </c>
+      <c r="B119" t="n">
+        <v>382.5895619940176</v>
+      </c>
+      <c r="C119" t="n">
+        <v>387.7884640317496</v>
+      </c>
+      <c r="D119" t="n">
+        <v>380.1693467763097</v>
+      </c>
+      <c r="E119" t="n">
+        <v>387.429931640625</v>
+      </c>
+      <c r="F119" t="n">
+        <v>33884700</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B120" t="n">
+        <v>388.9537605304631</v>
+      </c>
+      <c r="C120" t="n">
+        <v>399.8496074643683</v>
+      </c>
+      <c r="D120" t="n">
+        <v>388.5852587696308</v>
+      </c>
+      <c r="E120" t="n">
+        <v>398.9831237792969</v>
+      </c>
+      <c r="F120" t="n">
+        <v>43625500</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B121" t="n">
+        <v>403.0765245044552</v>
+      </c>
+      <c r="C121" t="n">
+        <v>405.8453028142193</v>
+      </c>
+      <c r="D121" t="n">
+        <v>397.1306190557743</v>
+      </c>
+      <c r="E121" t="n">
+        <v>400.0986022949219</v>
+      </c>
+      <c r="F121" t="n">
+        <v>34405900</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B122" t="n">
+        <v>389.3023679559341</v>
+      </c>
+      <c r="C122" t="n">
+        <v>395.2183958601928</v>
+      </c>
+      <c r="D122" t="n">
+        <v>388.3064040716401</v>
+      </c>
+      <c r="E122" t="n">
+        <v>391.1548461914062</v>
+      </c>
+      <c r="F122" t="n">
+        <v>51367200</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B123" t="n">
+        <v>391.2743390590049</v>
+      </c>
+      <c r="C123" t="n">
+        <v>399.5707348557469</v>
+      </c>
+      <c r="D123" t="n">
+        <v>389.0533591512552</v>
+      </c>
+      <c r="E123" t="n">
+        <v>396.9413757324219</v>
+      </c>
+      <c r="F123" t="n">
+        <v>35474900</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B124" t="n">
+        <v>391.5532542396072</v>
+      </c>
+      <c r="C124" t="n">
+        <v>405.0585220162706</v>
+      </c>
+      <c r="D124" t="n">
+        <v>391.0851500003899</v>
+      </c>
+      <c r="E124" t="n">
+        <v>402.2996826171875</v>
+      </c>
+      <c r="F124" t="n">
+        <v>38199200</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B125" t="n">
+        <v>399.6504140582061</v>
+      </c>
+      <c r="C125" t="n">
+        <v>409.3710312257941</v>
+      </c>
+      <c r="D125" t="n">
+        <v>398.6942972465368</v>
+      </c>
+      <c r="E125" t="n">
+        <v>403.5645751953125</v>
+      </c>
+      <c r="F125" t="n">
+        <v>35808000</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B126" t="n">
+        <v>402.7877173292459</v>
+      </c>
+      <c r="C126" t="n">
+        <v>409.9486695143622</v>
+      </c>
+      <c r="D126" t="n">
+        <v>402.7677785996419</v>
+      </c>
+      <c r="E126" t="n">
+        <v>409.0224304199219</v>
+      </c>
+      <c r="F126" t="n">
+        <v>39001300</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B127" t="n">
+        <v>407.5484392107423</v>
+      </c>
+      <c r="C127" t="n">
+        <v>411.3828759024364</v>
+      </c>
+      <c r="D127" t="n">
+        <v>406.8612216895844</v>
+      </c>
+      <c r="E127" t="n">
+        <v>407.3093872070312</v>
+      </c>
+      <c r="F127" t="n">
+        <v>31123900</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B128" t="n">
+        <v>403.2857003455267</v>
+      </c>
+      <c r="C128" t="n">
+        <v>408.5543272911556</v>
+      </c>
+      <c r="D128" t="n">
+        <v>401.8714182880504</v>
+      </c>
+      <c r="E128" t="n">
+        <v>407.757568359375</v>
+      </c>
+      <c r="F128" t="n">
+        <v>30131900</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B129" t="n">
+        <v>408.3750692869274</v>
+      </c>
+      <c r="C129" t="n">
+        <v>408.5443965203919</v>
+      </c>
+      <c r="D129" t="n">
+        <v>401.3037196464309</v>
+      </c>
+      <c r="E129" t="n">
+        <v>404.122314453125</v>
+      </c>
+      <c r="F129" t="n">
+        <v>31706400</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B130" t="n">
+        <v>403.9330670994013</v>
+      </c>
+      <c r="C130" t="n">
+        <v>407.3591851847947</v>
+      </c>
+      <c r="D130" t="n">
+        <v>399.9691200230297</v>
+      </c>
+      <c r="E130" t="n">
+        <v>403.245849609375</v>
+      </c>
+      <c r="F130" t="n">
+        <v>25512100</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B131" t="n">
+        <v>402.9968458288957</v>
+      </c>
+      <c r="C131" t="n">
+        <v>404.4808221962511</v>
+      </c>
+      <c r="D131" t="n">
+        <v>400.0886180975</v>
+      </c>
+      <c r="E131" t="n">
+        <v>400.2380065917969</v>
+      </c>
+      <c r="F131" t="n">
+        <v>27263900</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B132" t="n">
+        <v>399.3815063856616</v>
+      </c>
+      <c r="C132" t="n">
+        <v>403.1661568819284</v>
+      </c>
+      <c r="D132" t="n">
+        <v>392.6587503554791</v>
+      </c>
+      <c r="E132" t="n">
+        <v>393.9534912109375</v>
+      </c>
+      <c r="F132" t="n">
+        <v>26848000</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B133" t="n">
+        <v>396.4633374914087</v>
+      </c>
+      <c r="C133" t="n">
+        <v>399.013002518604</v>
+      </c>
+      <c r="D133" t="n">
+        <v>393.1965772756644</v>
+      </c>
+      <c r="E133" t="n">
+        <v>398.3357543945312</v>
+      </c>
+      <c r="F133" t="n">
+        <v>27733700</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B134" t="n">
+        <v>398.6544574759768</v>
+      </c>
+      <c r="C134" t="n">
+        <v>402.7677932271478</v>
+      </c>
+      <c r="D134" t="n">
+        <v>396.1446394015159</v>
+      </c>
+      <c r="E134" t="n">
+        <v>397.7979431152344</v>
+      </c>
+      <c r="F134" t="n">
+        <v>26228300</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B135" t="n">
+        <v>395.5271224277118</v>
+      </c>
+      <c r="C135" t="n">
+        <v>396.3936061005556</v>
+      </c>
+      <c r="D135" t="n">
+        <v>389.421859259591</v>
+      </c>
+      <c r="E135" t="n">
+        <v>390.2086791992188</v>
+      </c>
+      <c r="F135" t="n">
+        <v>25908500</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B136" t="n">
+        <v>388.5255176358589</v>
+      </c>
+      <c r="C136" t="n">
+        <v>390.9058555160312</v>
+      </c>
+      <c r="D136" t="n">
+        <v>385.4977789148814</v>
+      </c>
+      <c r="E136" t="n">
+        <v>387.4498596191406</v>
+      </c>
+      <c r="F136" t="n">
+        <v>25138800</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="n">
+        <v>385.2288602760525</v>
+      </c>
+      <c r="C137" t="n">
+        <v>385.4380041709834</v>
+      </c>
+      <c r="D137" t="n">
+        <v>378.5857681226169</v>
+      </c>
+      <c r="E137" t="n">
+        <v>380.3287048339844</v>
+      </c>
+      <c r="F137" t="n">
+        <v>50853200</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B138" t="n">
+        <v>382.3505545919761</v>
+      </c>
+      <c r="C138" t="n">
+        <v>385.6471928372158</v>
+      </c>
+      <c r="D138" t="n">
+        <v>380.1395134056624</v>
+      </c>
+      <c r="E138" t="n">
+        <v>381.4541931152344</v>
+      </c>
+      <c r="F138" t="n">
+        <v>29680100</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B139" t="n">
+        <v>380.8167328036651</v>
+      </c>
+      <c r="C139" t="n">
+        <v>380.9263046350485</v>
+      </c>
+      <c r="D139" t="n">
+        <v>370.3491731415432</v>
+      </c>
+      <c r="E139" t="n">
+        <v>371.2355651855469</v>
+      </c>
+      <c r="F139" t="n">
+        <v>42733600</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B140" t="n">
+        <v>375.3987224826456</v>
+      </c>
+      <c r="C140" t="n">
+        <v>375.5381416220395</v>
+      </c>
+      <c r="D140" t="n">
+        <v>368.1381372201017</v>
+      </c>
+      <c r="E140" t="n">
+        <v>369.5424499511719</v>
+      </c>
+      <c r="F140" t="n">
+        <v>31181200</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B141" t="n">
+        <v>369.3233201292261</v>
+      </c>
+      <c r="C141" t="n">
+        <v>373.2075730440749</v>
+      </c>
+      <c r="D141" t="n">
+        <v>363.7160388213271</v>
+      </c>
+      <c r="E141" t="n">
+        <v>364.4928894042969</v>
+      </c>
+      <c r="F141" t="n">
+        <v>36836600</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B142" t="n">
+        <v>360.4393475355787</v>
+      </c>
+      <c r="C142" t="n">
+        <v>360.9871459448897</v>
+      </c>
+      <c r="D142" t="n">
+        <v>355.0711176485405</v>
+      </c>
+      <c r="E142" t="n">
+        <v>355.3300476074219</v>
+      </c>
+      <c r="F142" t="n">
+        <v>37883400</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>46111</v>
+      </c>
+      <c r="B143" t="n">
+        <v>360.4393363053819</v>
+      </c>
+      <c r="C143" t="n">
+        <v>363.8853629556265</v>
+      </c>
+      <c r="D143" t="n">
+        <v>354.8420239421825</v>
+      </c>
+      <c r="E143" t="n">
+        <v>357.5111999511719</v>
+      </c>
+      <c r="F143" t="n">
+        <v>44797000</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>46112</v>
+      </c>
+      <c r="B144" t="n">
+        <v>363.0786217954557</v>
+      </c>
+      <c r="C144" t="n">
+        <v>371.3949263066763</v>
+      </c>
+      <c r="D144" t="n">
+        <v>361.6046146993887</v>
+      </c>
+      <c r="E144" t="n">
+        <v>368.6759643554688</v>
+      </c>
+      <c r="F144" t="n">
+        <v>45244400</v>
+      </c>
+      <c r="G144" t="n">
+        <v>0</v>
+      </c>
+      <c r="H144" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B145" t="n">
+        <v>371.9825473134139</v>
+      </c>
+      <c r="C145" t="n">
+        <v>372.4805292634522</v>
+      </c>
+      <c r="D145" t="n">
+        <v>366.7139201659809</v>
+      </c>
+      <c r="E145" t="n">
+        <v>367.8791809082031</v>
+      </c>
+      <c r="F145" t="n">
+        <v>29417200</v>
+      </c>
+      <c r="G145" t="n">
+        <v>0</v>
+      </c>
+      <c r="H145" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>46114</v>
+      </c>
+      <c r="B146" t="n">
+        <v>365.7278929006101</v>
+      </c>
+      <c r="C146" t="n">
+        <v>372.1319638369453</v>
+      </c>
+      <c r="D146" t="n">
+        <v>362.680245817395</v>
+      </c>
+      <c r="E146" t="n">
+        <v>371.9526672363281</v>
+      </c>
+      <c r="F146" t="n">
+        <v>24099100</v>
+      </c>
+      <c r="G146" t="n">
+        <v>0</v>
+      </c>
+      <c r="H146" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>46118</v>
+      </c>
+      <c r="B147" t="n">
+        <v>371.9825539180967</v>
+      </c>
+      <c r="C147" t="n">
+        <v>372.2216059265558</v>
+      </c>
+      <c r="D147" t="n">
+        <v>368.0086676124431</v>
+      </c>
+      <c r="E147" t="n">
+        <v>371.3750305175781</v>
+      </c>
+      <c r="F147" t="n">
+        <v>16146600</v>
+      </c>
+      <c r="G147" t="n">
+        <v>0</v>
+      </c>
+      <c r="H147" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>46119</v>
+      </c>
+      <c r="B148" t="n">
+        <v>368.8452727581139</v>
+      </c>
+      <c r="C148" t="n">
+        <v>370.9467724245638</v>
+      </c>
+      <c r="D148" t="n">
+        <v>365.080530373921</v>
+      </c>
+      <c r="E148" t="n">
+        <v>370.7874145507812</v>
+      </c>
+      <c r="F148" t="n">
+        <v>21443300</v>
+      </c>
+      <c r="G148" t="n">
+        <v>0</v>
+      </c>
+      <c r="H148" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>46120</v>
+      </c>
+      <c r="B149" t="n">
+        <v>383.4261612830284</v>
+      </c>
+      <c r="C149" t="n">
+        <v>383.4460696173869</v>
+      </c>
+      <c r="D149" t="n">
+        <v>369.9109249891301</v>
+      </c>
+      <c r="E149" t="n">
+        <v>372.8191223144531</v>
+      </c>
+      <c r="F149" t="n">
+        <v>33064800</v>
+      </c>
+      <c r="G149" t="n">
+        <v>0</v>
+      </c>
+      <c r="H149" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>46121</v>
+      </c>
+      <c r="B150" t="n">
+        <v>370.9965328148009</v>
+      </c>
+      <c r="C150" t="n">
+        <v>371.9924966612836</v>
+      </c>
+      <c r="D150" t="n">
+        <v>365.5685176937085</v>
+      </c>
+      <c r="E150" t="n">
+        <v>371.5642395019531</v>
+      </c>
+      <c r="F150" t="n">
+        <v>30435300</v>
+      </c>
+      <c r="G150" t="n">
+        <v>0</v>
+      </c>
+      <c r="H150" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>46122</v>
+      </c>
+      <c r="B151" t="n">
+        <v>371.4746074371751</v>
+      </c>
+      <c r="C151" t="n">
+        <v>374.1238749235223</v>
+      </c>
+      <c r="D151" t="n">
+        <v>368.5365019241105</v>
+      </c>
+      <c r="E151" t="n">
+        <v>369.3731079101562</v>
+      </c>
+      <c r="F151" t="n">
+        <v>28111100</v>
+      </c>
+      <c r="G151" t="n">
+        <v>0</v>
+      </c>
+      <c r="H151" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>46125</v>
+      </c>
+      <c r="B152" t="n">
+        <v>372.1020528926679</v>
+      </c>
+      <c r="C152" t="n">
+        <v>382.9879612673769</v>
+      </c>
+      <c r="D152" t="n">
+        <v>369.5225100750242</v>
+      </c>
+      <c r="E152" t="n">
+        <v>382.8186340332031</v>
+      </c>
+      <c r="F152" t="n">
+        <v>35745800</v>
+      </c>
+      <c r="G152" t="n">
+        <v>0</v>
+      </c>
+      <c r="H152" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>46126</v>
+      </c>
+      <c r="B153" t="n">
+        <v>386.3543213772784</v>
+      </c>
+      <c r="C153" t="n">
+        <v>393.0969858972055</v>
+      </c>
+      <c r="D153" t="n">
+        <v>384.95994763093</v>
+      </c>
+      <c r="E153" t="n">
+        <v>391.5233459472656</v>
+      </c>
+      <c r="F153" t="n">
+        <v>37504500</v>
+      </c>
+      <c r="G153" t="n">
+        <v>0</v>
+      </c>
+      <c r="H153" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>46127</v>
+      </c>
+      <c r="B154" t="n">
+        <v>396.3936283702306</v>
+      </c>
+      <c r="C154" t="n">
+        <v>412.6975523926047</v>
+      </c>
+      <c r="D154" t="n">
+        <v>395.1287651714373</v>
+      </c>
+      <c r="E154" t="n">
+        <v>409.5602722167969</v>
+      </c>
+      <c r="F154" t="n">
+        <v>45063400</v>
+      </c>
+      <c r="G154" t="n">
+        <v>0</v>
+      </c>
+      <c r="H154" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>46128</v>
+      </c>
+      <c r="B155" t="n">
+        <v>418.1653718785589</v>
+      </c>
+      <c r="C155" t="n">
+        <v>419.1215190686066</v>
+      </c>
+      <c r="D155" t="n">
+        <v>410.4765600541581</v>
+      </c>
+      <c r="E155" t="n">
+        <v>418.5637817382812</v>
+      </c>
+      <c r="F155" t="n">
+        <v>41642400</v>
+      </c>
+      <c r="G155" t="n">
+        <v>0</v>
+      </c>
+      <c r="H155" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>46129</v>
+      </c>
+      <c r="B156" t="n">
+        <v>423.105393156615</v>
+      </c>
+      <c r="C156" t="n">
+        <v>429.8380884820792</v>
+      </c>
+      <c r="D156" t="n">
+        <v>418.9920573683891</v>
+      </c>
+      <c r="E156" t="n">
+        <v>421.0835876464844</v>
+      </c>
+      <c r="F156" t="n">
+        <v>48568200</v>
+      </c>
+      <c r="G156" t="n">
+        <v>0</v>
+      </c>
+      <c r="H156" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>46132</v>
+      </c>
+      <c r="B157" t="n">
+        <v>419.4501847919345</v>
+      </c>
+      <c r="C157" t="n">
+        <v>421.6213787702164</v>
+      </c>
+      <c r="D157" t="n">
+        <v>414.6197538627068</v>
+      </c>
+      <c r="E157" t="n">
+        <v>416.3826293945312</v>
+      </c>
+      <c r="F157" t="n">
+        <v>27582200</v>
+      </c>
+      <c r="G157" t="n">
+        <v>0</v>
+      </c>
+      <c r="H157" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>46133</v>
+      </c>
+      <c r="B158" t="n">
+        <v>418.5438369146158</v>
+      </c>
+      <c r="C158" t="n">
+        <v>425.4558284373716</v>
+      </c>
+      <c r="D158" t="n">
+        <v>415.516128706763</v>
+      </c>
+      <c r="E158" t="n">
+        <v>422.4480285644531</v>
+      </c>
+      <c r="F158" t="n">
+        <v>32048500</v>
+      </c>
+      <c r="G158" t="n">
+        <v>0</v>
+      </c>
+      <c r="H158" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>46134</v>
+      </c>
+      <c r="B159" t="n">
+        <v>424.4698510786937</v>
+      </c>
+      <c r="C159" t="n">
+        <v>431.9495495900464</v>
+      </c>
+      <c r="D159" t="n">
+        <v>421.9600330275293</v>
+      </c>
+      <c r="E159" t="n">
+        <v>431.1726989746094</v>
+      </c>
+      <c r="F159" t="n">
+        <v>29378200</v>
+      </c>
+      <c r="G159" t="n">
+        <v>0</v>
+      </c>
+      <c r="H159" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>46135</v>
+      </c>
+      <c r="B160" t="n">
+        <v>418.195296097549</v>
+      </c>
+      <c r="C160" t="n">
+        <v>421.9500690544079</v>
+      </c>
+      <c r="D160" t="n">
+        <v>409.7495112929088</v>
+      </c>
+      <c r="E160" t="n">
+        <v>414.0719909667969</v>
+      </c>
+      <c r="F160" t="n">
+        <v>38308000</v>
+      </c>
+      <c r="G160" t="n">
+        <v>0</v>
+      </c>
+      <c r="H160" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>46136</v>
+      </c>
+      <c r="B161" t="n">
+        <v>415.2870711617039</v>
+      </c>
+      <c r="C161" t="n">
+        <v>423.2348740747397</v>
+      </c>
+      <c r="D161" t="n">
+        <v>414.1217800179737</v>
+      </c>
+      <c r="E161" t="n">
+        <v>422.9061889648438</v>
+      </c>
+      <c r="F161" t="n">
+        <v>27457400</v>
+      </c>
+      <c r="G161" t="n">
+        <v>0</v>
+      </c>
+      <c r="H161" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B162" t="n">
+        <v>420.6752229306716</v>
+      </c>
+      <c r="C162" t="n">
+        <v>425.3861125683125</v>
+      </c>
+      <c r="D162" t="n">
+        <v>415.3866572294081</v>
+      </c>
+      <c r="E162" t="n">
+        <v>423.1053771972656</v>
+      </c>
+      <c r="F162" t="n">
+        <v>30867300</v>
+      </c>
+      <c r="G162" t="n">
+        <v>0</v>
+      </c>
+      <c r="H162" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B163" t="n">
+        <v>422.8563830057505</v>
+      </c>
+      <c r="C163" t="n">
+        <v>428.1847957314844</v>
+      </c>
+      <c r="D163" t="n">
+        <v>420.197146128082</v>
+      </c>
+      <c r="E163" t="n">
+        <v>427.5174865722656</v>
+      </c>
+      <c r="F163" t="n">
+        <v>30438100</v>
+      </c>
+      <c r="G163" t="n">
+        <v>0</v>
+      </c>
+      <c r="H163" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B164" t="n">
+        <v>422.8663369761165</v>
+      </c>
+      <c r="C164" t="n">
+        <v>425.0973167681131</v>
+      </c>
+      <c r="D164" t="n">
+        <v>418.593673752453</v>
+      </c>
+      <c r="E164" t="n">
+        <v>422.746826171875</v>
+      </c>
+      <c r="F164" t="n">
+        <v>38288300</v>
+      </c>
+      <c r="G164" t="n">
+        <v>0</v>
+      </c>
+      <c r="H164" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B165" t="n">
+        <v>409.1519246549498</v>
+      </c>
+      <c r="C165" t="n">
+        <v>412.7473701155562</v>
+      </c>
+      <c r="D165" t="n">
+        <v>396.4035989759817</v>
+      </c>
+      <c r="E165" t="n">
+        <v>406.1341552734375</v>
+      </c>
+      <c r="F165" t="n">
+        <v>70909400</v>
+      </c>
+      <c r="G165" t="n">
+        <v>0</v>
+      </c>
+      <c r="H165" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B166" t="n">
+        <v>411.1338775963461</v>
+      </c>
+      <c r="C166" t="n">
+        <v>415.4264794885345</v>
+      </c>
+      <c r="D166" t="n">
+        <v>408.7834174283456</v>
+      </c>
+      <c r="E166" t="n">
+        <v>412.7672729492188</v>
+      </c>
+      <c r="F166" t="n">
+        <v>31372400</v>
+      </c>
+      <c r="G166" t="n">
+        <v>0</v>
+      </c>
+      <c r="H166" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B167" t="n">
+        <v>409.8789700952638</v>
+      </c>
+      <c r="C167" t="n">
+        <v>419.0816663151199</v>
+      </c>
+      <c r="D167" t="n">
+        <v>409.1419361803058</v>
+      </c>
+      <c r="E167" t="n">
+        <v>411.9505615234375</v>
+      </c>
+      <c r="F167" t="n">
+        <v>28066500</v>
+      </c>
+      <c r="G167" t="n">
+        <v>0</v>
+      </c>
+      <c r="H167" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B168" t="n">
+        <v>413.6437044066962</v>
+      </c>
+      <c r="C168" t="n">
+        <v>415.0978030853789</v>
+      </c>
+      <c r="D168" t="n">
+        <v>407.1500007946646</v>
+      </c>
+      <c r="E168" t="n">
+        <v>409.7196044921875</v>
+      </c>
+      <c r="F168" t="n">
+        <v>25700900</v>
+      </c>
+      <c r="G168" t="n">
+        <v>0</v>
+      </c>
+      <c r="H168" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B169" t="n">
+        <v>406.3532485673598</v>
+      </c>
+      <c r="C169" t="n">
+        <v>416.7312052008779</v>
+      </c>
+      <c r="D169" t="n">
+        <v>403.4748984673602</v>
+      </c>
+      <c r="E169" t="n">
+        <v>412.2891845703125</v>
+      </c>
+      <c r="F169" t="n">
+        <v>30285900</v>
+      </c>
+      <c r="G169" t="n">
+        <v>0</v>
+      </c>
+      <c r="H169" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B170" t="n">
+        <v>418.4143764918961</v>
+      </c>
+      <c r="C170" t="n">
+        <v>426.2526378609755</v>
+      </c>
+      <c r="D170" t="n">
+        <v>417.0698495518934</v>
+      </c>
+      <c r="E170" t="n">
+        <v>419.0717163085938</v>
+      </c>
+      <c r="F170" t="n">
+        <v>34942400</v>
+      </c>
+      <c r="G170" t="n">
+        <v>0</v>
+      </c>
+      <c r="H170" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B171" t="n">
+        <v>415.7053764922729</v>
+      </c>
+      <c r="C171" t="n">
+        <v>416.9403619714099</v>
+      </c>
+      <c r="D171" t="n">
+        <v>412.3290443657605</v>
+      </c>
+      <c r="E171" t="n">
+        <v>413.4445190429688</v>
+      </c>
+      <c r="F171" t="n">
+        <v>33383800</v>
+      </c>
+      <c r="G171" t="n">
+        <v>0</v>
+      </c>
+      <c r="H171" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>46153</v>
+      </c>
+      <c r="B172" t="n">
+        <v>406.223770451025</v>
+      </c>
+      <c r="C172" t="n">
+        <v>411.0243235004914</v>
+      </c>
+      <c r="D172" t="n">
+        <v>403.8633409907068</v>
+      </c>
+      <c r="E172" t="n">
+        <v>410.9944458007812</v>
+      </c>
+      <c r="F172" t="n">
+        <v>35657900</v>
+      </c>
+      <c r="G172" t="n">
+        <v>0</v>
+      </c>
+      <c r="H172" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B173" t="n">
+        <v>412.8071154720842</v>
+      </c>
+      <c r="C173" t="n">
+        <v>413.8229876767416</v>
+      </c>
+      <c r="D173" t="n">
+        <v>404.9987623844293</v>
+      </c>
+      <c r="E173" t="n">
+        <v>406.1241760253906</v>
+      </c>
+      <c r="F173" t="n">
+        <v>38594200</v>
+      </c>
+      <c r="G173" t="n">
+        <v>0</v>
+      </c>
+      <c r="H173" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>46155</v>
+      </c>
+      <c r="B174" t="n">
+        <v>401.5726571524119</v>
+      </c>
+      <c r="C174" t="n">
+        <v>404.6700902960666</v>
+      </c>
+      <c r="D174" t="n">
+        <v>399.4114021131033</v>
+      </c>
+      <c r="E174" t="n">
+        <v>403.5745239257812</v>
+      </c>
+      <c r="F174" t="n">
+        <v>29667100</v>
+      </c>
+      <c r="G174" t="n">
+        <v>0</v>
+      </c>
+      <c r="H174" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B175" t="n">
+        <v>402.8474630718804</v>
+      </c>
+      <c r="C175" t="n">
+        <v>410.1777423108794</v>
+      </c>
+      <c r="D175" t="n">
+        <v>399.2619871856725</v>
+      </c>
+      <c r="E175" t="n">
+        <v>407.7774658203125</v>
+      </c>
+      <c r="F175" t="n">
+        <v>27077500</v>
+      </c>
+      <c r="G175" t="n">
+        <v>0</v>
+      </c>
+      <c r="H175" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B176" t="n">
+        <v>412.5979239362014</v>
+      </c>
+      <c r="C176" t="n">
+        <v>426.4418454559798</v>
+      </c>
+      <c r="D176" t="n">
+        <v>411.2434277199191</v>
+      </c>
+      <c r="E176" t="n">
+        <v>420.2170715332031</v>
+      </c>
+      <c r="F176" t="n">
+        <v>50771200</v>
+      </c>
+      <c r="G176" t="n">
+        <v>0</v>
+      </c>
+      <c r="H176" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B177" t="n">
+        <v>414.9384827190711</v>
+      </c>
+      <c r="C177" t="n">
+        <v>423.4041760233977</v>
+      </c>
+      <c r="D177" t="n">
+        <v>413.9325494355234</v>
+      </c>
+      <c r="E177" t="n">
+        <v>421.83056640625</v>
+      </c>
+      <c r="F177" t="n">
+        <v>32564100</v>
+      </c>
+      <c r="G177" t="n">
+        <v>0</v>
+      </c>
+      <c r="H177" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B178" t="n">
+        <v>428.1648698947521</v>
+      </c>
+      <c r="C178" t="n">
+        <v>430.9535870211983</v>
+      </c>
+      <c r="D178" t="n">
+        <v>414.808990493047</v>
+      </c>
+      <c r="E178" t="n">
+        <v>415.7352600097656</v>
+      </c>
+      <c r="F178" t="n">
+        <v>33018700</v>
+      </c>
+      <c r="G178" t="n">
+        <v>0</v>
+      </c>
+      <c r="H178" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B179" t="n">
+        <v>412.4983595724376</v>
+      </c>
+      <c r="C179" t="n">
+        <v>420.3963455784958</v>
+      </c>
+      <c r="D179" t="n">
+        <v>409.6399178024174</v>
+      </c>
+      <c r="E179" t="n">
+        <v>419.3605346679688</v>
+      </c>
+      <c r="F179" t="n">
+        <v>27864000</v>
+      </c>
+      <c r="G179" t="n">
+        <v>0</v>
+      </c>
+      <c r="H179" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B180" t="n">
+        <v>423.9518891931334</v>
+      </c>
+      <c r="C180" t="n">
+        <v>425.5388979071037</v>
+      </c>
+      <c r="D180" t="n">
+        <v>414.928866942535</v>
+      </c>
+      <c r="E180" t="n">
+        <v>418.3025207519531</v>
+      </c>
+      <c r="F180" t="n">
+        <v>31393500</v>
+      </c>
+      <c r="G180" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H180" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B181" t="n">
+        <v>418.7517174636334</v>
+      </c>
+      <c r="C181" t="n">
+        <v>423.602571187628</v>
+      </c>
+      <c r="D181" t="n">
+        <v>415.547726934082</v>
+      </c>
+      <c r="E181" t="n">
+        <v>417.7835388183594</v>
+      </c>
+      <c r="F181" t="n">
+        <v>22390300</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>46168</v>
+      </c>
+      <c r="B182" t="n">
+        <v>415.6475333356961</v>
+      </c>
+      <c r="C182" t="n">
+        <v>418.9812539216563</v>
+      </c>
+      <c r="D182" t="n">
+        <v>412.2439369671584</v>
+      </c>
+      <c r="E182" t="n">
+        <v>415.248291015625</v>
+      </c>
+      <c r="F182" t="n">
+        <v>30398000</v>
+      </c>
+      <c r="G182" t="n">
+        <v>0</v>
+      </c>
+      <c r="H182" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>46169</v>
+      </c>
+      <c r="B183" t="n">
+        <v>410.2377382218162</v>
+      </c>
+      <c r="C183" t="n">
+        <v>415.15846763645</v>
+      </c>
+      <c r="D183" t="n">
+        <v>408.8104019854481</v>
+      </c>
+      <c r="E183" t="n">
+        <v>411.8946228027344</v>
+      </c>
+      <c r="F183" t="n">
+        <v>28901500</v>
+      </c>
+      <c r="G183" t="n">
+        <v>0</v>
+      </c>
+      <c r="H183" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>46170</v>
+      </c>
+      <c r="B184" t="n">
+        <v>412.2040283766931</v>
+      </c>
+      <c r="C184" t="n">
+        <v>428.6829856468207</v>
+      </c>
+      <c r="D184" t="n">
+        <v>411.8946132983843</v>
+      </c>
+      <c r="E184" t="n">
+        <v>426.1876831054688</v>
+      </c>
+      <c r="F184" t="n">
+        <v>47250500</v>
+      </c>
+      <c r="G184" t="n">
+        <v>0</v>
+      </c>
+      <c r="H184" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>46171</v>
+      </c>
+      <c r="B185" t="n">
+        <v>431.7372486144539</v>
+      </c>
+      <c r="C185" t="n">
+        <v>449.4838396905727</v>
+      </c>
+      <c r="D185" t="n">
+        <v>431.5476031778621</v>
+      </c>
+      <c r="E185" t="n">
+        <v>449.3940124511719</v>
+      </c>
+      <c r="F185" t="n">
+        <v>79654400</v>
+      </c>
+      <c r="G185" t="n">
+        <v>0</v>
+      </c>
+      <c r="H185" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>46174</v>
+      </c>
+      <c r="B186" t="n">
+        <v>463.9665838370572</v>
+      </c>
+      <c r="C186" t="n">
+        <v>465.4438139523178</v>
+      </c>
+      <c r="D186" t="n">
+        <v>457.4089212477423</v>
+      </c>
+      <c r="E186" t="n">
+        <v>459.6546936035156</v>
+      </c>
+      <c r="F186" t="n">
+        <v>53628900</v>
+      </c>
+      <c r="G186" t="n">
+        <v>0</v>
+      </c>
+      <c r="H186" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>46175</v>
+      </c>
+      <c r="B187" t="n">
+        <v>446.0403151791343</v>
+      </c>
+      <c r="C187" t="n">
+        <v>452.647871293284</v>
+      </c>
+      <c r="D187" t="n">
+        <v>439.6024225764256</v>
+      </c>
+      <c r="E187" t="n">
+        <v>440.4807739257812</v>
+      </c>
+      <c r="F187" t="n">
+        <v>37036800</v>
+      </c>
+      <c r="G187" t="n">
+        <v>0</v>
+      </c>
+      <c r="H187" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>46176</v>
+      </c>
+      <c r="B188" t="n">
+        <v>437.6261891093521</v>
+      </c>
+      <c r="C188" t="n">
+        <v>439.5625463944663</v>
+      </c>
+      <c r="D188" t="n">
+        <v>423.4528579325815</v>
+      </c>
+      <c r="E188" t="n">
+        <v>426.5370483398438</v>
+      </c>
+      <c r="F188" t="n">
+        <v>39037000</v>
+      </c>
+      <c r="G188" t="n">
+        <v>0</v>
+      </c>
+      <c r="H188" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>46177</v>
+      </c>
+      <c r="B189" t="n">
+        <v>434.9911260035114</v>
+      </c>
+      <c r="C189" t="n">
+        <v>435.3304835003211</v>
+      </c>
+      <c r="D189" t="n">
+        <v>425.6087943627414</v>
+      </c>
+      <c r="E189" t="n">
+        <v>427.2456970214844</v>
+      </c>
+      <c r="F189" t="n">
+        <v>26899500</v>
+      </c>
+      <c r="G189" t="n">
+        <v>0</v>
+      </c>
+      <c r="H189" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>46178</v>
+      </c>
+      <c r="B190" t="n">
+        <v>427.5351398188391</v>
+      </c>
+      <c r="C190" t="n">
+        <v>428.6630214075295</v>
+      </c>
+      <c r="D190" t="n">
+        <v>413.6213308264138</v>
+      </c>
+      <c r="E190" t="n">
+        <v>415.8870849609375</v>
+      </c>
+      <c r="F190" t="n">
+        <v>34782200</v>
+      </c>
+      <c r="G190" t="n">
+        <v>0</v>
+      </c>
+      <c r="H190" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>46181</v>
+      </c>
+      <c r="B191" t="n">
+        <v>413.3618539280056</v>
+      </c>
+      <c r="C191" t="n">
+        <v>416.3761684433352</v>
+      </c>
+      <c r="D191" t="n">
+        <v>407.7923215775376</v>
+      </c>
+      <c r="E191" t="n">
+        <v>410.9663391113281</v>
+      </c>
+      <c r="F191" t="n">
+        <v>32086700</v>
+      </c>
+      <c r="G191" t="n">
+        <v>0</v>
+      </c>
+      <c r="H191" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>46182</v>
+      </c>
+      <c r="B192" t="n">
+        <v>408.2614433672717</v>
+      </c>
+      <c r="C192" t="n">
+        <v>411.2059125875929</v>
+      </c>
+      <c r="D192" t="n">
+        <v>397.7312786929967</v>
+      </c>
+      <c r="E192" t="n">
+        <v>402.6520080566406</v>
+      </c>
+      <c r="F192" t="n">
+        <v>35317300</v>
+      </c>
+      <c r="G192" t="n">
+        <v>0</v>
+      </c>
+      <c r="H192" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>46183</v>
+      </c>
+      <c r="B193" t="n">
+        <v>397.8011087010324</v>
+      </c>
+      <c r="C193" t="n">
+        <v>404.2789346443135</v>
+      </c>
+      <c r="D193" t="n">
+        <v>396.4137363631365</v>
+      </c>
+      <c r="E193" t="n">
+        <v>396.6133422851562</v>
+      </c>
+      <c r="F193" t="n">
+        <v>32576000</v>
+      </c>
+      <c r="G193" t="n">
+        <v>0</v>
+      </c>
+      <c r="H193" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>46184</v>
+      </c>
+      <c r="B194" t="n">
+        <v>394.4674120274286</v>
+      </c>
+      <c r="C194" t="n">
+        <v>396.1043451719433</v>
+      </c>
+      <c r="D194" t="n">
+        <v>383.278483574852</v>
+      </c>
+      <c r="E194" t="n">
+        <v>389.6065673828125</v>
+      </c>
+      <c r="F194" t="n">
+        <v>47224100</v>
+      </c>
+      <c r="G194" t="n">
+        <v>0</v>
+      </c>
+      <c r="H194" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>46185</v>
+      </c>
+      <c r="B195" t="n">
+        <v>390.6945042817559</v>
+      </c>
+      <c r="C195" t="n">
+        <v>391.003919361718</v>
+      </c>
+      <c r="D195" t="n">
+        <v>381.55171206616</v>
+      </c>
+      <c r="E195" t="n">
+        <v>390.0057983398438</v>
+      </c>
+      <c r="F195" t="n">
+        <v>34865800</v>
+      </c>
+      <c r="G195" t="n">
+        <v>0</v>
+      </c>
+      <c r="H195" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>46188</v>
+      </c>
+      <c r="B196" t="n">
+        <v>396.0544203764563</v>
+      </c>
+      <c r="C196" t="n">
+        <v>400.9951317570601</v>
+      </c>
+      <c r="D196" t="n">
+        <v>392.1118605058895</v>
+      </c>
+      <c r="E196" t="n">
+        <v>399.0088806152344</v>
+      </c>
+      <c r="F196" t="n">
+        <v>32266400</v>
+      </c>
+      <c r="G196" t="n">
+        <v>0</v>
+      </c>
+      <c r="H196" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>46189</v>
+      </c>
+      <c r="B197" t="n">
+        <v>395.0463355104342</v>
+      </c>
+      <c r="C197" t="n">
+        <v>396.094350419825</v>
+      </c>
+      <c r="D197" t="n">
+        <v>389.9559121071713</v>
+      </c>
+      <c r="E197" t="n">
+        <v>393.0899963378906</v>
+      </c>
+      <c r="F197" t="n">
+        <v>31506800</v>
+      </c>
+      <c r="G197" t="n">
+        <v>0</v>
+      </c>
+      <c r="H197" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>46190</v>
+      </c>
+      <c r="B198" t="n">
+        <v>389.5167169534323</v>
+      </c>
+      <c r="C198" t="n">
+        <v>389.6364865987809</v>
+      </c>
+      <c r="D198" t="n">
+        <v>376.6110198431126</v>
+      </c>
+      <c r="E198" t="n">
+        <v>378.1980285644531</v>
+      </c>
+      <c r="F198" t="n">
+        <v>41987800</v>
+      </c>
+      <c r="G198" t="n">
+        <v>0</v>
+      </c>
+      <c r="H198" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>46191</v>
+      </c>
+      <c r="B199" t="n">
+        <v>377.1100854858111</v>
+      </c>
+      <c r="C199" t="n">
+        <v>380.6534028700893</v>
+      </c>
+      <c r="D199" t="n">
+        <v>372.5786075934489</v>
+      </c>
+      <c r="E199" t="n">
+        <v>378.6871032714844</v>
+      </c>
+      <c r="F199" t="n">
+        <v>59714200</v>
+      </c>
+      <c r="G199" t="n">
+        <v>0</v>
+      </c>
+      <c r="H199" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>46195</v>
+      </c>
+      <c r="B200" t="n">
+        <v>375.0339909424311</v>
+      </c>
+      <c r="C200" t="n">
+        <v>380.9129385065033</v>
+      </c>
+      <c r="D200" t="n">
+        <v>366.3802985575179</v>
+      </c>
+      <c r="E200" t="n">
+        <v>366.6497802734375</v>
+      </c>
+      <c r="F200" t="n">
+        <v>45171100</v>
+      </c>
+      <c r="G200" t="n">
+        <v>0</v>
+      </c>
+      <c r="H200" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>46196</v>
+      </c>
+      <c r="B201" t="n">
+        <v>371.6802994138851</v>
+      </c>
+      <c r="C201" t="n">
+        <v>376.5112013539488</v>
+      </c>
+      <c r="D201" t="n">
+        <v>369.9735210485466</v>
+      </c>
+      <c r="E201" t="n">
+        <v>373.2373657226562</v>
+      </c>
+      <c r="F201" t="n">
+        <v>40647600</v>
+      </c>
+      <c r="G201" t="n">
+        <v>0</v>
+      </c>
+      <c r="H201" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>46197</v>
+      </c>
+      <c r="B202" t="n">
+        <v>370.8718509685315</v>
+      </c>
+      <c r="C202" t="n">
+        <v>378.1681135077346</v>
+      </c>
+      <c r="D202" t="n">
+        <v>364.0946004167936</v>
+      </c>
+      <c r="E202" t="n">
+        <v>364.7733154296875</v>
+      </c>
+      <c r="F202" t="n">
+        <v>44509900</v>
+      </c>
+      <c r="G202" t="n">
+        <v>0</v>
+      </c>
+      <c r="H202" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>46198</v>
+      </c>
+      <c r="B203" t="n">
+        <v>362.0883479855026</v>
+      </c>
+      <c r="C203" t="n">
+        <v>363.5456265920902</v>
+      </c>
+      <c r="D203" t="n">
+        <v>348.5438690238404</v>
+      </c>
+      <c r="E203" t="n">
+        <v>352.1670227050781</v>
+      </c>
+      <c r="F203" t="n">
+        <v>66179000</v>
+      </c>
+      <c r="G203" t="n">
+        <v>0</v>
+      </c>
+      <c r="H203" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>46199</v>
+      </c>
+      <c r="B204" t="n">
+        <v>356.4789138154501</v>
+      </c>
+      <c r="C204" t="n">
+        <v>375.9023402058053</v>
+      </c>
+      <c r="D204" t="n">
+        <v>354.762144454129</v>
+      </c>
+      <c r="E204" t="n">
+        <v>372.2691955566406</v>
+      </c>
+      <c r="F204" t="n">
+        <v>186201600</v>
+      </c>
+      <c r="G204" t="n">
+        <v>0</v>
+      </c>
+      <c r="H204" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" s="1" t="n">
+        <v>46202</v>
+      </c>
+      <c r="B205" t="n">
+        <v>376.790685328561</v>
+      </c>
+      <c r="C205" t="n">
+        <v>379.7850483907747</v>
+      </c>
+      <c r="D205" t="n">
+        <v>359.2237492715265</v>
+      </c>
+      <c r="E205" t="n">
+        <v>367.8774719238281</v>
+      </c>
+      <c r="F205" t="n">
+        <v>51229900</v>
+      </c>
+      <c r="G205" t="n">
+        <v>0</v>
+      </c>
+      <c r="H205" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" s="1" t="n">
+        <v>46203</v>
+      </c>
+      <c r="B206" t="n">
+        <v>370.3328407149792</v>
+      </c>
+      <c r="C206" t="n">
+        <v>373.4469734227558</v>
+      </c>
+      <c r="D206" t="n">
+        <v>366.7595808670141</v>
+      </c>
+      <c r="E206" t="n">
+        <v>372.319091796875</v>
+      </c>
+      <c r="F206" t="n">
+        <v>44945700</v>
+      </c>
+      <c r="G206" t="n">
+        <v>0</v>
+      </c>
+      <c r="H206" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" s="1" t="n">
+        <v>46204</v>
+      </c>
+      <c r="B207" t="n">
+        <v>380.1144231011508</v>
+      </c>
+      <c r="C207" t="n">
+        <v>388.099391438806</v>
+      </c>
+      <c r="D207" t="n">
+        <v>374.1856121338598</v>
+      </c>
+      <c r="E207" t="n">
+        <v>383.5579528808594</v>
+      </c>
+      <c r="F207" t="n">
+        <v>48065800</v>
+      </c>
+      <c r="G207" t="n">
+        <v>0</v>
+      </c>
+      <c r="H207" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" s="1" t="n">
+        <v>46205</v>
+      </c>
+      <c r="B208" t="n">
+        <v>383.7575696594082</v>
+      </c>
+      <c r="C208" t="n">
+        <v>391.4630649298244</v>
+      </c>
+      <c r="D208" t="n">
+        <v>382.9790365046874</v>
+      </c>
+      <c r="E208" t="n">
+        <v>389.7562561035156</v>
+      </c>
+      <c r="F208" t="n">
+        <v>42128900</v>
+      </c>
+      <c r="G208" t="n">
+        <v>0</v>
+      </c>
+      <c r="H208" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" s="1" t="n">
+        <v>46209</v>
+      </c>
+      <c r="B209" t="n">
+        <v>386.3127602401041</v>
+      </c>
+      <c r="C209" t="n">
+        <v>388.418780928489</v>
+      </c>
+      <c r="D209" t="n">
+        <v>380.5036887115837</v>
+      </c>
+      <c r="E209" t="n">
+        <v>386.0133056640625</v>
+      </c>
+      <c r="F209" t="n">
+        <v>34224500</v>
+      </c>
+      <c r="G209" t="n">
+        <v>0</v>
+      </c>
+      <c r="H209" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" s="1" t="n">
+        <v>46210</v>
+      </c>
+      <c r="B210" t="n">
+        <v>391.7525106425778</v>
+      </c>
+      <c r="C210" t="n">
+        <v>394.8267404517197</v>
+      </c>
+      <c r="D210" t="n">
+        <v>387.4905448392632</v>
+      </c>
+      <c r="E210" t="n">
+        <v>388.109375</v>
+      </c>
+      <c r="F210" t="n">
+        <v>29297500</v>
+      </c>
+      <c r="G210" t="n">
+        <v>0</v>
+      </c>
+      <c r="H210" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" s="1" t="n">
+        <v>46211</v>
+      </c>
+      <c r="B211" t="n">
+        <v>383.3084264217563</v>
+      </c>
+      <c r="C211" t="n">
+        <v>384.5860201500421</v>
+      </c>
+      <c r="D211" t="n">
+        <v>380.6134873969759</v>
+      </c>
+      <c r="E211" t="n">
+        <v>382.6197204589844</v>
+      </c>
+      <c r="F211" t="n">
+        <v>25908300</v>
+      </c>
+      <c r="G211" t="n">
+        <v>0</v>
+      </c>
+      <c r="H211" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" s="1" t="n">
+        <v>46212</v>
+      </c>
+      <c r="B212" t="n">
+        <v>373.7464342011831</v>
+      </c>
+      <c r="C212" t="n">
+        <v>383.927250494608</v>
+      </c>
+      <c r="D212" t="n">
+        <v>372.6484949692805</v>
+      </c>
+      <c r="E212" t="n">
+        <v>383.6377868652344</v>
+      </c>
+      <c r="F212" t="n">
+        <v>31083200</v>
+      </c>
+      <c r="G212" t="n">
+        <v>0</v>
+      </c>
+      <c r="H212" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" s="1" t="n">
+        <v>46213</v>
+      </c>
+      <c r="B213" t="n">
+        <v>387.071312236775</v>
+      </c>
+      <c r="C213" t="n">
+        <v>391.1736053926777</v>
+      </c>
+      <c r="D213" t="n">
+        <v>380.783162110783</v>
+      </c>
+      <c r="E213" t="n">
+        <v>384.3764038085938</v>
+      </c>
+      <c r="F213" t="n">
+        <v>24644600</v>
+      </c>
+      <c r="G213" t="n">
+        <v>0</v>
+      </c>
+      <c r="H213" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" s="1" t="n">
+        <v>46216</v>
+      </c>
+      <c r="B214" t="n">
+        <v>387.0214381132942</v>
+      </c>
+      <c r="C214" t="n">
+        <v>392.9103462310944</v>
+      </c>
+      <c r="D214" t="n">
+        <v>383.4281962321871</v>
+      </c>
+      <c r="E214" t="n">
+        <v>390.2553405761719</v>
+      </c>
+      <c r="F214" t="n">
+        <v>28914900</v>
+      </c>
+      <c r="G214" t="n">
+        <v>0</v>
+      </c>
+      <c r="H214" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" s="1" t="n">
+        <v>46217</v>
+      </c>
+      <c r="B215" t="n">
+        <v>382.1007052927433</v>
+      </c>
+      <c r="C215" t="n">
+        <v>387.460610424238</v>
+      </c>
+      <c r="D215" t="n">
+        <v>377.93852713765</v>
+      </c>
+      <c r="E215" t="n">
+        <v>384.2067260742188</v>
+      </c>
+      <c r="F215" t="n">
+        <v>27863900</v>
+      </c>
+      <c r="G215" t="n">
+        <v>0</v>
+      </c>
+      <c r="H215" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="n">
+        <v>46218</v>
+      </c>
+      <c r="B216" t="n">
+        <v>387.0713224899768</v>
+      </c>
+      <c r="C216" t="n">
+        <v>398.2103568181361</v>
+      </c>
+      <c r="D216" t="n">
+        <v>385.6739591427675</v>
+      </c>
+      <c r="E216" t="n">
+        <v>394.8866271972656</v>
+      </c>
+      <c r="F216" t="n">
+        <v>36253700</v>
+      </c>
+      <c r="G216" t="n">
+        <v>0</v>
+      </c>
+      <c r="H216" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="n">
+        <v>46219</v>
+      </c>
+      <c r="B217" t="n">
+        <v>397.5615778418718</v>
+      </c>
+      <c r="C217" t="n">
+        <v>405.2271399033625</v>
+      </c>
+      <c r="D217" t="n">
+        <v>391.3133305596497</v>
+      </c>
+      <c r="E217" t="n">
+        <v>400.3463439941406</v>
+      </c>
+      <c r="F217" t="n">
+        <v>37047400</v>
+      </c>
+      <c r="G217" t="n">
+        <v>0</v>
+      </c>
+      <c r="H217" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="n">
+        <v>46220</v>
+      </c>
+      <c r="B218" t="n">
+        <v>394.1180409920291</v>
+      </c>
+      <c r="C218" t="n">
+        <v>397.6414373419786</v>
+      </c>
+      <c r="D218" t="n">
+        <v>388.6583483977542</v>
+      </c>
+      <c r="E218" t="n">
+        <v>393.0800170898438</v>
+      </c>
+      <c r="F218" t="n">
+        <v>33049800</v>
+      </c>
+      <c r="G218" t="n">
+        <v>0</v>
+      </c>
+      <c r="H218" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="n">
+        <v>46223</v>
+      </c>
+      <c r="B219" t="n">
+        <v>390.6745569462133</v>
+      </c>
+      <c r="C219" t="n">
+        <v>402.4224305318551</v>
+      </c>
+      <c r="D219" t="n">
+        <v>388.9178541819168</v>
+      </c>
+      <c r="E219" t="n">
+        <v>401.5341186523438</v>
+      </c>
+      <c r="F219" t="n">
+        <v>27915800</v>
+      </c>
+      <c r="G219" t="n">
+        <v>0</v>
+      </c>
+      <c r="H219" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="n">
+        <v>46224</v>
+      </c>
+      <c r="B220" t="n">
+        <v>398.0606303262699</v>
+      </c>
+      <c r="C220" t="n">
+        <v>400.7156358198418</v>
+      </c>
+      <c r="D220" t="n">
+        <v>395.5753188038175</v>
+      </c>
+      <c r="E220" t="n">
+        <v>397.0026245117188</v>
+      </c>
+      <c r="F220" t="n">
+        <v>24126600</v>
+      </c>
+      <c r="G220" t="n">
+        <v>0</v>
+      </c>
+      <c r="H220" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="n">
+        <v>46225</v>
+      </c>
+      <c r="B221" t="n">
+        <v>398.8291961465565</v>
+      </c>
+      <c r="C221" t="n">
+        <v>400.246541441447</v>
+      </c>
+      <c r="D221" t="n">
+        <v>386.2329133568751</v>
+      </c>
+      <c r="E221" t="n">
+        <v>389.6065673828125</v>
+      </c>
+      <c r="F221" t="n">
+        <v>28142500</v>
+      </c>
+      <c r="G221" t="n">
+        <v>0</v>
+      </c>
+      <c r="H221" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="n">
+        <v>46226</v>
+      </c>
+      <c r="B222" t="n">
+        <v>389.237256596515</v>
+      </c>
+      <c r="C222" t="n">
+        <v>391.0438532115061</v>
+      </c>
+      <c r="D222" t="n">
+        <v>376.6809075284274</v>
+      </c>
+      <c r="E222" t="n">
+        <v>380.8630065917969</v>
+      </c>
+      <c r="F222" t="n">
+        <v>30351800</v>
+      </c>
+      <c r="G222" t="n">
+        <v>0</v>
+      </c>
+      <c r="H222" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="n">
+        <v>46227</v>
+      </c>
+      <c r="B223" t="n">
+        <v>386.3227418757343</v>
+      </c>
+      <c r="C223" t="n">
+        <v>388.299032528898</v>
+      </c>
+      <c r="D223" t="n">
+        <v>379.9347732203772</v>
+      </c>
+      <c r="E223" t="n">
+        <v>380.9828186035156</v>
+      </c>
+      <c r="F223" t="n">
+        <v>27659400</v>
+      </c>
+      <c r="G223" t="n">
+        <v>0</v>
+      </c>
+      <c r="H223" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="n">
+        <v>46230</v>
+      </c>
+      <c r="B224" t="n">
+        <v>389.3470355932277</v>
+      </c>
+      <c r="C224" t="n">
+        <v>393.4593197982184</v>
+      </c>
+      <c r="D224" t="n">
+        <v>387.2609663085435</v>
+      </c>
+      <c r="E224" t="n">
+        <v>388.368896484375</v>
+      </c>
+      <c r="F224" t="n">
+        <v>27856200</v>
+      </c>
+      <c r="G224" t="n">
+        <v>0</v>
+      </c>
+      <c r="H224" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="n">
+        <v>46231</v>
+      </c>
+      <c r="B225" t="n">
+        <v>392.4212554523594</v>
+      </c>
+      <c r="C225" t="n">
+        <v>399.567805457337</v>
+      </c>
+      <c r="D225" t="n">
+        <v>390.5647345556998</v>
+      </c>
+      <c r="E225" t="n">
+        <v>392.6109008789062</v>
+      </c>
+      <c r="F225" t="n">
+        <v>32367500</v>
+      </c>
+      <c r="G225" t="n">
+        <v>0</v>
+      </c>
+      <c r="H225" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="n">
+        <v>46232</v>
+      </c>
+      <c r="B226" t="n">
+        <v>392.6607942930367</v>
+      </c>
+      <c r="C226" t="n">
+        <v>400.4960502148319</v>
+      </c>
+      <c r="D226" t="n">
+        <v>388.0095467898306</v>
+      </c>
+      <c r="E226" t="n">
+        <v>389.8061828613281</v>
+      </c>
+      <c r="F226" t="n">
+        <v>47209000</v>
+      </c>
+      <c r="G226" t="n">
+        <v>0</v>
+      </c>
+      <c r="H226" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="n">
+        <v>46233</v>
+      </c>
+      <c r="B227" t="n">
+        <v>437.0772008696947</v>
+      </c>
+      <c r="C227" t="n">
+        <v>457.8281459885008</v>
+      </c>
+      <c r="D227" t="n">
+        <v>431.6274684759506</v>
+      </c>
+      <c r="E227" t="n">
+        <v>450.2524108886719</v>
+      </c>
+      <c r="F227" t="n">
+        <v>110160700</v>
+      </c>
+      <c r="G227" t="n">
+        <v>0</v>
+      </c>
+      <c r="H227" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="n">
+        <v>46234</v>
+      </c>
+      <c r="B228" t="n">
+        <v>449.1544591210436</v>
+      </c>
+      <c r="C228" t="n">
+        <v>465.962813447145</v>
+      </c>
+      <c r="D228" t="n">
+        <v>448.4857046349594</v>
+      </c>
+      <c r="E228" t="n">
+        <v>463.8468017578125</v>
+      </c>
+      <c r="F228" t="n">
+        <v>60846000</v>
+      </c>
+      <c r="G228" t="n">
+        <v>0</v>
+      </c>
+      <c r="H228" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="n">
+        <v>46237</v>
+      </c>
+      <c r="B229" t="n">
+        <v>475.2353605631651</v>
+      </c>
+      <c r="C229" t="n">
+        <v>490.7261876465455</v>
+      </c>
+      <c r="D229" t="n">
+        <v>474.1074789501303</v>
+      </c>
+      <c r="E229" t="n">
+        <v>486.7337036132812</v>
+      </c>
+      <c r="F229" t="n">
+        <v>66762100</v>
+      </c>
+      <c r="G229" t="n">
+        <v>0</v>
+      </c>
+      <c r="H229" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="n">
+        <v>46238</v>
+      </c>
+      <c r="B230" t="n">
+        <v>479.9964078184842</v>
+      </c>
+      <c r="C230" t="n">
+        <v>498.5015806515744</v>
+      </c>
+      <c r="D230" t="n">
+        <v>478.2696778930625</v>
+      </c>
+      <c r="E230" t="n">
+        <v>491.884033203125</v>
+      </c>
+      <c r="F230" t="n">
+        <v>50455500</v>
+      </c>
+      <c r="G230" t="n">
+        <v>0</v>
+      </c>
+      <c r="H230" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="n">
+        <v>46239</v>
+      </c>
+      <c r="B231" t="n">
+        <v>495.4273384327132</v>
+      </c>
+      <c r="C231" t="n">
+        <v>497.3038108374591</v>
+      </c>
+      <c r="D231" t="n">
+        <v>484.7674131728324</v>
+      </c>
+      <c r="E231" t="n">
+        <v>486.5440673828125</v>
+      </c>
+      <c r="F231" t="n">
+        <v>33388900</v>
+      </c>
+      <c r="G231" t="n">
+        <v>0</v>
+      </c>
+      <c r="H231" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="n">
+        <v>46240</v>
+      </c>
+      <c r="B232" t="n">
+        <v>487.6319998350186</v>
+      </c>
+      <c r="C232" t="n">
+        <v>500.6175637248969</v>
+      </c>
+      <c r="D232" t="n">
+        <v>487.6020574235835</v>
+      </c>
+      <c r="E232" t="n">
+        <v>498.9207458496094</v>
+      </c>
+      <c r="F232" t="n">
+        <v>36441500</v>
+      </c>
+      <c r="G232" t="n">
+        <v>0</v>
+      </c>
+      <c r="H232" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="n">
+        <v>46241</v>
+      </c>
+      <c r="B233" t="n">
+        <v>498.2719734340298</v>
+      </c>
+      <c r="C233" t="n">
+        <v>504.2307569931746</v>
+      </c>
+      <c r="D233" t="n">
+        <v>497.7928948509335</v>
+      </c>
+      <c r="E233" t="n">
+        <v>499.0505065917969</v>
+      </c>
+      <c r="F233" t="n">
+        <v>28846200</v>
+      </c>
+      <c r="G233" t="n">
+        <v>0</v>
+      </c>
+      <c r="H233" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="n">
+        <v>46244</v>
+      </c>
+      <c r="B234" t="n">
+        <v>502.4940586092805</v>
+      </c>
+      <c r="C234" t="n">
+        <v>512.7647021753171</v>
+      </c>
+      <c r="D234" t="n">
+        <v>501.326243590453</v>
+      </c>
+      <c r="E234" t="n">
+        <v>505.109130859375</v>
+      </c>
+      <c r="F234" t="n">
+        <v>31206100</v>
+      </c>
+      <c r="G234" t="n">
+        <v>0</v>
+      </c>
+      <c r="H234" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="n">
+        <v>46245</v>
+      </c>
+      <c r="B235" t="n">
+        <v>503.3823542433026</v>
+      </c>
+      <c r="C235" t="n">
+        <v>504.3804752506704</v>
+      </c>
+      <c r="D235" t="n">
+        <v>498.6113370464939</v>
+      </c>
+      <c r="E235" t="n">
+        <v>502.8633422851562</v>
+      </c>
+      <c r="F235" t="n">
+        <v>23049800</v>
+      </c>
+      <c r="G235" t="n">
+        <v>0</v>
+      </c>
+      <c r="H235" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="n">
+        <v>46246</v>
+      </c>
+      <c r="B236" t="n">
+        <v>499.0505227551261</v>
+      </c>
+      <c r="C236" t="n">
+        <v>500.557695253814</v>
+      </c>
+      <c r="D236" t="n">
+        <v>490.5964364344239</v>
+      </c>
+      <c r="E236" t="n">
+        <v>491.5047302246094</v>
+      </c>
+      <c r="F236" t="n">
+        <v>29001500</v>
+      </c>
+      <c r="G236" t="n">
+        <v>0</v>
+      </c>
+      <c r="H236" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="n">
+        <v>46247</v>
+      </c>
+      <c r="B237" t="n">
+        <v>492.3431478695614</v>
+      </c>
+      <c r="C237" t="n">
+        <v>500.3979918654044</v>
+      </c>
+      <c r="D237" t="n">
+        <v>492.0836571155829</v>
+      </c>
+      <c r="E237" t="n">
+        <v>495.9463806152344</v>
+      </c>
+      <c r="F237" t="n">
+        <v>23039000</v>
+      </c>
+      <c r="G237" t="n">
+        <v>0</v>
+      </c>
+      <c r="H237" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="n">
+        <v>46248</v>
+      </c>
+      <c r="B238" t="n">
+        <v>495.427334377905</v>
+      </c>
+      <c r="C238" t="n">
+        <v>499.0705004655026</v>
+      </c>
+      <c r="D238" t="n">
+        <v>492.991947114923</v>
+      </c>
+      <c r="E238" t="n">
+        <v>494.4691467285156</v>
+      </c>
+      <c r="F238" t="n">
+        <v>16217600</v>
+      </c>
+      <c r="G238" t="n">
+        <v>0</v>
+      </c>
+      <c r="H238" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="239">
+      <c r="A239" s="1" t="n">
+        <v>46251</v>
+      </c>
+      <c r="B239" t="n">
+        <v>489.2190622628328</v>
+      </c>
+      <c r="C239" t="n">
+        <v>491.7343163235842</v>
+      </c>
+      <c r="D239" t="n">
+        <v>477.5110914717105</v>
+      </c>
+      <c r="E239" t="n">
+        <v>479.4474487304688</v>
+      </c>
+      <c r="F239" t="n">
+        <v>29635800</v>
+      </c>
+      <c r="G239" t="n">
+        <v>0</v>
+      </c>
+      <c r="H239" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="240">
+      <c r="A240" s="1" t="n">
+        <v>46252</v>
+      </c>
+      <c r="B240" t="n">
+        <v>480.6352093836093</v>
+      </c>
+      <c r="C240" t="n">
+        <v>483.3600603013466</v>
+      </c>
+      <c r="D240" t="n">
+        <v>476.2534434403709</v>
+      </c>
+      <c r="E240" t="n">
+        <v>480.7250366210938</v>
+      </c>
+      <c r="F240" t="n">
+        <v>24087600</v>
+      </c>
+      <c r="G240" t="n">
+        <v>0</v>
+      </c>
+      <c r="H240" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="241">
+      <c r="A241" s="1" t="n">
+        <v>46253</v>
+      </c>
+      <c r="B241" t="n">
+        <v>479.1679704739861</v>
+      </c>
+      <c r="C241" t="n">
+        <v>488.3806080919379</v>
+      </c>
+      <c r="D241" t="n">
+        <v>478.4592826108848</v>
+      </c>
+      <c r="E241" t="n">
+        <v>483.3999938964844</v>
+      </c>
+      <c r="F241" t="n">
+        <v>19961900</v>
+      </c>
+      <c r="G241" t="n">
+        <v>0</v>
+      </c>
+      <c r="H241" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="242">
+      <c r="A242" s="1" t="n">
+        <v>46254</v>
+      </c>
+      <c r="B242" t="n">
+        <v>483.2999877929688</v>
+      </c>
+      <c r="C242" t="n">
+        <v>484.1600036621094</v>
+      </c>
+      <c r="D242" t="n">
+        <v>479.5</v>
+      </c>
+      <c r="E242" t="n">
+        <v>481.1499938964844</v>
+      </c>
+      <c r="F242" t="n">
+        <v>20020800</v>
+      </c>
+      <c r="G242" t="n">
+        <v>0.91</v>
+      </c>
+      <c r="H242" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243">
+      <c r="A243" s="1" t="n">
+        <v>46255</v>
+      </c>
+      <c r="B243" t="n">
+        <v>479.8800048828125</v>
+      </c>
+      <c r="C243" t="n">
+        <v>486.3599853515625</v>
+      </c>
+      <c r="D243" t="n">
+        <v>478.5299987792969</v>
+      </c>
+      <c r="E243" t="n">
+        <v>483.239990234375</v>
+      </c>
+      <c r="F243" t="n">
+        <v>22510800</v>
+      </c>
+      <c r="G243" t="n">
+        <v>0</v>
+      </c>
+      <c r="H243" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="244">
+      <c r="A244" s="1" t="n">
+        <v>46258</v>
+      </c>
+      <c r="B244" t="n">
+        <v>483.2099914550781</v>
+      </c>
+      <c r="C244" t="n">
+        <v>490.6099853515625</v>
+      </c>
+      <c r="D244" t="n">
+        <v>481.8599853515625</v>
+      </c>
+      <c r="E244" t="n">
+        <v>487.3099975585938</v>
+      </c>
+      <c r="F244" t="n">
+        <v>17230800</v>
+      </c>
+      <c r="G244" t="n">
+        <v>0</v>
+      </c>
+      <c r="H244" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="245">
+      <c r="A245" s="1" t="n">
+        <v>46259</v>
+      </c>
+      <c r="B245" t="n">
+        <v>485.4400024414062</v>
+      </c>
+      <c r="C245" t="n">
+        <v>492.4400024414062</v>
+      </c>
+      <c r="D245" t="n">
+        <v>484.2999877929688</v>
+      </c>
+      <c r="E245" t="n">
+        <v>491.7099914550781</v>
+      </c>
+      <c r="F245" t="n">
+        <v>19519000</v>
+      </c>
+      <c r="G245" t="n">
+        <v>0</v>
+      </c>
+      <c r="H245" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="246">
+      <c r="A246" s="1" t="n">
+        <v>46260</v>
+      </c>
+      <c r="B246" t="n">
+        <v>487.8500061035156</v>
+      </c>
+      <c r="C246" t="n">
+        <v>497.3999938964844</v>
+      </c>
+      <c r="D246" t="n">
+        <v>487.3099975585938</v>
+      </c>
+      <c r="E246" t="n">
+        <v>496.3699951171875</v>
+      </c>
+      <c r="F246" t="n">
+        <v>20758900</v>
+      </c>
+      <c r="G246" t="n">
+        <v>0</v>
+      </c>
+      <c r="H246" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" s="1" t="n">
+        <v>46261</v>
+      </c>
+      <c r="B247" t="n">
+        <v>494.8800048828125</v>
+      </c>
+      <c r="C247" t="n">
+        <v>506.4800109863281</v>
+      </c>
+      <c r="D247" t="n">
+        <v>490.0799865722656</v>
+      </c>
+      <c r="E247" t="n">
+        <v>505.0599975585938</v>
+      </c>
+      <c r="F247" t="n">
+        <v>28688800</v>
+      </c>
+      <c r="G247" t="n">
+        <v>0</v>
+      </c>
+      <c r="H247" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" s="1" t="n">
+        <v>46262</v>
+      </c>
+      <c r="B248" t="n">
+        <v>505.3299865722656</v>
+      </c>
+      <c r="C248" t="n">
+        <v>517.780029296875</v>
+      </c>
+      <c r="D248" t="n">
+        <v>504.8699951171875</v>
+      </c>
+      <c r="E248" t="n">
+        <v>513.530029296875</v>
+      </c>
+      <c r="F248" t="n">
+        <v>29207300</v>
+      </c>
+      <c r="G248" t="n">
+        <v>0</v>
+      </c>
+      <c r="H248" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" s="1" t="n">
+        <v>46265</v>
+      </c>
+      <c r="B249" t="n">
+        <v>510.3800048828125</v>
+      </c>
+      <c r="C249" t="n">
+        <v>512.1900024414062</v>
+      </c>
+      <c r="D249" t="n">
+        <v>506.3900146484375</v>
+      </c>
+      <c r="E249" t="n">
+        <v>507.2900085449219</v>
+      </c>
+      <c r="F249" t="n">
+        <v>27208900</v>
+      </c>
+      <c r="G249" t="n">
+        <v>0</v>
+      </c>
+      <c r="H249" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" s="1" t="n">
+        <v>46266</v>
+      </c>
+      <c r="B250" t="n">
+        <v>497.5199890136719</v>
+      </c>
+      <c r="C250" t="n">
+        <v>505.9700012207031</v>
+      </c>
+      <c r="D250" t="n">
+        <v>496.7799987792969</v>
+      </c>
+      <c r="E250" t="n">
+        <v>501.0199890136719</v>
+      </c>
+      <c r="F250" t="n">
+        <v>21046900</v>
+      </c>
+      <c r="G250" t="n">
+        <v>0</v>
+      </c>
+      <c r="H250" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" s="1" t="n">
+        <v>46267</v>
+      </c>
+      <c r="B251" t="n">
+        <v>499.8500061035156</v>
+      </c>
+      <c r="C251" t="n">
+        <v>500.2699890136719</v>
+      </c>
+      <c r="D251" t="n">
+        <v>493.8099975585938</v>
+      </c>
+      <c r="E251" t="n">
+        <v>496.8200073242188</v>
+      </c>
+      <c r="F251" t="n">
+        <v>15336100</v>
+      </c>
+      <c r="G251" t="n">
+        <v>0</v>
+      </c>
+      <c r="H251" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" s="1" t="n">
+        <v>46268</v>
+      </c>
+      <c r="B252" t="n">
+        <v>501.6600036621094</v>
+      </c>
+      <c r="C252" t="n">
+        <v>515.6500244140625</v>
+      </c>
+      <c r="D252" t="n">
+        <v>500.7999877929688</v>
+      </c>
+      <c r="E252" t="n">
+        <v>510.1199951171875</v>
+      </c>
+      <c r="F252" t="n">
+        <v>24125900</v>
+      </c>
+      <c r="G252" t="n">
+        <v>0</v>
+      </c>
+      <c r="H252" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" s="1" t="n">
         <v>46269</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B253" t="n">
         <v>510</v>
       </c>
-      <c r="C24" t="n">
+      <c r="C253" t="n">
         <v>511</v>
       </c>
-      <c r="D24" t="n">
+      <c r="D253" t="n">
         <v>499.3599853515625</v>
       </c>
-      <c r="E24" t="n">
+      <c r="E253" t="n">
         <v>499.7000122070312</v>
       </c>
-      <c r="F24" t="n">
+      <c r="F253" t="n">
         <v>18074400</v>
       </c>
-      <c r="G24" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" t="n">
+      <c r="G253" t="n">
+        <v>0</v>
+      </c>
+      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -5055,7 +11009,7 @@
         <v>499.36</v>
       </c>
       <c r="H2" t="n">
-        <v>17437000</v>
+        <v>18101758</v>
       </c>
       <c r="I2" t="n">
         <v>36783650</v>
@@ -5145,7 +11099,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-06 22:59:11</t>
+          <t>2026-09-07 03:08:00</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -472,16 +472,16 @@
         <v>45905</v>
       </c>
       <c r="B2" t="n">
-        <v>504.9157608525771</v>
+        <v>504.9157294675595</v>
       </c>
       <c r="C2" t="n">
-        <v>507.7920894589463</v>
+        <v>507.7920578951392</v>
       </c>
       <c r="D2" t="n">
-        <v>488.3520284612672</v>
+        <v>488.3519981058333</v>
       </c>
       <c r="E2" t="n">
-        <v>490.9605712890625</v>
+        <v>490.9605407714844</v>
       </c>
       <c r="F2" t="n">
         <v>31994800</v>
@@ -498,16 +498,16 @@
         <v>45908</v>
       </c>
       <c r="B3" t="n">
-        <v>494.0451377441344</v>
+        <v>494.0451682561979</v>
       </c>
       <c r="C3" t="n">
-        <v>497.1099483047291</v>
+        <v>497.1099790060742</v>
       </c>
       <c r="D3" t="n">
-        <v>490.990285532587</v>
+        <v>490.9903158559839</v>
       </c>
       <c r="E3" t="n">
-        <v>494.1344299316406</v>
+        <v>494.1344604492188</v>
       </c>
       <c r="F3" t="n">
         <v>16771000</v>
@@ -550,16 +550,16 @@
         <v>45910</v>
       </c>
       <c r="B5" t="n">
-        <v>498.8754600894228</v>
+        <v>498.8754294126598</v>
       </c>
       <c r="C5" t="n">
-        <v>499.1234199731124</v>
+        <v>499.1233892811019</v>
       </c>
       <c r="D5" t="n">
-        <v>492.6665349159027</v>
+        <v>492.6665046209378</v>
       </c>
       <c r="E5" t="n">
-        <v>496.2867431640625</v>
+        <v>496.2867126464844</v>
       </c>
       <c r="F5" t="n">
         <v>21611800</v>
@@ -576,16 +576,16 @@
         <v>45911</v>
       </c>
       <c r="B6" t="n">
-        <v>498.1513800613702</v>
+        <v>498.1514106544788</v>
       </c>
       <c r="C6" t="n">
-        <v>499.0638857033828</v>
+        <v>499.0639163525314</v>
       </c>
       <c r="D6" t="n">
-        <v>493.8170463660224</v>
+        <v>493.8170766929454</v>
       </c>
       <c r="E6" t="n">
-        <v>496.9215087890625</v>
+        <v>496.9215393066406</v>
       </c>
       <c r="F6" t="n">
         <v>18881600</v>
@@ -628,16 +628,16 @@
         <v>45915</v>
       </c>
       <c r="B8" t="n">
-        <v>504.6379958107742</v>
+        <v>504.6380560678344</v>
       </c>
       <c r="C8" t="n">
-        <v>511.2634457193681</v>
+        <v>511.2635067675502</v>
       </c>
       <c r="D8" t="n">
-        <v>502.8625947427051</v>
+        <v>502.8626547877709</v>
       </c>
       <c r="E8" t="n">
-        <v>511.1543579101562</v>
+        <v>511.1544189453125</v>
       </c>
       <c r="F8" t="n">
         <v>17143800</v>
@@ -706,16 +706,16 @@
         <v>45918</v>
       </c>
       <c r="B11" t="n">
-        <v>507.3159513893766</v>
+        <v>507.3159820894167</v>
       </c>
       <c r="C11" t="n">
-        <v>508.883074673213</v>
+        <v>508.883105468087</v>
       </c>
       <c r="D11" t="n">
-        <v>503.5172196080818</v>
+        <v>503.517250078243</v>
       </c>
       <c r="E11" t="n">
-        <v>504.30078125</v>
+        <v>504.3008117675781</v>
       </c>
       <c r="F11" t="n">
         <v>18913700</v>
@@ -732,16 +732,16 @@
         <v>45919</v>
       </c>
       <c r="B12" t="n">
-        <v>506.3935778296786</v>
+        <v>506.3935176630351</v>
       </c>
       <c r="C12" t="n">
-        <v>515.0622454615835</v>
+        <v>515.0621842649809</v>
       </c>
       <c r="D12" t="n">
-        <v>506.1456179521661</v>
+        <v>506.1455578149837</v>
       </c>
       <c r="E12" t="n">
-        <v>513.7034301757812</v>
+        <v>513.703369140625</v>
       </c>
       <c r="F12" t="n">
         <v>52474100</v>
@@ -810,16 +810,16 @@
         <v>45924</v>
       </c>
       <c r="B15" t="n">
-        <v>506.2150114062044</v>
+        <v>506.215041937542</v>
       </c>
       <c r="C15" t="n">
-        <v>508.297849987297</v>
+        <v>508.2978806442567</v>
       </c>
       <c r="D15" t="n">
-        <v>502.7832554652563</v>
+        <v>502.7832857896144</v>
       </c>
       <c r="E15" t="n">
-        <v>505.9868774414062</v>
+        <v>505.9869079589844</v>
       </c>
       <c r="F15" t="n">
         <v>13533700</v>
@@ -862,16 +862,16 @@
         <v>45926</v>
       </c>
       <c r="B17" t="n">
-        <v>505.8976246789574</v>
+        <v>505.8975942449135</v>
       </c>
       <c r="C17" t="n">
-        <v>509.7459665668783</v>
+        <v>509.745935901324</v>
       </c>
       <c r="D17" t="n">
-        <v>502.4856945681329</v>
+        <v>502.4856643393456</v>
       </c>
       <c r="E17" t="n">
-        <v>507.2861938476562</v>
+        <v>507.2861633300781</v>
       </c>
       <c r="F17" t="n">
         <v>16213100</v>
@@ -888,16 +888,16 @@
         <v>45929</v>
       </c>
       <c r="B18" t="n">
-        <v>507.3258652143003</v>
+        <v>507.325895548039</v>
       </c>
       <c r="C18" t="n">
-        <v>512.6321819161793</v>
+        <v>512.6322125671903</v>
       </c>
       <c r="D18" t="n">
-        <v>504.7272507672145</v>
+        <v>504.7272809455783</v>
       </c>
       <c r="E18" t="n">
-        <v>510.4005432128906</v>
+        <v>510.4005737304688</v>
       </c>
       <c r="F18" t="n">
         <v>17617800</v>
@@ -940,16 +940,16 @@
         <v>45931</v>
       </c>
       <c r="B20" t="n">
-        <v>510.5989067561486</v>
+        <v>510.5989672146665</v>
       </c>
       <c r="C20" t="n">
-        <v>516.2623314762835</v>
+        <v>516.262392605391</v>
       </c>
       <c r="D20" t="n">
-        <v>507.5143007767599</v>
+        <v>507.5143608700387</v>
       </c>
       <c r="E20" t="n">
-        <v>515.4688720703125</v>
+        <v>515.4689331054688</v>
       </c>
       <c r="F20" t="n">
         <v>22632300</v>
@@ -1044,16 +1044,16 @@
         <v>45937</v>
       </c>
       <c r="B24" t="n">
-        <v>523.9788663400786</v>
+        <v>523.9788048028778</v>
       </c>
       <c r="C24" t="n">
-        <v>525.4765536672338</v>
+        <v>525.4764919541412</v>
       </c>
       <c r="D24" t="n">
-        <v>517.1847899970462</v>
+        <v>517.1847292577561</v>
       </c>
       <c r="E24" t="n">
-        <v>519.7040405273438</v>
+        <v>519.7039794921875</v>
       </c>
       <c r="F24" t="n">
         <v>14615200</v>
@@ -1096,16 +1096,16 @@
         <v>45939</v>
       </c>
       <c r="B26" t="n">
-        <v>518.0773939158137</v>
+        <v>518.07745494396</v>
       </c>
       <c r="C26" t="n">
-        <v>520.0511445409561</v>
+        <v>520.0512058016051</v>
       </c>
       <c r="D26" t="n">
-        <v>513.1777050939771</v>
+        <v>513.1777655449532</v>
       </c>
       <c r="E26" t="n">
-        <v>518.1369018554688</v>
+        <v>518.136962890625</v>
       </c>
       <c r="F26" t="n">
         <v>18343600</v>
@@ -1148,16 +1148,16 @@
         <v>45943</v>
       </c>
       <c r="B28" t="n">
-        <v>512.1958293204747</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="C28" t="n">
-        <v>512.1958293204747</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="D28" t="n">
-        <v>507.5044476763347</v>
+        <v>507.504417299456</v>
       </c>
       <c r="E28" t="n">
-        <v>509.8551025390625</v>
+        <v>509.8550720214844</v>
       </c>
       <c r="F28" t="n">
         <v>14284200</v>
@@ -1174,16 +1174,16 @@
         <v>45944</v>
       </c>
       <c r="B29" t="n">
-        <v>506.0661970064178</v>
+        <v>506.0662879637401</v>
       </c>
       <c r="C29" t="n">
-        <v>511.0750038311887</v>
+        <v>511.0750956887641</v>
       </c>
       <c r="D29" t="n">
-        <v>501.8707057043513</v>
+        <v>501.870795907601</v>
       </c>
       <c r="E29" t="n">
-        <v>509.3789367675781</v>
+        <v>509.3790283203125</v>
       </c>
       <c r="F29" t="n">
         <v>14684300</v>
@@ -1200,16 +1200,16 @@
         <v>45945</v>
       </c>
       <c r="B30" t="n">
-        <v>510.7576863019565</v>
+        <v>510.7576556934355</v>
       </c>
       <c r="C30" t="n">
-        <v>512.9694689959882</v>
+        <v>512.9694382549203</v>
       </c>
       <c r="D30" t="n">
-        <v>505.838140631098</v>
+        <v>505.838110317394</v>
       </c>
       <c r="E30" t="n">
-        <v>509.2401428222656</v>
+        <v>509.2401123046875</v>
       </c>
       <c r="F30" t="n">
         <v>14694700</v>
@@ -1226,16 +1226,16 @@
         <v>45946</v>
       </c>
       <c r="B31" t="n">
-        <v>508.3970522124076</v>
+        <v>508.3970827878481</v>
       </c>
       <c r="C31" t="n">
-        <v>512.6321652486282</v>
+        <v>512.6321960787722</v>
       </c>
       <c r="D31" t="n">
-        <v>503.983354813105</v>
+        <v>503.9833851231019</v>
       </c>
       <c r="E31" t="n">
-        <v>507.4349365234375</v>
+        <v>507.4349670410156</v>
       </c>
       <c r="F31" t="n">
         <v>15559600</v>
@@ -1252,16 +1252,16 @@
         <v>45947</v>
       </c>
       <c r="B32" t="n">
-        <v>504.8859867353243</v>
+        <v>504.8859262397143</v>
       </c>
       <c r="C32" t="n">
-        <v>511.2734052578957</v>
+        <v>511.273343996943</v>
       </c>
       <c r="D32" t="n">
-        <v>503.1700935064365</v>
+        <v>503.1700332164253</v>
       </c>
       <c r="E32" t="n">
-        <v>509.3889465332031</v>
+        <v>509.3888854980469</v>
       </c>
       <c r="F32" t="n">
         <v>19867800</v>
@@ -1278,16 +1278,16 @@
         <v>45950</v>
       </c>
       <c r="B33" t="n">
-        <v>510.4104293345006</v>
+        <v>510.4104901121901</v>
       </c>
       <c r="C33" t="n">
-        <v>514.4670788802013</v>
+        <v>514.4671401409408</v>
       </c>
       <c r="D33" t="n">
-        <v>509.2400661752128</v>
+        <v>509.2401268135401</v>
       </c>
       <c r="E33" t="n">
-        <v>512.5726318359375</v>
+        <v>512.5726928710938</v>
       </c>
       <c r="F33" t="n">
         <v>14665600</v>
@@ -1304,16 +1304,16 @@
         <v>45951</v>
       </c>
       <c r="B34" t="n">
-        <v>513.2769402267872</v>
+        <v>513.2770012430817</v>
       </c>
       <c r="C34" t="n">
-        <v>514.4572316509175</v>
+        <v>514.4572928075203</v>
       </c>
       <c r="D34" t="n">
-        <v>508.8533142722573</v>
+        <v>508.8533747626889</v>
       </c>
       <c r="E34" t="n">
-        <v>513.4356079101562</v>
+        <v>513.4356689453125</v>
       </c>
       <c r="F34" t="n">
         <v>15586200</v>
@@ -1330,16 +1330,16 @@
         <v>45952</v>
       </c>
       <c r="B35" t="n">
-        <v>516.8971212574951</v>
+        <v>516.8971823641815</v>
       </c>
       <c r="C35" t="n">
-        <v>520.9437823737373</v>
+        <v>520.943843958813</v>
       </c>
       <c r="D35" t="n">
-        <v>513.4851913413816</v>
+        <v>513.4852520447155</v>
       </c>
       <c r="E35" t="n">
-        <v>516.2920532226562</v>
+        <v>516.2921142578125</v>
       </c>
       <c r="F35" t="n">
         <v>18962700</v>
@@ -1356,16 +1356,16 @@
         <v>45953</v>
       </c>
       <c r="B36" t="n">
-        <v>518.1964698863214</v>
+        <v>518.1964086283891</v>
       </c>
       <c r="C36" t="n">
-        <v>519.6743010066873</v>
+        <v>519.6742395740552</v>
       </c>
       <c r="D36" t="n">
-        <v>514.3778516149157</v>
+        <v>514.3777908083965</v>
       </c>
       <c r="E36" t="n">
-        <v>516.3119506835938</v>
+        <v>516.3118896484375</v>
       </c>
       <c r="F36" t="n">
         <v>14023500</v>
@@ -1434,16 +1434,16 @@
         <v>45958</v>
       </c>
       <c r="B39" t="n">
-        <v>545.5116410650497</v>
+        <v>545.511702993095</v>
       </c>
       <c r="C39" t="n">
-        <v>549.2012543795508</v>
+        <v>549.2013167264516</v>
       </c>
       <c r="D39" t="n">
-        <v>536.3569832604931</v>
+        <v>536.3570441492753</v>
       </c>
       <c r="E39" t="n">
-        <v>537.6463623046875</v>
+        <v>537.6464233398438</v>
       </c>
       <c r="F39" t="n">
         <v>29986700</v>
@@ -1460,16 +1460,16 @@
         <v>45959</v>
       </c>
       <c r="B40" t="n">
-        <v>540.4929039137475</v>
+        <v>540.4929653309738</v>
       </c>
       <c r="C40" t="n">
-        <v>541.8120671168963</v>
+        <v>541.8121286840217</v>
       </c>
       <c r="D40" t="n">
-        <v>532.3498815675878</v>
+        <v>532.3499420595073</v>
       </c>
       <c r="E40" t="n">
-        <v>537.1305541992188</v>
+        <v>537.130615234375</v>
       </c>
       <c r="F40" t="n">
         <v>36023000</v>
@@ -1538,16 +1538,16 @@
         <v>45964</v>
       </c>
       <c r="B43" t="n">
-        <v>515.5680119038287</v>
+        <v>515.5680732671589</v>
       </c>
       <c r="C43" t="n">
-        <v>520.6760087890081</v>
+        <v>520.6760707602963</v>
       </c>
       <c r="D43" t="n">
-        <v>510.3906395365282</v>
+        <v>510.3907002836433</v>
       </c>
       <c r="E43" t="n">
-        <v>512.8107299804688</v>
+        <v>512.810791015625</v>
       </c>
       <c r="F43" t="n">
         <v>22374700</v>
@@ -1564,16 +1564,16 @@
         <v>45965</v>
       </c>
       <c r="B44" t="n">
-        <v>507.5838081580189</v>
+        <v>507.5837170627558</v>
       </c>
       <c r="C44" t="n">
-        <v>511.342858187808</v>
+        <v>511.3427664179142</v>
       </c>
       <c r="D44" t="n">
-        <v>503.6957838776707</v>
+        <v>503.6956934801851</v>
       </c>
       <c r="E44" t="n">
-        <v>510.1328430175781</v>
+        <v>510.1327514648438</v>
       </c>
       <c r="F44" t="n">
         <v>20958700</v>
@@ -1668,16 +1668,16 @@
         <v>45971</v>
       </c>
       <c r="B48" t="n">
-        <v>495.9594034527451</v>
+        <v>495.9593732946225</v>
       </c>
       <c r="C48" t="n">
-        <v>502.7138276367279</v>
+        <v>502.7137970678847</v>
       </c>
       <c r="D48" t="n">
-        <v>494.7295019610679</v>
+        <v>494.7294718777327</v>
       </c>
       <c r="E48" t="n">
-        <v>501.8707580566406</v>
+        <v>501.8707275390625</v>
       </c>
       <c r="F48" t="n">
         <v>26101500</v>
@@ -1772,16 +1772,16 @@
         <v>45975</v>
       </c>
       <c r="B52" t="n">
-        <v>494.1641988801248</v>
+        <v>494.164169077362</v>
       </c>
       <c r="C52" t="n">
-        <v>507.4250879884235</v>
+        <v>507.425057385904</v>
       </c>
       <c r="D52" t="n">
-        <v>493.3806372096086</v>
+        <v>493.3806074541019</v>
       </c>
       <c r="E52" t="n">
-        <v>506.0166625976562</v>
+        <v>506.0166320800781</v>
       </c>
       <c r="F52" t="n">
         <v>28505700</v>
@@ -1824,16 +1824,16 @@
         <v>45979</v>
       </c>
       <c r="B54" t="n">
-        <v>491.3275301094218</v>
+        <v>491.3274994941962</v>
       </c>
       <c r="C54" t="n">
-        <v>498.8754444722887</v>
+        <v>498.8754133867433</v>
       </c>
       <c r="D54" t="n">
-        <v>482.8076324047851</v>
+        <v>482.8076023204449</v>
       </c>
       <c r="E54" t="n">
-        <v>489.7604370117188</v>
+        <v>489.7604064941406</v>
       </c>
       <c r="F54" t="n">
         <v>33815100</v>
@@ -1902,16 +1902,16 @@
         <v>45982</v>
       </c>
       <c r="B57" t="n">
-        <v>475.4834610910571</v>
+        <v>475.4834301610789</v>
       </c>
       <c r="C57" t="n">
-        <v>475.9008266883901</v>
+        <v>475.9007957312625</v>
       </c>
       <c r="D57" t="n">
-        <v>465.31794169549</v>
+        <v>465.3179114267742</v>
       </c>
       <c r="E57" t="n">
-        <v>469.1436767578125</v>
+        <v>469.1436462402344</v>
       </c>
       <c r="F57" t="n">
         <v>31769200</v>
@@ -1954,16 +1954,16 @@
         <v>45986</v>
       </c>
       <c r="B59" t="n">
-        <v>471.0813659766461</v>
+        <v>471.0813963074052</v>
       </c>
       <c r="C59" t="n">
-        <v>476.1293271988991</v>
+        <v>476.1293578546732</v>
       </c>
       <c r="D59" t="n">
-        <v>461.9592459889855</v>
+        <v>461.9592757324133</v>
       </c>
       <c r="E59" t="n">
-        <v>473.9829406738281</v>
+        <v>473.9829711914062</v>
       </c>
       <c r="F59" t="n">
         <v>28019800</v>
@@ -1980,16 +1980,16 @@
         <v>45987</v>
       </c>
       <c r="B60" t="n">
-        <v>483.244191691805</v>
+        <v>483.244222260298</v>
       </c>
       <c r="C60" t="n">
-        <v>485.2315832491155</v>
+        <v>485.2316139433245</v>
       </c>
       <c r="D60" t="n">
-        <v>478.1664208189674</v>
+        <v>478.1664510662567</v>
       </c>
       <c r="E60" t="n">
-        <v>482.4393005371094</v>
+        <v>482.4393310546875</v>
       </c>
       <c r="F60" t="n">
         <v>25709100</v>
@@ -2084,16 +2084,16 @@
         <v>45994</v>
       </c>
       <c r="B64" t="n">
-        <v>473.3171775583083</v>
+        <v>473.3172079858148</v>
       </c>
       <c r="C64" t="n">
-        <v>481.1872310931236</v>
+        <v>481.1872620265617</v>
       </c>
       <c r="D64" t="n">
-        <v>472.2042431453193</v>
+        <v>472.2042735012802</v>
       </c>
       <c r="E64" t="n">
-        <v>474.7182922363281</v>
+        <v>474.7183227539062</v>
       </c>
       <c r="F64" t="n">
         <v>34615100</v>
@@ -2110,16 +2110,16 @@
         <v>45995</v>
       </c>
       <c r="B65" t="n">
-        <v>476.7355071807625</v>
+        <v>476.7355376297969</v>
       </c>
       <c r="C65" t="n">
-        <v>478.2856702042714</v>
+        <v>478.2857007523145</v>
       </c>
       <c r="D65" t="n">
-        <v>473.4861025034468</v>
+        <v>473.4861327449422</v>
       </c>
       <c r="E65" t="n">
-        <v>477.8086853027344</v>
+        <v>477.8087158203125</v>
       </c>
       <c r="F65" t="n">
         <v>22318200</v>
@@ -2136,16 +2136,16 @@
         <v>45996</v>
       </c>
       <c r="B66" t="n">
-        <v>479.4780643507397</v>
+        <v>479.4781253050461</v>
       </c>
       <c r="C66" t="n">
-        <v>480.3525214663767</v>
+        <v>480.3525825318497</v>
       </c>
       <c r="D66" t="n">
-        <v>475.8610275749173</v>
+        <v>475.861088069403</v>
       </c>
       <c r="E66" t="n">
-        <v>480.1140441894531</v>
+        <v>480.1141052246094</v>
       </c>
       <c r="F66" t="n">
         <v>22608700</v>
@@ -2162,16 +2162,16 @@
         <v>45999</v>
       </c>
       <c r="B67" t="n">
-        <v>481.8331998835391</v>
+        <v>481.8331697469475</v>
       </c>
       <c r="C67" t="n">
-        <v>489.1964595164875</v>
+        <v>489.1964289193556</v>
       </c>
       <c r="D67" t="n">
-        <v>481.3264052911177</v>
+        <v>481.3263751862239</v>
       </c>
       <c r="E67" t="n">
-        <v>487.9245300292969</v>
+        <v>487.9244995117188</v>
       </c>
       <c r="F67" t="n">
         <v>21965900</v>
@@ -2188,16 +2188,16 @@
         <v>46000</v>
       </c>
       <c r="B68" t="n">
-        <v>486.0166380400449</v>
+        <v>486.016607703579</v>
       </c>
       <c r="C68" t="n">
-        <v>489.0175885389743</v>
+        <v>489.0175580151932</v>
       </c>
       <c r="D68" t="n">
-        <v>485.4204144751398</v>
+        <v>485.4203841758892</v>
       </c>
       <c r="E68" t="n">
-        <v>488.918212890625</v>
+        <v>488.9181823730469</v>
       </c>
       <c r="F68" t="n">
         <v>14696100</v>
@@ -2240,16 +2240,16 @@
         <v>46002</v>
       </c>
       <c r="B70" t="n">
-        <v>473.6252433732215</v>
+        <v>473.6252734590456</v>
       </c>
       <c r="C70" t="n">
-        <v>482.9659780129214</v>
+        <v>482.9660086920916</v>
       </c>
       <c r="D70" t="n">
-        <v>472.8600781839672</v>
+        <v>472.8601082211862</v>
       </c>
       <c r="E70" t="n">
-        <v>480.422119140625</v>
+        <v>480.4221496582031</v>
       </c>
       <c r="F70" t="n">
         <v>24669200</v>
@@ -2292,16 +2292,16 @@
         <v>46006</v>
       </c>
       <c r="B72" t="n">
-        <v>477.0733729131614</v>
+        <v>477.0733420562278</v>
       </c>
       <c r="C72" t="n">
-        <v>477.6894594742654</v>
+        <v>477.6894285774835</v>
       </c>
       <c r="D72" t="n">
-        <v>469.5411415575728</v>
+        <v>469.5411111878212</v>
       </c>
       <c r="E72" t="n">
-        <v>471.82666015625</v>
+        <v>471.8266296386719</v>
       </c>
       <c r="F72" t="n">
         <v>23727700</v>
@@ -2318,16 +2318,16 @@
         <v>46007</v>
       </c>
       <c r="B73" t="n">
-        <v>468.9349812365753</v>
+        <v>468.9350114671635</v>
       </c>
       <c r="C73" t="n">
-        <v>474.8772929441188</v>
+        <v>474.8773235577871</v>
       </c>
       <c r="D73" t="n">
-        <v>467.9114757916915</v>
+        <v>467.911505956298</v>
       </c>
       <c r="E73" t="n">
-        <v>473.3867492675781</v>
+        <v>473.3867797851562</v>
       </c>
       <c r="F73" t="n">
         <v>20705600</v>
@@ -2448,16 +2448,16 @@
         <v>46014</v>
       </c>
       <c r="B78" t="n">
-        <v>481.9226163967179</v>
+        <v>481.922585996358</v>
       </c>
       <c r="C78" t="n">
-        <v>484.7546252629152</v>
+        <v>484.7545946839082</v>
       </c>
       <c r="D78" t="n">
-        <v>481.6841087754749</v>
+        <v>481.6840783901604</v>
       </c>
       <c r="E78" t="n">
-        <v>483.7808227539062</v>
+        <v>483.7807922363281</v>
       </c>
       <c r="F78" t="n">
         <v>14683600</v>
@@ -2474,16 +2474,16 @@
         <v>46015</v>
       </c>
       <c r="B79" t="n">
-        <v>482.6181758435609</v>
+        <v>482.6181454723109</v>
       </c>
       <c r="C79" t="n">
-        <v>486.0762481946253</v>
+        <v>486.0762176057581</v>
       </c>
       <c r="D79" t="n">
-        <v>481.7735283363114</v>
+        <v>481.7734980182152</v>
       </c>
       <c r="E79" t="n">
-        <v>484.9434204101562</v>
+        <v>484.9433898925781</v>
       </c>
       <c r="F79" t="n">
         <v>5855900</v>
@@ -2500,16 +2500,16 @@
         <v>46017</v>
       </c>
       <c r="B80" t="n">
-        <v>483.6417106195734</v>
+        <v>483.6416801645685</v>
       </c>
       <c r="C80" t="n">
-        <v>485.0428254417362</v>
+        <v>485.0427948985028</v>
       </c>
       <c r="D80" t="n">
-        <v>482.8964387136479</v>
+        <v>482.8964083055729</v>
       </c>
       <c r="E80" t="n">
-        <v>484.6354064941406</v>
+        <v>484.6353759765625</v>
       </c>
       <c r="F80" t="n">
         <v>8842200</v>
@@ -2578,16 +2578,16 @@
         <v>46022</v>
       </c>
       <c r="B83" t="n">
-        <v>484.7645645601486</v>
+        <v>484.7645337762783</v>
       </c>
       <c r="C83" t="n">
-        <v>485.0626915008752</v>
+        <v>485.0626606980731</v>
       </c>
       <c r="D83" t="n">
-        <v>480.253177052155</v>
+        <v>480.2531465547701</v>
       </c>
       <c r="E83" t="n">
-        <v>480.5711669921875</v>
+        <v>480.5711364746094</v>
       </c>
       <c r="F83" t="n">
         <v>15601600</v>
@@ -2630,16 +2630,16 @@
         <v>46027</v>
       </c>
       <c r="B85" t="n">
-        <v>471.071443053882</v>
+        <v>471.0714124582114</v>
       </c>
       <c r="C85" t="n">
-        <v>473.0687813775576</v>
+        <v>473.0687506521617</v>
       </c>
       <c r="D85" t="n">
-        <v>466.5401924921144</v>
+        <v>466.5401621907445</v>
       </c>
       <c r="E85" t="n">
-        <v>469.8690795898438</v>
+        <v>469.8690490722656</v>
       </c>
       <c r="F85" t="n">
         <v>25250300</v>
@@ -2682,16 +2682,16 @@
         <v>46029</v>
       </c>
       <c r="B87" t="n">
-        <v>476.7355161407656</v>
+        <v>476.7355464241618</v>
       </c>
       <c r="C87" t="n">
-        <v>486.6128550141313</v>
+        <v>486.61288592496</v>
       </c>
       <c r="D87" t="n">
-        <v>474.936929133209</v>
+        <v>474.9369593023546</v>
       </c>
       <c r="E87" t="n">
-        <v>480.422119140625</v>
+        <v>480.4221496582031</v>
       </c>
       <c r="F87" t="n">
         <v>25564200</v>
@@ -2786,16 +2786,16 @@
         <v>46035</v>
       </c>
       <c r="B91" t="n">
-        <v>471.6875193976834</v>
+        <v>471.687550175263</v>
       </c>
       <c r="C91" t="n">
-        <v>472.7805908527595</v>
+        <v>472.7806217016619</v>
       </c>
       <c r="D91" t="n">
-        <v>463.0125743921384</v>
+        <v>463.0126046036784</v>
       </c>
       <c r="E91" t="n">
-        <v>467.7028198242188</v>
+        <v>467.7028503417969</v>
       </c>
       <c r="F91" t="n">
         <v>28545800</v>
@@ -2864,16 +2864,16 @@
         <v>46038</v>
       </c>
       <c r="B94" t="n">
-        <v>454.9437666153887</v>
+        <v>454.9437362325269</v>
       </c>
       <c r="C94" t="n">
-        <v>460.2699922453042</v>
+        <v>460.2699615067369</v>
       </c>
       <c r="D94" t="n">
-        <v>453.6023014516422</v>
+        <v>453.6022711583685</v>
       </c>
       <c r="E94" t="n">
-        <v>456.9609680175781</v>
+        <v>456.9609375</v>
       </c>
       <c r="F94" t="n">
         <v>34246700</v>
@@ -2916,16 +2916,16 @@
         <v>46043</v>
       </c>
       <c r="B96" t="n">
-        <v>449.7467088388933</v>
+        <v>449.7467399398739</v>
       </c>
       <c r="C96" t="n">
-        <v>449.8361378186282</v>
+        <v>449.836168925793</v>
       </c>
       <c r="D96" t="n">
-        <v>435.9144504613163</v>
+        <v>435.9144806057656</v>
       </c>
       <c r="E96" t="n">
-        <v>441.3102111816406</v>
+        <v>441.3102416992188</v>
       </c>
       <c r="F96" t="n">
         <v>37980500</v>
@@ -3046,16 +3046,16 @@
         <v>46050</v>
       </c>
       <c r="B101" t="n">
-        <v>480.1637149068934</v>
+        <v>480.1637455245844</v>
       </c>
       <c r="C101" t="n">
-        <v>480.6903724414303</v>
+        <v>480.6904030927037</v>
       </c>
       <c r="D101" t="n">
-        <v>474.9865685400099</v>
+        <v>474.9865988275796</v>
       </c>
       <c r="E101" t="n">
-        <v>478.5936889648438</v>
+        <v>478.5937194824219</v>
       </c>
       <c r="F101" t="n">
         <v>36875400</v>
@@ -3072,16 +3072,16 @@
         <v>46051</v>
       </c>
       <c r="B102" t="n">
-        <v>437.2162272399066</v>
+        <v>437.2161962654454</v>
       </c>
       <c r="C102" t="n">
-        <v>439.7104135269112</v>
+        <v>439.7103823757502</v>
       </c>
       <c r="D102" t="n">
-        <v>418.365815756604</v>
+        <v>418.365786117595</v>
       </c>
       <c r="E102" t="n">
-        <v>430.7671508789062</v>
+        <v>430.7671203613281</v>
       </c>
       <c r="F102" t="n">
         <v>128855300</v>
@@ -3098,16 +3098,16 @@
         <v>46052</v>
       </c>
       <c r="B103" t="n">
-        <v>436.4013853645445</v>
+        <v>436.4014165119217</v>
       </c>
       <c r="C103" t="n">
-        <v>436.8286672682951</v>
+        <v>436.8286984461687</v>
       </c>
       <c r="D103" t="n">
-        <v>423.7615739365565</v>
+        <v>423.7616041817895</v>
       </c>
       <c r="E103" t="n">
-        <v>427.5773620605469</v>
+        <v>427.577392578125</v>
       </c>
       <c r="F103" t="n">
         <v>58566800</v>
@@ -3150,16 +3150,16 @@
         <v>46056</v>
       </c>
       <c r="B105" t="n">
-        <v>419.3495781995532</v>
+        <v>419.3496095186449</v>
       </c>
       <c r="C105" t="n">
-        <v>419.3893041977899</v>
+        <v>419.3893355198486</v>
       </c>
       <c r="D105" t="n">
-        <v>405.9843574339844</v>
+        <v>405.9843877548956</v>
       </c>
       <c r="E105" t="n">
-        <v>408.6176452636719</v>
+        <v>408.61767578125</v>
       </c>
       <c r="F105" t="n">
         <v>61424100</v>
@@ -3176,16 +3176,16 @@
         <v>46057</v>
       </c>
       <c r="B106" t="n">
-        <v>408.4089957411405</v>
+        <v>408.4089654586022</v>
       </c>
       <c r="C106" t="n">
-        <v>417.1535071208501</v>
+        <v>417.1534761899275</v>
       </c>
       <c r="D106" t="n">
-        <v>406.6600813351222</v>
+        <v>406.6600511822617</v>
       </c>
       <c r="E106" t="n">
-        <v>411.5788879394531</v>
+        <v>411.578857421875</v>
       </c>
       <c r="F106" t="n">
         <v>45012400</v>
@@ -3202,16 +3202,16 @@
         <v>46058</v>
       </c>
       <c r="B107" t="n">
-        <v>404.8714440282318</v>
+        <v>404.8714124431945</v>
       </c>
       <c r="C107" t="n">
-        <v>405.7260079125925</v>
+        <v>405.7259762608884</v>
       </c>
       <c r="D107" t="n">
-        <v>389.8467674620769</v>
+        <v>389.8467370491522</v>
       </c>
       <c r="E107" t="n">
-        <v>391.1882629394531</v>
+        <v>391.188232421875</v>
       </c>
       <c r="F107" t="n">
         <v>66289200</v>
@@ -3280,16 +3280,16 @@
         <v>46063</v>
       </c>
       <c r="B110" t="n">
-        <v>416.9746165751398</v>
+        <v>416.9746475616288</v>
       </c>
       <c r="C110" t="n">
-        <v>421.009018998737</v>
+        <v>421.0090502850332</v>
       </c>
       <c r="D110" t="n">
-        <v>410.0982587889407</v>
+        <v>410.0982892644293</v>
       </c>
       <c r="E110" t="n">
-        <v>410.6646423339844</v>
+        <v>410.6646728515625</v>
       </c>
       <c r="F110" t="n">
         <v>44857900</v>
@@ -3358,16 +3358,16 @@
         <v>46066</v>
       </c>
       <c r="B113" t="n">
-        <v>401.900281272875</v>
+        <v>401.900312028468</v>
       </c>
       <c r="C113" t="n">
-        <v>402.9834060634867</v>
+        <v>402.9834369019663</v>
       </c>
       <c r="D113" t="n">
-        <v>395.5406038478973</v>
+        <v>395.5406341168134</v>
       </c>
       <c r="E113" t="n">
-        <v>398.7900085449219</v>
+        <v>398.7900390625</v>
       </c>
       <c r="F113" t="n">
         <v>34091600</v>
@@ -3384,16 +3384,16 @@
         <v>46070</v>
       </c>
       <c r="B114" t="n">
-        <v>396.7032617740463</v>
+        <v>396.7032310749887</v>
       </c>
       <c r="C114" t="n">
-        <v>397.9950542597942</v>
+        <v>397.9950234607705</v>
       </c>
       <c r="D114" t="n">
-        <v>392.0428257724806</v>
+        <v>392.0427954340728</v>
       </c>
       <c r="E114" t="n">
-        <v>394.3581237792969</v>
+        <v>394.3580932617188</v>
       </c>
       <c r="F114" t="n">
         <v>32078800</v>
@@ -3410,16 +3410,16 @@
         <v>46071</v>
       </c>
       <c r="B115" t="n">
-        <v>395.6201070500213</v>
+        <v>395.6201374553349</v>
       </c>
       <c r="C115" t="n">
-        <v>400.0221720919145</v>
+        <v>400.0222028355481</v>
       </c>
       <c r="D115" t="n">
-        <v>393.8215201082963</v>
+        <v>393.8215503753798</v>
       </c>
       <c r="E115" t="n">
-        <v>397.0808410644531</v>
+        <v>397.0808715820312</v>
       </c>
       <c r="F115" t="n">
         <v>23223400</v>
@@ -11099,7 +11099,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-07 03:08:00</t>
+          <t>2026-09-08 08:51:52</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H253"/>
+  <dimension ref="A1:H252"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45905</v>
+        <v>45909</v>
       </c>
       <c r="B2" t="n">
-        <v>504.9157294675595</v>
+        <v>497.3380566961471</v>
       </c>
       <c r="C2" t="n">
-        <v>507.7920578951392</v>
+        <v>498.1513723235736</v>
       </c>
       <c r="D2" t="n">
-        <v>488.3519981058333</v>
+        <v>493.6385148559323</v>
       </c>
       <c r="E2" t="n">
-        <v>490.9605407714844</v>
+        <v>494.3427124023438</v>
       </c>
       <c r="F2" t="n">
-        <v>31994800</v>
+        <v>14410500</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45908</v>
+        <v>45910</v>
       </c>
       <c r="B3" t="n">
-        <v>494.0451682561979</v>
+        <v>498.8754294126598</v>
       </c>
       <c r="C3" t="n">
-        <v>497.1099790060742</v>
+        <v>499.1233892811019</v>
       </c>
       <c r="D3" t="n">
-        <v>490.9903158559839</v>
+        <v>492.6665046209378</v>
       </c>
       <c r="E3" t="n">
-        <v>494.1344604492188</v>
+        <v>496.2867126464844</v>
       </c>
       <c r="F3" t="n">
-        <v>16771000</v>
+        <v>21611800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45909</v>
+        <v>45911</v>
       </c>
       <c r="B4" t="n">
-        <v>497.3380566961471</v>
+        <v>498.1513800613702</v>
       </c>
       <c r="C4" t="n">
-        <v>498.1513723235736</v>
+        <v>499.0638857033828</v>
       </c>
       <c r="D4" t="n">
-        <v>493.6385148559323</v>
+        <v>493.8170463660224</v>
       </c>
       <c r="E4" t="n">
-        <v>494.3427124023438</v>
+        <v>496.9215087890625</v>
       </c>
       <c r="F4" t="n">
-        <v>14410500</v>
+        <v>18881600</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45910</v>
+        <v>45912</v>
       </c>
       <c r="B5" t="n">
-        <v>498.8754294126598</v>
+        <v>502.515443953693</v>
       </c>
       <c r="C5" t="n">
-        <v>499.1233892811019</v>
+        <v>508.3672905695674</v>
       </c>
       <c r="D5" t="n">
-        <v>492.6665046209378</v>
+        <v>499.7383056416454</v>
       </c>
       <c r="E5" t="n">
-        <v>496.2867126464844</v>
+        <v>505.7389221191406</v>
       </c>
       <c r="F5" t="n">
-        <v>21611800</v>
+        <v>23624900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45911</v>
+        <v>45915</v>
       </c>
       <c r="B6" t="n">
-        <v>498.1514106544788</v>
+        <v>504.6380259393043</v>
       </c>
       <c r="C6" t="n">
-        <v>499.0639163525314</v>
+        <v>511.2634762434591</v>
       </c>
       <c r="D6" t="n">
-        <v>493.8170766929454</v>
+        <v>502.862624765238</v>
       </c>
       <c r="E6" t="n">
-        <v>496.9215393066406</v>
+        <v>511.1543884277344</v>
       </c>
       <c r="F6" t="n">
-        <v>18881600</v>
+        <v>17143800</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45912</v>
+        <v>45916</v>
       </c>
       <c r="B7" t="n">
-        <v>502.5154742767582</v>
+        <v>512.6619733694059</v>
       </c>
       <c r="C7" t="n">
-        <v>508.367321245748</v>
+        <v>513.0090929577493</v>
       </c>
       <c r="D7" t="n">
-        <v>499.738335797131</v>
+        <v>504.449544036503</v>
       </c>
       <c r="E7" t="n">
-        <v>505.7389526367188</v>
+        <v>504.8859558105469</v>
       </c>
       <c r="F7" t="n">
-        <v>23624900</v>
+        <v>19711900</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45915</v>
+        <v>45917</v>
       </c>
       <c r="B8" t="n">
-        <v>504.6380560678344</v>
+        <v>506.4530503919847</v>
       </c>
       <c r="C8" t="n">
-        <v>511.2635067675502</v>
+        <v>507.1175961354426</v>
       </c>
       <c r="D8" t="n">
-        <v>502.8626547877709</v>
+        <v>501.8013209933916</v>
       </c>
       <c r="E8" t="n">
-        <v>511.1544189453125</v>
+        <v>505.8579406738281</v>
       </c>
       <c r="F8" t="n">
-        <v>17143800</v>
+        <v>15816600</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45916</v>
+        <v>45918</v>
       </c>
       <c r="B9" t="n">
-        <v>512.6619733694059</v>
+        <v>507.3159820894167</v>
       </c>
       <c r="C9" t="n">
-        <v>513.0090929577493</v>
+        <v>508.883105468087</v>
       </c>
       <c r="D9" t="n">
-        <v>504.449544036503</v>
+        <v>503.517250078243</v>
       </c>
       <c r="E9" t="n">
-        <v>504.8859558105469</v>
+        <v>504.3008117675781</v>
       </c>
       <c r="F9" t="n">
-        <v>19711900</v>
+        <v>18913700</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45917</v>
+        <v>45919</v>
       </c>
       <c r="B10" t="n">
-        <v>506.4530503919847</v>
+        <v>506.3935176630351</v>
       </c>
       <c r="C10" t="n">
-        <v>507.1175961354426</v>
+        <v>515.0621842649809</v>
       </c>
       <c r="D10" t="n">
-        <v>501.8013209933916</v>
+        <v>506.1455578149837</v>
       </c>
       <c r="E10" t="n">
-        <v>505.8579406738281</v>
+        <v>513.703369140625</v>
       </c>
       <c r="F10" t="n">
-        <v>15816600</v>
+        <v>52474100</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45918</v>
+        <v>45922</v>
       </c>
       <c r="B11" t="n">
-        <v>507.3159820894167</v>
+        <v>511.3826037577857</v>
       </c>
       <c r="C11" t="n">
-        <v>508.883105468087</v>
+        <v>513.5150225661836</v>
       </c>
       <c r="D11" t="n">
-        <v>503.517250078243</v>
+        <v>508.3574445613838</v>
       </c>
       <c r="E11" t="n">
-        <v>504.3008117675781</v>
+        <v>510.2518920898438</v>
       </c>
       <c r="F11" t="n">
-        <v>18913700</v>
+        <v>20009300</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45919</v>
+        <v>45923</v>
       </c>
       <c r="B12" t="n">
-        <v>506.3935176630351</v>
+        <v>509.6071158201621</v>
       </c>
       <c r="C12" t="n">
-        <v>515.0621842649809</v>
+        <v>510.3907077578639</v>
       </c>
       <c r="D12" t="n">
-        <v>506.1455578149837</v>
+        <v>503.170087241692</v>
       </c>
       <c r="E12" t="n">
-        <v>513.703369140625</v>
+        <v>505.0744323730469</v>
       </c>
       <c r="F12" t="n">
-        <v>52474100</v>
+        <v>19799600</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45922</v>
+        <v>45924</v>
       </c>
       <c r="B13" t="n">
-        <v>511.382573172581</v>
+        <v>506.215041937542</v>
       </c>
       <c r="C13" t="n">
-        <v>513.5149918534414</v>
+        <v>508.2978806442567</v>
       </c>
       <c r="D13" t="n">
-        <v>508.3574141571104</v>
+        <v>502.7832857896144</v>
       </c>
       <c r="E13" t="n">
-        <v>510.2518615722656</v>
+        <v>505.9869079589844</v>
       </c>
       <c r="F13" t="n">
-        <v>20009300</v>
+        <v>13533700</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45923</v>
+        <v>45925</v>
       </c>
       <c r="B14" t="n">
-        <v>509.6071158201621</v>
+        <v>504.1519897302721</v>
       </c>
       <c r="C14" t="n">
-        <v>510.3907077578639</v>
+        <v>505.8480570147519</v>
       </c>
       <c r="D14" t="n">
-        <v>503.170087241692</v>
+        <v>500.9186136455738</v>
       </c>
       <c r="E14" t="n">
-        <v>505.0744323730469</v>
+        <v>502.8923645019531</v>
       </c>
       <c r="F14" t="n">
-        <v>19799600</v>
+        <v>15786500</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45924</v>
+        <v>45926</v>
       </c>
       <c r="B15" t="n">
-        <v>506.215041937542</v>
+        <v>505.8976246789574</v>
       </c>
       <c r="C15" t="n">
-        <v>508.2978806442567</v>
+        <v>509.7459665668783</v>
       </c>
       <c r="D15" t="n">
-        <v>502.7832857896144</v>
+        <v>502.4856945681329</v>
       </c>
       <c r="E15" t="n">
-        <v>505.9869079589844</v>
+        <v>507.2861938476562</v>
       </c>
       <c r="F15" t="n">
-        <v>13533700</v>
+        <v>16213100</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45925</v>
+        <v>45929</v>
       </c>
       <c r="B16" t="n">
-        <v>504.1519897302721</v>
+        <v>507.3258652143003</v>
       </c>
       <c r="C16" t="n">
-        <v>505.8480570147519</v>
+        <v>512.6321819161793</v>
       </c>
       <c r="D16" t="n">
-        <v>500.9186136455738</v>
+        <v>504.7272507672145</v>
       </c>
       <c r="E16" t="n">
-        <v>502.8923645019531</v>
+        <v>510.4005432128906</v>
       </c>
       <c r="F16" t="n">
-        <v>15786500</v>
+        <v>17617800</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45926</v>
+        <v>45930</v>
       </c>
       <c r="B17" t="n">
-        <v>505.8975942449135</v>
+        <v>509.0516808953516</v>
       </c>
       <c r="C17" t="n">
-        <v>509.745935901324</v>
+        <v>513.9315141469417</v>
       </c>
       <c r="D17" t="n">
-        <v>502.4856643393456</v>
+        <v>505.5009089039439</v>
       </c>
       <c r="E17" t="n">
-        <v>507.2861633300781</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="F17" t="n">
-        <v>16213100</v>
+        <v>19728200</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45929</v>
+        <v>45931</v>
       </c>
       <c r="B18" t="n">
-        <v>507.325895548039</v>
+        <v>510.5989672146665</v>
       </c>
       <c r="C18" t="n">
-        <v>512.6322125671903</v>
+        <v>516.262392605391</v>
       </c>
       <c r="D18" t="n">
-        <v>504.7272809455783</v>
+        <v>507.5143608700387</v>
       </c>
       <c r="E18" t="n">
-        <v>510.4005737304688</v>
+        <v>515.4689331054688</v>
       </c>
       <c r="F18" t="n">
-        <v>17617800</v>
+        <v>22632300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45930</v>
+        <v>45932</v>
       </c>
       <c r="B19" t="n">
-        <v>509.0516808953516</v>
+        <v>513.4158303625842</v>
       </c>
       <c r="C19" t="n">
-        <v>513.9315141469417</v>
+        <v>517.343476169315</v>
       </c>
       <c r="D19" t="n">
-        <v>505.5009089039439</v>
+        <v>506.5126054199375</v>
       </c>
       <c r="E19" t="n">
-        <v>513.7232666015625</v>
+        <v>511.5313110351562</v>
       </c>
       <c r="F19" t="n">
-        <v>19728200</v>
+        <v>21222900</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45931</v>
+        <v>45933</v>
       </c>
       <c r="B20" t="n">
-        <v>510.5989672146665</v>
+        <v>512.8801529316524</v>
       </c>
       <c r="C20" t="n">
-        <v>516.262392605391</v>
+        <v>516.2425031799986</v>
       </c>
       <c r="D20" t="n">
-        <v>507.5143608700387</v>
+        <v>510.7973143114264</v>
       </c>
       <c r="E20" t="n">
-        <v>515.4689331054688</v>
+        <v>513.1281127929688</v>
       </c>
       <c r="F20" t="n">
-        <v>22632300</v>
+        <v>15112300</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45932</v>
+        <v>45936</v>
       </c>
       <c r="B21" t="n">
-        <v>513.4157691025699</v>
+        <v>514.377848960065</v>
       </c>
       <c r="C21" t="n">
-        <v>517.3434144406598</v>
+        <v>526.6965386672223</v>
       </c>
       <c r="D21" t="n">
-        <v>506.5125449836057</v>
+        <v>513.9712214168786</v>
       </c>
       <c r="E21" t="n">
-        <v>511.53125</v>
+        <v>524.256591796875</v>
       </c>
       <c r="F21" t="n">
-        <v>21222900</v>
+        <v>21388600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45933</v>
+        <v>45937</v>
       </c>
       <c r="B22" t="n">
-        <v>512.8800919259904</v>
+        <v>523.9788048028778</v>
       </c>
       <c r="C22" t="n">
-        <v>516.2424417743944</v>
+        <v>525.4764919541412</v>
       </c>
       <c r="D22" t="n">
-        <v>510.7972535535121</v>
+        <v>517.1847292577561</v>
       </c>
       <c r="E22" t="n">
-        <v>513.1280517578125</v>
+        <v>519.7039794921875</v>
       </c>
       <c r="F22" t="n">
-        <v>15112300</v>
+        <v>14615200</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45936</v>
+        <v>45938</v>
       </c>
       <c r="B23" t="n">
-        <v>514.377848960065</v>
+        <v>519.0097599169904</v>
       </c>
       <c r="C23" t="n">
-        <v>526.6965386672223</v>
+        <v>522.6497936321297</v>
       </c>
       <c r="D23" t="n">
-        <v>513.9712214168786</v>
+        <v>518.8213080060119</v>
       </c>
       <c r="E23" t="n">
-        <v>524.256591796875</v>
+        <v>520.56689453125</v>
       </c>
       <c r="F23" t="n">
-        <v>21388600</v>
+        <v>13363400</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45937</v>
+        <v>45939</v>
       </c>
       <c r="B24" t="n">
-        <v>523.9788048028778</v>
+        <v>518.07745494396</v>
       </c>
       <c r="C24" t="n">
-        <v>525.4764919541412</v>
+        <v>520.0512058016051</v>
       </c>
       <c r="D24" t="n">
-        <v>517.1847292577561</v>
+        <v>513.1777655449532</v>
       </c>
       <c r="E24" t="n">
-        <v>519.7039794921875</v>
+        <v>518.136962890625</v>
       </c>
       <c r="F24" t="n">
-        <v>14615200</v>
+        <v>18343600</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45938</v>
+        <v>45940</v>
       </c>
       <c r="B25" t="n">
-        <v>519.0097599169904</v>
+        <v>515.3994727403434</v>
       </c>
       <c r="C25" t="n">
-        <v>522.6497936321297</v>
+        <v>519.3073226434543</v>
       </c>
       <c r="D25" t="n">
-        <v>518.8213080060119</v>
+        <v>505.4711500363669</v>
       </c>
       <c r="E25" t="n">
-        <v>520.56689453125</v>
+        <v>506.790283203125</v>
       </c>
       <c r="F25" t="n">
-        <v>13363400</v>
+        <v>24133800</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45939</v>
+        <v>45943</v>
       </c>
       <c r="B26" t="n">
-        <v>518.07745494396</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="C26" t="n">
-        <v>520.0512058016051</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="D26" t="n">
-        <v>513.1777655449532</v>
+        <v>507.504417299456</v>
       </c>
       <c r="E26" t="n">
-        <v>518.136962890625</v>
+        <v>509.8550720214844</v>
       </c>
       <c r="F26" t="n">
-        <v>18343600</v>
+        <v>14284200</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45940</v>
+        <v>45944</v>
       </c>
       <c r="B27" t="n">
-        <v>515.3994727403434</v>
+        <v>506.0662879637401</v>
       </c>
       <c r="C27" t="n">
-        <v>519.3073226434543</v>
+        <v>511.0750956887641</v>
       </c>
       <c r="D27" t="n">
-        <v>505.4711500363669</v>
+        <v>501.870795907601</v>
       </c>
       <c r="E27" t="n">
-        <v>506.790283203125</v>
+        <v>509.3790283203125</v>
       </c>
       <c r="F27" t="n">
-        <v>24133800</v>
+        <v>14684300</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45943</v>
+        <v>45945</v>
       </c>
       <c r="B28" t="n">
-        <v>512.1957986627914</v>
+        <v>510.7576863019565</v>
       </c>
       <c r="C28" t="n">
-        <v>512.1957986627914</v>
+        <v>512.9694689959882</v>
       </c>
       <c r="D28" t="n">
-        <v>507.504417299456</v>
+        <v>505.838140631098</v>
       </c>
       <c r="E28" t="n">
-        <v>509.8550720214844</v>
+        <v>509.2401428222656</v>
       </c>
       <c r="F28" t="n">
-        <v>14284200</v>
+        <v>14694700</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45944</v>
+        <v>45946</v>
       </c>
       <c r="B29" t="n">
-        <v>506.0662879637401</v>
+        <v>508.3970827878481</v>
       </c>
       <c r="C29" t="n">
-        <v>511.0750956887641</v>
+        <v>512.6321960787722</v>
       </c>
       <c r="D29" t="n">
-        <v>501.870795907601</v>
+        <v>503.9833851231019</v>
       </c>
       <c r="E29" t="n">
-        <v>509.3790283203125</v>
+        <v>507.4349670410156</v>
       </c>
       <c r="F29" t="n">
-        <v>14684300</v>
+        <v>15559600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45945</v>
+        <v>45947</v>
       </c>
       <c r="B30" t="n">
-        <v>510.7576556934355</v>
+        <v>504.8859262397143</v>
       </c>
       <c r="C30" t="n">
-        <v>512.9694382549203</v>
+        <v>511.273343996943</v>
       </c>
       <c r="D30" t="n">
-        <v>505.838110317394</v>
+        <v>503.1700332164253</v>
       </c>
       <c r="E30" t="n">
-        <v>509.2401123046875</v>
+        <v>509.3888854980469</v>
       </c>
       <c r="F30" t="n">
-        <v>14694700</v>
+        <v>19867800</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45946</v>
+        <v>45950</v>
       </c>
       <c r="B31" t="n">
-        <v>508.3970827878481</v>
+        <v>510.4105508898797</v>
       </c>
       <c r="C31" t="n">
-        <v>512.6321960787722</v>
+        <v>514.4672014016805</v>
       </c>
       <c r="D31" t="n">
-        <v>503.9833851231019</v>
+        <v>509.2401874518674</v>
       </c>
       <c r="E31" t="n">
-        <v>507.4349670410156</v>
+        <v>512.57275390625</v>
       </c>
       <c r="F31" t="n">
-        <v>15559600</v>
+        <v>14665600</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45947</v>
+        <v>45951</v>
       </c>
       <c r="B32" t="n">
-        <v>504.8859262397143</v>
+        <v>513.2769402267872</v>
       </c>
       <c r="C32" t="n">
-        <v>511.273343996943</v>
+        <v>514.4572316509175</v>
       </c>
       <c r="D32" t="n">
-        <v>503.1700332164253</v>
+        <v>508.8533142722573</v>
       </c>
       <c r="E32" t="n">
-        <v>509.3888854980469</v>
+        <v>513.4356079101562</v>
       </c>
       <c r="F32" t="n">
-        <v>19867800</v>
+        <v>15586200</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45950</v>
+        <v>45952</v>
       </c>
       <c r="B33" t="n">
-        <v>510.4104901121901</v>
+        <v>516.8971823641815</v>
       </c>
       <c r="C33" t="n">
-        <v>514.4671401409408</v>
+        <v>520.943843958813</v>
       </c>
       <c r="D33" t="n">
-        <v>509.2401268135401</v>
+        <v>513.4852520447155</v>
       </c>
       <c r="E33" t="n">
-        <v>512.5726928710938</v>
+        <v>516.2921142578125</v>
       </c>
       <c r="F33" t="n">
-        <v>14665600</v>
+        <v>18962700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45951</v>
+        <v>45953</v>
       </c>
       <c r="B34" t="n">
-        <v>513.2770012430817</v>
+        <v>518.1964086283891</v>
       </c>
       <c r="C34" t="n">
-        <v>514.4572928075203</v>
+        <v>519.6742395740552</v>
       </c>
       <c r="D34" t="n">
-        <v>508.8533747626889</v>
+        <v>514.3777908083965</v>
       </c>
       <c r="E34" t="n">
-        <v>513.4356689453125</v>
+        <v>516.3118896484375</v>
       </c>
       <c r="F34" t="n">
-        <v>15586200</v>
+        <v>14023500</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45952</v>
+        <v>45954</v>
       </c>
       <c r="B35" t="n">
-        <v>516.8971823641815</v>
+        <v>518.5237814648117</v>
       </c>
       <c r="C35" t="n">
-        <v>520.943843958813</v>
+        <v>521.0628883153897</v>
       </c>
       <c r="D35" t="n">
-        <v>513.4852520447155</v>
+        <v>516.4607987679614</v>
       </c>
       <c r="E35" t="n">
-        <v>516.2921142578125</v>
+        <v>519.3370971679688</v>
       </c>
       <c r="F35" t="n">
-        <v>18962700</v>
+        <v>15532400</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45953</v>
+        <v>45957</v>
       </c>
       <c r="B36" t="n">
-        <v>518.1964086283891</v>
+        <v>527.440383046071</v>
       </c>
       <c r="C36" t="n">
-        <v>519.6742395740552</v>
+        <v>530.2175212473691</v>
       </c>
       <c r="D36" t="n">
-        <v>514.3777908083965</v>
+        <v>524.6929685473742</v>
       </c>
       <c r="E36" t="n">
-        <v>516.3118896484375</v>
+        <v>527.1824951171875</v>
       </c>
       <c r="F36" t="n">
-        <v>14023500</v>
+        <v>18734700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45954</v>
+        <v>45958</v>
       </c>
       <c r="B37" t="n">
-        <v>518.5237205252405</v>
+        <v>545.5116410650497</v>
       </c>
       <c r="C37" t="n">
-        <v>521.0628270774097</v>
+        <v>549.2012543795508</v>
       </c>
       <c r="D37" t="n">
-        <v>516.4607380708425</v>
+        <v>536.3569832604931</v>
       </c>
       <c r="E37" t="n">
-        <v>519.3370361328125</v>
+        <v>537.6463623046875</v>
       </c>
       <c r="F37" t="n">
-        <v>15532400</v>
+        <v>29986700</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45957</v>
+        <v>45959</v>
       </c>
       <c r="B38" t="n">
-        <v>527.4404441110845</v>
+        <v>540.4929653309738</v>
       </c>
       <c r="C38" t="n">
-        <v>530.2175826339089</v>
+        <v>541.8121286840217</v>
       </c>
       <c r="D38" t="n">
-        <v>524.6930292943027</v>
+        <v>532.3499420595073</v>
       </c>
       <c r="E38" t="n">
-        <v>527.1825561523438</v>
+        <v>537.130615234375</v>
       </c>
       <c r="F38" t="n">
-        <v>18734700</v>
+        <v>36023000</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45958</v>
+        <v>45960</v>
       </c>
       <c r="B39" t="n">
-        <v>545.511702993095</v>
+        <v>526.150935240438</v>
       </c>
       <c r="C39" t="n">
-        <v>549.2013167264516</v>
+        <v>530.6042843733296</v>
       </c>
       <c r="D39" t="n">
-        <v>536.3570441492753</v>
+        <v>517.8591725476514</v>
       </c>
       <c r="E39" t="n">
-        <v>537.6464233398438</v>
+        <v>521.469482421875</v>
       </c>
       <c r="F39" t="n">
-        <v>29986700</v>
+        <v>41023100</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45959</v>
+        <v>45961</v>
       </c>
       <c r="B40" t="n">
-        <v>540.4929653309738</v>
+        <v>524.5640822050067</v>
       </c>
       <c r="C40" t="n">
-        <v>541.8121286840217</v>
+        <v>525.0004940086545</v>
       </c>
       <c r="D40" t="n">
-        <v>532.3499420595073</v>
+        <v>510.8965047694123</v>
       </c>
       <c r="E40" t="n">
-        <v>537.130615234375</v>
+        <v>513.5844116210938</v>
       </c>
       <c r="F40" t="n">
-        <v>36023000</v>
+        <v>34006400</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45960</v>
+        <v>45964</v>
       </c>
       <c r="B41" t="n">
-        <v>526.150935240438</v>
+        <v>515.5680732671589</v>
       </c>
       <c r="C41" t="n">
-        <v>530.6042843733296</v>
+        <v>520.6760707602963</v>
       </c>
       <c r="D41" t="n">
-        <v>517.8591725476514</v>
+        <v>510.3907002836433</v>
       </c>
       <c r="E41" t="n">
-        <v>521.469482421875</v>
+        <v>512.810791015625</v>
       </c>
       <c r="F41" t="n">
-        <v>41023100</v>
+        <v>22374700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45961</v>
+        <v>45965</v>
       </c>
       <c r="B42" t="n">
-        <v>524.5640198650095</v>
+        <v>507.5837474278435</v>
       </c>
       <c r="C42" t="n">
-        <v>525.0004316167937</v>
+        <v>511.3427970078787</v>
       </c>
       <c r="D42" t="n">
-        <v>510.896444053691</v>
+        <v>503.6957236126803</v>
       </c>
       <c r="E42" t="n">
-        <v>513.5843505859375</v>
+        <v>510.1327819824219</v>
       </c>
       <c r="F42" t="n">
-        <v>34006400</v>
+        <v>20958700</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45964</v>
+        <v>45966</v>
       </c>
       <c r="B43" t="n">
-        <v>515.5680732671589</v>
+        <v>509.1111797792271</v>
       </c>
       <c r="C43" t="n">
-        <v>520.6760707602963</v>
+        <v>510.6287232020861</v>
       </c>
       <c r="D43" t="n">
-        <v>510.3907002836433</v>
+        <v>502.4460174356622</v>
       </c>
       <c r="E43" t="n">
-        <v>512.810791015625</v>
+        <v>503.0213012695312</v>
       </c>
       <c r="F43" t="n">
-        <v>22374700</v>
+        <v>23024300</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45965</v>
+        <v>45967</v>
       </c>
       <c r="B44" t="n">
-        <v>507.5837170627558</v>
+        <v>501.5335392553728</v>
       </c>
       <c r="C44" t="n">
-        <v>511.3427664179142</v>
+        <v>501.5732213085109</v>
       </c>
       <c r="D44" t="n">
-        <v>503.6956934801851</v>
+        <v>491.7639146320967</v>
       </c>
       <c r="E44" t="n">
-        <v>510.1327514648438</v>
+        <v>493.0433959960938</v>
       </c>
       <c r="F44" t="n">
-        <v>20958700</v>
+        <v>27406500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45966</v>
+        <v>45968</v>
       </c>
       <c r="B45" t="n">
-        <v>509.1111797792271</v>
+        <v>492.8946300074654</v>
       </c>
       <c r="C45" t="n">
-        <v>510.6287232020861</v>
+        <v>495.304792622274</v>
       </c>
       <c r="D45" t="n">
-        <v>502.4460174356622</v>
+        <v>489.2248119110569</v>
       </c>
       <c r="E45" t="n">
-        <v>503.0213012695312</v>
+        <v>492.7656860351562</v>
       </c>
       <c r="F45" t="n">
-        <v>23024300</v>
+        <v>24019800</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45967</v>
+        <v>45971</v>
       </c>
       <c r="B46" t="n">
-        <v>501.5335392553728</v>
+        <v>495.9594336108676</v>
       </c>
       <c r="C46" t="n">
-        <v>501.5732213085109</v>
+        <v>502.7138582055711</v>
       </c>
       <c r="D46" t="n">
-        <v>491.7639146320967</v>
+        <v>494.729532044403</v>
       </c>
       <c r="E46" t="n">
-        <v>493.0433959960938</v>
+        <v>501.8707885742188</v>
       </c>
       <c r="F46" t="n">
-        <v>27406500</v>
+        <v>26101500</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45968</v>
+        <v>45972</v>
       </c>
       <c r="B47" t="n">
-        <v>492.8946300074654</v>
+        <v>500.6805581155917</v>
       </c>
       <c r="C47" t="n">
-        <v>495.304792622274</v>
+        <v>505.4414057875519</v>
       </c>
       <c r="D47" t="n">
-        <v>489.2248119110569</v>
+        <v>498.2505695472254</v>
       </c>
       <c r="E47" t="n">
-        <v>492.7656860351562</v>
+        <v>504.5289001464844</v>
       </c>
       <c r="F47" t="n">
-        <v>24019800</v>
+        <v>17980000</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45971</v>
+        <v>45973</v>
       </c>
       <c r="B48" t="n">
-        <v>495.9593732946225</v>
+        <v>505.203338237195</v>
       </c>
       <c r="C48" t="n">
-        <v>502.7137970678847</v>
+        <v>507.494515261433</v>
       </c>
       <c r="D48" t="n">
-        <v>494.7294718777327</v>
+        <v>495.0469117437556</v>
       </c>
       <c r="E48" t="n">
-        <v>501.8707275390625</v>
+        <v>506.9688415527344</v>
       </c>
       <c r="F48" t="n">
-        <v>26101500</v>
+        <v>26574900</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45972</v>
+        <v>45974</v>
       </c>
       <c r="B49" t="n">
-        <v>500.6805581155917</v>
+        <v>506.1455939798088</v>
       </c>
       <c r="C49" t="n">
-        <v>505.4414057875519</v>
+        <v>509.3095642884979</v>
       </c>
       <c r="D49" t="n">
-        <v>498.2505695472254</v>
+        <v>497.1992129195551</v>
       </c>
       <c r="E49" t="n">
-        <v>504.5289001464844</v>
+        <v>499.1828918457031</v>
       </c>
       <c r="F49" t="n">
-        <v>17980000</v>
+        <v>25273100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45973</v>
+        <v>45975</v>
       </c>
       <c r="B50" t="n">
-        <v>505.203338237195</v>
+        <v>494.164169077362</v>
       </c>
       <c r="C50" t="n">
-        <v>507.494515261433</v>
+        <v>507.425057385904</v>
       </c>
       <c r="D50" t="n">
-        <v>495.0469117437556</v>
+        <v>493.3806074541019</v>
       </c>
       <c r="E50" t="n">
-        <v>506.9688415527344</v>
+        <v>506.0166320800781</v>
       </c>
       <c r="F50" t="n">
-        <v>26574900</v>
+        <v>28505700</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45974</v>
+        <v>45978</v>
       </c>
       <c r="B51" t="n">
-        <v>506.1455939798088</v>
+        <v>504.3008205535495</v>
       </c>
       <c r="C51" t="n">
-        <v>509.3095642884979</v>
+        <v>507.9408546740634</v>
       </c>
       <c r="D51" t="n">
-        <v>497.1992129195551</v>
+        <v>500.7897001462128</v>
       </c>
       <c r="E51" t="n">
-        <v>499.1828918457031</v>
+        <v>503.3486328125</v>
       </c>
       <c r="F51" t="n">
-        <v>25273100</v>
+        <v>19092800</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45975</v>
+        <v>45979</v>
       </c>
       <c r="B52" t="n">
-        <v>494.164169077362</v>
+        <v>491.3274994941962</v>
       </c>
       <c r="C52" t="n">
-        <v>507.425057385904</v>
+        <v>498.8754133867433</v>
       </c>
       <c r="D52" t="n">
-        <v>493.3806074541019</v>
+        <v>482.8076023204449</v>
       </c>
       <c r="E52" t="n">
-        <v>506.0166320800781</v>
+        <v>489.7604064941406</v>
       </c>
       <c r="F52" t="n">
-        <v>28505700</v>
+        <v>33815100</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45978</v>
+        <v>45980</v>
       </c>
       <c r="B53" t="n">
-        <v>504.300789978241</v>
+        <v>486.1005289347495</v>
       </c>
       <c r="C53" t="n">
-        <v>507.9408238780629</v>
+        <v>491.1489881906385</v>
       </c>
       <c r="D53" t="n">
-        <v>500.7896697837805</v>
+        <v>478.8898366362471</v>
       </c>
       <c r="E53" t="n">
-        <v>503.3486022949219</v>
+        <v>483.1448364257812</v>
       </c>
       <c r="F53" t="n">
-        <v>19092800</v>
+        <v>23245300</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45979</v>
+        <v>45981</v>
       </c>
       <c r="B54" t="n">
-        <v>491.3274994941962</v>
+        <v>489.6038543571071</v>
       </c>
       <c r="C54" t="n">
-        <v>498.8754133867433</v>
+        <v>490.4584485233347</v>
       </c>
       <c r="D54" t="n">
-        <v>482.8076023204449</v>
+        <v>472.5023579474745</v>
       </c>
       <c r="E54" t="n">
-        <v>489.7604064941406</v>
+        <v>475.4138793945312</v>
       </c>
       <c r="F54" t="n">
-        <v>33815100</v>
+        <v>26802500</v>
       </c>
       <c r="G54" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45980</v>
+        <v>45982</v>
       </c>
       <c r="B55" t="n">
-        <v>486.1005289347495</v>
+        <v>475.4834301610789</v>
       </c>
       <c r="C55" t="n">
-        <v>491.1489881906385</v>
+        <v>475.9007957312625</v>
       </c>
       <c r="D55" t="n">
-        <v>478.8898366362471</v>
+        <v>465.3179114267742</v>
       </c>
       <c r="E55" t="n">
-        <v>483.1448364257812</v>
+        <v>469.1436462402344</v>
       </c>
       <c r="F55" t="n">
-        <v>23245300</v>
+        <v>31769200</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,25 +1873,25 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45981</v>
+        <v>45985</v>
       </c>
       <c r="B56" t="n">
-        <v>489.6038543571071</v>
+        <v>472.0055061050608</v>
       </c>
       <c r="C56" t="n">
-        <v>490.4584485233347</v>
+        <v>473.8935220644432</v>
       </c>
       <c r="D56" t="n">
-        <v>472.5023579474745</v>
+        <v>465.0694984877541</v>
       </c>
       <c r="E56" t="n">
-        <v>475.4138793945312</v>
+        <v>471.0118103027344</v>
       </c>
       <c r="F56" t="n">
-        <v>26802500</v>
+        <v>34421000</v>
       </c>
       <c r="G56" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45982</v>
+        <v>45986</v>
       </c>
       <c r="B57" t="n">
-        <v>475.4834301610789</v>
+        <v>471.0813963074052</v>
       </c>
       <c r="C57" t="n">
-        <v>475.9007957312625</v>
+        <v>476.1293578546732</v>
       </c>
       <c r="D57" t="n">
-        <v>465.3179114267742</v>
+        <v>461.9592757324133</v>
       </c>
       <c r="E57" t="n">
-        <v>469.1436462402344</v>
+        <v>473.9829711914062</v>
       </c>
       <c r="F57" t="n">
-        <v>31769200</v>
+        <v>28019800</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45985</v>
+        <v>45987</v>
       </c>
       <c r="B58" t="n">
-        <v>472.0055061050608</v>
+        <v>483.244222260298</v>
       </c>
       <c r="C58" t="n">
-        <v>473.8935220644432</v>
+        <v>485.2316139433245</v>
       </c>
       <c r="D58" t="n">
-        <v>465.0694984877541</v>
+        <v>478.1664510662567</v>
       </c>
       <c r="E58" t="n">
-        <v>471.0118103027344</v>
+        <v>482.4393310546875</v>
       </c>
       <c r="F58" t="n">
-        <v>34421000</v>
+        <v>25709100</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45986</v>
+        <v>45989</v>
       </c>
       <c r="B59" t="n">
-        <v>471.0813963074052</v>
+        <v>484.5260924315005</v>
       </c>
       <c r="C59" t="n">
-        <v>476.1293578546732</v>
+        <v>489.5243812398697</v>
       </c>
       <c r="D59" t="n">
-        <v>461.9592757324133</v>
+        <v>483.5820692635899</v>
       </c>
       <c r="E59" t="n">
-        <v>473.9829711914062</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="F59" t="n">
-        <v>28019800</v>
+        <v>14386700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45987</v>
+        <v>45992</v>
       </c>
       <c r="B60" t="n">
-        <v>483.244222260298</v>
+        <v>485.3607732415945</v>
       </c>
       <c r="C60" t="n">
-        <v>485.2316139433245</v>
+        <v>486.7718042788117</v>
       </c>
       <c r="D60" t="n">
-        <v>478.1664510662567</v>
+        <v>481.5946577130528</v>
       </c>
       <c r="E60" t="n">
-        <v>482.4393310546875</v>
+        <v>483.6714782714844</v>
       </c>
       <c r="F60" t="n">
-        <v>25709100</v>
+        <v>23964000</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45989</v>
+        <v>45993</v>
       </c>
       <c r="B61" t="n">
-        <v>484.5260924315005</v>
+        <v>483.6516286444489</v>
       </c>
       <c r="C61" t="n">
-        <v>489.5243812398697</v>
+        <v>490.3888850620814</v>
       </c>
       <c r="D61" t="n">
-        <v>483.5820692635899</v>
+        <v>483.2541563831954</v>
       </c>
       <c r="E61" t="n">
-        <v>488.9082946777344</v>
+        <v>486.9109497070312</v>
       </c>
       <c r="F61" t="n">
-        <v>14386700</v>
+        <v>19562700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45992</v>
+        <v>45994</v>
       </c>
       <c r="B62" t="n">
-        <v>485.3608038657598</v>
+        <v>473.3171775583083</v>
       </c>
       <c r="C62" t="n">
-        <v>486.771834992007</v>
+        <v>481.1872310931236</v>
       </c>
       <c r="D62" t="n">
-        <v>481.5946880995925</v>
+        <v>472.2042431453193</v>
       </c>
       <c r="E62" t="n">
-        <v>483.6715087890625</v>
+        <v>474.7182922363281</v>
       </c>
       <c r="F62" t="n">
-        <v>23964000</v>
+        <v>34615100</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45993</v>
+        <v>45995</v>
       </c>
       <c r="B63" t="n">
-        <v>483.6516286444489</v>
+        <v>476.7355376297969</v>
       </c>
       <c r="C63" t="n">
-        <v>490.3888850620814</v>
+        <v>478.2857007523145</v>
       </c>
       <c r="D63" t="n">
-        <v>483.2541563831954</v>
+        <v>473.4861327449422</v>
       </c>
       <c r="E63" t="n">
-        <v>486.9109497070312</v>
+        <v>477.8087158203125</v>
       </c>
       <c r="F63" t="n">
-        <v>19562700</v>
+        <v>22318200</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45994</v>
+        <v>45996</v>
       </c>
       <c r="B64" t="n">
-        <v>473.3172079858148</v>
+        <v>479.4780948278929</v>
       </c>
       <c r="C64" t="n">
-        <v>481.1872620265617</v>
+        <v>480.3525519991132</v>
       </c>
       <c r="D64" t="n">
-        <v>472.2042735012802</v>
+        <v>475.8610578221601</v>
       </c>
       <c r="E64" t="n">
-        <v>474.7183227539062</v>
+        <v>480.1140747070312</v>
       </c>
       <c r="F64" t="n">
-        <v>34615100</v>
+        <v>22608700</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45995</v>
+        <v>45999</v>
       </c>
       <c r="B65" t="n">
-        <v>476.7355376297969</v>
+        <v>481.8331697469475</v>
       </c>
       <c r="C65" t="n">
-        <v>478.2857007523145</v>
+        <v>489.1964289193556</v>
       </c>
       <c r="D65" t="n">
-        <v>473.4861327449422</v>
+        <v>481.3263751862239</v>
       </c>
       <c r="E65" t="n">
-        <v>477.8087158203125</v>
+        <v>487.9244995117188</v>
       </c>
       <c r="F65" t="n">
-        <v>22318200</v>
+        <v>21965900</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>45996</v>
+        <v>46000</v>
       </c>
       <c r="B66" t="n">
-        <v>479.4781253050461</v>
+        <v>486.0166380400449</v>
       </c>
       <c r="C66" t="n">
-        <v>480.3525825318497</v>
+        <v>489.0175885389743</v>
       </c>
       <c r="D66" t="n">
-        <v>475.861088069403</v>
+        <v>485.4204144751398</v>
       </c>
       <c r="E66" t="n">
-        <v>480.1141052246094</v>
+        <v>488.918212890625</v>
       </c>
       <c r="F66" t="n">
-        <v>22608700</v>
+        <v>14696100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>45999</v>
+        <v>46001</v>
       </c>
       <c r="B67" t="n">
-        <v>481.8331697469475</v>
+        <v>480.978577549523</v>
       </c>
       <c r="C67" t="n">
-        <v>489.1964289193556</v>
+        <v>481.1971918388435</v>
       </c>
       <c r="D67" t="n">
-        <v>481.3263751862239</v>
+        <v>472.084987996716</v>
       </c>
       <c r="E67" t="n">
-        <v>487.9244995117188</v>
+        <v>475.5430603027344</v>
       </c>
       <c r="F67" t="n">
-        <v>21965900</v>
+        <v>35756200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46000</v>
+        <v>46002</v>
       </c>
       <c r="B68" t="n">
-        <v>486.016607703579</v>
+        <v>473.6252734590456</v>
       </c>
       <c r="C68" t="n">
-        <v>489.0175580151932</v>
+        <v>482.9660086920916</v>
       </c>
       <c r="D68" t="n">
-        <v>485.4203841758892</v>
+        <v>472.8601082211862</v>
       </c>
       <c r="E68" t="n">
-        <v>488.9181823730469</v>
+        <v>480.4221496582031</v>
       </c>
       <c r="F68" t="n">
-        <v>14696100</v>
+        <v>24669200</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46001</v>
+        <v>46003</v>
       </c>
       <c r="B69" t="n">
-        <v>480.978577549523</v>
+        <v>476.7951512874317</v>
       </c>
       <c r="C69" t="n">
-        <v>481.1971918388435</v>
+        <v>479.4085762318817</v>
       </c>
       <c r="D69" t="n">
-        <v>472.084987996716</v>
+        <v>473.3370788032073</v>
       </c>
       <c r="E69" t="n">
-        <v>475.5430603027344</v>
+        <v>475.5132751464844</v>
       </c>
       <c r="F69" t="n">
-        <v>35756200</v>
+        <v>21248100</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46002</v>
+        <v>46006</v>
       </c>
       <c r="B70" t="n">
-        <v>473.6252734590456</v>
+        <v>477.0733729131614</v>
       </c>
       <c r="C70" t="n">
-        <v>482.9660086920916</v>
+        <v>477.6894594742654</v>
       </c>
       <c r="D70" t="n">
-        <v>472.8601082211862</v>
+        <v>469.5411415575728</v>
       </c>
       <c r="E70" t="n">
-        <v>480.4221496582031</v>
+        <v>471.82666015625</v>
       </c>
       <c r="F70" t="n">
-        <v>24669200</v>
+        <v>23727700</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46003</v>
+        <v>46007</v>
       </c>
       <c r="B71" t="n">
-        <v>476.7951512874317</v>
+        <v>468.9350114671635</v>
       </c>
       <c r="C71" t="n">
-        <v>479.4085762318817</v>
+        <v>474.8773235577871</v>
       </c>
       <c r="D71" t="n">
-        <v>473.3370788032073</v>
+        <v>467.911505956298</v>
       </c>
       <c r="E71" t="n">
-        <v>475.5132751464844</v>
+        <v>473.3867797851562</v>
       </c>
       <c r="F71" t="n">
-        <v>21248100</v>
+        <v>20705600</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46006</v>
+        <v>46008</v>
       </c>
       <c r="B72" t="n">
-        <v>477.0733420562278</v>
+        <v>473.903466892556</v>
       </c>
       <c r="C72" t="n">
-        <v>477.6894285774835</v>
+        <v>476.9739832708393</v>
       </c>
       <c r="D72" t="n">
-        <v>469.5411111878212</v>
+        <v>472.0055042784347</v>
       </c>
       <c r="E72" t="n">
-        <v>471.8266296386719</v>
+        <v>473.1184387207031</v>
       </c>
       <c r="F72" t="n">
-        <v>23727700</v>
+        <v>24527200</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46007</v>
+        <v>46009</v>
       </c>
       <c r="B73" t="n">
-        <v>468.9350114671635</v>
+        <v>475.1754171439269</v>
       </c>
       <c r="C73" t="n">
-        <v>474.8773235577871</v>
+        <v>486.5134903409316</v>
       </c>
       <c r="D73" t="n">
-        <v>467.911505956298</v>
+        <v>474.8773205213831</v>
       </c>
       <c r="E73" t="n">
-        <v>473.3867797851562</v>
+        <v>480.9289245605469</v>
       </c>
       <c r="F73" t="n">
-        <v>20705600</v>
+        <v>28573500</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46008</v>
+        <v>46010</v>
       </c>
       <c r="B74" t="n">
-        <v>473.903466892556</v>
+        <v>484.2875835443981</v>
       </c>
       <c r="C74" t="n">
-        <v>476.9739832708393</v>
+        <v>484.7745151206103</v>
       </c>
       <c r="D74" t="n">
-        <v>472.0055042784347</v>
+        <v>479.4482897203998</v>
       </c>
       <c r="E74" t="n">
-        <v>473.1184387207031</v>
+        <v>482.856689453125</v>
       </c>
       <c r="F74" t="n">
-        <v>24527200</v>
+        <v>70836100</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46009</v>
+        <v>46013</v>
       </c>
       <c r="B75" t="n">
-        <v>475.1754171439269</v>
+        <v>483.05539282771</v>
       </c>
       <c r="C75" t="n">
-        <v>486.5134903409316</v>
+        <v>485.6489546100234</v>
       </c>
       <c r="D75" t="n">
-        <v>474.8773205213831</v>
+        <v>479.6470235443271</v>
       </c>
       <c r="E75" t="n">
-        <v>480.9289245605469</v>
+        <v>481.8629760742188</v>
       </c>
       <c r="F75" t="n">
-        <v>28573500</v>
+        <v>16963000</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46010</v>
+        <v>46014</v>
       </c>
       <c r="B76" t="n">
-        <v>484.2875835443981</v>
+        <v>481.922585996358</v>
       </c>
       <c r="C76" t="n">
-        <v>484.7745151206103</v>
+        <v>484.7545946839082</v>
       </c>
       <c r="D76" t="n">
-        <v>479.4482897203998</v>
+        <v>481.6840783901604</v>
       </c>
       <c r="E76" t="n">
-        <v>482.856689453125</v>
+        <v>483.7807922363281</v>
       </c>
       <c r="F76" t="n">
-        <v>70836100</v>
+        <v>14683600</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46013</v>
+        <v>46015</v>
       </c>
       <c r="B77" t="n">
-        <v>483.05539282771</v>
+        <v>482.6181758435609</v>
       </c>
       <c r="C77" t="n">
-        <v>485.6489546100234</v>
+        <v>486.0762481946253</v>
       </c>
       <c r="D77" t="n">
-        <v>479.6470235443271</v>
+        <v>481.7735283363114</v>
       </c>
       <c r="E77" t="n">
-        <v>481.8629760742188</v>
+        <v>484.9434204101562</v>
       </c>
       <c r="F77" t="n">
-        <v>16963000</v>
+        <v>5855900</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46014</v>
+        <v>46017</v>
       </c>
       <c r="B78" t="n">
-        <v>481.922585996358</v>
+        <v>483.6417106195734</v>
       </c>
       <c r="C78" t="n">
-        <v>484.7545946839082</v>
+        <v>485.0428254417362</v>
       </c>
       <c r="D78" t="n">
-        <v>481.6840783901604</v>
+        <v>482.8964387136479</v>
       </c>
       <c r="E78" t="n">
-        <v>483.7807922363281</v>
+        <v>484.6354064941406</v>
       </c>
       <c r="F78" t="n">
-        <v>14683600</v>
+        <v>8842200</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46015</v>
+        <v>46020</v>
       </c>
       <c r="B79" t="n">
-        <v>482.6181454723109</v>
+        <v>481.8033366009864</v>
       </c>
       <c r="C79" t="n">
-        <v>486.0762176057581</v>
+        <v>485.2713556042012</v>
       </c>
       <c r="D79" t="n">
-        <v>481.7734980182152</v>
+        <v>481.1276307272214</v>
       </c>
       <c r="E79" t="n">
-        <v>484.9433898925781</v>
+        <v>484.0292358398438</v>
       </c>
       <c r="F79" t="n">
-        <v>5855900</v>
+        <v>10893400</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46017</v>
+        <v>46021</v>
       </c>
       <c r="B80" t="n">
-        <v>483.6416801645685</v>
+        <v>482.8666136001516</v>
       </c>
       <c r="C80" t="n">
-        <v>485.0427948985028</v>
+        <v>486.5929730105466</v>
       </c>
       <c r="D80" t="n">
-        <v>482.8964083055729</v>
+        <v>482.4393316658054</v>
       </c>
       <c r="E80" t="n">
-        <v>484.6353759765625</v>
+        <v>484.4068603515625</v>
       </c>
       <c r="F80" t="n">
-        <v>8842200</v>
+        <v>13944500</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46020</v>
+        <v>46022</v>
       </c>
       <c r="B81" t="n">
-        <v>481.8033366009864</v>
+        <v>484.7645645601486</v>
       </c>
       <c r="C81" t="n">
-        <v>485.2713556042012</v>
+        <v>485.0626915008752</v>
       </c>
       <c r="D81" t="n">
-        <v>481.1276307272214</v>
+        <v>480.253177052155</v>
       </c>
       <c r="E81" t="n">
-        <v>484.0292358398438</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="F81" t="n">
-        <v>10893400</v>
+        <v>15601600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46021</v>
+        <v>46024</v>
       </c>
       <c r="B82" t="n">
-        <v>482.8666136001516</v>
+        <v>481.3363251826272</v>
       </c>
       <c r="C82" t="n">
-        <v>486.5929730105466</v>
+        <v>481.6046121327098</v>
       </c>
       <c r="D82" t="n">
-        <v>482.4393316658054</v>
+        <v>467.1960229709088</v>
       </c>
       <c r="E82" t="n">
-        <v>484.4068603515625</v>
+        <v>469.95849609375</v>
       </c>
       <c r="F82" t="n">
-        <v>13944500</v>
+        <v>25571600</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46022</v>
+        <v>46027</v>
       </c>
       <c r="B83" t="n">
-        <v>484.7645337762783</v>
+        <v>471.071443053882</v>
       </c>
       <c r="C83" t="n">
-        <v>485.0626606980731</v>
+        <v>473.0687813775576</v>
       </c>
       <c r="D83" t="n">
-        <v>480.2531465547701</v>
+        <v>466.5401924921144</v>
       </c>
       <c r="E83" t="n">
-        <v>480.5711364746094</v>
+        <v>469.8690795898438</v>
       </c>
       <c r="F83" t="n">
-        <v>15601600</v>
+        <v>25250300</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46024</v>
+        <v>46028</v>
       </c>
       <c r="B84" t="n">
-        <v>481.3363251826272</v>
+        <v>470.8130487247203</v>
       </c>
       <c r="C84" t="n">
-        <v>481.6046121327098</v>
+        <v>475.7219083069673</v>
       </c>
       <c r="D84" t="n">
-        <v>467.1960229709088</v>
+        <v>466.7885929433101</v>
       </c>
       <c r="E84" t="n">
-        <v>469.95849609375</v>
+        <v>475.4933776855469</v>
       </c>
       <c r="F84" t="n">
-        <v>25571600</v>
+        <v>23037700</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46027</v>
+        <v>46029</v>
       </c>
       <c r="B85" t="n">
-        <v>471.0714124582114</v>
+        <v>476.7355464241618</v>
       </c>
       <c r="C85" t="n">
-        <v>473.0687506521617</v>
+        <v>486.61288592496</v>
       </c>
       <c r="D85" t="n">
-        <v>466.5401621907445</v>
+        <v>474.9369593023546</v>
       </c>
       <c r="E85" t="n">
-        <v>469.8690490722656</v>
+        <v>480.4221496582031</v>
       </c>
       <c r="F85" t="n">
-        <v>25250300</v>
+        <v>25564200</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46028</v>
+        <v>46030</v>
       </c>
       <c r="B86" t="n">
-        <v>470.8130487247203</v>
+        <v>478.206189665966</v>
       </c>
       <c r="C86" t="n">
-        <v>475.7219083069673</v>
+        <v>479.6172511411785</v>
       </c>
       <c r="D86" t="n">
-        <v>466.7885929433101</v>
+        <v>472.8601010457309</v>
       </c>
       <c r="E86" t="n">
-        <v>475.4933776855469</v>
+        <v>475.0959167480469</v>
       </c>
       <c r="F86" t="n">
-        <v>23037700</v>
+        <v>18162600</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46029</v>
+        <v>46031</v>
       </c>
       <c r="B87" t="n">
-        <v>476.7355464241618</v>
+        <v>471.071451381159</v>
       </c>
       <c r="C87" t="n">
-        <v>486.61288592496</v>
+        <v>476.7951491709672</v>
       </c>
       <c r="D87" t="n">
-        <v>474.9369593023546</v>
+        <v>469.2231916595613</v>
       </c>
       <c r="E87" t="n">
-        <v>480.4221496582031</v>
+        <v>476.258544921875</v>
       </c>
       <c r="F87" t="n">
-        <v>25564200</v>
+        <v>18491000</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46030</v>
+        <v>46034</v>
       </c>
       <c r="B88" t="n">
-        <v>478.206189665966</v>
+        <v>473.6649886945649</v>
       </c>
       <c r="C88" t="n">
-        <v>479.6172511411785</v>
+        <v>477.9577314886077</v>
       </c>
       <c r="D88" t="n">
-        <v>472.8601010457309</v>
+        <v>472.681209234831</v>
       </c>
       <c r="E88" t="n">
-        <v>475.0959167480469</v>
+        <v>474.1717529296875</v>
       </c>
       <c r="F88" t="n">
-        <v>18162600</v>
+        <v>23519900</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46031</v>
+        <v>46035</v>
       </c>
       <c r="B89" t="n">
-        <v>471.071451381159</v>
+        <v>471.6875193976834</v>
       </c>
       <c r="C89" t="n">
-        <v>476.7951491709672</v>
+        <v>472.7805908527595</v>
       </c>
       <c r="D89" t="n">
-        <v>469.2231916595613</v>
+        <v>463.0125743921384</v>
       </c>
       <c r="E89" t="n">
-        <v>476.258544921875</v>
+        <v>467.7028198242188</v>
       </c>
       <c r="F89" t="n">
-        <v>18491000</v>
+        <v>28545800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46034</v>
+        <v>46036</v>
       </c>
       <c r="B90" t="n">
-        <v>473.6649886945649</v>
+        <v>463.5193621312372</v>
       </c>
       <c r="C90" t="n">
-        <v>477.9577314886077</v>
+        <v>465.2484135478969</v>
       </c>
       <c r="D90" t="n">
-        <v>472.681209234831</v>
+        <v>454.2879494306214</v>
       </c>
       <c r="E90" t="n">
-        <v>474.1717529296875</v>
+        <v>456.4840087890625</v>
       </c>
       <c r="F90" t="n">
-        <v>23519900</v>
+        <v>28184300</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46035</v>
+        <v>46037</v>
       </c>
       <c r="B91" t="n">
-        <v>471.687550175263</v>
+        <v>461.1940901109254</v>
       </c>
       <c r="C91" t="n">
-        <v>472.7806217016619</v>
+        <v>461.3232754170305</v>
       </c>
       <c r="D91" t="n">
-        <v>463.0126046036784</v>
+        <v>453.0259094171898</v>
       </c>
       <c r="E91" t="n">
-        <v>467.7028503417969</v>
+        <v>453.7811279296875</v>
       </c>
       <c r="F91" t="n">
-        <v>28545800</v>
+        <v>23225800</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46036</v>
+        <v>46038</v>
       </c>
       <c r="B92" t="n">
-        <v>463.5193621312372</v>
+        <v>454.9437362325269</v>
       </c>
       <c r="C92" t="n">
-        <v>465.2484135478969</v>
+        <v>460.2699615067369</v>
       </c>
       <c r="D92" t="n">
-        <v>454.2879494306214</v>
+        <v>453.6022711583685</v>
       </c>
       <c r="E92" t="n">
-        <v>456.4840087890625</v>
+        <v>456.9609375</v>
       </c>
       <c r="F92" t="n">
-        <v>28184300</v>
+        <v>34246700</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46037</v>
+        <v>46042</v>
       </c>
       <c r="B93" t="n">
-        <v>461.1940901109254</v>
+        <v>448.3754180557273</v>
       </c>
       <c r="C93" t="n">
-        <v>461.3232754170305</v>
+        <v>453.9202272514996</v>
       </c>
       <c r="D93" t="n">
-        <v>453.0259094171898</v>
+        <v>446.4476457864541</v>
       </c>
       <c r="E93" t="n">
-        <v>453.7811279296875</v>
+        <v>451.6546020507812</v>
       </c>
       <c r="F93" t="n">
-        <v>23225800</v>
+        <v>26130000</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46038</v>
+        <v>46043</v>
       </c>
       <c r="B94" t="n">
-        <v>454.9437362325269</v>
+        <v>449.7467088388933</v>
       </c>
       <c r="C94" t="n">
-        <v>460.2699615067369</v>
+        <v>449.8361378186282</v>
       </c>
       <c r="D94" t="n">
-        <v>453.6022711583685</v>
+        <v>435.9144504613163</v>
       </c>
       <c r="E94" t="n">
-        <v>456.9609375</v>
+        <v>441.3102111816406</v>
       </c>
       <c r="F94" t="n">
-        <v>34246700</v>
+        <v>37980500</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46042</v>
+        <v>46044</v>
       </c>
       <c r="B95" t="n">
-        <v>448.3754180557273</v>
+        <v>444.7981306791853</v>
       </c>
       <c r="C95" t="n">
-        <v>453.9202272514996</v>
+        <v>449.9852242193297</v>
       </c>
       <c r="D95" t="n">
-        <v>446.4476457864541</v>
+        <v>441.8965557848095</v>
       </c>
       <c r="E95" t="n">
-        <v>451.6546020507812</v>
+        <v>448.2959594726562</v>
       </c>
       <c r="F95" t="n">
-        <v>26130000</v>
+        <v>25349400</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46043</v>
+        <v>46045</v>
       </c>
       <c r="B96" t="n">
-        <v>449.7467399398739</v>
+        <v>449.0213193023424</v>
       </c>
       <c r="C96" t="n">
-        <v>449.836168925793</v>
+        <v>468.1301005814363</v>
       </c>
       <c r="D96" t="n">
-        <v>435.9144806057656</v>
+        <v>447.6897705604439</v>
       </c>
       <c r="E96" t="n">
-        <v>441.3102416992188</v>
+        <v>463.0125732421875</v>
       </c>
       <c r="F96" t="n">
-        <v>37980500</v>
+        <v>38000200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46044</v>
+        <v>46048</v>
       </c>
       <c r="B97" t="n">
-        <v>444.7981003997206</v>
+        <v>462.3766075757791</v>
       </c>
       <c r="C97" t="n">
-        <v>449.9851935867555</v>
+        <v>471.2602507862521</v>
       </c>
       <c r="D97" t="n">
-        <v>441.8965257028684</v>
+        <v>459.0874767807031</v>
       </c>
       <c r="E97" t="n">
-        <v>448.2959289550781</v>
+        <v>467.3152770996094</v>
       </c>
       <c r="F97" t="n">
-        <v>25349400</v>
+        <v>29291200</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46045</v>
+        <v>46049</v>
       </c>
       <c r="B98" t="n">
-        <v>449.0213193023424</v>
+        <v>470.7137217228436</v>
       </c>
       <c r="C98" t="n">
-        <v>468.1301005814363</v>
+        <v>479.8258954035317</v>
       </c>
       <c r="D98" t="n">
-        <v>447.6897705604439</v>
+        <v>470.1771174893794</v>
       </c>
       <c r="E98" t="n">
-        <v>463.0125732421875</v>
+        <v>477.5503234863281</v>
       </c>
       <c r="F98" t="n">
-        <v>38000200</v>
+        <v>29213900</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46048</v>
+        <v>46050</v>
       </c>
       <c r="B99" t="n">
-        <v>462.3766075757791</v>
+        <v>480.1637455245844</v>
       </c>
       <c r="C99" t="n">
-        <v>471.2602507862521</v>
+        <v>480.6904030927037</v>
       </c>
       <c r="D99" t="n">
-        <v>459.0874767807031</v>
+        <v>474.9865988275796</v>
       </c>
       <c r="E99" t="n">
-        <v>467.3152770996094</v>
+        <v>478.5937194824219</v>
       </c>
       <c r="F99" t="n">
-        <v>29291200</v>
+        <v>36875400</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46049</v>
+        <v>46051</v>
       </c>
       <c r="B100" t="n">
-        <v>470.7137217228436</v>
+        <v>437.2162272399066</v>
       </c>
       <c r="C100" t="n">
-        <v>479.8258954035317</v>
+        <v>439.7104135269112</v>
       </c>
       <c r="D100" t="n">
-        <v>470.1771174893794</v>
+        <v>418.365815756604</v>
       </c>
       <c r="E100" t="n">
-        <v>477.5503234863281</v>
+        <v>430.7671508789062</v>
       </c>
       <c r="F100" t="n">
-        <v>29213900</v>
+        <v>128855300</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46050</v>
+        <v>46052</v>
       </c>
       <c r="B101" t="n">
-        <v>480.1637455245844</v>
+        <v>436.4014165119217</v>
       </c>
       <c r="C101" t="n">
-        <v>480.6904030927037</v>
+        <v>436.8286984461687</v>
       </c>
       <c r="D101" t="n">
-        <v>474.9865988275796</v>
+        <v>423.7616041817895</v>
       </c>
       <c r="E101" t="n">
-        <v>478.5937194824219</v>
+        <v>427.577392578125</v>
       </c>
       <c r="F101" t="n">
-        <v>36875400</v>
+        <v>58566800</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46051</v>
+        <v>46055</v>
       </c>
       <c r="B102" t="n">
-        <v>437.2161962654454</v>
+        <v>427.5276741085398</v>
       </c>
       <c r="C102" t="n">
-        <v>439.7103823757502</v>
+        <v>428.0245220118177</v>
       </c>
       <c r="D102" t="n">
-        <v>418.365786117595</v>
+        <v>419.588054318219</v>
       </c>
       <c r="E102" t="n">
-        <v>430.7671203613281</v>
+        <v>420.7009887695312</v>
       </c>
       <c r="F102" t="n">
-        <v>128855300</v>
+        <v>42219900</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46052</v>
+        <v>46056</v>
       </c>
       <c r="B103" t="n">
-        <v>436.4014165119217</v>
+        <v>419.3496095186449</v>
       </c>
       <c r="C103" t="n">
-        <v>436.8286984461687</v>
+        <v>419.3893355198486</v>
       </c>
       <c r="D103" t="n">
-        <v>423.7616041817895</v>
+        <v>405.9843877548956</v>
       </c>
       <c r="E103" t="n">
-        <v>427.577392578125</v>
+        <v>408.61767578125</v>
       </c>
       <c r="F103" t="n">
-        <v>58566800</v>
+        <v>61424100</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46055</v>
+        <v>46057</v>
       </c>
       <c r="B104" t="n">
-        <v>427.5276741085398</v>
+        <v>408.4089957411405</v>
       </c>
       <c r="C104" t="n">
-        <v>428.0245220118177</v>
+        <v>417.1535071208501</v>
       </c>
       <c r="D104" t="n">
-        <v>419.588054318219</v>
+        <v>406.6600813351222</v>
       </c>
       <c r="E104" t="n">
-        <v>420.7009887695312</v>
+        <v>411.5788879394531</v>
       </c>
       <c r="F104" t="n">
-        <v>42219900</v>
+        <v>45012400</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46056</v>
+        <v>46058</v>
       </c>
       <c r="B105" t="n">
-        <v>419.3496095186449</v>
+        <v>404.8714440282318</v>
       </c>
       <c r="C105" t="n">
-        <v>419.3893355198486</v>
+        <v>405.7260079125925</v>
       </c>
       <c r="D105" t="n">
-        <v>405.9843877548956</v>
+        <v>389.8467674620769</v>
       </c>
       <c r="E105" t="n">
-        <v>408.61767578125</v>
+        <v>391.1882629394531</v>
       </c>
       <c r="F105" t="n">
-        <v>61424100</v>
+        <v>66289200</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46057</v>
+        <v>46059</v>
       </c>
       <c r="B106" t="n">
-        <v>408.4089654586022</v>
+        <v>396.653593461728</v>
       </c>
       <c r="C106" t="n">
-        <v>417.1534761899275</v>
+        <v>399.2570717870675</v>
       </c>
       <c r="D106" t="n">
-        <v>406.6600511822617</v>
+        <v>390.4429942790701</v>
       </c>
       <c r="E106" t="n">
-        <v>411.578857421875</v>
+        <v>398.6111755371094</v>
       </c>
       <c r="F106" t="n">
-        <v>45012400</v>
+        <v>53515300</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46058</v>
+        <v>46062</v>
       </c>
       <c r="B107" t="n">
-        <v>404.8714124431945</v>
+        <v>402.2977759502542</v>
       </c>
       <c r="C107" t="n">
-        <v>405.7259762608884</v>
+        <v>412.2744908996196</v>
       </c>
       <c r="D107" t="n">
-        <v>389.8467370491522</v>
+        <v>398.3428555009064</v>
       </c>
       <c r="E107" t="n">
-        <v>391.188232421875</v>
+        <v>410.9926147460938</v>
       </c>
       <c r="F107" t="n">
-        <v>66289200</v>
+        <v>45480500</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46059</v>
+        <v>46063</v>
       </c>
       <c r="B108" t="n">
-        <v>396.6535630940219</v>
+        <v>416.9746165751398</v>
       </c>
       <c r="C108" t="n">
-        <v>399.2570412200398</v>
+        <v>421.009018998737</v>
       </c>
       <c r="D108" t="n">
-        <v>390.4429643868461</v>
+        <v>410.0982587889407</v>
       </c>
       <c r="E108" t="n">
-        <v>398.6111450195312</v>
+        <v>410.6646423339844</v>
       </c>
       <c r="F108" t="n">
-        <v>53515300</v>
+        <v>44857900</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46062</v>
+        <v>46064</v>
       </c>
       <c r="B109" t="n">
-        <v>402.2977759502542</v>
+        <v>413.5563153661985</v>
       </c>
       <c r="C109" t="n">
-        <v>412.2744908996196</v>
+        <v>413.8345489802859</v>
       </c>
       <c r="D109" t="n">
-        <v>398.3428555009064</v>
+        <v>398.4819668946231</v>
       </c>
       <c r="E109" t="n">
-        <v>410.9926147460938</v>
+        <v>401.8207702636719</v>
       </c>
       <c r="F109" t="n">
-        <v>45480500</v>
+        <v>42491000</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46063</v>
+        <v>46065</v>
       </c>
       <c r="B110" t="n">
-        <v>416.9746475616288</v>
+        <v>402.4468454245618</v>
       </c>
       <c r="C110" t="n">
-        <v>421.0090502850332</v>
+        <v>403.6392926521932</v>
       </c>
       <c r="D110" t="n">
-        <v>410.0982892644293</v>
+        <v>395.50092068537</v>
       </c>
       <c r="E110" t="n">
-        <v>410.6646728515625</v>
+        <v>399.3067626953125</v>
       </c>
       <c r="F110" t="n">
-        <v>44857900</v>
+        <v>40802400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46064</v>
+        <v>46066</v>
       </c>
       <c r="B111" t="n">
-        <v>413.5563153661985</v>
+        <v>401.900281272875</v>
       </c>
       <c r="C111" t="n">
-        <v>413.8345489802859</v>
+        <v>402.9834060634867</v>
       </c>
       <c r="D111" t="n">
-        <v>398.4819668946231</v>
+        <v>395.5406038478973</v>
       </c>
       <c r="E111" t="n">
-        <v>401.8207702636719</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="F111" t="n">
-        <v>42491000</v>
+        <v>34091600</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46065</v>
+        <v>46070</v>
       </c>
       <c r="B112" t="n">
-        <v>402.4468146669985</v>
+        <v>396.7032617740463</v>
       </c>
       <c r="C112" t="n">
-        <v>403.6392618034954</v>
+        <v>397.9950542597942</v>
       </c>
       <c r="D112" t="n">
-        <v>395.5008904586587</v>
+        <v>392.0428257724806</v>
       </c>
       <c r="E112" t="n">
-        <v>399.3067321777344</v>
+        <v>394.3581237792969</v>
       </c>
       <c r="F112" t="n">
-        <v>40802400</v>
+        <v>32078800</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46066</v>
+        <v>46071</v>
       </c>
       <c r="B113" t="n">
-        <v>401.900312028468</v>
+        <v>395.6201070500213</v>
       </c>
       <c r="C113" t="n">
-        <v>402.9834369019663</v>
+        <v>400.0221720919145</v>
       </c>
       <c r="D113" t="n">
-        <v>395.5406341168134</v>
+        <v>393.8215201082963</v>
       </c>
       <c r="E113" t="n">
-        <v>398.7900390625</v>
+        <v>397.0808410644531</v>
       </c>
       <c r="F113" t="n">
-        <v>34091600</v>
+        <v>23223400</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46070</v>
+        <v>46072</v>
       </c>
       <c r="B114" t="n">
-        <v>396.7032310749887</v>
+        <v>399.0727866126232</v>
       </c>
       <c r="C114" t="n">
-        <v>397.9950234607705</v>
+        <v>402.7976819572589</v>
       </c>
       <c r="D114" t="n">
-        <v>392.0427954340728</v>
+        <v>395.0690225854118</v>
       </c>
       <c r="E114" t="n">
-        <v>394.3580932617188</v>
+        <v>396.8517761230469</v>
       </c>
       <c r="F114" t="n">
-        <v>32078800</v>
+        <v>28234000</v>
       </c>
       <c r="G114" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46071</v>
+        <v>46073</v>
       </c>
       <c r="B115" t="n">
-        <v>395.6201374553349</v>
+        <v>394.5112344348997</v>
       </c>
       <c r="C115" t="n">
-        <v>400.0222028355481</v>
+        <v>398.5050592846536</v>
       </c>
       <c r="D115" t="n">
-        <v>393.8215503753798</v>
+        <v>393.5650869938952</v>
       </c>
       <c r="E115" t="n">
-        <v>397.0808715820312</v>
+        <v>395.6267395019531</v>
       </c>
       <c r="F115" t="n">
-        <v>23223400</v>
+        <v>34015200</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,25 +3433,25 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46072</v>
+        <v>46076</v>
       </c>
       <c r="B116" t="n">
-        <v>399.0727866126232</v>
+        <v>393.405742102137</v>
       </c>
       <c r="C116" t="n">
-        <v>402.7976819572589</v>
+        <v>393.7642745182822</v>
       </c>
       <c r="D116" t="n">
-        <v>395.0690225854118</v>
+        <v>381.5537777227514</v>
       </c>
       <c r="E116" t="n">
-        <v>396.8517761230469</v>
+        <v>382.9182434082031</v>
       </c>
       <c r="F116" t="n">
-        <v>28234000</v>
+        <v>43238300</v>
       </c>
       <c r="G116" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46073</v>
+        <v>46077</v>
       </c>
       <c r="B117" t="n">
-        <v>394.5112344348997</v>
+        <v>382.5895619940176</v>
       </c>
       <c r="C117" t="n">
-        <v>398.5050592846536</v>
+        <v>387.7884640317496</v>
       </c>
       <c r="D117" t="n">
-        <v>393.5650869938952</v>
+        <v>380.1693467763097</v>
       </c>
       <c r="E117" t="n">
-        <v>395.6267395019531</v>
+        <v>387.429931640625</v>
       </c>
       <c r="F117" t="n">
-        <v>34015200</v>
+        <v>33884700</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46076</v>
+        <v>46078</v>
       </c>
       <c r="B118" t="n">
-        <v>393.405742102137</v>
+        <v>388.9537605304631</v>
       </c>
       <c r="C118" t="n">
-        <v>393.7642745182822</v>
+        <v>399.8496074643683</v>
       </c>
       <c r="D118" t="n">
-        <v>381.5537777227514</v>
+        <v>388.5852587696308</v>
       </c>
       <c r="E118" t="n">
-        <v>382.9182434082031</v>
+        <v>398.9831237792969</v>
       </c>
       <c r="F118" t="n">
-        <v>43238300</v>
+        <v>43625500</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46077</v>
+        <v>46079</v>
       </c>
       <c r="B119" t="n">
-        <v>382.5895619940176</v>
+        <v>403.0765245044552</v>
       </c>
       <c r="C119" t="n">
-        <v>387.7884640317496</v>
+        <v>405.8453028142193</v>
       </c>
       <c r="D119" t="n">
-        <v>380.1693467763097</v>
+        <v>397.1306190557743</v>
       </c>
       <c r="E119" t="n">
-        <v>387.429931640625</v>
+        <v>400.0986022949219</v>
       </c>
       <c r="F119" t="n">
-        <v>33884700</v>
+        <v>34405900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46078</v>
+        <v>46080</v>
       </c>
       <c r="B120" t="n">
-        <v>388.9537605304631</v>
+        <v>389.3023679559341</v>
       </c>
       <c r="C120" t="n">
-        <v>399.8496074643683</v>
+        <v>395.2183958601928</v>
       </c>
       <c r="D120" t="n">
-        <v>388.5852587696308</v>
+        <v>388.3064040716401</v>
       </c>
       <c r="E120" t="n">
-        <v>398.9831237792969</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="F120" t="n">
-        <v>43625500</v>
+        <v>51367200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46079</v>
+        <v>46083</v>
       </c>
       <c r="B121" t="n">
-        <v>403.0765245044552</v>
+        <v>391.2743390590049</v>
       </c>
       <c r="C121" t="n">
-        <v>405.8453028142193</v>
+        <v>399.5707348557469</v>
       </c>
       <c r="D121" t="n">
-        <v>397.1306190557743</v>
+        <v>389.0533591512552</v>
       </c>
       <c r="E121" t="n">
-        <v>400.0986022949219</v>
+        <v>396.9413757324219</v>
       </c>
       <c r="F121" t="n">
-        <v>34405900</v>
+        <v>35474900</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46080</v>
+        <v>46084</v>
       </c>
       <c r="B122" t="n">
-        <v>389.3023679559341</v>
+        <v>391.5532542396072</v>
       </c>
       <c r="C122" t="n">
-        <v>395.2183958601928</v>
+        <v>405.0585220162706</v>
       </c>
       <c r="D122" t="n">
-        <v>388.3064040716401</v>
+        <v>391.0851500003899</v>
       </c>
       <c r="E122" t="n">
-        <v>391.1548461914062</v>
+        <v>402.2996826171875</v>
       </c>
       <c r="F122" t="n">
-        <v>51367200</v>
+        <v>38199200</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46083</v>
+        <v>46085</v>
       </c>
       <c r="B123" t="n">
-        <v>391.2743390590049</v>
+        <v>399.6504140582061</v>
       </c>
       <c r="C123" t="n">
-        <v>399.5707348557469</v>
+        <v>409.3710312257941</v>
       </c>
       <c r="D123" t="n">
-        <v>389.0533591512552</v>
+        <v>398.6942972465368</v>
       </c>
       <c r="E123" t="n">
-        <v>396.9413757324219</v>
+        <v>403.5645751953125</v>
       </c>
       <c r="F123" t="n">
-        <v>35474900</v>
+        <v>35808000</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46084</v>
+        <v>46086</v>
       </c>
       <c r="B124" t="n">
-        <v>391.5532542396072</v>
+        <v>402.7877173292459</v>
       </c>
       <c r="C124" t="n">
-        <v>405.0585220162706</v>
+        <v>409.9486695143622</v>
       </c>
       <c r="D124" t="n">
-        <v>391.0851500003899</v>
+        <v>402.7677785996419</v>
       </c>
       <c r="E124" t="n">
-        <v>402.2996826171875</v>
+        <v>409.0224304199219</v>
       </c>
       <c r="F124" t="n">
-        <v>38199200</v>
+        <v>39001300</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46085</v>
+        <v>46087</v>
       </c>
       <c r="B125" t="n">
-        <v>399.6504140582061</v>
+        <v>407.5484392107423</v>
       </c>
       <c r="C125" t="n">
-        <v>409.3710312257941</v>
+        <v>411.3828759024364</v>
       </c>
       <c r="D125" t="n">
-        <v>398.6942972465368</v>
+        <v>406.8612216895844</v>
       </c>
       <c r="E125" t="n">
-        <v>403.5645751953125</v>
+        <v>407.3093872070312</v>
       </c>
       <c r="F125" t="n">
-        <v>35808000</v>
+        <v>31123900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46086</v>
+        <v>46090</v>
       </c>
       <c r="B126" t="n">
-        <v>402.7877173292459</v>
+        <v>403.2857003455267</v>
       </c>
       <c r="C126" t="n">
-        <v>409.9486695143622</v>
+        <v>408.5543272911556</v>
       </c>
       <c r="D126" t="n">
-        <v>402.7677785996419</v>
+        <v>401.8714182880504</v>
       </c>
       <c r="E126" t="n">
-        <v>409.0224304199219</v>
+        <v>407.757568359375</v>
       </c>
       <c r="F126" t="n">
-        <v>39001300</v>
+        <v>30131900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46087</v>
+        <v>46091</v>
       </c>
       <c r="B127" t="n">
-        <v>407.5484392107423</v>
+        <v>408.3750692869274</v>
       </c>
       <c r="C127" t="n">
-        <v>411.3828759024364</v>
+        <v>408.5443965203919</v>
       </c>
       <c r="D127" t="n">
-        <v>406.8612216895844</v>
+        <v>401.3037196464309</v>
       </c>
       <c r="E127" t="n">
-        <v>407.3093872070312</v>
+        <v>404.122314453125</v>
       </c>
       <c r="F127" t="n">
-        <v>31123900</v>
+        <v>31706400</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46090</v>
+        <v>46092</v>
       </c>
       <c r="B128" t="n">
-        <v>403.2857003455267</v>
+        <v>403.9330670994013</v>
       </c>
       <c r="C128" t="n">
-        <v>408.5543272911556</v>
+        <v>407.3591851847947</v>
       </c>
       <c r="D128" t="n">
-        <v>401.8714182880504</v>
+        <v>399.9691200230297</v>
       </c>
       <c r="E128" t="n">
-        <v>407.757568359375</v>
+        <v>403.245849609375</v>
       </c>
       <c r="F128" t="n">
-        <v>30131900</v>
+        <v>25512100</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46091</v>
+        <v>46093</v>
       </c>
       <c r="B129" t="n">
-        <v>408.3750692869274</v>
+        <v>402.9968458288957</v>
       </c>
       <c r="C129" t="n">
-        <v>408.5443965203919</v>
+        <v>404.4808221962511</v>
       </c>
       <c r="D129" t="n">
-        <v>401.3037196464309</v>
+        <v>400.0886180975</v>
       </c>
       <c r="E129" t="n">
-        <v>404.122314453125</v>
+        <v>400.2380065917969</v>
       </c>
       <c r="F129" t="n">
-        <v>31706400</v>
+        <v>27263900</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46092</v>
+        <v>46094</v>
       </c>
       <c r="B130" t="n">
-        <v>403.9330670994013</v>
+        <v>399.3815063856616</v>
       </c>
       <c r="C130" t="n">
-        <v>407.3591851847947</v>
+        <v>403.1661568819284</v>
       </c>
       <c r="D130" t="n">
-        <v>399.9691200230297</v>
+        <v>392.6587503554791</v>
       </c>
       <c r="E130" t="n">
-        <v>403.245849609375</v>
+        <v>393.9534912109375</v>
       </c>
       <c r="F130" t="n">
-        <v>25512100</v>
+        <v>26848000</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46093</v>
+        <v>46097</v>
       </c>
       <c r="B131" t="n">
-        <v>402.9968458288957</v>
+        <v>396.4633374914087</v>
       </c>
       <c r="C131" t="n">
-        <v>404.4808221962511</v>
+        <v>399.013002518604</v>
       </c>
       <c r="D131" t="n">
-        <v>400.0886180975</v>
+        <v>393.1965772756644</v>
       </c>
       <c r="E131" t="n">
-        <v>400.2380065917969</v>
+        <v>398.3357543945312</v>
       </c>
       <c r="F131" t="n">
-        <v>27263900</v>
+        <v>27733700</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46094</v>
+        <v>46098</v>
       </c>
       <c r="B132" t="n">
-        <v>399.3815063856616</v>
+        <v>398.6544574759768</v>
       </c>
       <c r="C132" t="n">
-        <v>403.1661568819284</v>
+        <v>402.7677932271478</v>
       </c>
       <c r="D132" t="n">
-        <v>392.6587503554791</v>
+        <v>396.1446394015159</v>
       </c>
       <c r="E132" t="n">
-        <v>393.9534912109375</v>
+        <v>397.7979431152344</v>
       </c>
       <c r="F132" t="n">
-        <v>26848000</v>
+        <v>26228300</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46097</v>
+        <v>46099</v>
       </c>
       <c r="B133" t="n">
-        <v>396.4633374914087</v>
+        <v>395.5271224277118</v>
       </c>
       <c r="C133" t="n">
-        <v>399.013002518604</v>
+        <v>396.3936061005556</v>
       </c>
       <c r="D133" t="n">
-        <v>393.1965772756644</v>
+        <v>389.421859259591</v>
       </c>
       <c r="E133" t="n">
-        <v>398.3357543945312</v>
+        <v>390.2086791992188</v>
       </c>
       <c r="F133" t="n">
-        <v>27733700</v>
+        <v>25908500</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46098</v>
+        <v>46100</v>
       </c>
       <c r="B134" t="n">
-        <v>398.6544574759768</v>
+        <v>388.5255176358589</v>
       </c>
       <c r="C134" t="n">
-        <v>402.7677932271478</v>
+        <v>390.9058555160312</v>
       </c>
       <c r="D134" t="n">
-        <v>396.1446394015159</v>
+        <v>385.4977789148814</v>
       </c>
       <c r="E134" t="n">
-        <v>397.7979431152344</v>
+        <v>387.4498596191406</v>
       </c>
       <c r="F134" t="n">
-        <v>26228300</v>
+        <v>25138800</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46099</v>
+        <v>46101</v>
       </c>
       <c r="B135" t="n">
-        <v>395.5271224277118</v>
+        <v>385.2288602760525</v>
       </c>
       <c r="C135" t="n">
-        <v>396.3936061005556</v>
+        <v>385.4380041709834</v>
       </c>
       <c r="D135" t="n">
-        <v>389.421859259591</v>
+        <v>378.5857681226169</v>
       </c>
       <c r="E135" t="n">
-        <v>390.2086791992188</v>
+        <v>380.3287048339844</v>
       </c>
       <c r="F135" t="n">
-        <v>25908500</v>
+        <v>50853200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46100</v>
+        <v>46104</v>
       </c>
       <c r="B136" t="n">
-        <v>388.5255176358589</v>
+        <v>382.3505545919761</v>
       </c>
       <c r="C136" t="n">
-        <v>390.9058555160312</v>
+        <v>385.6471928372158</v>
       </c>
       <c r="D136" t="n">
-        <v>385.4977789148814</v>
+        <v>380.1395134056624</v>
       </c>
       <c r="E136" t="n">
-        <v>387.4498596191406</v>
+        <v>381.4541931152344</v>
       </c>
       <c r="F136" t="n">
-        <v>25138800</v>
+        <v>29680100</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46101</v>
+        <v>46105</v>
       </c>
       <c r="B137" t="n">
-        <v>385.2288602760525</v>
+        <v>380.8167328036651</v>
       </c>
       <c r="C137" t="n">
-        <v>385.4380041709834</v>
+        <v>380.9263046350485</v>
       </c>
       <c r="D137" t="n">
-        <v>378.5857681226169</v>
+        <v>370.3491731415432</v>
       </c>
       <c r="E137" t="n">
-        <v>380.3287048339844</v>
+        <v>371.2355651855469</v>
       </c>
       <c r="F137" t="n">
-        <v>50853200</v>
+        <v>42733600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46104</v>
+        <v>46106</v>
       </c>
       <c r="B138" t="n">
-        <v>382.3505545919761</v>
+        <v>375.3987224826456</v>
       </c>
       <c r="C138" t="n">
-        <v>385.6471928372158</v>
+        <v>375.5381416220395</v>
       </c>
       <c r="D138" t="n">
-        <v>380.1395134056624</v>
+        <v>368.1381372201017</v>
       </c>
       <c r="E138" t="n">
-        <v>381.4541931152344</v>
+        <v>369.5424499511719</v>
       </c>
       <c r="F138" t="n">
-        <v>29680100</v>
+        <v>31181200</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46105</v>
+        <v>46107</v>
       </c>
       <c r="B139" t="n">
-        <v>380.8167328036651</v>
+        <v>369.3233201292261</v>
       </c>
       <c r="C139" t="n">
-        <v>380.9263046350485</v>
+        <v>373.2075730440749</v>
       </c>
       <c r="D139" t="n">
-        <v>370.3491731415432</v>
+        <v>363.7160388213271</v>
       </c>
       <c r="E139" t="n">
-        <v>371.2355651855469</v>
+        <v>364.4928894042969</v>
       </c>
       <c r="F139" t="n">
-        <v>42733600</v>
+        <v>36836600</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46106</v>
+        <v>46108</v>
       </c>
       <c r="B140" t="n">
-        <v>375.3987224826456</v>
+        <v>360.4393475355787</v>
       </c>
       <c r="C140" t="n">
-        <v>375.5381416220395</v>
+        <v>360.9871459448897</v>
       </c>
       <c r="D140" t="n">
-        <v>368.1381372201017</v>
+        <v>355.0711176485405</v>
       </c>
       <c r="E140" t="n">
-        <v>369.5424499511719</v>
+        <v>355.3300476074219</v>
       </c>
       <c r="F140" t="n">
-        <v>31181200</v>
+        <v>37883400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46107</v>
+        <v>46111</v>
       </c>
       <c r="B141" t="n">
-        <v>369.3233201292261</v>
+        <v>360.4393363053819</v>
       </c>
       <c r="C141" t="n">
-        <v>373.2075730440749</v>
+        <v>363.8853629556265</v>
       </c>
       <c r="D141" t="n">
-        <v>363.7160388213271</v>
+        <v>354.8420239421825</v>
       </c>
       <c r="E141" t="n">
-        <v>364.4928894042969</v>
+        <v>357.5111999511719</v>
       </c>
       <c r="F141" t="n">
-        <v>36836600</v>
+        <v>44797000</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46108</v>
+        <v>46112</v>
       </c>
       <c r="B142" t="n">
-        <v>360.4393475355787</v>
+        <v>363.0786217954557</v>
       </c>
       <c r="C142" t="n">
-        <v>360.9871459448897</v>
+        <v>371.3949263066763</v>
       </c>
       <c r="D142" t="n">
-        <v>355.0711176485405</v>
+        <v>361.6046146993887</v>
       </c>
       <c r="E142" t="n">
-        <v>355.3300476074219</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="F142" t="n">
-        <v>37883400</v>
+        <v>45244400</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46111</v>
+        <v>46113</v>
       </c>
       <c r="B143" t="n">
-        <v>360.4393363053819</v>
+        <v>371.9825473134139</v>
       </c>
       <c r="C143" t="n">
-        <v>363.8853629556265</v>
+        <v>372.4805292634522</v>
       </c>
       <c r="D143" t="n">
-        <v>354.8420239421825</v>
+        <v>366.7139201659809</v>
       </c>
       <c r="E143" t="n">
-        <v>357.5111999511719</v>
+        <v>367.8791809082031</v>
       </c>
       <c r="F143" t="n">
-        <v>44797000</v>
+        <v>29417200</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46112</v>
+        <v>46114</v>
       </c>
       <c r="B144" t="n">
-        <v>363.0786217954557</v>
+        <v>365.7278929006101</v>
       </c>
       <c r="C144" t="n">
-        <v>371.3949263066763</v>
+        <v>372.1319638369453</v>
       </c>
       <c r="D144" t="n">
-        <v>361.6046146993887</v>
+        <v>362.680245817395</v>
       </c>
       <c r="E144" t="n">
-        <v>368.6759643554688</v>
+        <v>371.9526672363281</v>
       </c>
       <c r="F144" t="n">
-        <v>45244400</v>
+        <v>24099100</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46113</v>
+        <v>46118</v>
       </c>
       <c r="B145" t="n">
-        <v>371.9825473134139</v>
+        <v>371.9825539180967</v>
       </c>
       <c r="C145" t="n">
-        <v>372.4805292634522</v>
+        <v>372.2216059265558</v>
       </c>
       <c r="D145" t="n">
-        <v>366.7139201659809</v>
+        <v>368.0086676124431</v>
       </c>
       <c r="E145" t="n">
-        <v>367.8791809082031</v>
+        <v>371.3750305175781</v>
       </c>
       <c r="F145" t="n">
-        <v>29417200</v>
+        <v>16146600</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46114</v>
+        <v>46119</v>
       </c>
       <c r="B146" t="n">
-        <v>365.7278929006101</v>
+        <v>368.8452727581139</v>
       </c>
       <c r="C146" t="n">
-        <v>372.1319638369453</v>
+        <v>370.9467724245638</v>
       </c>
       <c r="D146" t="n">
-        <v>362.680245817395</v>
+        <v>365.080530373921</v>
       </c>
       <c r="E146" t="n">
-        <v>371.9526672363281</v>
+        <v>370.7874145507812</v>
       </c>
       <c r="F146" t="n">
-        <v>24099100</v>
+        <v>21443300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46118</v>
+        <v>46120</v>
       </c>
       <c r="B147" t="n">
-        <v>371.9825539180967</v>
+        <v>383.4261612830284</v>
       </c>
       <c r="C147" t="n">
-        <v>372.2216059265558</v>
+        <v>383.4460696173869</v>
       </c>
       <c r="D147" t="n">
-        <v>368.0086676124431</v>
+        <v>369.9109249891301</v>
       </c>
       <c r="E147" t="n">
-        <v>371.3750305175781</v>
+        <v>372.8191223144531</v>
       </c>
       <c r="F147" t="n">
-        <v>16146600</v>
+        <v>33064800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="B148" t="n">
-        <v>368.8452727581139</v>
+        <v>370.9965328148009</v>
       </c>
       <c r="C148" t="n">
-        <v>370.9467724245638</v>
+        <v>371.9924966612836</v>
       </c>
       <c r="D148" t="n">
-        <v>365.080530373921</v>
+        <v>365.5685176937085</v>
       </c>
       <c r="E148" t="n">
-        <v>370.7874145507812</v>
+        <v>371.5642395019531</v>
       </c>
       <c r="F148" t="n">
-        <v>21443300</v>
+        <v>30435300</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46120</v>
+        <v>46122</v>
       </c>
       <c r="B149" t="n">
-        <v>383.4261612830284</v>
+        <v>371.4746074371751</v>
       </c>
       <c r="C149" t="n">
-        <v>383.4460696173869</v>
+        <v>374.1238749235223</v>
       </c>
       <c r="D149" t="n">
-        <v>369.9109249891301</v>
+        <v>368.5365019241105</v>
       </c>
       <c r="E149" t="n">
-        <v>372.8191223144531</v>
+        <v>369.3731079101562</v>
       </c>
       <c r="F149" t="n">
-        <v>33064800</v>
+        <v>28111100</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46121</v>
+        <v>46125</v>
       </c>
       <c r="B150" t="n">
-        <v>370.9965328148009</v>
+        <v>372.1020528926679</v>
       </c>
       <c r="C150" t="n">
-        <v>371.9924966612836</v>
+        <v>382.9879612673769</v>
       </c>
       <c r="D150" t="n">
-        <v>365.5685176937085</v>
+        <v>369.5225100750242</v>
       </c>
       <c r="E150" t="n">
-        <v>371.5642395019531</v>
+        <v>382.8186340332031</v>
       </c>
       <c r="F150" t="n">
-        <v>30435300</v>
+        <v>35745800</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46122</v>
+        <v>46126</v>
       </c>
       <c r="B151" t="n">
-        <v>371.4746074371751</v>
+        <v>386.3543213772784</v>
       </c>
       <c r="C151" t="n">
-        <v>374.1238749235223</v>
+        <v>393.0969858972055</v>
       </c>
       <c r="D151" t="n">
-        <v>368.5365019241105</v>
+        <v>384.95994763093</v>
       </c>
       <c r="E151" t="n">
-        <v>369.3731079101562</v>
+        <v>391.5233459472656</v>
       </c>
       <c r="F151" t="n">
-        <v>28111100</v>
+        <v>37504500</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46125</v>
+        <v>46127</v>
       </c>
       <c r="B152" t="n">
-        <v>372.1020528926679</v>
+        <v>396.3936283702306</v>
       </c>
       <c r="C152" t="n">
-        <v>382.9879612673769</v>
+        <v>412.6975523926047</v>
       </c>
       <c r="D152" t="n">
-        <v>369.5225100750242</v>
+        <v>395.1287651714373</v>
       </c>
       <c r="E152" t="n">
-        <v>382.8186340332031</v>
+        <v>409.5602722167969</v>
       </c>
       <c r="F152" t="n">
-        <v>35745800</v>
+        <v>45063400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46126</v>
+        <v>46128</v>
       </c>
       <c r="B153" t="n">
-        <v>386.3543213772784</v>
+        <v>418.1653718785589</v>
       </c>
       <c r="C153" t="n">
-        <v>393.0969858972055</v>
+        <v>419.1215190686066</v>
       </c>
       <c r="D153" t="n">
-        <v>384.95994763093</v>
+        <v>410.4765600541581</v>
       </c>
       <c r="E153" t="n">
-        <v>391.5233459472656</v>
+        <v>418.5637817382812</v>
       </c>
       <c r="F153" t="n">
-        <v>37504500</v>
+        <v>41642400</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46127</v>
+        <v>46129</v>
       </c>
       <c r="B154" t="n">
-        <v>396.3936283702306</v>
+        <v>423.105393156615</v>
       </c>
       <c r="C154" t="n">
-        <v>412.6975523926047</v>
+        <v>429.8380884820792</v>
       </c>
       <c r="D154" t="n">
-        <v>395.1287651714373</v>
+        <v>418.9920573683891</v>
       </c>
       <c r="E154" t="n">
-        <v>409.5602722167969</v>
+        <v>421.0835876464844</v>
       </c>
       <c r="F154" t="n">
-        <v>45063400</v>
+        <v>48568200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46128</v>
+        <v>46132</v>
       </c>
       <c r="B155" t="n">
-        <v>418.1653718785589</v>
+        <v>419.4501847919345</v>
       </c>
       <c r="C155" t="n">
-        <v>419.1215190686066</v>
+        <v>421.6213787702164</v>
       </c>
       <c r="D155" t="n">
-        <v>410.4765600541581</v>
+        <v>414.6197538627068</v>
       </c>
       <c r="E155" t="n">
-        <v>418.5637817382812</v>
+        <v>416.3826293945312</v>
       </c>
       <c r="F155" t="n">
-        <v>41642400</v>
+        <v>27582200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46129</v>
+        <v>46133</v>
       </c>
       <c r="B156" t="n">
-        <v>423.105393156615</v>
+        <v>418.5438369146158</v>
       </c>
       <c r="C156" t="n">
-        <v>429.8380884820792</v>
+        <v>425.4558284373716</v>
       </c>
       <c r="D156" t="n">
-        <v>418.9920573683891</v>
+        <v>415.516128706763</v>
       </c>
       <c r="E156" t="n">
-        <v>421.0835876464844</v>
+        <v>422.4480285644531</v>
       </c>
       <c r="F156" t="n">
-        <v>48568200</v>
+        <v>32048500</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46132</v>
+        <v>46134</v>
       </c>
       <c r="B157" t="n">
-        <v>419.4501847919345</v>
+        <v>424.4698510786937</v>
       </c>
       <c r="C157" t="n">
-        <v>421.6213787702164</v>
+        <v>431.9495495900464</v>
       </c>
       <c r="D157" t="n">
-        <v>414.6197538627068</v>
+        <v>421.9600330275293</v>
       </c>
       <c r="E157" t="n">
-        <v>416.3826293945312</v>
+        <v>431.1726989746094</v>
       </c>
       <c r="F157" t="n">
-        <v>27582200</v>
+        <v>29378200</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46133</v>
+        <v>46135</v>
       </c>
       <c r="B158" t="n">
-        <v>418.5438369146158</v>
+        <v>418.195296097549</v>
       </c>
       <c r="C158" t="n">
-        <v>425.4558284373716</v>
+        <v>421.9500690544079</v>
       </c>
       <c r="D158" t="n">
-        <v>415.516128706763</v>
+        <v>409.7495112929088</v>
       </c>
       <c r="E158" t="n">
-        <v>422.4480285644531</v>
+        <v>414.0719909667969</v>
       </c>
       <c r="F158" t="n">
-        <v>32048500</v>
+        <v>38308000</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46134</v>
+        <v>46136</v>
       </c>
       <c r="B159" t="n">
-        <v>424.4698510786937</v>
+        <v>415.2870711617039</v>
       </c>
       <c r="C159" t="n">
-        <v>431.9495495900464</v>
+        <v>423.2348740747397</v>
       </c>
       <c r="D159" t="n">
-        <v>421.9600330275293</v>
+        <v>414.1217800179737</v>
       </c>
       <c r="E159" t="n">
-        <v>431.1726989746094</v>
+        <v>422.9061889648438</v>
       </c>
       <c r="F159" t="n">
-        <v>29378200</v>
+        <v>27457400</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46135</v>
+        <v>46139</v>
       </c>
       <c r="B160" t="n">
-        <v>418.195296097549</v>
+        <v>420.6752229306716</v>
       </c>
       <c r="C160" t="n">
-        <v>421.9500690544079</v>
+        <v>425.3861125683125</v>
       </c>
       <c r="D160" t="n">
-        <v>409.7495112929088</v>
+        <v>415.3866572294081</v>
       </c>
       <c r="E160" t="n">
-        <v>414.0719909667969</v>
+        <v>423.1053771972656</v>
       </c>
       <c r="F160" t="n">
-        <v>38308000</v>
+        <v>30867300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46136</v>
+        <v>46140</v>
       </c>
       <c r="B161" t="n">
-        <v>415.2870711617039</v>
+        <v>422.8563830057505</v>
       </c>
       <c r="C161" t="n">
-        <v>423.2348740747397</v>
+        <v>428.1847957314844</v>
       </c>
       <c r="D161" t="n">
-        <v>414.1217800179737</v>
+        <v>420.197146128082</v>
       </c>
       <c r="E161" t="n">
-        <v>422.9061889648438</v>
+        <v>427.5174865722656</v>
       </c>
       <c r="F161" t="n">
-        <v>27457400</v>
+        <v>30438100</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46139</v>
+        <v>46141</v>
       </c>
       <c r="B162" t="n">
-        <v>420.6752229306716</v>
+        <v>422.8663369761165</v>
       </c>
       <c r="C162" t="n">
-        <v>425.3861125683125</v>
+        <v>425.0973167681131</v>
       </c>
       <c r="D162" t="n">
-        <v>415.3866572294081</v>
+        <v>418.593673752453</v>
       </c>
       <c r="E162" t="n">
-        <v>423.1053771972656</v>
+        <v>422.746826171875</v>
       </c>
       <c r="F162" t="n">
-        <v>30867300</v>
+        <v>38288300</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46140</v>
+        <v>46142</v>
       </c>
       <c r="B163" t="n">
-        <v>422.8563830057505</v>
+        <v>409.1519246549498</v>
       </c>
       <c r="C163" t="n">
-        <v>428.1847957314844</v>
+        <v>412.7473701155562</v>
       </c>
       <c r="D163" t="n">
-        <v>420.197146128082</v>
+        <v>396.4035989759817</v>
       </c>
       <c r="E163" t="n">
-        <v>427.5174865722656</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="F163" t="n">
-        <v>30438100</v>
+        <v>70909400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46141</v>
+        <v>46143</v>
       </c>
       <c r="B164" t="n">
-        <v>422.8663369761165</v>
+        <v>411.1338775963461</v>
       </c>
       <c r="C164" t="n">
-        <v>425.0973167681131</v>
+        <v>415.4264794885345</v>
       </c>
       <c r="D164" t="n">
-        <v>418.593673752453</v>
+        <v>408.7834174283456</v>
       </c>
       <c r="E164" t="n">
-        <v>422.746826171875</v>
+        <v>412.7672729492188</v>
       </c>
       <c r="F164" t="n">
-        <v>38288300</v>
+        <v>31372400</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46142</v>
+        <v>46146</v>
       </c>
       <c r="B165" t="n">
-        <v>409.1519246549498</v>
+        <v>409.8789700952638</v>
       </c>
       <c r="C165" t="n">
-        <v>412.7473701155562</v>
+        <v>419.0816663151199</v>
       </c>
       <c r="D165" t="n">
-        <v>396.4035989759817</v>
+        <v>409.1419361803058</v>
       </c>
       <c r="E165" t="n">
-        <v>406.1341552734375</v>
+        <v>411.9505615234375</v>
       </c>
       <c r="F165" t="n">
-        <v>70909400</v>
+        <v>28066500</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46143</v>
+        <v>46147</v>
       </c>
       <c r="B166" t="n">
-        <v>411.1338775963461</v>
+        <v>413.6437044066962</v>
       </c>
       <c r="C166" t="n">
-        <v>415.4264794885345</v>
+        <v>415.0978030853789</v>
       </c>
       <c r="D166" t="n">
-        <v>408.7834174283456</v>
+        <v>407.1500007946646</v>
       </c>
       <c r="E166" t="n">
-        <v>412.7672729492188</v>
+        <v>409.7196044921875</v>
       </c>
       <c r="F166" t="n">
-        <v>31372400</v>
+        <v>25700900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46146</v>
+        <v>46148</v>
       </c>
       <c r="B167" t="n">
-        <v>409.8789700952638</v>
+        <v>406.3532485673598</v>
       </c>
       <c r="C167" t="n">
-        <v>419.0816663151199</v>
+        <v>416.7312052008779</v>
       </c>
       <c r="D167" t="n">
-        <v>409.1419361803058</v>
+        <v>403.4748984673602</v>
       </c>
       <c r="E167" t="n">
-        <v>411.9505615234375</v>
+        <v>412.2891845703125</v>
       </c>
       <c r="F167" t="n">
-        <v>28066500</v>
+        <v>30285900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46147</v>
+        <v>46149</v>
       </c>
       <c r="B168" t="n">
-        <v>413.6437044066962</v>
+        <v>418.4143764918961</v>
       </c>
       <c r="C168" t="n">
-        <v>415.0978030853789</v>
+        <v>426.2526378609755</v>
       </c>
       <c r="D168" t="n">
-        <v>407.1500007946646</v>
+        <v>417.0698495518934</v>
       </c>
       <c r="E168" t="n">
-        <v>409.7196044921875</v>
+        <v>419.0717163085938</v>
       </c>
       <c r="F168" t="n">
-        <v>25700900</v>
+        <v>34942400</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46148</v>
+        <v>46150</v>
       </c>
       <c r="B169" t="n">
-        <v>406.3532485673598</v>
+        <v>415.7053764922729</v>
       </c>
       <c r="C169" t="n">
-        <v>416.7312052008779</v>
+        <v>416.9403619714099</v>
       </c>
       <c r="D169" t="n">
-        <v>403.4748984673602</v>
+        <v>412.3290443657605</v>
       </c>
       <c r="E169" t="n">
-        <v>412.2891845703125</v>
+        <v>413.4445190429688</v>
       </c>
       <c r="F169" t="n">
-        <v>30285900</v>
+        <v>33383800</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46149</v>
+        <v>46153</v>
       </c>
       <c r="B170" t="n">
-        <v>418.4143764918961</v>
+        <v>406.223770451025</v>
       </c>
       <c r="C170" t="n">
-        <v>426.2526378609755</v>
+        <v>411.0243235004914</v>
       </c>
       <c r="D170" t="n">
-        <v>417.0698495518934</v>
+        <v>403.8633409907068</v>
       </c>
       <c r="E170" t="n">
-        <v>419.0717163085938</v>
+        <v>410.9944458007812</v>
       </c>
       <c r="F170" t="n">
-        <v>34942400</v>
+        <v>35657900</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46150</v>
+        <v>46154</v>
       </c>
       <c r="B171" t="n">
-        <v>415.7053764922729</v>
+        <v>412.8071154720842</v>
       </c>
       <c r="C171" t="n">
-        <v>416.9403619714099</v>
+        <v>413.8229876767416</v>
       </c>
       <c r="D171" t="n">
-        <v>412.3290443657605</v>
+        <v>404.9987623844293</v>
       </c>
       <c r="E171" t="n">
-        <v>413.4445190429688</v>
+        <v>406.1241760253906</v>
       </c>
       <c r="F171" t="n">
-        <v>33383800</v>
+        <v>38594200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46153</v>
+        <v>46155</v>
       </c>
       <c r="B172" t="n">
-        <v>406.223770451025</v>
+        <v>401.5726571524119</v>
       </c>
       <c r="C172" t="n">
-        <v>411.0243235004914</v>
+        <v>404.6700902960666</v>
       </c>
       <c r="D172" t="n">
-        <v>403.8633409907068</v>
+        <v>399.4114021131033</v>
       </c>
       <c r="E172" t="n">
-        <v>410.9944458007812</v>
+        <v>403.5745239257812</v>
       </c>
       <c r="F172" t="n">
-        <v>35657900</v>
+        <v>29667100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46154</v>
+        <v>46156</v>
       </c>
       <c r="B173" t="n">
-        <v>412.8071154720842</v>
+        <v>402.8474630718804</v>
       </c>
       <c r="C173" t="n">
-        <v>413.8229876767416</v>
+        <v>410.1777423108794</v>
       </c>
       <c r="D173" t="n">
-        <v>404.9987623844293</v>
+        <v>399.2619871856725</v>
       </c>
       <c r="E173" t="n">
-        <v>406.1241760253906</v>
+        <v>407.7774658203125</v>
       </c>
       <c r="F173" t="n">
-        <v>38594200</v>
+        <v>27077500</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46155</v>
+        <v>46157</v>
       </c>
       <c r="B174" t="n">
-        <v>401.5726571524119</v>
+        <v>412.5979239362014</v>
       </c>
       <c r="C174" t="n">
-        <v>404.6700902960666</v>
+        <v>426.4418454559798</v>
       </c>
       <c r="D174" t="n">
-        <v>399.4114021131033</v>
+        <v>411.2434277199191</v>
       </c>
       <c r="E174" t="n">
-        <v>403.5745239257812</v>
+        <v>420.2170715332031</v>
       </c>
       <c r="F174" t="n">
-        <v>29667100</v>
+        <v>50771200</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46156</v>
+        <v>46160</v>
       </c>
       <c r="B175" t="n">
-        <v>402.8474630718804</v>
+        <v>414.9384827190711</v>
       </c>
       <c r="C175" t="n">
-        <v>410.1777423108794</v>
+        <v>423.4041760233977</v>
       </c>
       <c r="D175" t="n">
-        <v>399.2619871856725</v>
+        <v>413.9325494355234</v>
       </c>
       <c r="E175" t="n">
-        <v>407.7774658203125</v>
+        <v>421.83056640625</v>
       </c>
       <c r="F175" t="n">
-        <v>27077500</v>
+        <v>32564100</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46157</v>
+        <v>46161</v>
       </c>
       <c r="B176" t="n">
-        <v>412.5979239362014</v>
+        <v>428.1648698947521</v>
       </c>
       <c r="C176" t="n">
-        <v>426.4418454559798</v>
+        <v>430.9535870211983</v>
       </c>
       <c r="D176" t="n">
-        <v>411.2434277199191</v>
+        <v>414.808990493047</v>
       </c>
       <c r="E176" t="n">
-        <v>420.2170715332031</v>
+        <v>415.7352600097656</v>
       </c>
       <c r="F176" t="n">
-        <v>50771200</v>
+        <v>33018700</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46160</v>
+        <v>46162</v>
       </c>
       <c r="B177" t="n">
-        <v>414.9384827190711</v>
+        <v>412.4983595724376</v>
       </c>
       <c r="C177" t="n">
-        <v>423.4041760233977</v>
+        <v>420.3963455784958</v>
       </c>
       <c r="D177" t="n">
-        <v>413.9325494355234</v>
+        <v>409.6399178024174</v>
       </c>
       <c r="E177" t="n">
-        <v>421.83056640625</v>
+        <v>419.3605346679688</v>
       </c>
       <c r="F177" t="n">
-        <v>32564100</v>
+        <v>27864000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46161</v>
+        <v>46163</v>
       </c>
       <c r="B178" t="n">
-        <v>428.1648698947521</v>
+        <v>423.9518891931334</v>
       </c>
       <c r="C178" t="n">
-        <v>430.9535870211983</v>
+        <v>425.5388979071037</v>
       </c>
       <c r="D178" t="n">
-        <v>414.808990493047</v>
+        <v>414.928866942535</v>
       </c>
       <c r="E178" t="n">
-        <v>415.7352600097656</v>
+        <v>418.3025207519531</v>
       </c>
       <c r="F178" t="n">
-        <v>33018700</v>
+        <v>31393500</v>
       </c>
       <c r="G178" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46162</v>
+        <v>46164</v>
       </c>
       <c r="B179" t="n">
-        <v>412.4983595724376</v>
+        <v>418.7517174636334</v>
       </c>
       <c r="C179" t="n">
-        <v>420.3963455784958</v>
+        <v>423.602571187628</v>
       </c>
       <c r="D179" t="n">
-        <v>409.6399178024174</v>
+        <v>415.547726934082</v>
       </c>
       <c r="E179" t="n">
-        <v>419.3605346679688</v>
+        <v>417.7835388183594</v>
       </c>
       <c r="F179" t="n">
-        <v>27864000</v>
+        <v>22390300</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,25 +5097,25 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46163</v>
+        <v>46168</v>
       </c>
       <c r="B180" t="n">
-        <v>423.9518891931334</v>
+        <v>415.6475333356961</v>
       </c>
       <c r="C180" t="n">
-        <v>425.5388979071037</v>
+        <v>418.9812539216563</v>
       </c>
       <c r="D180" t="n">
-        <v>414.928866942535</v>
+        <v>412.2439369671584</v>
       </c>
       <c r="E180" t="n">
-        <v>418.3025207519531</v>
+        <v>415.248291015625</v>
       </c>
       <c r="F180" t="n">
-        <v>31393500</v>
+        <v>30398000</v>
       </c>
       <c r="G180" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46164</v>
+        <v>46169</v>
       </c>
       <c r="B181" t="n">
-        <v>418.7517174636334</v>
+        <v>410.2377382218162</v>
       </c>
       <c r="C181" t="n">
-        <v>423.602571187628</v>
+        <v>415.15846763645</v>
       </c>
       <c r="D181" t="n">
-        <v>415.547726934082</v>
+        <v>408.8104019854481</v>
       </c>
       <c r="E181" t="n">
-        <v>417.7835388183594</v>
+        <v>411.8946228027344</v>
       </c>
       <c r="F181" t="n">
-        <v>22390300</v>
+        <v>28901500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46168</v>
+        <v>46170</v>
       </c>
       <c r="B182" t="n">
-        <v>415.6475333356961</v>
+        <v>412.2040283766931</v>
       </c>
       <c r="C182" t="n">
-        <v>418.9812539216563</v>
+        <v>428.6829856468207</v>
       </c>
       <c r="D182" t="n">
-        <v>412.2439369671584</v>
+        <v>411.8946132983843</v>
       </c>
       <c r="E182" t="n">
-        <v>415.248291015625</v>
+        <v>426.1876831054688</v>
       </c>
       <c r="F182" t="n">
-        <v>30398000</v>
+        <v>47250500</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46169</v>
+        <v>46171</v>
       </c>
       <c r="B183" t="n">
-        <v>410.2377382218162</v>
+        <v>431.7372486144539</v>
       </c>
       <c r="C183" t="n">
-        <v>415.15846763645</v>
+        <v>449.4838396905727</v>
       </c>
       <c r="D183" t="n">
-        <v>408.8104019854481</v>
+        <v>431.5476031778621</v>
       </c>
       <c r="E183" t="n">
-        <v>411.8946228027344</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="F183" t="n">
-        <v>28901500</v>
+        <v>79654400</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46170</v>
+        <v>46174</v>
       </c>
       <c r="B184" t="n">
-        <v>412.2040283766931</v>
+        <v>463.9665838370572</v>
       </c>
       <c r="C184" t="n">
-        <v>428.6829856468207</v>
+        <v>465.4438139523178</v>
       </c>
       <c r="D184" t="n">
-        <v>411.8946132983843</v>
+        <v>457.4089212477423</v>
       </c>
       <c r="E184" t="n">
-        <v>426.1876831054688</v>
+        <v>459.6546936035156</v>
       </c>
       <c r="F184" t="n">
-        <v>47250500</v>
+        <v>53628900</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46171</v>
+        <v>46175</v>
       </c>
       <c r="B185" t="n">
-        <v>431.7372486144539</v>
+        <v>446.0403151791343</v>
       </c>
       <c r="C185" t="n">
-        <v>449.4838396905727</v>
+        <v>452.647871293284</v>
       </c>
       <c r="D185" t="n">
-        <v>431.5476031778621</v>
+        <v>439.6024225764256</v>
       </c>
       <c r="E185" t="n">
-        <v>449.3940124511719</v>
+        <v>440.4807739257812</v>
       </c>
       <c r="F185" t="n">
-        <v>79654400</v>
+        <v>37036800</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46174</v>
+        <v>46176</v>
       </c>
       <c r="B186" t="n">
-        <v>463.9665838370572</v>
+        <v>437.6261891093521</v>
       </c>
       <c r="C186" t="n">
-        <v>465.4438139523178</v>
+        <v>439.5625463944663</v>
       </c>
       <c r="D186" t="n">
-        <v>457.4089212477423</v>
+        <v>423.4528579325815</v>
       </c>
       <c r="E186" t="n">
-        <v>459.6546936035156</v>
+        <v>426.5370483398438</v>
       </c>
       <c r="F186" t="n">
-        <v>53628900</v>
+        <v>39037000</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46175</v>
+        <v>46177</v>
       </c>
       <c r="B187" t="n">
-        <v>446.0403151791343</v>
+        <v>434.9911260035114</v>
       </c>
       <c r="C187" t="n">
-        <v>452.647871293284</v>
+        <v>435.3304835003211</v>
       </c>
       <c r="D187" t="n">
-        <v>439.6024225764256</v>
+        <v>425.6087943627414</v>
       </c>
       <c r="E187" t="n">
-        <v>440.4807739257812</v>
+        <v>427.2456970214844</v>
       </c>
       <c r="F187" t="n">
-        <v>37036800</v>
+        <v>26899500</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46176</v>
+        <v>46178</v>
       </c>
       <c r="B188" t="n">
-        <v>437.6261891093521</v>
+        <v>427.5351398188391</v>
       </c>
       <c r="C188" t="n">
-        <v>439.5625463944663</v>
+        <v>428.6630214075295</v>
       </c>
       <c r="D188" t="n">
-        <v>423.4528579325815</v>
+        <v>413.6213308264138</v>
       </c>
       <c r="E188" t="n">
-        <v>426.5370483398438</v>
+        <v>415.8870849609375</v>
       </c>
       <c r="F188" t="n">
-        <v>39037000</v>
+        <v>34782200</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46177</v>
+        <v>46181</v>
       </c>
       <c r="B189" t="n">
-        <v>434.9911260035114</v>
+        <v>413.3618539280056</v>
       </c>
       <c r="C189" t="n">
-        <v>435.3304835003211</v>
+        <v>416.3761684433352</v>
       </c>
       <c r="D189" t="n">
-        <v>425.6087943627414</v>
+        <v>407.7923215775376</v>
       </c>
       <c r="E189" t="n">
-        <v>427.2456970214844</v>
+        <v>410.9663391113281</v>
       </c>
       <c r="F189" t="n">
-        <v>26899500</v>
+        <v>32086700</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46178</v>
+        <v>46182</v>
       </c>
       <c r="B190" t="n">
-        <v>427.5351398188391</v>
+        <v>408.2614433672717</v>
       </c>
       <c r="C190" t="n">
-        <v>428.6630214075295</v>
+        <v>411.2059125875929</v>
       </c>
       <c r="D190" t="n">
-        <v>413.6213308264138</v>
+        <v>397.7312786929967</v>
       </c>
       <c r="E190" t="n">
-        <v>415.8870849609375</v>
+        <v>402.6520080566406</v>
       </c>
       <c r="F190" t="n">
-        <v>34782200</v>
+        <v>35317300</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46181</v>
+        <v>46183</v>
       </c>
       <c r="B191" t="n">
-        <v>413.3618539280056</v>
+        <v>397.8011087010324</v>
       </c>
       <c r="C191" t="n">
-        <v>416.3761684433352</v>
+        <v>404.2789346443135</v>
       </c>
       <c r="D191" t="n">
-        <v>407.7923215775376</v>
+        <v>396.4137363631365</v>
       </c>
       <c r="E191" t="n">
-        <v>410.9663391113281</v>
+        <v>396.6133422851562</v>
       </c>
       <c r="F191" t="n">
-        <v>32086700</v>
+        <v>32576000</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46182</v>
+        <v>46184</v>
       </c>
       <c r="B192" t="n">
-        <v>408.2614433672717</v>
+        <v>394.4674120274286</v>
       </c>
       <c r="C192" t="n">
-        <v>411.2059125875929</v>
+        <v>396.1043451719433</v>
       </c>
       <c r="D192" t="n">
-        <v>397.7312786929967</v>
+        <v>383.278483574852</v>
       </c>
       <c r="E192" t="n">
-        <v>402.6520080566406</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F192" t="n">
-        <v>35317300</v>
+        <v>47224100</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46183</v>
+        <v>46185</v>
       </c>
       <c r="B193" t="n">
-        <v>397.8011087010324</v>
+        <v>390.6945042817559</v>
       </c>
       <c r="C193" t="n">
-        <v>404.2789346443135</v>
+        <v>391.003919361718</v>
       </c>
       <c r="D193" t="n">
-        <v>396.4137363631365</v>
+        <v>381.55171206616</v>
       </c>
       <c r="E193" t="n">
-        <v>396.6133422851562</v>
+        <v>390.0057983398438</v>
       </c>
       <c r="F193" t="n">
-        <v>32576000</v>
+        <v>34865800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46184</v>
+        <v>46188</v>
       </c>
       <c r="B194" t="n">
-        <v>394.4674120274286</v>
+        <v>396.0544203764563</v>
       </c>
       <c r="C194" t="n">
-        <v>396.1043451719433</v>
+        <v>400.9951317570601</v>
       </c>
       <c r="D194" t="n">
-        <v>383.278483574852</v>
+        <v>392.1118605058895</v>
       </c>
       <c r="E194" t="n">
-        <v>389.6065673828125</v>
+        <v>399.0088806152344</v>
       </c>
       <c r="F194" t="n">
-        <v>47224100</v>
+        <v>32266400</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46185</v>
+        <v>46189</v>
       </c>
       <c r="B195" t="n">
-        <v>390.6945042817559</v>
+        <v>395.0463355104342</v>
       </c>
       <c r="C195" t="n">
-        <v>391.003919361718</v>
+        <v>396.094350419825</v>
       </c>
       <c r="D195" t="n">
-        <v>381.55171206616</v>
+        <v>389.9559121071713</v>
       </c>
       <c r="E195" t="n">
-        <v>390.0057983398438</v>
+        <v>393.0899963378906</v>
       </c>
       <c r="F195" t="n">
-        <v>34865800</v>
+        <v>31506800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46188</v>
+        <v>46190</v>
       </c>
       <c r="B196" t="n">
-        <v>396.0544203764563</v>
+        <v>389.5167169534323</v>
       </c>
       <c r="C196" t="n">
-        <v>400.9951317570601</v>
+        <v>389.6364865987809</v>
       </c>
       <c r="D196" t="n">
-        <v>392.1118605058895</v>
+        <v>376.6110198431126</v>
       </c>
       <c r="E196" t="n">
-        <v>399.0088806152344</v>
+        <v>378.1980285644531</v>
       </c>
       <c r="F196" t="n">
-        <v>32266400</v>
+        <v>41987800</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46189</v>
+        <v>46191</v>
       </c>
       <c r="B197" t="n">
-        <v>395.0463355104342</v>
+        <v>377.1100854858111</v>
       </c>
       <c r="C197" t="n">
-        <v>396.094350419825</v>
+        <v>380.6534028700893</v>
       </c>
       <c r="D197" t="n">
-        <v>389.9559121071713</v>
+        <v>372.5786075934489</v>
       </c>
       <c r="E197" t="n">
-        <v>393.0899963378906</v>
+        <v>378.6871032714844</v>
       </c>
       <c r="F197" t="n">
-        <v>31506800</v>
+        <v>59714200</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46190</v>
+        <v>46195</v>
       </c>
       <c r="B198" t="n">
-        <v>389.5167169534323</v>
+        <v>375.0339909424311</v>
       </c>
       <c r="C198" t="n">
-        <v>389.6364865987809</v>
+        <v>380.9129385065033</v>
       </c>
       <c r="D198" t="n">
-        <v>376.6110198431126</v>
+        <v>366.3802985575179</v>
       </c>
       <c r="E198" t="n">
-        <v>378.1980285644531</v>
+        <v>366.6497802734375</v>
       </c>
       <c r="F198" t="n">
-        <v>41987800</v>
+        <v>45171100</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46191</v>
+        <v>46196</v>
       </c>
       <c r="B199" t="n">
-        <v>377.1100854858111</v>
+        <v>371.6802994138851</v>
       </c>
       <c r="C199" t="n">
-        <v>380.6534028700893</v>
+        <v>376.5112013539488</v>
       </c>
       <c r="D199" t="n">
-        <v>372.5786075934489</v>
+        <v>369.9735210485466</v>
       </c>
       <c r="E199" t="n">
-        <v>378.6871032714844</v>
+        <v>373.2373657226562</v>
       </c>
       <c r="F199" t="n">
-        <v>59714200</v>
+        <v>40647600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46195</v>
+        <v>46197</v>
       </c>
       <c r="B200" t="n">
-        <v>375.0339909424311</v>
+        <v>370.8718509685315</v>
       </c>
       <c r="C200" t="n">
-        <v>380.9129385065033</v>
+        <v>378.1681135077346</v>
       </c>
       <c r="D200" t="n">
-        <v>366.3802985575179</v>
+        <v>364.0946004167936</v>
       </c>
       <c r="E200" t="n">
-        <v>366.6497802734375</v>
+        <v>364.7733154296875</v>
       </c>
       <c r="F200" t="n">
-        <v>45171100</v>
+        <v>44509900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46196</v>
+        <v>46198</v>
       </c>
       <c r="B201" t="n">
-        <v>371.6802994138851</v>
+        <v>362.0883479855026</v>
       </c>
       <c r="C201" t="n">
-        <v>376.5112013539488</v>
+        <v>363.5456265920902</v>
       </c>
       <c r="D201" t="n">
-        <v>369.9735210485466</v>
+        <v>348.5438690238404</v>
       </c>
       <c r="E201" t="n">
-        <v>373.2373657226562</v>
+        <v>352.1670227050781</v>
       </c>
       <c r="F201" t="n">
-        <v>40647600</v>
+        <v>66179000</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46197</v>
+        <v>46199</v>
       </c>
       <c r="B202" t="n">
-        <v>370.8718509685315</v>
+        <v>356.4789138154501</v>
       </c>
       <c r="C202" t="n">
-        <v>378.1681135077346</v>
+        <v>375.9023402058053</v>
       </c>
       <c r="D202" t="n">
-        <v>364.0946004167936</v>
+        <v>354.762144454129</v>
       </c>
       <c r="E202" t="n">
-        <v>364.7733154296875</v>
+        <v>372.2691955566406</v>
       </c>
       <c r="F202" t="n">
-        <v>44509900</v>
+        <v>186201600</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46198</v>
+        <v>46202</v>
       </c>
       <c r="B203" t="n">
-        <v>362.0883479855026</v>
+        <v>376.790685328561</v>
       </c>
       <c r="C203" t="n">
-        <v>363.5456265920902</v>
+        <v>379.7850483907747</v>
       </c>
       <c r="D203" t="n">
-        <v>348.5438690238404</v>
+        <v>359.2237492715265</v>
       </c>
       <c r="E203" t="n">
-        <v>352.1670227050781</v>
+        <v>367.8774719238281</v>
       </c>
       <c r="F203" t="n">
-        <v>66179000</v>
+        <v>51229900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46199</v>
+        <v>46203</v>
       </c>
       <c r="B204" t="n">
-        <v>356.4789138154501</v>
+        <v>370.3328407149792</v>
       </c>
       <c r="C204" t="n">
-        <v>375.9023402058053</v>
+        <v>373.4469734227558</v>
       </c>
       <c r="D204" t="n">
-        <v>354.762144454129</v>
+        <v>366.7595808670141</v>
       </c>
       <c r="E204" t="n">
-        <v>372.2691955566406</v>
+        <v>372.319091796875</v>
       </c>
       <c r="F204" t="n">
-        <v>186201600</v>
+        <v>44945700</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46202</v>
+        <v>46204</v>
       </c>
       <c r="B205" t="n">
-        <v>376.790685328561</v>
+        <v>380.1144231011508</v>
       </c>
       <c r="C205" t="n">
-        <v>379.7850483907747</v>
+        <v>388.099391438806</v>
       </c>
       <c r="D205" t="n">
-        <v>359.2237492715265</v>
+        <v>374.1856121338598</v>
       </c>
       <c r="E205" t="n">
-        <v>367.8774719238281</v>
+        <v>383.5579528808594</v>
       </c>
       <c r="F205" t="n">
-        <v>51229900</v>
+        <v>48065800</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46203</v>
+        <v>46205</v>
       </c>
       <c r="B206" t="n">
-        <v>370.3328407149792</v>
+        <v>383.7575696594082</v>
       </c>
       <c r="C206" t="n">
-        <v>373.4469734227558</v>
+        <v>391.4630649298244</v>
       </c>
       <c r="D206" t="n">
-        <v>366.7595808670141</v>
+        <v>382.9790365046874</v>
       </c>
       <c r="E206" t="n">
-        <v>372.319091796875</v>
+        <v>389.7562561035156</v>
       </c>
       <c r="F206" t="n">
-        <v>44945700</v>
+        <v>42128900</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46204</v>
+        <v>46209</v>
       </c>
       <c r="B207" t="n">
-        <v>380.1144231011508</v>
+        <v>386.3127602401041</v>
       </c>
       <c r="C207" t="n">
-        <v>388.099391438806</v>
+        <v>388.418780928489</v>
       </c>
       <c r="D207" t="n">
-        <v>374.1856121338598</v>
+        <v>380.5036887115837</v>
       </c>
       <c r="E207" t="n">
-        <v>383.5579528808594</v>
+        <v>386.0133056640625</v>
       </c>
       <c r="F207" t="n">
-        <v>48065800</v>
+        <v>34224500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46205</v>
+        <v>46210</v>
       </c>
       <c r="B208" t="n">
-        <v>383.7575696594082</v>
+        <v>391.7525106425778</v>
       </c>
       <c r="C208" t="n">
-        <v>391.4630649298244</v>
+        <v>394.8267404517197</v>
       </c>
       <c r="D208" t="n">
-        <v>382.9790365046874</v>
+        <v>387.4905448392632</v>
       </c>
       <c r="E208" t="n">
-        <v>389.7562561035156</v>
+        <v>388.109375</v>
       </c>
       <c r="F208" t="n">
-        <v>42128900</v>
+        <v>29297500</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46209</v>
+        <v>46211</v>
       </c>
       <c r="B209" t="n">
-        <v>386.3127602401041</v>
+        <v>383.3084264217563</v>
       </c>
       <c r="C209" t="n">
-        <v>388.418780928489</v>
+        <v>384.5860201500421</v>
       </c>
       <c r="D209" t="n">
-        <v>380.5036887115837</v>
+        <v>380.6134873969759</v>
       </c>
       <c r="E209" t="n">
-        <v>386.0133056640625</v>
+        <v>382.6197204589844</v>
       </c>
       <c r="F209" t="n">
-        <v>34224500</v>
+        <v>25908300</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46210</v>
+        <v>46212</v>
       </c>
       <c r="B210" t="n">
-        <v>391.7525106425778</v>
+        <v>373.7464342011831</v>
       </c>
       <c r="C210" t="n">
-        <v>394.8267404517197</v>
+        <v>383.927250494608</v>
       </c>
       <c r="D210" t="n">
-        <v>387.4905448392632</v>
+        <v>372.6484949692805</v>
       </c>
       <c r="E210" t="n">
-        <v>388.109375</v>
+        <v>383.6377868652344</v>
       </c>
       <c r="F210" t="n">
-        <v>29297500</v>
+        <v>31083200</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46211</v>
+        <v>46213</v>
       </c>
       <c r="B211" t="n">
-        <v>383.3084264217563</v>
+        <v>387.071312236775</v>
       </c>
       <c r="C211" t="n">
-        <v>384.5860201500421</v>
+        <v>391.1736053926777</v>
       </c>
       <c r="D211" t="n">
-        <v>380.6134873969759</v>
+        <v>380.783162110783</v>
       </c>
       <c r="E211" t="n">
-        <v>382.6197204589844</v>
+        <v>384.3764038085938</v>
       </c>
       <c r="F211" t="n">
-        <v>25908300</v>
+        <v>24644600</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46212</v>
+        <v>46216</v>
       </c>
       <c r="B212" t="n">
-        <v>373.7464342011831</v>
+        <v>387.0214381132942</v>
       </c>
       <c r="C212" t="n">
-        <v>383.927250494608</v>
+        <v>392.9103462310944</v>
       </c>
       <c r="D212" t="n">
-        <v>372.6484949692805</v>
+        <v>383.4281962321871</v>
       </c>
       <c r="E212" t="n">
-        <v>383.6377868652344</v>
+        <v>390.2553405761719</v>
       </c>
       <c r="F212" t="n">
-        <v>31083200</v>
+        <v>28914900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46213</v>
+        <v>46217</v>
       </c>
       <c r="B213" t="n">
-        <v>387.071312236775</v>
+        <v>382.1007052927433</v>
       </c>
       <c r="C213" t="n">
-        <v>391.1736053926777</v>
+        <v>387.460610424238</v>
       </c>
       <c r="D213" t="n">
-        <v>380.783162110783</v>
+        <v>377.93852713765</v>
       </c>
       <c r="E213" t="n">
-        <v>384.3764038085938</v>
+        <v>384.2067260742188</v>
       </c>
       <c r="F213" t="n">
-        <v>24644600</v>
+        <v>27863900</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B214" t="n">
-        <v>387.0214381132942</v>
+        <v>387.0713224899768</v>
       </c>
       <c r="C214" t="n">
-        <v>392.9103462310944</v>
+        <v>398.2103568181361</v>
       </c>
       <c r="D214" t="n">
-        <v>383.4281962321871</v>
+        <v>385.6739591427675</v>
       </c>
       <c r="E214" t="n">
-        <v>390.2553405761719</v>
+        <v>394.8866271972656</v>
       </c>
       <c r="F214" t="n">
-        <v>28914900</v>
+        <v>36253700</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46217</v>
+        <v>46219</v>
       </c>
       <c r="B215" t="n">
-        <v>382.1007052927433</v>
+        <v>397.5615778418718</v>
       </c>
       <c r="C215" t="n">
-        <v>387.460610424238</v>
+        <v>405.2271399033625</v>
       </c>
       <c r="D215" t="n">
-        <v>377.93852713765</v>
+        <v>391.3133305596497</v>
       </c>
       <c r="E215" t="n">
-        <v>384.2067260742188</v>
+        <v>400.3463439941406</v>
       </c>
       <c r="F215" t="n">
-        <v>27863900</v>
+        <v>37047400</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46218</v>
+        <v>46220</v>
       </c>
       <c r="B216" t="n">
-        <v>387.0713224899768</v>
+        <v>394.1180409920291</v>
       </c>
       <c r="C216" t="n">
-        <v>398.2103568181361</v>
+        <v>397.6414373419786</v>
       </c>
       <c r="D216" t="n">
-        <v>385.6739591427675</v>
+        <v>388.6583483977542</v>
       </c>
       <c r="E216" t="n">
-        <v>394.8866271972656</v>
+        <v>393.0800170898438</v>
       </c>
       <c r="F216" t="n">
-        <v>36253700</v>
+        <v>33049800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46219</v>
+        <v>46223</v>
       </c>
       <c r="B217" t="n">
-        <v>397.5615778418718</v>
+        <v>390.6745569462133</v>
       </c>
       <c r="C217" t="n">
-        <v>405.2271399033625</v>
+        <v>402.4224305318551</v>
       </c>
       <c r="D217" t="n">
-        <v>391.3133305596497</v>
+        <v>388.9178541819168</v>
       </c>
       <c r="E217" t="n">
-        <v>400.3463439941406</v>
+        <v>401.5341186523438</v>
       </c>
       <c r="F217" t="n">
-        <v>37047400</v>
+        <v>27915800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B218" t="n">
-        <v>394.1180409920291</v>
+        <v>398.0606303262699</v>
       </c>
       <c r="C218" t="n">
-        <v>397.6414373419786</v>
+        <v>400.7156358198418</v>
       </c>
       <c r="D218" t="n">
-        <v>388.6583483977542</v>
+        <v>395.5753188038175</v>
       </c>
       <c r="E218" t="n">
-        <v>393.0800170898438</v>
+        <v>397.0026245117188</v>
       </c>
       <c r="F218" t="n">
-        <v>33049800</v>
+        <v>24126600</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46223</v>
+        <v>46225</v>
       </c>
       <c r="B219" t="n">
-        <v>390.6745569462133</v>
+        <v>398.8291961465565</v>
       </c>
       <c r="C219" t="n">
-        <v>402.4224305318551</v>
+        <v>400.246541441447</v>
       </c>
       <c r="D219" t="n">
-        <v>388.9178541819168</v>
+        <v>386.2329133568751</v>
       </c>
       <c r="E219" t="n">
-        <v>401.5341186523438</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F219" t="n">
-        <v>27915800</v>
+        <v>28142500</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46224</v>
+        <v>46226</v>
       </c>
       <c r="B220" t="n">
-        <v>398.0606303262699</v>
+        <v>389.237256596515</v>
       </c>
       <c r="C220" t="n">
-        <v>400.7156358198418</v>
+        <v>391.0438532115061</v>
       </c>
       <c r="D220" t="n">
-        <v>395.5753188038175</v>
+        <v>376.6809075284274</v>
       </c>
       <c r="E220" t="n">
-        <v>397.0026245117188</v>
+        <v>380.8630065917969</v>
       </c>
       <c r="F220" t="n">
-        <v>24126600</v>
+        <v>30351800</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B221" t="n">
-        <v>398.8291961465565</v>
+        <v>386.3227418757343</v>
       </c>
       <c r="C221" t="n">
-        <v>400.246541441447</v>
+        <v>388.299032528898</v>
       </c>
       <c r="D221" t="n">
-        <v>386.2329133568751</v>
+        <v>379.9347732203772</v>
       </c>
       <c r="E221" t="n">
-        <v>389.6065673828125</v>
+        <v>380.9828186035156</v>
       </c>
       <c r="F221" t="n">
-        <v>28142500</v>
+        <v>27659400</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B222" t="n">
-        <v>389.237256596515</v>
+        <v>389.3470355932277</v>
       </c>
       <c r="C222" t="n">
-        <v>391.0438532115061</v>
+        <v>393.4593197982184</v>
       </c>
       <c r="D222" t="n">
-        <v>376.6809075284274</v>
+        <v>387.2609663085435</v>
       </c>
       <c r="E222" t="n">
-        <v>380.8630065917969</v>
+        <v>388.368896484375</v>
       </c>
       <c r="F222" t="n">
-        <v>30351800</v>
+        <v>27856200</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46227</v>
+        <v>46231</v>
       </c>
       <c r="B223" t="n">
-        <v>386.3227418757343</v>
+        <v>392.4212554523594</v>
       </c>
       <c r="C223" t="n">
-        <v>388.299032528898</v>
+        <v>399.567805457337</v>
       </c>
       <c r="D223" t="n">
-        <v>379.9347732203772</v>
+        <v>390.5647345556998</v>
       </c>
       <c r="E223" t="n">
-        <v>380.9828186035156</v>
+        <v>392.6109008789062</v>
       </c>
       <c r="F223" t="n">
-        <v>27659400</v>
+        <v>32367500</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46230</v>
+        <v>46232</v>
       </c>
       <c r="B224" t="n">
-        <v>389.3470355932277</v>
+        <v>392.6607942930367</v>
       </c>
       <c r="C224" t="n">
-        <v>393.4593197982184</v>
+        <v>400.4960502148319</v>
       </c>
       <c r="D224" t="n">
-        <v>387.2609663085435</v>
+        <v>388.0095467898306</v>
       </c>
       <c r="E224" t="n">
-        <v>388.368896484375</v>
+        <v>389.8061828613281</v>
       </c>
       <c r="F224" t="n">
-        <v>27856200</v>
+        <v>47209000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B225" t="n">
-        <v>392.4212554523594</v>
+        <v>437.0772008696947</v>
       </c>
       <c r="C225" t="n">
-        <v>399.567805457337</v>
+        <v>457.8281459885008</v>
       </c>
       <c r="D225" t="n">
-        <v>390.5647345556998</v>
+        <v>431.6274684759506</v>
       </c>
       <c r="E225" t="n">
-        <v>392.6109008789062</v>
+        <v>450.2524108886719</v>
       </c>
       <c r="F225" t="n">
-        <v>32367500</v>
+        <v>110160700</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B226" t="n">
-        <v>392.6607942930367</v>
+        <v>449.1544591210436</v>
       </c>
       <c r="C226" t="n">
-        <v>400.4960502148319</v>
+        <v>465.962813447145</v>
       </c>
       <c r="D226" t="n">
-        <v>388.0095467898306</v>
+        <v>448.4857046349594</v>
       </c>
       <c r="E226" t="n">
-        <v>389.8061828613281</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="F226" t="n">
-        <v>47209000</v>
+        <v>60846000</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B227" t="n">
-        <v>437.0772008696947</v>
+        <v>475.2353605631651</v>
       </c>
       <c r="C227" t="n">
-        <v>457.8281459885008</v>
+        <v>490.7261876465455</v>
       </c>
       <c r="D227" t="n">
-        <v>431.6274684759506</v>
+        <v>474.1074789501303</v>
       </c>
       <c r="E227" t="n">
-        <v>450.2524108886719</v>
+        <v>486.7337036132812</v>
       </c>
       <c r="F227" t="n">
-        <v>110160700</v>
+        <v>66762100</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46234</v>
+        <v>46238</v>
       </c>
       <c r="B228" t="n">
-        <v>449.1544591210436</v>
+        <v>479.9964078184842</v>
       </c>
       <c r="C228" t="n">
-        <v>465.962813447145</v>
+        <v>498.5015806515744</v>
       </c>
       <c r="D228" t="n">
-        <v>448.4857046349594</v>
+        <v>478.2696778930625</v>
       </c>
       <c r="E228" t="n">
-        <v>463.8468017578125</v>
+        <v>491.884033203125</v>
       </c>
       <c r="F228" t="n">
-        <v>60846000</v>
+        <v>50455500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B229" t="n">
-        <v>475.2353605631651</v>
+        <v>495.4273384327132</v>
       </c>
       <c r="C229" t="n">
-        <v>490.7261876465455</v>
+        <v>497.3038108374591</v>
       </c>
       <c r="D229" t="n">
-        <v>474.1074789501303</v>
+        <v>484.7674131728324</v>
       </c>
       <c r="E229" t="n">
-        <v>486.7337036132812</v>
+        <v>486.5440673828125</v>
       </c>
       <c r="F229" t="n">
-        <v>66762100</v>
+        <v>33388900</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B230" t="n">
-        <v>479.9964078184842</v>
+        <v>487.6319998350186</v>
       </c>
       <c r="C230" t="n">
-        <v>498.5015806515744</v>
+        <v>500.6175637248969</v>
       </c>
       <c r="D230" t="n">
-        <v>478.2696778930625</v>
+        <v>487.6020574235835</v>
       </c>
       <c r="E230" t="n">
-        <v>491.884033203125</v>
+        <v>498.9207458496094</v>
       </c>
       <c r="F230" t="n">
-        <v>50455500</v>
+        <v>36441500</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B231" t="n">
-        <v>495.4273384327132</v>
+        <v>498.2719734340298</v>
       </c>
       <c r="C231" t="n">
-        <v>497.3038108374591</v>
+        <v>504.2307569931746</v>
       </c>
       <c r="D231" t="n">
-        <v>484.7674131728324</v>
+        <v>497.7928948509335</v>
       </c>
       <c r="E231" t="n">
-        <v>486.5440673828125</v>
+        <v>499.0505065917969</v>
       </c>
       <c r="F231" t="n">
-        <v>33388900</v>
+        <v>28846200</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="B232" t="n">
-        <v>487.6319998350186</v>
+        <v>502.4940586092805</v>
       </c>
       <c r="C232" t="n">
-        <v>500.6175637248969</v>
+        <v>512.7647021753171</v>
       </c>
       <c r="D232" t="n">
-        <v>487.6020574235835</v>
+        <v>501.326243590453</v>
       </c>
       <c r="E232" t="n">
-        <v>498.9207458496094</v>
+        <v>505.109130859375</v>
       </c>
       <c r="F232" t="n">
-        <v>36441500</v>
+        <v>31206100</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46241</v>
+        <v>46245</v>
       </c>
       <c r="B233" t="n">
-        <v>498.2719734340298</v>
+        <v>503.3823542433026</v>
       </c>
       <c r="C233" t="n">
-        <v>504.2307569931746</v>
+        <v>504.3804752506704</v>
       </c>
       <c r="D233" t="n">
-        <v>497.7928948509335</v>
+        <v>498.6113370464939</v>
       </c>
       <c r="E233" t="n">
-        <v>499.0505065917969</v>
+        <v>502.8633422851562</v>
       </c>
       <c r="F233" t="n">
-        <v>28846200</v>
+        <v>23049800</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46244</v>
+        <v>46246</v>
       </c>
       <c r="B234" t="n">
-        <v>502.4940586092805</v>
+        <v>499.0505227551261</v>
       </c>
       <c r="C234" t="n">
-        <v>512.7647021753171</v>
+        <v>500.557695253814</v>
       </c>
       <c r="D234" t="n">
-        <v>501.326243590453</v>
+        <v>490.5964364344239</v>
       </c>
       <c r="E234" t="n">
-        <v>505.109130859375</v>
+        <v>491.5047302246094</v>
       </c>
       <c r="F234" t="n">
-        <v>31206100</v>
+        <v>29001500</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B235" t="n">
-        <v>503.3823542433026</v>
+        <v>492.3431478695614</v>
       </c>
       <c r="C235" t="n">
-        <v>504.3804752506704</v>
+        <v>500.3979918654044</v>
       </c>
       <c r="D235" t="n">
-        <v>498.6113370464939</v>
+        <v>492.0836571155829</v>
       </c>
       <c r="E235" t="n">
-        <v>502.8633422851562</v>
+        <v>495.9463806152344</v>
       </c>
       <c r="F235" t="n">
-        <v>23049800</v>
+        <v>23039000</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46246</v>
+        <v>46248</v>
       </c>
       <c r="B236" t="n">
-        <v>499.0505227551261</v>
+        <v>495.427334377905</v>
       </c>
       <c r="C236" t="n">
-        <v>500.557695253814</v>
+        <v>499.0705004655026</v>
       </c>
       <c r="D236" t="n">
-        <v>490.5964364344239</v>
+        <v>492.991947114923</v>
       </c>
       <c r="E236" t="n">
-        <v>491.5047302246094</v>
+        <v>494.4691467285156</v>
       </c>
       <c r="F236" t="n">
-        <v>29001500</v>
+        <v>16217600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B237" t="n">
-        <v>492.3431478695614</v>
+        <v>489.2190622628328</v>
       </c>
       <c r="C237" t="n">
-        <v>500.3979918654044</v>
+        <v>491.7343163235842</v>
       </c>
       <c r="D237" t="n">
-        <v>492.0836571155829</v>
+        <v>477.5110914717105</v>
       </c>
       <c r="E237" t="n">
-        <v>495.9463806152344</v>
+        <v>479.4474487304688</v>
       </c>
       <c r="F237" t="n">
-        <v>23039000</v>
+        <v>29635800</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46248</v>
+        <v>46252</v>
       </c>
       <c r="B238" t="n">
-        <v>495.427334377905</v>
+        <v>480.6352093836093</v>
       </c>
       <c r="C238" t="n">
-        <v>499.0705004655026</v>
+        <v>483.3600603013466</v>
       </c>
       <c r="D238" t="n">
-        <v>492.991947114923</v>
+        <v>476.2534434403709</v>
       </c>
       <c r="E238" t="n">
-        <v>494.4691467285156</v>
+        <v>480.7250366210938</v>
       </c>
       <c r="F238" t="n">
-        <v>16217600</v>
+        <v>24087600</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B239" t="n">
-        <v>489.2190622628328</v>
+        <v>479.1679704739861</v>
       </c>
       <c r="C239" t="n">
-        <v>491.7343163235842</v>
+        <v>488.3806080919379</v>
       </c>
       <c r="D239" t="n">
-        <v>477.5110914717105</v>
+        <v>478.4592826108848</v>
       </c>
       <c r="E239" t="n">
-        <v>479.4474487304688</v>
+        <v>483.3999938964844</v>
       </c>
       <c r="F239" t="n">
-        <v>29635800</v>
+        <v>19961900</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46252</v>
+        <v>46254</v>
       </c>
       <c r="B240" t="n">
-        <v>480.6352093836093</v>
+        <v>483.2999877929688</v>
       </c>
       <c r="C240" t="n">
-        <v>483.3600603013466</v>
+        <v>484.1600036621094</v>
       </c>
       <c r="D240" t="n">
-        <v>476.2534434403709</v>
+        <v>479.5</v>
       </c>
       <c r="E240" t="n">
-        <v>480.7250366210938</v>
+        <v>481.1499938964844</v>
       </c>
       <c r="F240" t="n">
-        <v>24087600</v>
+        <v>20020800</v>
       </c>
       <c r="G240" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46253</v>
+        <v>46255</v>
       </c>
       <c r="B241" t="n">
-        <v>479.1679704739861</v>
+        <v>479.8800048828125</v>
       </c>
       <c r="C241" t="n">
-        <v>488.3806080919379</v>
+        <v>486.3599853515625</v>
       </c>
       <c r="D241" t="n">
-        <v>478.4592826108848</v>
+        <v>478.5299987792969</v>
       </c>
       <c r="E241" t="n">
-        <v>483.3999938964844</v>
+        <v>483.239990234375</v>
       </c>
       <c r="F241" t="n">
-        <v>19961900</v>
+        <v>22510800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,25 +6709,25 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="B242" t="n">
-        <v>483.2999877929688</v>
+        <v>483.2099914550781</v>
       </c>
       <c r="C242" t="n">
-        <v>484.1600036621094</v>
+        <v>490.6099853515625</v>
       </c>
       <c r="D242" t="n">
-        <v>479.5</v>
+        <v>481.8599853515625</v>
       </c>
       <c r="E242" t="n">
-        <v>481.1499938964844</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="F242" t="n">
-        <v>20020800</v>
+        <v>17230800</v>
       </c>
       <c r="G242" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46255</v>
+        <v>46259</v>
       </c>
       <c r="B243" t="n">
-        <v>479.8800048828125</v>
+        <v>485.4400024414062</v>
       </c>
       <c r="C243" t="n">
-        <v>486.3599853515625</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="D243" t="n">
-        <v>478.5299987792969</v>
+        <v>484.2999877929688</v>
       </c>
       <c r="E243" t="n">
-        <v>483.239990234375</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="F243" t="n">
-        <v>22510800</v>
+        <v>19519000</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="B244" t="n">
-        <v>483.2099914550781</v>
+        <v>487.8500061035156</v>
       </c>
       <c r="C244" t="n">
-        <v>490.6099853515625</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="D244" t="n">
-        <v>481.8599853515625</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="E244" t="n">
-        <v>487.3099975585938</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="F244" t="n">
-        <v>17230800</v>
+        <v>20758900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B245" t="n">
-        <v>485.4400024414062</v>
+        <v>494.8800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>492.4400024414062</v>
+        <v>506.4800109863281</v>
       </c>
       <c r="D245" t="n">
-        <v>484.2999877929688</v>
+        <v>490.0799865722656</v>
       </c>
       <c r="E245" t="n">
-        <v>491.7099914550781</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="F245" t="n">
-        <v>19519000</v>
+        <v>28688800</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46260</v>
+        <v>46262</v>
       </c>
       <c r="B246" t="n">
-        <v>487.8500061035156</v>
+        <v>505.3299865722656</v>
       </c>
       <c r="C246" t="n">
-        <v>497.3999938964844</v>
+        <v>517.780029296875</v>
       </c>
       <c r="D246" t="n">
-        <v>487.3099975585938</v>
+        <v>504.8699951171875</v>
       </c>
       <c r="E246" t="n">
-        <v>496.3699951171875</v>
+        <v>513.530029296875</v>
       </c>
       <c r="F246" t="n">
-        <v>20758900</v>
+        <v>29207300</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46261</v>
+        <v>46265</v>
       </c>
       <c r="B247" t="n">
-        <v>494.8800048828125</v>
+        <v>510.3800048828125</v>
       </c>
       <c r="C247" t="n">
-        <v>506.4800109863281</v>
+        <v>512.1900024414062</v>
       </c>
       <c r="D247" t="n">
-        <v>490.0799865722656</v>
+        <v>506.3900146484375</v>
       </c>
       <c r="E247" t="n">
-        <v>505.0599975585938</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="F247" t="n">
-        <v>28688800</v>
+        <v>27208900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46262</v>
+        <v>46266</v>
       </c>
       <c r="B248" t="n">
-        <v>505.3299865722656</v>
+        <v>497.5199890136719</v>
       </c>
       <c r="C248" t="n">
-        <v>517.780029296875</v>
+        <v>505.9700012207031</v>
       </c>
       <c r="D248" t="n">
-        <v>504.8699951171875</v>
+        <v>496.7799987792969</v>
       </c>
       <c r="E248" t="n">
-        <v>513.530029296875</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="F248" t="n">
-        <v>29207300</v>
+        <v>21046900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46265</v>
+        <v>46267</v>
       </c>
       <c r="B249" t="n">
-        <v>510.3800048828125</v>
+        <v>499.8500061035156</v>
       </c>
       <c r="C249" t="n">
-        <v>512.1900024414062</v>
+        <v>500.2699890136719</v>
       </c>
       <c r="D249" t="n">
-        <v>506.3900146484375</v>
+        <v>493.8099975585938</v>
       </c>
       <c r="E249" t="n">
-        <v>507.2900085449219</v>
+        <v>496.8200073242188</v>
       </c>
       <c r="F249" t="n">
-        <v>27208900</v>
+        <v>15336100</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46266</v>
+        <v>46268</v>
       </c>
       <c r="B250" t="n">
-        <v>497.5199890136719</v>
+        <v>501.6600036621094</v>
       </c>
       <c r="C250" t="n">
-        <v>505.9700012207031</v>
+        <v>515.6500244140625</v>
       </c>
       <c r="D250" t="n">
-        <v>496.7799987792969</v>
+        <v>500.7999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>501.0199890136719</v>
+        <v>510.1199951171875</v>
       </c>
       <c r="F250" t="n">
-        <v>21046900</v>
+        <v>24125900</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46267</v>
+        <v>46269</v>
       </c>
       <c r="B251" t="n">
-        <v>499.8500061035156</v>
+        <v>510</v>
       </c>
       <c r="C251" t="n">
-        <v>500.2699890136719</v>
+        <v>511</v>
       </c>
       <c r="D251" t="n">
-        <v>493.8099975585938</v>
+        <v>499.3599853515625</v>
       </c>
       <c r="E251" t="n">
-        <v>496.8200073242188</v>
+        <v>499.7000122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>15336100</v>
+        <v>18074400</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,53 +6969,19 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46268</v>
-      </c>
-      <c r="B252" t="n">
-        <v>501.6600036621094</v>
-      </c>
-      <c r="C252" t="n">
-        <v>515.6500244140625</v>
-      </c>
-      <c r="D252" t="n">
-        <v>500.7999877929688</v>
-      </c>
-      <c r="E252" t="n">
-        <v>510.1199951171875</v>
-      </c>
+        <v>46273</v>
+      </c>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
       <c r="F252" t="n">
-        <v>24125900</v>
+        <v>18684730</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="253">
-      <c r="A253" s="1" t="n">
-        <v>46269</v>
-      </c>
-      <c r="B253" t="n">
-        <v>510</v>
-      </c>
-      <c r="C253" t="n">
-        <v>511</v>
-      </c>
-      <c r="D253" t="n">
-        <v>499.3599853515625</v>
-      </c>
-      <c r="E253" t="n">
-        <v>499.7000122070312</v>
-      </c>
-      <c r="F253" t="n">
-        <v>18074400</v>
-      </c>
-      <c r="G253" t="n">
-        <v>0</v>
-      </c>
-      <c r="H253" t="n">
         <v>0</v>
       </c>
     </row>
@@ -10994,34 +10960,34 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>493.95</v>
+      </c>
+      <c r="D2" t="n">
         <v>499.7</v>
       </c>
-      <c r="D2" t="n">
-        <v>510.12</v>
-      </c>
       <c r="E2" t="n">
-        <v>510</v>
+        <v>493.01</v>
       </c>
       <c r="F2" t="n">
-        <v>511</v>
+        <v>495.19</v>
       </c>
       <c r="G2" t="n">
-        <v>499.36</v>
+        <v>490.15</v>
       </c>
       <c r="H2" t="n">
-        <v>18101758</v>
+        <v>18684730</v>
       </c>
       <c r="I2" t="n">
-        <v>36783650</v>
+        <v>36859408</v>
       </c>
       <c r="J2" t="n">
-        <v>3710545297408</v>
+        <v>3667848331264</v>
       </c>
       <c r="K2" t="n">
-        <v>27.853958</v>
+        <v>27.533445</v>
       </c>
       <c r="L2" t="n">
-        <v>21.19773</v>
+        <v>20.95381</v>
       </c>
       <c r="M2" t="n">
         <v>17.94</v>
@@ -11060,7 +11026,7 @@
         <v>59.565</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.389155000000001</v>
+        <v>8.292622</v>
       </c>
       <c r="Z2" t="n">
         <v>0.317</v>
@@ -11072,7 +11038,7 @@
         <v>331839012864</v>
       </c>
       <c r="AC2" t="n">
-        <v>3762515083264</v>
+        <v>3719818117120</v>
       </c>
       <c r="AD2" t="n">
         <v>194237005824</v>
@@ -11099,7 +11065,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-08 08:51:52</t>
+          <t>2026-09-09 09:14:48</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45909</v>
+        <v>45910</v>
       </c>
       <c r="B2" t="n">
-        <v>497.3380566961471</v>
+        <v>498.8754294126598</v>
       </c>
       <c r="C2" t="n">
-        <v>498.1513723235736</v>
+        <v>499.1233892811019</v>
       </c>
       <c r="D2" t="n">
-        <v>493.6385148559323</v>
+        <v>492.6665046209378</v>
       </c>
       <c r="E2" t="n">
-        <v>494.3427124023438</v>
+        <v>496.2867126464844</v>
       </c>
       <c r="F2" t="n">
-        <v>14410500</v>
+        <v>21611800</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B3" t="n">
-        <v>498.8754294126598</v>
+        <v>498.1513800613702</v>
       </c>
       <c r="C3" t="n">
-        <v>499.1233892811019</v>
+        <v>499.0638857033828</v>
       </c>
       <c r="D3" t="n">
-        <v>492.6665046209378</v>
+        <v>493.8170463660224</v>
       </c>
       <c r="E3" t="n">
-        <v>496.2867126464844</v>
+        <v>496.9215087890625</v>
       </c>
       <c r="F3" t="n">
-        <v>21611800</v>
+        <v>18881600</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B4" t="n">
-        <v>498.1513800613702</v>
+        <v>502.5154742767582</v>
       </c>
       <c r="C4" t="n">
-        <v>499.0638857033828</v>
+        <v>508.367321245748</v>
       </c>
       <c r="D4" t="n">
-        <v>493.8170463660224</v>
+        <v>499.738335797131</v>
       </c>
       <c r="E4" t="n">
-        <v>496.9215087890625</v>
+        <v>505.7389526367188</v>
       </c>
       <c r="F4" t="n">
-        <v>18881600</v>
+        <v>23624900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B5" t="n">
-        <v>502.515443953693</v>
+        <v>504.6380259393043</v>
       </c>
       <c r="C5" t="n">
-        <v>508.3672905695674</v>
+        <v>511.2634762434591</v>
       </c>
       <c r="D5" t="n">
-        <v>499.7383056416454</v>
+        <v>502.862624765238</v>
       </c>
       <c r="E5" t="n">
-        <v>505.7389221191406</v>
+        <v>511.1543884277344</v>
       </c>
       <c r="F5" t="n">
-        <v>23624900</v>
+        <v>17143800</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B6" t="n">
-        <v>504.6380259393043</v>
+        <v>512.6620043570016</v>
       </c>
       <c r="C6" t="n">
-        <v>511.2634762434591</v>
+        <v>513.0091239663263</v>
       </c>
       <c r="D6" t="n">
-        <v>502.862624765238</v>
+        <v>504.4495745277025</v>
       </c>
       <c r="E6" t="n">
-        <v>511.1543884277344</v>
+        <v>504.885986328125</v>
       </c>
       <c r="F6" t="n">
-        <v>17143800</v>
+        <v>19711900</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B7" t="n">
-        <v>512.6619733694059</v>
+        <v>506.4530503919847</v>
       </c>
       <c r="C7" t="n">
-        <v>513.0090929577493</v>
+        <v>507.1175961354426</v>
       </c>
       <c r="D7" t="n">
-        <v>504.449544036503</v>
+        <v>501.8013209933916</v>
       </c>
       <c r="E7" t="n">
-        <v>504.8859558105469</v>
+        <v>505.8579406738281</v>
       </c>
       <c r="F7" t="n">
-        <v>19711900</v>
+        <v>15816600</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B8" t="n">
-        <v>506.4530503919847</v>
+        <v>507.3159820894167</v>
       </c>
       <c r="C8" t="n">
-        <v>507.1175961354426</v>
+        <v>508.883105468087</v>
       </c>
       <c r="D8" t="n">
-        <v>501.8013209933916</v>
+        <v>503.517250078243</v>
       </c>
       <c r="E8" t="n">
-        <v>505.8579406738281</v>
+        <v>504.3008117675781</v>
       </c>
       <c r="F8" t="n">
-        <v>15816600</v>
+        <v>18913700</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B9" t="n">
-        <v>507.3159820894167</v>
+        <v>506.3935778296786</v>
       </c>
       <c r="C9" t="n">
-        <v>508.883105468087</v>
+        <v>515.0622454615835</v>
       </c>
       <c r="D9" t="n">
-        <v>503.517250078243</v>
+        <v>506.1456179521661</v>
       </c>
       <c r="E9" t="n">
-        <v>504.3008117675781</v>
+        <v>513.7034301757812</v>
       </c>
       <c r="F9" t="n">
-        <v>18913700</v>
+        <v>52474100</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B10" t="n">
-        <v>506.3935176630351</v>
+        <v>511.3826037577857</v>
       </c>
       <c r="C10" t="n">
-        <v>515.0621842649809</v>
+        <v>513.5150225661836</v>
       </c>
       <c r="D10" t="n">
-        <v>506.1455578149837</v>
+        <v>508.3574445613838</v>
       </c>
       <c r="E10" t="n">
-        <v>513.703369140625</v>
+        <v>510.2518920898438</v>
       </c>
       <c r="F10" t="n">
-        <v>52474100</v>
+        <v>20009300</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B11" t="n">
-        <v>511.3826037577857</v>
+        <v>509.6071158201621</v>
       </c>
       <c r="C11" t="n">
-        <v>513.5150225661836</v>
+        <v>510.3907077578639</v>
       </c>
       <c r="D11" t="n">
-        <v>508.3574445613838</v>
+        <v>503.170087241692</v>
       </c>
       <c r="E11" t="n">
-        <v>510.2518920898438</v>
+        <v>505.0744323730469</v>
       </c>
       <c r="F11" t="n">
-        <v>20009300</v>
+        <v>19799600</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B12" t="n">
-        <v>509.6071158201621</v>
+        <v>506.2150114062044</v>
       </c>
       <c r="C12" t="n">
-        <v>510.3907077578639</v>
+        <v>508.297849987297</v>
       </c>
       <c r="D12" t="n">
-        <v>503.170087241692</v>
+        <v>502.7832554652563</v>
       </c>
       <c r="E12" t="n">
-        <v>505.0744323730469</v>
+        <v>505.9868774414062</v>
       </c>
       <c r="F12" t="n">
-        <v>19799600</v>
+        <v>13533700</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B13" t="n">
-        <v>506.215041937542</v>
+        <v>504.1519897302721</v>
       </c>
       <c r="C13" t="n">
-        <v>508.2978806442567</v>
+        <v>505.8480570147519</v>
       </c>
       <c r="D13" t="n">
-        <v>502.7832857896144</v>
+        <v>500.9186136455738</v>
       </c>
       <c r="E13" t="n">
-        <v>505.9869079589844</v>
+        <v>502.8923645019531</v>
       </c>
       <c r="F13" t="n">
-        <v>13533700</v>
+        <v>15786500</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B14" t="n">
-        <v>504.1519897302721</v>
+        <v>505.8976246789574</v>
       </c>
       <c r="C14" t="n">
-        <v>505.8480570147519</v>
+        <v>509.7459665668783</v>
       </c>
       <c r="D14" t="n">
-        <v>500.9186136455738</v>
+        <v>502.4856945681329</v>
       </c>
       <c r="E14" t="n">
-        <v>502.8923645019531</v>
+        <v>507.2861938476562</v>
       </c>
       <c r="F14" t="n">
-        <v>15786500</v>
+        <v>16213100</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B15" t="n">
-        <v>505.8976246789574</v>
+        <v>507.3258652143003</v>
       </c>
       <c r="C15" t="n">
-        <v>509.7459665668783</v>
+        <v>512.6321819161793</v>
       </c>
       <c r="D15" t="n">
-        <v>502.4856945681329</v>
+        <v>504.7272507672145</v>
       </c>
       <c r="E15" t="n">
-        <v>507.2861938476562</v>
+        <v>510.4005432128906</v>
       </c>
       <c r="F15" t="n">
-        <v>16213100</v>
+        <v>17617800</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B16" t="n">
-        <v>507.3258652143003</v>
+        <v>509.0516808953516</v>
       </c>
       <c r="C16" t="n">
-        <v>512.6321819161793</v>
+        <v>513.9315141469417</v>
       </c>
       <c r="D16" t="n">
-        <v>504.7272507672145</v>
+        <v>505.5009089039439</v>
       </c>
       <c r="E16" t="n">
-        <v>510.4005432128906</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="F16" t="n">
-        <v>17617800</v>
+        <v>19728200</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B17" t="n">
-        <v>509.0516808953516</v>
+        <v>510.5989067561486</v>
       </c>
       <c r="C17" t="n">
-        <v>513.9315141469417</v>
+        <v>516.2623314762835</v>
       </c>
       <c r="D17" t="n">
-        <v>505.5009089039439</v>
+        <v>507.5143007767599</v>
       </c>
       <c r="E17" t="n">
-        <v>513.7232666015625</v>
+        <v>515.4688720703125</v>
       </c>
       <c r="F17" t="n">
-        <v>19728200</v>
+        <v>22632300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B18" t="n">
-        <v>510.5989672146665</v>
+        <v>513.4157691025699</v>
       </c>
       <c r="C18" t="n">
-        <v>516.262392605391</v>
+        <v>517.3434144406598</v>
       </c>
       <c r="D18" t="n">
-        <v>507.5143608700387</v>
+        <v>506.5125449836057</v>
       </c>
       <c r="E18" t="n">
-        <v>515.4689331054688</v>
+        <v>511.53125</v>
       </c>
       <c r="F18" t="n">
-        <v>22632300</v>
+        <v>21222900</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B19" t="n">
-        <v>513.4158303625842</v>
+        <v>512.8801529316524</v>
       </c>
       <c r="C19" t="n">
-        <v>517.343476169315</v>
+        <v>516.2425031799986</v>
       </c>
       <c r="D19" t="n">
-        <v>506.5126054199375</v>
+        <v>510.7973143114264</v>
       </c>
       <c r="E19" t="n">
-        <v>511.5313110351562</v>
+        <v>513.1281127929688</v>
       </c>
       <c r="F19" t="n">
-        <v>21222900</v>
+        <v>15112300</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B20" t="n">
-        <v>512.8801529316524</v>
+        <v>514.377848960065</v>
       </c>
       <c r="C20" t="n">
-        <v>516.2425031799986</v>
+        <v>526.6965386672223</v>
       </c>
       <c r="D20" t="n">
-        <v>510.7973143114264</v>
+        <v>513.9712214168786</v>
       </c>
       <c r="E20" t="n">
-        <v>513.1281127929688</v>
+        <v>524.256591796875</v>
       </c>
       <c r="F20" t="n">
-        <v>15112300</v>
+        <v>21388600</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B21" t="n">
-        <v>514.377848960065</v>
+        <v>523.9788048028778</v>
       </c>
       <c r="C21" t="n">
-        <v>526.6965386672223</v>
+        <v>525.4764919541412</v>
       </c>
       <c r="D21" t="n">
-        <v>513.9712214168786</v>
+        <v>517.1847292577561</v>
       </c>
       <c r="E21" t="n">
-        <v>524.256591796875</v>
+        <v>519.7039794921875</v>
       </c>
       <c r="F21" t="n">
-        <v>21388600</v>
+        <v>14615200</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B22" t="n">
-        <v>523.9788048028778</v>
+        <v>519.0098207695767</v>
       </c>
       <c r="C22" t="n">
-        <v>525.4764919541412</v>
+        <v>522.6498549115006</v>
       </c>
       <c r="D22" t="n">
-        <v>517.1847292577561</v>
+        <v>518.8213688365025</v>
       </c>
       <c r="E22" t="n">
-        <v>519.7039794921875</v>
+        <v>520.5669555664062</v>
       </c>
       <c r="F22" t="n">
-        <v>14615200</v>
+        <v>13363400</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B23" t="n">
-        <v>519.0097599169904</v>
+        <v>518.0773939158137</v>
       </c>
       <c r="C23" t="n">
-        <v>522.6497936321297</v>
+        <v>520.0511445409561</v>
       </c>
       <c r="D23" t="n">
-        <v>518.8213080060119</v>
+        <v>513.1777050939771</v>
       </c>
       <c r="E23" t="n">
-        <v>520.56689453125</v>
+        <v>518.1369018554688</v>
       </c>
       <c r="F23" t="n">
-        <v>13363400</v>
+        <v>18343600</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B24" t="n">
-        <v>518.07745494396</v>
+        <v>515.3995037763443</v>
       </c>
       <c r="C24" t="n">
-        <v>520.0512058016051</v>
+        <v>519.3073539147757</v>
       </c>
       <c r="D24" t="n">
-        <v>513.1777655449532</v>
+        <v>505.4711804745103</v>
       </c>
       <c r="E24" t="n">
-        <v>518.136962890625</v>
+        <v>506.7903137207031</v>
       </c>
       <c r="F24" t="n">
-        <v>18343600</v>
+        <v>24133800</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B25" t="n">
-        <v>515.3994727403434</v>
+        <v>512.1958293204747</v>
       </c>
       <c r="C25" t="n">
-        <v>519.3073226434543</v>
+        <v>512.1958293204747</v>
       </c>
       <c r="D25" t="n">
-        <v>505.4711500363669</v>
+        <v>507.5044476763347</v>
       </c>
       <c r="E25" t="n">
-        <v>506.790283203125</v>
+        <v>509.8551025390625</v>
       </c>
       <c r="F25" t="n">
-        <v>24133800</v>
+        <v>14284200</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B26" t="n">
-        <v>512.1957986627914</v>
+        <v>506.0662273255252</v>
       </c>
       <c r="C26" t="n">
-        <v>512.1957986627914</v>
+        <v>511.0750344503804</v>
       </c>
       <c r="D26" t="n">
-        <v>507.504417299456</v>
+        <v>501.8707357721012</v>
       </c>
       <c r="E26" t="n">
-        <v>509.8550720214844</v>
+        <v>509.3789672851562</v>
       </c>
       <c r="F26" t="n">
-        <v>14284200</v>
+        <v>14684300</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B27" t="n">
-        <v>506.0662879637401</v>
+        <v>510.7577169104775</v>
       </c>
       <c r="C27" t="n">
-        <v>511.0750956887641</v>
+        <v>512.9694997370561</v>
       </c>
       <c r="D27" t="n">
-        <v>501.870795907601</v>
+        <v>505.8381709448021</v>
       </c>
       <c r="E27" t="n">
-        <v>509.3790283203125</v>
+        <v>509.2401733398438</v>
       </c>
       <c r="F27" t="n">
-        <v>14684300</v>
+        <v>14694700</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B28" t="n">
-        <v>510.7576863019565</v>
+        <v>508.3970827878481</v>
       </c>
       <c r="C28" t="n">
-        <v>512.9694689959882</v>
+        <v>512.6321960787722</v>
       </c>
       <c r="D28" t="n">
-        <v>505.838140631098</v>
+        <v>503.9833851231019</v>
       </c>
       <c r="E28" t="n">
-        <v>509.2401428222656</v>
+        <v>507.4349670410156</v>
       </c>
       <c r="F28" t="n">
-        <v>14694700</v>
+        <v>15559600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B29" t="n">
-        <v>508.3970827878481</v>
+        <v>504.8859564875193</v>
       </c>
       <c r="C29" t="n">
-        <v>512.6321960787722</v>
+        <v>511.2733746274193</v>
       </c>
       <c r="D29" t="n">
-        <v>503.9833851231019</v>
+        <v>503.1700633614309</v>
       </c>
       <c r="E29" t="n">
-        <v>507.4349670410156</v>
+        <v>509.388916015625</v>
       </c>
       <c r="F29" t="n">
-        <v>15559600</v>
+        <v>19867800</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B30" t="n">
-        <v>504.8859262397143</v>
+        <v>510.4104901121901</v>
       </c>
       <c r="C30" t="n">
-        <v>511.273343996943</v>
+        <v>514.4671401409408</v>
       </c>
       <c r="D30" t="n">
-        <v>503.1700332164253</v>
+        <v>509.2401268135401</v>
       </c>
       <c r="E30" t="n">
-        <v>509.3888854980469</v>
+        <v>512.5726928710938</v>
       </c>
       <c r="F30" t="n">
-        <v>19867800</v>
+        <v>14665600</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B31" t="n">
-        <v>510.4105508898797</v>
+        <v>513.2769402267872</v>
       </c>
       <c r="C31" t="n">
-        <v>514.4672014016805</v>
+        <v>514.4572316509175</v>
       </c>
       <c r="D31" t="n">
-        <v>509.2401874518674</v>
+        <v>508.8533142722573</v>
       </c>
       <c r="E31" t="n">
-        <v>512.57275390625</v>
+        <v>513.4356079101562</v>
       </c>
       <c r="F31" t="n">
-        <v>14665600</v>
+        <v>15586200</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B32" t="n">
-        <v>513.2769402267872</v>
+        <v>516.8971823641815</v>
       </c>
       <c r="C32" t="n">
-        <v>514.4572316509175</v>
+        <v>520.943843958813</v>
       </c>
       <c r="D32" t="n">
-        <v>508.8533142722573</v>
+        <v>513.4852520447155</v>
       </c>
       <c r="E32" t="n">
-        <v>513.4356079101562</v>
+        <v>516.2921142578125</v>
       </c>
       <c r="F32" t="n">
-        <v>15586200</v>
+        <v>18962700</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B33" t="n">
-        <v>516.8971823641815</v>
+        <v>518.1964698863214</v>
       </c>
       <c r="C33" t="n">
-        <v>520.943843958813</v>
+        <v>519.6743010066873</v>
       </c>
       <c r="D33" t="n">
-        <v>513.4852520447155</v>
+        <v>514.3778516149157</v>
       </c>
       <c r="E33" t="n">
-        <v>516.2921142578125</v>
+        <v>516.3119506835938</v>
       </c>
       <c r="F33" t="n">
-        <v>18962700</v>
+        <v>14023500</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B34" t="n">
-        <v>518.1964086283891</v>
+        <v>518.5237205252405</v>
       </c>
       <c r="C34" t="n">
-        <v>519.6742395740552</v>
+        <v>521.0628270774097</v>
       </c>
       <c r="D34" t="n">
-        <v>514.3777908083965</v>
+        <v>516.4607380708425</v>
       </c>
       <c r="E34" t="n">
-        <v>516.3118896484375</v>
+        <v>519.3370361328125</v>
       </c>
       <c r="F34" t="n">
-        <v>14023500</v>
+        <v>15532400</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B35" t="n">
-        <v>518.5237814648117</v>
+        <v>527.440383046071</v>
       </c>
       <c r="C35" t="n">
-        <v>521.0628883153897</v>
+        <v>530.2175212473691</v>
       </c>
       <c r="D35" t="n">
-        <v>516.4607987679614</v>
+        <v>524.6929685473742</v>
       </c>
       <c r="E35" t="n">
-        <v>519.3370971679688</v>
+        <v>527.1824951171875</v>
       </c>
       <c r="F35" t="n">
-        <v>15532400</v>
+        <v>18734700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B36" t="n">
-        <v>527.440383046071</v>
+        <v>545.5116410650497</v>
       </c>
       <c r="C36" t="n">
-        <v>530.2175212473691</v>
+        <v>549.2012543795508</v>
       </c>
       <c r="D36" t="n">
-        <v>524.6929685473742</v>
+        <v>536.3569832604931</v>
       </c>
       <c r="E36" t="n">
-        <v>527.1824951171875</v>
+        <v>537.6463623046875</v>
       </c>
       <c r="F36" t="n">
-        <v>18734700</v>
+        <v>29986700</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B37" t="n">
-        <v>545.5116410650497</v>
+        <v>540.4929653309738</v>
       </c>
       <c r="C37" t="n">
-        <v>549.2012543795508</v>
+        <v>541.8121286840217</v>
       </c>
       <c r="D37" t="n">
-        <v>536.3569832604931</v>
+        <v>532.3499420595073</v>
       </c>
       <c r="E37" t="n">
-        <v>537.6463623046875</v>
+        <v>537.130615234375</v>
       </c>
       <c r="F37" t="n">
-        <v>29986700</v>
+        <v>36023000</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B38" t="n">
-        <v>540.4929653309738</v>
+        <v>526.1509968235328</v>
       </c>
       <c r="C38" t="n">
-        <v>541.8121286840217</v>
+        <v>530.6043464776645</v>
       </c>
       <c r="D38" t="n">
-        <v>532.3499420595073</v>
+        <v>517.8592331602406</v>
       </c>
       <c r="E38" t="n">
-        <v>537.130615234375</v>
+        <v>521.4695434570312</v>
       </c>
       <c r="F38" t="n">
-        <v>36023000</v>
+        <v>41023100</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B39" t="n">
-        <v>526.150935240438</v>
+        <v>524.5640198650095</v>
       </c>
       <c r="C39" t="n">
-        <v>530.6042843733296</v>
+        <v>525.0004316167937</v>
       </c>
       <c r="D39" t="n">
-        <v>517.8591725476514</v>
+        <v>510.896444053691</v>
       </c>
       <c r="E39" t="n">
-        <v>521.469482421875</v>
+        <v>513.5843505859375</v>
       </c>
       <c r="F39" t="n">
-        <v>41023100</v>
+        <v>34006400</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B40" t="n">
-        <v>524.5640822050067</v>
+        <v>515.5680119038287</v>
       </c>
       <c r="C40" t="n">
-        <v>525.0004940086545</v>
+        <v>520.6760087890081</v>
       </c>
       <c r="D40" t="n">
-        <v>510.8965047694123</v>
+        <v>510.3906395365282</v>
       </c>
       <c r="E40" t="n">
-        <v>513.5844116210938</v>
+        <v>512.8107299804688</v>
       </c>
       <c r="F40" t="n">
-        <v>34006400</v>
+        <v>22374700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B41" t="n">
-        <v>515.5680732671589</v>
+        <v>507.5837474278435</v>
       </c>
       <c r="C41" t="n">
-        <v>520.6760707602963</v>
+        <v>511.3427970078787</v>
       </c>
       <c r="D41" t="n">
-        <v>510.3907002836433</v>
+        <v>503.6957236126803</v>
       </c>
       <c r="E41" t="n">
-        <v>512.810791015625</v>
+        <v>510.1327819824219</v>
       </c>
       <c r="F41" t="n">
-        <v>22374700</v>
+        <v>20958700</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B42" t="n">
-        <v>507.5837474278435</v>
+        <v>509.1111797792271</v>
       </c>
       <c r="C42" t="n">
-        <v>511.3427970078787</v>
+        <v>510.6287232020861</v>
       </c>
       <c r="D42" t="n">
-        <v>503.6957236126803</v>
+        <v>502.4460174356622</v>
       </c>
       <c r="E42" t="n">
-        <v>510.1327819824219</v>
+        <v>503.0213012695312</v>
       </c>
       <c r="F42" t="n">
-        <v>20958700</v>
+        <v>23024300</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B43" t="n">
-        <v>509.1111797792271</v>
+        <v>501.5335392553728</v>
       </c>
       <c r="C43" t="n">
-        <v>510.6287232020861</v>
+        <v>501.5732213085109</v>
       </c>
       <c r="D43" t="n">
-        <v>502.4460174356622</v>
+        <v>491.7639146320967</v>
       </c>
       <c r="E43" t="n">
-        <v>503.0213012695312</v>
+        <v>493.0433959960938</v>
       </c>
       <c r="F43" t="n">
-        <v>23024300</v>
+        <v>27406500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B44" t="n">
-        <v>501.5335392553728</v>
+        <v>492.8946300074654</v>
       </c>
       <c r="C44" t="n">
-        <v>501.5732213085109</v>
+        <v>495.304792622274</v>
       </c>
       <c r="D44" t="n">
-        <v>491.7639146320967</v>
+        <v>489.2248119110569</v>
       </c>
       <c r="E44" t="n">
-        <v>493.0433959960938</v>
+        <v>492.7656860351562</v>
       </c>
       <c r="F44" t="n">
-        <v>27406500</v>
+        <v>24019800</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B45" t="n">
-        <v>492.8946300074654</v>
+        <v>495.9594336108676</v>
       </c>
       <c r="C45" t="n">
-        <v>495.304792622274</v>
+        <v>502.7138582055711</v>
       </c>
       <c r="D45" t="n">
-        <v>489.2248119110569</v>
+        <v>494.729532044403</v>
       </c>
       <c r="E45" t="n">
-        <v>492.7656860351562</v>
+        <v>501.8707885742188</v>
       </c>
       <c r="F45" t="n">
-        <v>24019800</v>
+        <v>26101500</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B46" t="n">
-        <v>495.9594336108676</v>
+        <v>500.6805884003941</v>
       </c>
       <c r="C46" t="n">
-        <v>502.7138582055711</v>
+        <v>505.441436360325</v>
       </c>
       <c r="D46" t="n">
-        <v>494.729532044403</v>
+        <v>498.2505996850444</v>
       </c>
       <c r="E46" t="n">
-        <v>501.8707885742188</v>
+        <v>504.5289306640625</v>
       </c>
       <c r="F46" t="n">
-        <v>26101500</v>
+        <v>17980000</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B47" t="n">
-        <v>500.6805581155917</v>
+        <v>505.203338237195</v>
       </c>
       <c r="C47" t="n">
-        <v>505.4414057875519</v>
+        <v>507.494515261433</v>
       </c>
       <c r="D47" t="n">
-        <v>498.2505695472254</v>
+        <v>495.0469117437556</v>
       </c>
       <c r="E47" t="n">
-        <v>504.5289001464844</v>
+        <v>506.9688415527344</v>
       </c>
       <c r="F47" t="n">
-        <v>17980000</v>
+        <v>26574900</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B48" t="n">
-        <v>505.203338237195</v>
+        <v>506.1455939798088</v>
       </c>
       <c r="C48" t="n">
-        <v>507.494515261433</v>
+        <v>509.3095642884979</v>
       </c>
       <c r="D48" t="n">
-        <v>495.0469117437556</v>
+        <v>497.1992129195551</v>
       </c>
       <c r="E48" t="n">
-        <v>506.9688415527344</v>
+        <v>499.1828918457031</v>
       </c>
       <c r="F48" t="n">
-        <v>26574900</v>
+        <v>25273100</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B49" t="n">
-        <v>506.1455939798088</v>
+        <v>494.1641988801248</v>
       </c>
       <c r="C49" t="n">
-        <v>509.3095642884979</v>
+        <v>507.4250879884235</v>
       </c>
       <c r="D49" t="n">
-        <v>497.1992129195551</v>
+        <v>493.3806372096086</v>
       </c>
       <c r="E49" t="n">
-        <v>499.1828918457031</v>
+        <v>506.0166625976562</v>
       </c>
       <c r="F49" t="n">
-        <v>25273100</v>
+        <v>28505700</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B50" t="n">
-        <v>494.164169077362</v>
+        <v>504.3008205535495</v>
       </c>
       <c r="C50" t="n">
-        <v>507.425057385904</v>
+        <v>507.9408546740634</v>
       </c>
       <c r="D50" t="n">
-        <v>493.3806074541019</v>
+        <v>500.7897001462128</v>
       </c>
       <c r="E50" t="n">
-        <v>506.0166320800781</v>
+        <v>503.3486328125</v>
       </c>
       <c r="F50" t="n">
-        <v>28505700</v>
+        <v>19092800</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B51" t="n">
-        <v>504.3008205535495</v>
+        <v>491.3274994941962</v>
       </c>
       <c r="C51" t="n">
-        <v>507.9408546740634</v>
+        <v>498.8754133867433</v>
       </c>
       <c r="D51" t="n">
-        <v>500.7897001462128</v>
+        <v>482.8076023204449</v>
       </c>
       <c r="E51" t="n">
-        <v>503.3486328125</v>
+        <v>489.7604064941406</v>
       </c>
       <c r="F51" t="n">
-        <v>19092800</v>
+        <v>33815100</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,22 +1769,22 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B52" t="n">
-        <v>491.3274994941962</v>
+        <v>486.1005289347495</v>
       </c>
       <c r="C52" t="n">
-        <v>498.8754133867433</v>
+        <v>491.1489881906385</v>
       </c>
       <c r="D52" t="n">
-        <v>482.8076023204449</v>
+        <v>478.8898366362471</v>
       </c>
       <c r="E52" t="n">
-        <v>489.7604064941406</v>
+        <v>483.1448364257812</v>
       </c>
       <c r="F52" t="n">
-        <v>33815100</v>
+        <v>23245300</v>
       </c>
       <c r="G52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B53" t="n">
-        <v>486.1005289347495</v>
+        <v>489.6038543571071</v>
       </c>
       <c r="C53" t="n">
-        <v>491.1489881906385</v>
+        <v>490.4584485233347</v>
       </c>
       <c r="D53" t="n">
-        <v>478.8898366362471</v>
+        <v>472.5023579474745</v>
       </c>
       <c r="E53" t="n">
-        <v>483.1448364257812</v>
+        <v>475.4138793945312</v>
       </c>
       <c r="F53" t="n">
-        <v>23245300</v>
+        <v>26802500</v>
       </c>
       <c r="G53" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,25 +1821,25 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B54" t="n">
-        <v>489.6038543571071</v>
+        <v>475.4834610910571</v>
       </c>
       <c r="C54" t="n">
-        <v>490.4584485233347</v>
+        <v>475.9008266883901</v>
       </c>
       <c r="D54" t="n">
-        <v>472.5023579474745</v>
+        <v>465.31794169549</v>
       </c>
       <c r="E54" t="n">
-        <v>475.4138793945312</v>
+        <v>469.1436767578125</v>
       </c>
       <c r="F54" t="n">
-        <v>26802500</v>
+        <v>31769200</v>
       </c>
       <c r="G54" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B55" t="n">
-        <v>475.4834301610789</v>
+        <v>472.0055061050608</v>
       </c>
       <c r="C55" t="n">
-        <v>475.9007957312625</v>
+        <v>473.8935220644432</v>
       </c>
       <c r="D55" t="n">
-        <v>465.3179114267742</v>
+        <v>465.0694984877541</v>
       </c>
       <c r="E55" t="n">
-        <v>469.1436462402344</v>
+        <v>471.0118103027344</v>
       </c>
       <c r="F55" t="n">
-        <v>31769200</v>
+        <v>34421000</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B56" t="n">
-        <v>472.0055061050608</v>
+        <v>471.0813659766461</v>
       </c>
       <c r="C56" t="n">
-        <v>473.8935220644432</v>
+        <v>476.1293271988991</v>
       </c>
       <c r="D56" t="n">
-        <v>465.0694984877541</v>
+        <v>461.9592459889855</v>
       </c>
       <c r="E56" t="n">
-        <v>471.0118103027344</v>
+        <v>473.9829406738281</v>
       </c>
       <c r="F56" t="n">
-        <v>34421000</v>
+        <v>28019800</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B57" t="n">
-        <v>471.0813963074052</v>
+        <v>483.244191691805</v>
       </c>
       <c r="C57" t="n">
-        <v>476.1293578546732</v>
+        <v>485.2315832491155</v>
       </c>
       <c r="D57" t="n">
-        <v>461.9592757324133</v>
+        <v>478.1664208189674</v>
       </c>
       <c r="E57" t="n">
-        <v>473.9829711914062</v>
+        <v>482.4393005371094</v>
       </c>
       <c r="F57" t="n">
-        <v>28019800</v>
+        <v>25709100</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B58" t="n">
-        <v>483.244222260298</v>
+        <v>484.5260924315005</v>
       </c>
       <c r="C58" t="n">
-        <v>485.2316139433245</v>
+        <v>489.5243812398697</v>
       </c>
       <c r="D58" t="n">
-        <v>478.1664510662567</v>
+        <v>483.5820692635899</v>
       </c>
       <c r="E58" t="n">
-        <v>482.4393310546875</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="F58" t="n">
-        <v>25709100</v>
+        <v>14386700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B59" t="n">
-        <v>484.5260924315005</v>
+        <v>485.3608038657598</v>
       </c>
       <c r="C59" t="n">
-        <v>489.5243812398697</v>
+        <v>486.771834992007</v>
       </c>
       <c r="D59" t="n">
-        <v>483.5820692635899</v>
+        <v>481.5946880995925</v>
       </c>
       <c r="E59" t="n">
-        <v>488.9082946777344</v>
+        <v>483.6715087890625</v>
       </c>
       <c r="F59" t="n">
-        <v>14386700</v>
+        <v>23964000</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B60" t="n">
-        <v>485.3607732415945</v>
+        <v>483.6516286444489</v>
       </c>
       <c r="C60" t="n">
-        <v>486.7718042788117</v>
+        <v>490.3888850620814</v>
       </c>
       <c r="D60" t="n">
-        <v>481.5946577130528</v>
+        <v>483.2541563831954</v>
       </c>
       <c r="E60" t="n">
-        <v>483.6714782714844</v>
+        <v>486.9109497070312</v>
       </c>
       <c r="F60" t="n">
-        <v>23964000</v>
+        <v>19562700</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B61" t="n">
-        <v>483.6516286444489</v>
+        <v>473.3171775583083</v>
       </c>
       <c r="C61" t="n">
-        <v>490.3888850620814</v>
+        <v>481.1872310931236</v>
       </c>
       <c r="D61" t="n">
-        <v>483.2541563831954</v>
+        <v>472.2042431453193</v>
       </c>
       <c r="E61" t="n">
-        <v>486.9109497070312</v>
+        <v>474.7182922363281</v>
       </c>
       <c r="F61" t="n">
-        <v>19562700</v>
+        <v>34615100</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B62" t="n">
-        <v>473.3171775583083</v>
+        <v>476.7355071807625</v>
       </c>
       <c r="C62" t="n">
-        <v>481.1872310931236</v>
+        <v>478.2856702042714</v>
       </c>
       <c r="D62" t="n">
-        <v>472.2042431453193</v>
+        <v>473.4861025034468</v>
       </c>
       <c r="E62" t="n">
-        <v>474.7182922363281</v>
+        <v>477.8086853027344</v>
       </c>
       <c r="F62" t="n">
-        <v>34615100</v>
+        <v>22318200</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B63" t="n">
-        <v>476.7355376297969</v>
+        <v>479.4780643507397</v>
       </c>
       <c r="C63" t="n">
-        <v>478.2857007523145</v>
+        <v>480.3525214663767</v>
       </c>
       <c r="D63" t="n">
-        <v>473.4861327449422</v>
+        <v>475.8610275749173</v>
       </c>
       <c r="E63" t="n">
-        <v>477.8087158203125</v>
+        <v>480.1140441894531</v>
       </c>
       <c r="F63" t="n">
-        <v>22318200</v>
+        <v>22608700</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B64" t="n">
-        <v>479.4780948278929</v>
+        <v>481.8331998835391</v>
       </c>
       <c r="C64" t="n">
-        <v>480.3525519991132</v>
+        <v>489.1964595164875</v>
       </c>
       <c r="D64" t="n">
-        <v>475.8610578221601</v>
+        <v>481.3264052911177</v>
       </c>
       <c r="E64" t="n">
-        <v>480.1140747070312</v>
+        <v>487.9245300292969</v>
       </c>
       <c r="F64" t="n">
-        <v>22608700</v>
+        <v>21965900</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B65" t="n">
-        <v>481.8331697469475</v>
+        <v>486.0166380400449</v>
       </c>
       <c r="C65" t="n">
-        <v>489.1964289193556</v>
+        <v>489.0175885389743</v>
       </c>
       <c r="D65" t="n">
-        <v>481.3263751862239</v>
+        <v>485.4204144751398</v>
       </c>
       <c r="E65" t="n">
-        <v>487.9244995117188</v>
+        <v>488.918212890625</v>
       </c>
       <c r="F65" t="n">
-        <v>21965900</v>
+        <v>14696100</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B66" t="n">
-        <v>486.0166380400449</v>
+        <v>480.978577549523</v>
       </c>
       <c r="C66" t="n">
-        <v>489.0175885389743</v>
+        <v>481.1971918388435</v>
       </c>
       <c r="D66" t="n">
-        <v>485.4204144751398</v>
+        <v>472.084987996716</v>
       </c>
       <c r="E66" t="n">
-        <v>488.918212890625</v>
+        <v>475.5430603027344</v>
       </c>
       <c r="F66" t="n">
-        <v>14696100</v>
+        <v>35756200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B67" t="n">
-        <v>480.978577549523</v>
+        <v>473.6252433732215</v>
       </c>
       <c r="C67" t="n">
-        <v>481.1971918388435</v>
+        <v>482.9659780129214</v>
       </c>
       <c r="D67" t="n">
-        <v>472.084987996716</v>
+        <v>472.8600781839672</v>
       </c>
       <c r="E67" t="n">
-        <v>475.5430603027344</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F67" t="n">
-        <v>35756200</v>
+        <v>24669200</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B68" t="n">
-        <v>473.6252734590456</v>
+        <v>476.7951512874317</v>
       </c>
       <c r="C68" t="n">
-        <v>482.9660086920916</v>
+        <v>479.4085762318817</v>
       </c>
       <c r="D68" t="n">
-        <v>472.8601082211862</v>
+        <v>473.3370788032073</v>
       </c>
       <c r="E68" t="n">
-        <v>480.4221496582031</v>
+        <v>475.5132751464844</v>
       </c>
       <c r="F68" t="n">
-        <v>24669200</v>
+        <v>21248100</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B69" t="n">
-        <v>476.7951512874317</v>
+        <v>477.0733729131614</v>
       </c>
       <c r="C69" t="n">
-        <v>479.4085762318817</v>
+        <v>477.6894594742654</v>
       </c>
       <c r="D69" t="n">
-        <v>473.3370788032073</v>
+        <v>469.5411415575728</v>
       </c>
       <c r="E69" t="n">
-        <v>475.5132751464844</v>
+        <v>471.82666015625</v>
       </c>
       <c r="F69" t="n">
-        <v>21248100</v>
+        <v>23727700</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B70" t="n">
-        <v>477.0733729131614</v>
+        <v>468.9349812365753</v>
       </c>
       <c r="C70" t="n">
-        <v>477.6894594742654</v>
+        <v>474.8772929441188</v>
       </c>
       <c r="D70" t="n">
-        <v>469.5411415575728</v>
+        <v>467.9114757916915</v>
       </c>
       <c r="E70" t="n">
-        <v>471.82666015625</v>
+        <v>473.3867492675781</v>
       </c>
       <c r="F70" t="n">
-        <v>23727700</v>
+        <v>20705600</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B71" t="n">
-        <v>468.9350114671635</v>
+        <v>473.903466892556</v>
       </c>
       <c r="C71" t="n">
-        <v>474.8773235577871</v>
+        <v>476.9739832708393</v>
       </c>
       <c r="D71" t="n">
-        <v>467.911505956298</v>
+        <v>472.0055042784347</v>
       </c>
       <c r="E71" t="n">
-        <v>473.3867797851562</v>
+        <v>473.1184387207031</v>
       </c>
       <c r="F71" t="n">
-        <v>20705600</v>
+        <v>24527200</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B72" t="n">
-        <v>473.903466892556</v>
+        <v>475.1754171439269</v>
       </c>
       <c r="C72" t="n">
-        <v>476.9739832708393</v>
+        <v>486.5134903409316</v>
       </c>
       <c r="D72" t="n">
-        <v>472.0055042784347</v>
+        <v>474.8773205213831</v>
       </c>
       <c r="E72" t="n">
-        <v>473.1184387207031</v>
+        <v>480.9289245605469</v>
       </c>
       <c r="F72" t="n">
-        <v>24527200</v>
+        <v>28573500</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B73" t="n">
-        <v>475.1754171439269</v>
+        <v>484.2875835443981</v>
       </c>
       <c r="C73" t="n">
-        <v>486.5134903409316</v>
+        <v>484.7745151206103</v>
       </c>
       <c r="D73" t="n">
-        <v>474.8773205213831</v>
+        <v>479.4482897203998</v>
       </c>
       <c r="E73" t="n">
-        <v>480.9289245605469</v>
+        <v>482.856689453125</v>
       </c>
       <c r="F73" t="n">
-        <v>28573500</v>
+        <v>70836100</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B74" t="n">
-        <v>484.2875835443981</v>
+        <v>483.05539282771</v>
       </c>
       <c r="C74" t="n">
-        <v>484.7745151206103</v>
+        <v>485.6489546100234</v>
       </c>
       <c r="D74" t="n">
-        <v>479.4482897203998</v>
+        <v>479.6470235443271</v>
       </c>
       <c r="E74" t="n">
-        <v>482.856689453125</v>
+        <v>481.8629760742188</v>
       </c>
       <c r="F74" t="n">
-        <v>70836100</v>
+        <v>16963000</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B75" t="n">
-        <v>483.05539282771</v>
+        <v>481.9226163967179</v>
       </c>
       <c r="C75" t="n">
-        <v>485.6489546100234</v>
+        <v>484.7546252629152</v>
       </c>
       <c r="D75" t="n">
-        <v>479.6470235443271</v>
+        <v>481.6841087754749</v>
       </c>
       <c r="E75" t="n">
-        <v>481.8629760742188</v>
+        <v>483.7808227539062</v>
       </c>
       <c r="F75" t="n">
-        <v>16963000</v>
+        <v>14683600</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B76" t="n">
-        <v>481.922585996358</v>
+        <v>482.6181758435609</v>
       </c>
       <c r="C76" t="n">
-        <v>484.7545946839082</v>
+        <v>486.0762481946253</v>
       </c>
       <c r="D76" t="n">
-        <v>481.6840783901604</v>
+        <v>481.7735283363114</v>
       </c>
       <c r="E76" t="n">
-        <v>483.7807922363281</v>
+        <v>484.9434204101562</v>
       </c>
       <c r="F76" t="n">
-        <v>14683600</v>
+        <v>5855900</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B77" t="n">
-        <v>482.6181758435609</v>
+        <v>483.6417106195734</v>
       </c>
       <c r="C77" t="n">
-        <v>486.0762481946253</v>
+        <v>485.0428254417362</v>
       </c>
       <c r="D77" t="n">
-        <v>481.7735283363114</v>
+        <v>482.8964387136479</v>
       </c>
       <c r="E77" t="n">
-        <v>484.9434204101562</v>
+        <v>484.6354064941406</v>
       </c>
       <c r="F77" t="n">
-        <v>5855900</v>
+        <v>8842200</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B78" t="n">
-        <v>483.6417106195734</v>
+        <v>481.8033366009864</v>
       </c>
       <c r="C78" t="n">
-        <v>485.0428254417362</v>
+        <v>485.2713556042012</v>
       </c>
       <c r="D78" t="n">
-        <v>482.8964387136479</v>
+        <v>481.1276307272214</v>
       </c>
       <c r="E78" t="n">
-        <v>484.6354064941406</v>
+        <v>484.0292358398438</v>
       </c>
       <c r="F78" t="n">
-        <v>8842200</v>
+        <v>10893400</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B79" t="n">
-        <v>481.8033366009864</v>
+        <v>482.8666136001516</v>
       </c>
       <c r="C79" t="n">
-        <v>485.2713556042012</v>
+        <v>486.5929730105466</v>
       </c>
       <c r="D79" t="n">
-        <v>481.1276307272214</v>
+        <v>482.4393316658054</v>
       </c>
       <c r="E79" t="n">
-        <v>484.0292358398438</v>
+        <v>484.4068603515625</v>
       </c>
       <c r="F79" t="n">
-        <v>10893400</v>
+        <v>13944500</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B80" t="n">
-        <v>482.8666136001516</v>
+        <v>484.7645645601486</v>
       </c>
       <c r="C80" t="n">
-        <v>486.5929730105466</v>
+        <v>485.0626915008752</v>
       </c>
       <c r="D80" t="n">
-        <v>482.4393316658054</v>
+        <v>480.253177052155</v>
       </c>
       <c r="E80" t="n">
-        <v>484.4068603515625</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="F80" t="n">
-        <v>13944500</v>
+        <v>15601600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B81" t="n">
-        <v>484.7645645601486</v>
+        <v>481.3363251826272</v>
       </c>
       <c r="C81" t="n">
-        <v>485.0626915008752</v>
+        <v>481.6046121327098</v>
       </c>
       <c r="D81" t="n">
-        <v>480.253177052155</v>
+        <v>467.1960229709088</v>
       </c>
       <c r="E81" t="n">
-        <v>480.5711669921875</v>
+        <v>469.95849609375</v>
       </c>
       <c r="F81" t="n">
-        <v>15601600</v>
+        <v>25571600</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B82" t="n">
-        <v>481.3363251826272</v>
+        <v>471.071443053882</v>
       </c>
       <c r="C82" t="n">
-        <v>481.6046121327098</v>
+        <v>473.0687813775576</v>
       </c>
       <c r="D82" t="n">
-        <v>467.1960229709088</v>
+        <v>466.5401924921144</v>
       </c>
       <c r="E82" t="n">
-        <v>469.95849609375</v>
+        <v>469.8690795898438</v>
       </c>
       <c r="F82" t="n">
-        <v>25571600</v>
+        <v>25250300</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B83" t="n">
-        <v>471.071443053882</v>
+        <v>470.8130487247203</v>
       </c>
       <c r="C83" t="n">
-        <v>473.0687813775576</v>
+        <v>475.7219083069673</v>
       </c>
       <c r="D83" t="n">
-        <v>466.5401924921144</v>
+        <v>466.7885929433101</v>
       </c>
       <c r="E83" t="n">
-        <v>469.8690795898438</v>
+        <v>475.4933776855469</v>
       </c>
       <c r="F83" t="n">
-        <v>25250300</v>
+        <v>23037700</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B84" t="n">
-        <v>470.8130487247203</v>
+        <v>476.7355161407656</v>
       </c>
       <c r="C84" t="n">
-        <v>475.7219083069673</v>
+        <v>486.6128550141313</v>
       </c>
       <c r="D84" t="n">
-        <v>466.7885929433101</v>
+        <v>474.936929133209</v>
       </c>
       <c r="E84" t="n">
-        <v>475.4933776855469</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F84" t="n">
-        <v>23037700</v>
+        <v>25564200</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B85" t="n">
-        <v>476.7355464241618</v>
+        <v>478.206189665966</v>
       </c>
       <c r="C85" t="n">
-        <v>486.61288592496</v>
+        <v>479.6172511411785</v>
       </c>
       <c r="D85" t="n">
-        <v>474.9369593023546</v>
+        <v>472.8601010457309</v>
       </c>
       <c r="E85" t="n">
-        <v>480.4221496582031</v>
+        <v>475.0959167480469</v>
       </c>
       <c r="F85" t="n">
-        <v>25564200</v>
+        <v>18162600</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B86" t="n">
-        <v>478.206189665966</v>
+        <v>471.071451381159</v>
       </c>
       <c r="C86" t="n">
-        <v>479.6172511411785</v>
+        <v>476.7951491709672</v>
       </c>
       <c r="D86" t="n">
-        <v>472.8601010457309</v>
+        <v>469.2231916595613</v>
       </c>
       <c r="E86" t="n">
-        <v>475.0959167480469</v>
+        <v>476.258544921875</v>
       </c>
       <c r="F86" t="n">
-        <v>18162600</v>
+        <v>18491000</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B87" t="n">
-        <v>471.071451381159</v>
+        <v>473.6649886945649</v>
       </c>
       <c r="C87" t="n">
-        <v>476.7951491709672</v>
+        <v>477.9577314886077</v>
       </c>
       <c r="D87" t="n">
-        <v>469.2231916595613</v>
+        <v>472.681209234831</v>
       </c>
       <c r="E87" t="n">
-        <v>476.258544921875</v>
+        <v>474.1717529296875</v>
       </c>
       <c r="F87" t="n">
-        <v>18491000</v>
+        <v>23519900</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B88" t="n">
-        <v>473.6649886945649</v>
+        <v>471.6875193976834</v>
       </c>
       <c r="C88" t="n">
-        <v>477.9577314886077</v>
+        <v>472.7805908527595</v>
       </c>
       <c r="D88" t="n">
-        <v>472.681209234831</v>
+        <v>463.0125743921384</v>
       </c>
       <c r="E88" t="n">
-        <v>474.1717529296875</v>
+        <v>467.7028198242188</v>
       </c>
       <c r="F88" t="n">
-        <v>23519900</v>
+        <v>28545800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B89" t="n">
-        <v>471.6875193976834</v>
+        <v>463.5193621312372</v>
       </c>
       <c r="C89" t="n">
-        <v>472.7805908527595</v>
+        <v>465.2484135478969</v>
       </c>
       <c r="D89" t="n">
-        <v>463.0125743921384</v>
+        <v>454.2879494306214</v>
       </c>
       <c r="E89" t="n">
-        <v>467.7028198242188</v>
+        <v>456.4840087890625</v>
       </c>
       <c r="F89" t="n">
-        <v>28545800</v>
+        <v>28184300</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B90" t="n">
-        <v>463.5193621312372</v>
+        <v>461.1940901109254</v>
       </c>
       <c r="C90" t="n">
-        <v>465.2484135478969</v>
+        <v>461.3232754170305</v>
       </c>
       <c r="D90" t="n">
-        <v>454.2879494306214</v>
+        <v>453.0259094171898</v>
       </c>
       <c r="E90" t="n">
-        <v>456.4840087890625</v>
+        <v>453.7811279296875</v>
       </c>
       <c r="F90" t="n">
-        <v>28184300</v>
+        <v>23225800</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B91" t="n">
-        <v>461.1940901109254</v>
+        <v>454.9437666153887</v>
       </c>
       <c r="C91" t="n">
-        <v>461.3232754170305</v>
+        <v>460.2699922453042</v>
       </c>
       <c r="D91" t="n">
-        <v>453.0259094171898</v>
+        <v>453.6023014516422</v>
       </c>
       <c r="E91" t="n">
-        <v>453.7811279296875</v>
+        <v>456.9609680175781</v>
       </c>
       <c r="F91" t="n">
-        <v>23225800</v>
+        <v>34246700</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B92" t="n">
-        <v>454.9437362325269</v>
+        <v>448.3754180557273</v>
       </c>
       <c r="C92" t="n">
-        <v>460.2699615067369</v>
+        <v>453.9202272514996</v>
       </c>
       <c r="D92" t="n">
-        <v>453.6022711583685</v>
+        <v>446.4476457864541</v>
       </c>
       <c r="E92" t="n">
-        <v>456.9609375</v>
+        <v>451.6546020507812</v>
       </c>
       <c r="F92" t="n">
-        <v>34246700</v>
+        <v>26130000</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B93" t="n">
-        <v>448.3754180557273</v>
+        <v>449.7467088388933</v>
       </c>
       <c r="C93" t="n">
-        <v>453.9202272514996</v>
+        <v>449.8361378186282</v>
       </c>
       <c r="D93" t="n">
-        <v>446.4476457864541</v>
+        <v>435.9144504613163</v>
       </c>
       <c r="E93" t="n">
-        <v>451.6546020507812</v>
+        <v>441.3102111816406</v>
       </c>
       <c r="F93" t="n">
-        <v>26130000</v>
+        <v>37980500</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B94" t="n">
-        <v>449.7467088388933</v>
+        <v>444.7981003997206</v>
       </c>
       <c r="C94" t="n">
-        <v>449.8361378186282</v>
+        <v>449.9851935867555</v>
       </c>
       <c r="D94" t="n">
-        <v>435.9144504613163</v>
+        <v>441.8965257028684</v>
       </c>
       <c r="E94" t="n">
-        <v>441.3102111816406</v>
+        <v>448.2959289550781</v>
       </c>
       <c r="F94" t="n">
-        <v>37980500</v>
+        <v>25349400</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B95" t="n">
-        <v>444.7981306791853</v>
+        <v>449.0213193023424</v>
       </c>
       <c r="C95" t="n">
-        <v>449.9852242193297</v>
+        <v>468.1301005814363</v>
       </c>
       <c r="D95" t="n">
-        <v>441.8965557848095</v>
+        <v>447.6897705604439</v>
       </c>
       <c r="E95" t="n">
-        <v>448.2959594726562</v>
+        <v>463.0125732421875</v>
       </c>
       <c r="F95" t="n">
-        <v>25349400</v>
+        <v>38000200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B96" t="n">
-        <v>449.0213193023424</v>
+        <v>462.3766075757791</v>
       </c>
       <c r="C96" t="n">
-        <v>468.1301005814363</v>
+        <v>471.2602507862521</v>
       </c>
       <c r="D96" t="n">
-        <v>447.6897705604439</v>
+        <v>459.0874767807031</v>
       </c>
       <c r="E96" t="n">
-        <v>463.0125732421875</v>
+        <v>467.3152770996094</v>
       </c>
       <c r="F96" t="n">
-        <v>38000200</v>
+        <v>29291200</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B97" t="n">
-        <v>462.3766075757791</v>
+        <v>470.7137217228436</v>
       </c>
       <c r="C97" t="n">
-        <v>471.2602507862521</v>
+        <v>479.8258954035317</v>
       </c>
       <c r="D97" t="n">
-        <v>459.0874767807031</v>
+        <v>470.1771174893794</v>
       </c>
       <c r="E97" t="n">
-        <v>467.3152770996094</v>
+        <v>477.5503234863281</v>
       </c>
       <c r="F97" t="n">
-        <v>29291200</v>
+        <v>29213900</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B98" t="n">
-        <v>470.7137217228436</v>
+        <v>480.1637149068934</v>
       </c>
       <c r="C98" t="n">
-        <v>479.8258954035317</v>
+        <v>480.6903724414303</v>
       </c>
       <c r="D98" t="n">
-        <v>470.1771174893794</v>
+        <v>474.9865685400099</v>
       </c>
       <c r="E98" t="n">
-        <v>477.5503234863281</v>
+        <v>478.5936889648438</v>
       </c>
       <c r="F98" t="n">
-        <v>29213900</v>
+        <v>36875400</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B99" t="n">
-        <v>480.1637455245844</v>
+        <v>437.2162272399066</v>
       </c>
       <c r="C99" t="n">
-        <v>480.6904030927037</v>
+        <v>439.7104135269112</v>
       </c>
       <c r="D99" t="n">
-        <v>474.9865988275796</v>
+        <v>418.365815756604</v>
       </c>
       <c r="E99" t="n">
-        <v>478.5937194824219</v>
+        <v>430.7671508789062</v>
       </c>
       <c r="F99" t="n">
-        <v>36875400</v>
+        <v>128855300</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B100" t="n">
-        <v>437.2162272399066</v>
+        <v>436.4013853645445</v>
       </c>
       <c r="C100" t="n">
-        <v>439.7104135269112</v>
+        <v>436.8286672682951</v>
       </c>
       <c r="D100" t="n">
-        <v>418.365815756604</v>
+        <v>423.7615739365565</v>
       </c>
       <c r="E100" t="n">
-        <v>430.7671508789062</v>
+        <v>427.5773620605469</v>
       </c>
       <c r="F100" t="n">
-        <v>128855300</v>
+        <v>58566800</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B101" t="n">
-        <v>436.4014165119217</v>
+        <v>427.5276741085398</v>
       </c>
       <c r="C101" t="n">
-        <v>436.8286984461687</v>
+        <v>428.0245220118177</v>
       </c>
       <c r="D101" t="n">
-        <v>423.7616041817895</v>
+        <v>419.588054318219</v>
       </c>
       <c r="E101" t="n">
-        <v>427.577392578125</v>
+        <v>420.7009887695312</v>
       </c>
       <c r="F101" t="n">
-        <v>58566800</v>
+        <v>42219900</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B102" t="n">
-        <v>427.5276741085398</v>
+        <v>419.3495781995532</v>
       </c>
       <c r="C102" t="n">
-        <v>428.0245220118177</v>
+        <v>419.3893041977899</v>
       </c>
       <c r="D102" t="n">
-        <v>419.588054318219</v>
+        <v>405.9843574339844</v>
       </c>
       <c r="E102" t="n">
-        <v>420.7009887695312</v>
+        <v>408.6176452636719</v>
       </c>
       <c r="F102" t="n">
-        <v>42219900</v>
+        <v>61424100</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B103" t="n">
-        <v>419.3496095186449</v>
+        <v>408.4089957411405</v>
       </c>
       <c r="C103" t="n">
-        <v>419.3893355198486</v>
+        <v>417.1535071208501</v>
       </c>
       <c r="D103" t="n">
-        <v>405.9843877548956</v>
+        <v>406.6600813351222</v>
       </c>
       <c r="E103" t="n">
-        <v>408.61767578125</v>
+        <v>411.5788879394531</v>
       </c>
       <c r="F103" t="n">
-        <v>61424100</v>
+        <v>45012400</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B104" t="n">
-        <v>408.4089957411405</v>
+        <v>404.8714440282318</v>
       </c>
       <c r="C104" t="n">
-        <v>417.1535071208501</v>
+        <v>405.7260079125925</v>
       </c>
       <c r="D104" t="n">
-        <v>406.6600813351222</v>
+        <v>389.8467674620769</v>
       </c>
       <c r="E104" t="n">
-        <v>411.5788879394531</v>
+        <v>391.1882629394531</v>
       </c>
       <c r="F104" t="n">
-        <v>45012400</v>
+        <v>66289200</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B105" t="n">
-        <v>404.8714440282318</v>
+        <v>396.6535630940219</v>
       </c>
       <c r="C105" t="n">
-        <v>405.7260079125925</v>
+        <v>399.2570412200398</v>
       </c>
       <c r="D105" t="n">
-        <v>389.8467674620769</v>
+        <v>390.4429643868461</v>
       </c>
       <c r="E105" t="n">
-        <v>391.1882629394531</v>
+        <v>398.6111450195312</v>
       </c>
       <c r="F105" t="n">
-        <v>66289200</v>
+        <v>53515300</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B106" t="n">
-        <v>396.653593461728</v>
+        <v>402.2977759502542</v>
       </c>
       <c r="C106" t="n">
-        <v>399.2570717870675</v>
+        <v>412.2744908996196</v>
       </c>
       <c r="D106" t="n">
-        <v>390.4429942790701</v>
+        <v>398.3428555009064</v>
       </c>
       <c r="E106" t="n">
-        <v>398.6111755371094</v>
+        <v>410.9926147460938</v>
       </c>
       <c r="F106" t="n">
-        <v>53515300</v>
+        <v>45480500</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B107" t="n">
-        <v>402.2977759502542</v>
+        <v>416.9746165751398</v>
       </c>
       <c r="C107" t="n">
-        <v>412.2744908996196</v>
+        <v>421.009018998737</v>
       </c>
       <c r="D107" t="n">
-        <v>398.3428555009064</v>
+        <v>410.0982587889407</v>
       </c>
       <c r="E107" t="n">
-        <v>410.9926147460938</v>
+        <v>410.6646423339844</v>
       </c>
       <c r="F107" t="n">
-        <v>45480500</v>
+        <v>44857900</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B108" t="n">
-        <v>416.9746165751398</v>
+        <v>413.5563153661985</v>
       </c>
       <c r="C108" t="n">
-        <v>421.009018998737</v>
+        <v>413.8345489802859</v>
       </c>
       <c r="D108" t="n">
-        <v>410.0982587889407</v>
+        <v>398.4819668946231</v>
       </c>
       <c r="E108" t="n">
-        <v>410.6646423339844</v>
+        <v>401.8207702636719</v>
       </c>
       <c r="F108" t="n">
-        <v>44857900</v>
+        <v>42491000</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B109" t="n">
-        <v>413.5563153661985</v>
+        <v>402.4468146669985</v>
       </c>
       <c r="C109" t="n">
-        <v>413.8345489802859</v>
+        <v>403.6392618034954</v>
       </c>
       <c r="D109" t="n">
-        <v>398.4819668946231</v>
+        <v>395.5008904586587</v>
       </c>
       <c r="E109" t="n">
-        <v>401.8207702636719</v>
+        <v>399.3067321777344</v>
       </c>
       <c r="F109" t="n">
-        <v>42491000</v>
+        <v>40802400</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B110" t="n">
-        <v>402.4468454245618</v>
+        <v>401.900281272875</v>
       </c>
       <c r="C110" t="n">
-        <v>403.6392926521932</v>
+        <v>402.9834060634867</v>
       </c>
       <c r="D110" t="n">
-        <v>395.50092068537</v>
+        <v>395.5406038478973</v>
       </c>
       <c r="E110" t="n">
-        <v>399.3067626953125</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="F110" t="n">
-        <v>40802400</v>
+        <v>34091600</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B111" t="n">
-        <v>401.900281272875</v>
+        <v>396.7032617740463</v>
       </c>
       <c r="C111" t="n">
-        <v>402.9834060634867</v>
+        <v>397.9950542597942</v>
       </c>
       <c r="D111" t="n">
-        <v>395.5406038478973</v>
+        <v>392.0428257724806</v>
       </c>
       <c r="E111" t="n">
-        <v>398.7900085449219</v>
+        <v>394.3581237792969</v>
       </c>
       <c r="F111" t="n">
-        <v>34091600</v>
+        <v>32078800</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,22 +3329,22 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B112" t="n">
-        <v>396.7032617740463</v>
+        <v>395.6201070500213</v>
       </c>
       <c r="C112" t="n">
-        <v>397.9950542597942</v>
+        <v>400.0221720919145</v>
       </c>
       <c r="D112" t="n">
-        <v>392.0428257724806</v>
+        <v>393.8215201082963</v>
       </c>
       <c r="E112" t="n">
-        <v>394.3581237792969</v>
+        <v>397.0808410644531</v>
       </c>
       <c r="F112" t="n">
-        <v>32078800</v>
+        <v>23223400</v>
       </c>
       <c r="G112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B113" t="n">
-        <v>395.6201070500213</v>
+        <v>399.0727866126232</v>
       </c>
       <c r="C113" t="n">
-        <v>400.0221720919145</v>
+        <v>402.7976819572589</v>
       </c>
       <c r="D113" t="n">
-        <v>393.8215201082963</v>
+        <v>395.0690225854118</v>
       </c>
       <c r="E113" t="n">
-        <v>397.0808410644531</v>
+        <v>396.8517761230469</v>
       </c>
       <c r="F113" t="n">
-        <v>23223400</v>
+        <v>28234000</v>
       </c>
       <c r="G113" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,25 +3381,25 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B114" t="n">
-        <v>399.0727866126232</v>
+        <v>394.5112344348997</v>
       </c>
       <c r="C114" t="n">
-        <v>402.7976819572589</v>
+        <v>398.5050592846536</v>
       </c>
       <c r="D114" t="n">
-        <v>395.0690225854118</v>
+        <v>393.5650869938952</v>
       </c>
       <c r="E114" t="n">
-        <v>396.8517761230469</v>
+        <v>395.6267395019531</v>
       </c>
       <c r="F114" t="n">
-        <v>28234000</v>
+        <v>34015200</v>
       </c>
       <c r="G114" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B115" t="n">
-        <v>394.5112344348997</v>
+        <v>393.405742102137</v>
       </c>
       <c r="C115" t="n">
-        <v>398.5050592846536</v>
+        <v>393.7642745182822</v>
       </c>
       <c r="D115" t="n">
-        <v>393.5650869938952</v>
+        <v>381.5537777227514</v>
       </c>
       <c r="E115" t="n">
-        <v>395.6267395019531</v>
+        <v>382.9182434082031</v>
       </c>
       <c r="F115" t="n">
-        <v>34015200</v>
+        <v>43238300</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B116" t="n">
-        <v>393.405742102137</v>
+        <v>382.5895619940176</v>
       </c>
       <c r="C116" t="n">
-        <v>393.7642745182822</v>
+        <v>387.7884640317496</v>
       </c>
       <c r="D116" t="n">
-        <v>381.5537777227514</v>
+        <v>380.1693467763097</v>
       </c>
       <c r="E116" t="n">
-        <v>382.9182434082031</v>
+        <v>387.429931640625</v>
       </c>
       <c r="F116" t="n">
-        <v>43238300</v>
+        <v>33884700</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B117" t="n">
-        <v>382.5895619940176</v>
+        <v>388.9537605304631</v>
       </c>
       <c r="C117" t="n">
-        <v>387.7884640317496</v>
+        <v>399.8496074643683</v>
       </c>
       <c r="D117" t="n">
-        <v>380.1693467763097</v>
+        <v>388.5852587696308</v>
       </c>
       <c r="E117" t="n">
-        <v>387.429931640625</v>
+        <v>398.9831237792969</v>
       </c>
       <c r="F117" t="n">
-        <v>33884700</v>
+        <v>43625500</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B118" t="n">
-        <v>388.9537605304631</v>
+        <v>403.0765245044552</v>
       </c>
       <c r="C118" t="n">
-        <v>399.8496074643683</v>
+        <v>405.8453028142193</v>
       </c>
       <c r="D118" t="n">
-        <v>388.5852587696308</v>
+        <v>397.1306190557743</v>
       </c>
       <c r="E118" t="n">
-        <v>398.9831237792969</v>
+        <v>400.0986022949219</v>
       </c>
       <c r="F118" t="n">
-        <v>43625500</v>
+        <v>34405900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B119" t="n">
-        <v>403.0765245044552</v>
+        <v>389.3023679559341</v>
       </c>
       <c r="C119" t="n">
-        <v>405.8453028142193</v>
+        <v>395.2183958601928</v>
       </c>
       <c r="D119" t="n">
-        <v>397.1306190557743</v>
+        <v>388.3064040716401</v>
       </c>
       <c r="E119" t="n">
-        <v>400.0986022949219</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="F119" t="n">
-        <v>34405900</v>
+        <v>51367200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B120" t="n">
-        <v>389.3023679559341</v>
+        <v>391.2743390590049</v>
       </c>
       <c r="C120" t="n">
-        <v>395.2183958601928</v>
+        <v>399.5707348557469</v>
       </c>
       <c r="D120" t="n">
-        <v>388.3064040716401</v>
+        <v>389.0533591512552</v>
       </c>
       <c r="E120" t="n">
-        <v>391.1548461914062</v>
+        <v>396.9413757324219</v>
       </c>
       <c r="F120" t="n">
-        <v>51367200</v>
+        <v>35474900</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B121" t="n">
-        <v>391.2743390590049</v>
+        <v>391.5532542396072</v>
       </c>
       <c r="C121" t="n">
-        <v>399.5707348557469</v>
+        <v>405.0585220162706</v>
       </c>
       <c r="D121" t="n">
-        <v>389.0533591512552</v>
+        <v>391.0851500003899</v>
       </c>
       <c r="E121" t="n">
-        <v>396.9413757324219</v>
+        <v>402.2996826171875</v>
       </c>
       <c r="F121" t="n">
-        <v>35474900</v>
+        <v>38199200</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B122" t="n">
-        <v>391.5532542396072</v>
+        <v>399.6504140582061</v>
       </c>
       <c r="C122" t="n">
-        <v>405.0585220162706</v>
+        <v>409.3710312257941</v>
       </c>
       <c r="D122" t="n">
-        <v>391.0851500003899</v>
+        <v>398.6942972465368</v>
       </c>
       <c r="E122" t="n">
-        <v>402.2996826171875</v>
+        <v>403.5645751953125</v>
       </c>
       <c r="F122" t="n">
-        <v>38199200</v>
+        <v>35808000</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B123" t="n">
-        <v>399.6504140582061</v>
+        <v>402.7877173292459</v>
       </c>
       <c r="C123" t="n">
-        <v>409.3710312257941</v>
+        <v>409.9486695143622</v>
       </c>
       <c r="D123" t="n">
-        <v>398.6942972465368</v>
+        <v>402.7677785996419</v>
       </c>
       <c r="E123" t="n">
-        <v>403.5645751953125</v>
+        <v>409.0224304199219</v>
       </c>
       <c r="F123" t="n">
-        <v>35808000</v>
+        <v>39001300</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B124" t="n">
-        <v>402.7877173292459</v>
+        <v>407.5484392107423</v>
       </c>
       <c r="C124" t="n">
-        <v>409.9486695143622</v>
+        <v>411.3828759024364</v>
       </c>
       <c r="D124" t="n">
-        <v>402.7677785996419</v>
+        <v>406.8612216895844</v>
       </c>
       <c r="E124" t="n">
-        <v>409.0224304199219</v>
+        <v>407.3093872070312</v>
       </c>
       <c r="F124" t="n">
-        <v>39001300</v>
+        <v>31123900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B125" t="n">
-        <v>407.5484392107423</v>
+        <v>403.2857003455267</v>
       </c>
       <c r="C125" t="n">
-        <v>411.3828759024364</v>
+        <v>408.5543272911556</v>
       </c>
       <c r="D125" t="n">
-        <v>406.8612216895844</v>
+        <v>401.8714182880504</v>
       </c>
       <c r="E125" t="n">
-        <v>407.3093872070312</v>
+        <v>407.757568359375</v>
       </c>
       <c r="F125" t="n">
-        <v>31123900</v>
+        <v>30131900</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B126" t="n">
-        <v>403.2857003455267</v>
+        <v>408.3750692869274</v>
       </c>
       <c r="C126" t="n">
-        <v>408.5543272911556</v>
+        <v>408.5443965203919</v>
       </c>
       <c r="D126" t="n">
-        <v>401.8714182880504</v>
+        <v>401.3037196464309</v>
       </c>
       <c r="E126" t="n">
-        <v>407.757568359375</v>
+        <v>404.122314453125</v>
       </c>
       <c r="F126" t="n">
-        <v>30131900</v>
+        <v>31706400</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B127" t="n">
-        <v>408.3750692869274</v>
+        <v>403.9330670994013</v>
       </c>
       <c r="C127" t="n">
-        <v>408.5443965203919</v>
+        <v>407.3591851847947</v>
       </c>
       <c r="D127" t="n">
-        <v>401.3037196464309</v>
+        <v>399.9691200230297</v>
       </c>
       <c r="E127" t="n">
-        <v>404.122314453125</v>
+        <v>403.245849609375</v>
       </c>
       <c r="F127" t="n">
-        <v>31706400</v>
+        <v>25512100</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B128" t="n">
-        <v>403.9330670994013</v>
+        <v>402.9968458288957</v>
       </c>
       <c r="C128" t="n">
-        <v>407.3591851847947</v>
+        <v>404.4808221962511</v>
       </c>
       <c r="D128" t="n">
-        <v>399.9691200230297</v>
+        <v>400.0886180975</v>
       </c>
       <c r="E128" t="n">
-        <v>403.245849609375</v>
+        <v>400.2380065917969</v>
       </c>
       <c r="F128" t="n">
-        <v>25512100</v>
+        <v>27263900</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B129" t="n">
-        <v>402.9968458288957</v>
+        <v>399.3815063856616</v>
       </c>
       <c r="C129" t="n">
-        <v>404.4808221962511</v>
+        <v>403.1661568819284</v>
       </c>
       <c r="D129" t="n">
-        <v>400.0886180975</v>
+        <v>392.6587503554791</v>
       </c>
       <c r="E129" t="n">
-        <v>400.2380065917969</v>
+        <v>393.9534912109375</v>
       </c>
       <c r="F129" t="n">
-        <v>27263900</v>
+        <v>26848000</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B130" t="n">
-        <v>399.3815063856616</v>
+        <v>396.4633374914087</v>
       </c>
       <c r="C130" t="n">
-        <v>403.1661568819284</v>
+        <v>399.013002518604</v>
       </c>
       <c r="D130" t="n">
-        <v>392.6587503554791</v>
+        <v>393.1965772756644</v>
       </c>
       <c r="E130" t="n">
-        <v>393.9534912109375</v>
+        <v>398.3357543945312</v>
       </c>
       <c r="F130" t="n">
-        <v>26848000</v>
+        <v>27733700</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B131" t="n">
-        <v>396.4633374914087</v>
+        <v>398.6544574759768</v>
       </c>
       <c r="C131" t="n">
-        <v>399.013002518604</v>
+        <v>402.7677932271478</v>
       </c>
       <c r="D131" t="n">
-        <v>393.1965772756644</v>
+        <v>396.1446394015159</v>
       </c>
       <c r="E131" t="n">
-        <v>398.3357543945312</v>
+        <v>397.7979431152344</v>
       </c>
       <c r="F131" t="n">
-        <v>27733700</v>
+        <v>26228300</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B132" t="n">
-        <v>398.6544574759768</v>
+        <v>395.5271224277118</v>
       </c>
       <c r="C132" t="n">
-        <v>402.7677932271478</v>
+        <v>396.3936061005556</v>
       </c>
       <c r="D132" t="n">
-        <v>396.1446394015159</v>
+        <v>389.421859259591</v>
       </c>
       <c r="E132" t="n">
-        <v>397.7979431152344</v>
+        <v>390.2086791992188</v>
       </c>
       <c r="F132" t="n">
-        <v>26228300</v>
+        <v>25908500</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B133" t="n">
-        <v>395.5271224277118</v>
+        <v>388.5255176358589</v>
       </c>
       <c r="C133" t="n">
-        <v>396.3936061005556</v>
+        <v>390.9058555160312</v>
       </c>
       <c r="D133" t="n">
-        <v>389.421859259591</v>
+        <v>385.4977789148814</v>
       </c>
       <c r="E133" t="n">
-        <v>390.2086791992188</v>
+        <v>387.4498596191406</v>
       </c>
       <c r="F133" t="n">
-        <v>25908500</v>
+        <v>25138800</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B134" t="n">
-        <v>388.5255176358589</v>
+        <v>385.2288602760525</v>
       </c>
       <c r="C134" t="n">
-        <v>390.9058555160312</v>
+        <v>385.4380041709834</v>
       </c>
       <c r="D134" t="n">
-        <v>385.4977789148814</v>
+        <v>378.5857681226169</v>
       </c>
       <c r="E134" t="n">
-        <v>387.4498596191406</v>
+        <v>380.3287048339844</v>
       </c>
       <c r="F134" t="n">
-        <v>25138800</v>
+        <v>50853200</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B135" t="n">
-        <v>385.2288602760525</v>
+        <v>382.3505545919761</v>
       </c>
       <c r="C135" t="n">
-        <v>385.4380041709834</v>
+        <v>385.6471928372158</v>
       </c>
       <c r="D135" t="n">
-        <v>378.5857681226169</v>
+        <v>380.1395134056624</v>
       </c>
       <c r="E135" t="n">
-        <v>380.3287048339844</v>
+        <v>381.4541931152344</v>
       </c>
       <c r="F135" t="n">
-        <v>50853200</v>
+        <v>29680100</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B136" t="n">
-        <v>382.3505545919761</v>
+        <v>380.8167328036651</v>
       </c>
       <c r="C136" t="n">
-        <v>385.6471928372158</v>
+        <v>380.9263046350485</v>
       </c>
       <c r="D136" t="n">
-        <v>380.1395134056624</v>
+        <v>370.3491731415432</v>
       </c>
       <c r="E136" t="n">
-        <v>381.4541931152344</v>
+        <v>371.2355651855469</v>
       </c>
       <c r="F136" t="n">
-        <v>29680100</v>
+        <v>42733600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B137" t="n">
-        <v>380.8167328036651</v>
+        <v>375.3987224826456</v>
       </c>
       <c r="C137" t="n">
-        <v>380.9263046350485</v>
+        <v>375.5381416220395</v>
       </c>
       <c r="D137" t="n">
-        <v>370.3491731415432</v>
+        <v>368.1381372201017</v>
       </c>
       <c r="E137" t="n">
-        <v>371.2355651855469</v>
+        <v>369.5424499511719</v>
       </c>
       <c r="F137" t="n">
-        <v>42733600</v>
+        <v>31181200</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B138" t="n">
-        <v>375.3987224826456</v>
+        <v>369.3233201292261</v>
       </c>
       <c r="C138" t="n">
-        <v>375.5381416220395</v>
+        <v>373.2075730440749</v>
       </c>
       <c r="D138" t="n">
-        <v>368.1381372201017</v>
+        <v>363.7160388213271</v>
       </c>
       <c r="E138" t="n">
-        <v>369.5424499511719</v>
+        <v>364.4928894042969</v>
       </c>
       <c r="F138" t="n">
-        <v>31181200</v>
+        <v>36836600</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B139" t="n">
-        <v>369.3233201292261</v>
+        <v>360.4393475355787</v>
       </c>
       <c r="C139" t="n">
-        <v>373.2075730440749</v>
+        <v>360.9871459448897</v>
       </c>
       <c r="D139" t="n">
-        <v>363.7160388213271</v>
+        <v>355.0711176485405</v>
       </c>
       <c r="E139" t="n">
-        <v>364.4928894042969</v>
+        <v>355.3300476074219</v>
       </c>
       <c r="F139" t="n">
-        <v>36836600</v>
+        <v>37883400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B140" t="n">
-        <v>360.4393475355787</v>
+        <v>360.4393363053819</v>
       </c>
       <c r="C140" t="n">
-        <v>360.9871459448897</v>
+        <v>363.8853629556265</v>
       </c>
       <c r="D140" t="n">
-        <v>355.0711176485405</v>
+        <v>354.8420239421825</v>
       </c>
       <c r="E140" t="n">
-        <v>355.3300476074219</v>
+        <v>357.5111999511719</v>
       </c>
       <c r="F140" t="n">
-        <v>37883400</v>
+        <v>44797000</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B141" t="n">
-        <v>360.4393363053819</v>
+        <v>363.0786217954557</v>
       </c>
       <c r="C141" t="n">
-        <v>363.8853629556265</v>
+        <v>371.3949263066763</v>
       </c>
       <c r="D141" t="n">
-        <v>354.8420239421825</v>
+        <v>361.6046146993887</v>
       </c>
       <c r="E141" t="n">
-        <v>357.5111999511719</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="F141" t="n">
-        <v>44797000</v>
+        <v>45244400</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B142" t="n">
-        <v>363.0786217954557</v>
+        <v>371.9825473134139</v>
       </c>
       <c r="C142" t="n">
-        <v>371.3949263066763</v>
+        <v>372.4805292634522</v>
       </c>
       <c r="D142" t="n">
-        <v>361.6046146993887</v>
+        <v>366.7139201659809</v>
       </c>
       <c r="E142" t="n">
-        <v>368.6759643554688</v>
+        <v>367.8791809082031</v>
       </c>
       <c r="F142" t="n">
-        <v>45244400</v>
+        <v>29417200</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B143" t="n">
-        <v>371.9825473134139</v>
+        <v>365.7278929006101</v>
       </c>
       <c r="C143" t="n">
-        <v>372.4805292634522</v>
+        <v>372.1319638369453</v>
       </c>
       <c r="D143" t="n">
-        <v>366.7139201659809</v>
+        <v>362.680245817395</v>
       </c>
       <c r="E143" t="n">
-        <v>367.8791809082031</v>
+        <v>371.9526672363281</v>
       </c>
       <c r="F143" t="n">
-        <v>29417200</v>
+        <v>24099100</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B144" t="n">
-        <v>365.7278929006101</v>
+        <v>371.9825539180967</v>
       </c>
       <c r="C144" t="n">
-        <v>372.1319638369453</v>
+        <v>372.2216059265558</v>
       </c>
       <c r="D144" t="n">
-        <v>362.680245817395</v>
+        <v>368.0086676124431</v>
       </c>
       <c r="E144" t="n">
-        <v>371.9526672363281</v>
+        <v>371.3750305175781</v>
       </c>
       <c r="F144" t="n">
-        <v>24099100</v>
+        <v>16146600</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B145" t="n">
-        <v>371.9825539180967</v>
+        <v>368.8452727581139</v>
       </c>
       <c r="C145" t="n">
-        <v>372.2216059265558</v>
+        <v>370.9467724245638</v>
       </c>
       <c r="D145" t="n">
-        <v>368.0086676124431</v>
+        <v>365.080530373921</v>
       </c>
       <c r="E145" t="n">
-        <v>371.3750305175781</v>
+        <v>370.7874145507812</v>
       </c>
       <c r="F145" t="n">
-        <v>16146600</v>
+        <v>21443300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B146" t="n">
-        <v>368.8452727581139</v>
+        <v>383.4261612830284</v>
       </c>
       <c r="C146" t="n">
-        <v>370.9467724245638</v>
+        <v>383.4460696173869</v>
       </c>
       <c r="D146" t="n">
-        <v>365.080530373921</v>
+        <v>369.9109249891301</v>
       </c>
       <c r="E146" t="n">
-        <v>370.7874145507812</v>
+        <v>372.8191223144531</v>
       </c>
       <c r="F146" t="n">
-        <v>21443300</v>
+        <v>33064800</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B147" t="n">
-        <v>383.4261612830284</v>
+        <v>370.9965328148009</v>
       </c>
       <c r="C147" t="n">
-        <v>383.4460696173869</v>
+        <v>371.9924966612836</v>
       </c>
       <c r="D147" t="n">
-        <v>369.9109249891301</v>
+        <v>365.5685176937085</v>
       </c>
       <c r="E147" t="n">
-        <v>372.8191223144531</v>
+        <v>371.5642395019531</v>
       </c>
       <c r="F147" t="n">
-        <v>33064800</v>
+        <v>30435300</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B148" t="n">
-        <v>370.9965328148009</v>
+        <v>371.4746074371751</v>
       </c>
       <c r="C148" t="n">
-        <v>371.9924966612836</v>
+        <v>374.1238749235223</v>
       </c>
       <c r="D148" t="n">
-        <v>365.5685176937085</v>
+        <v>368.5365019241105</v>
       </c>
       <c r="E148" t="n">
-        <v>371.5642395019531</v>
+        <v>369.3731079101562</v>
       </c>
       <c r="F148" t="n">
-        <v>30435300</v>
+        <v>28111100</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B149" t="n">
-        <v>371.4746074371751</v>
+        <v>372.1020528926679</v>
       </c>
       <c r="C149" t="n">
-        <v>374.1238749235223</v>
+        <v>382.9879612673769</v>
       </c>
       <c r="D149" t="n">
-        <v>368.5365019241105</v>
+        <v>369.5225100750242</v>
       </c>
       <c r="E149" t="n">
-        <v>369.3731079101562</v>
+        <v>382.8186340332031</v>
       </c>
       <c r="F149" t="n">
-        <v>28111100</v>
+        <v>35745800</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B150" t="n">
-        <v>372.1020528926679</v>
+        <v>386.3543213772784</v>
       </c>
       <c r="C150" t="n">
-        <v>382.9879612673769</v>
+        <v>393.0969858972055</v>
       </c>
       <c r="D150" t="n">
-        <v>369.5225100750242</v>
+        <v>384.95994763093</v>
       </c>
       <c r="E150" t="n">
-        <v>382.8186340332031</v>
+        <v>391.5233459472656</v>
       </c>
       <c r="F150" t="n">
-        <v>35745800</v>
+        <v>37504500</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B151" t="n">
-        <v>386.3543213772784</v>
+        <v>396.3936283702306</v>
       </c>
       <c r="C151" t="n">
-        <v>393.0969858972055</v>
+        <v>412.6975523926047</v>
       </c>
       <c r="D151" t="n">
-        <v>384.95994763093</v>
+        <v>395.1287651714373</v>
       </c>
       <c r="E151" t="n">
-        <v>391.5233459472656</v>
+        <v>409.5602722167969</v>
       </c>
       <c r="F151" t="n">
-        <v>37504500</v>
+        <v>45063400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B152" t="n">
-        <v>396.3936283702306</v>
+        <v>418.1653718785589</v>
       </c>
       <c r="C152" t="n">
-        <v>412.6975523926047</v>
+        <v>419.1215190686066</v>
       </c>
       <c r="D152" t="n">
-        <v>395.1287651714373</v>
+        <v>410.4765600541581</v>
       </c>
       <c r="E152" t="n">
-        <v>409.5602722167969</v>
+        <v>418.5637817382812</v>
       </c>
       <c r="F152" t="n">
-        <v>45063400</v>
+        <v>41642400</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B153" t="n">
-        <v>418.1653718785589</v>
+        <v>423.105393156615</v>
       </c>
       <c r="C153" t="n">
-        <v>419.1215190686066</v>
+        <v>429.8380884820792</v>
       </c>
       <c r="D153" t="n">
-        <v>410.4765600541581</v>
+        <v>418.9920573683891</v>
       </c>
       <c r="E153" t="n">
-        <v>418.5637817382812</v>
+        <v>421.0835876464844</v>
       </c>
       <c r="F153" t="n">
-        <v>41642400</v>
+        <v>48568200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B154" t="n">
-        <v>423.105393156615</v>
+        <v>419.4501847919345</v>
       </c>
       <c r="C154" t="n">
-        <v>429.8380884820792</v>
+        <v>421.6213787702164</v>
       </c>
       <c r="D154" t="n">
-        <v>418.9920573683891</v>
+        <v>414.6197538627068</v>
       </c>
       <c r="E154" t="n">
-        <v>421.0835876464844</v>
+        <v>416.3826293945312</v>
       </c>
       <c r="F154" t="n">
-        <v>48568200</v>
+        <v>27582200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B155" t="n">
-        <v>419.4501847919345</v>
+        <v>418.5438369146158</v>
       </c>
       <c r="C155" t="n">
-        <v>421.6213787702164</v>
+        <v>425.4558284373716</v>
       </c>
       <c r="D155" t="n">
-        <v>414.6197538627068</v>
+        <v>415.516128706763</v>
       </c>
       <c r="E155" t="n">
-        <v>416.3826293945312</v>
+        <v>422.4480285644531</v>
       </c>
       <c r="F155" t="n">
-        <v>27582200</v>
+        <v>32048500</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B156" t="n">
-        <v>418.5438369146158</v>
+        <v>424.4698510786937</v>
       </c>
       <c r="C156" t="n">
-        <v>425.4558284373716</v>
+        <v>431.9495495900464</v>
       </c>
       <c r="D156" t="n">
-        <v>415.516128706763</v>
+        <v>421.9600330275293</v>
       </c>
       <c r="E156" t="n">
-        <v>422.4480285644531</v>
+        <v>431.1726989746094</v>
       </c>
       <c r="F156" t="n">
-        <v>32048500</v>
+        <v>29378200</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B157" t="n">
-        <v>424.4698510786937</v>
+        <v>418.195296097549</v>
       </c>
       <c r="C157" t="n">
-        <v>431.9495495900464</v>
+        <v>421.9500690544079</v>
       </c>
       <c r="D157" t="n">
-        <v>421.9600330275293</v>
+        <v>409.7495112929088</v>
       </c>
       <c r="E157" t="n">
-        <v>431.1726989746094</v>
+        <v>414.0719909667969</v>
       </c>
       <c r="F157" t="n">
-        <v>29378200</v>
+        <v>38308000</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B158" t="n">
-        <v>418.195296097549</v>
+        <v>415.2870711617039</v>
       </c>
       <c r="C158" t="n">
-        <v>421.9500690544079</v>
+        <v>423.2348740747397</v>
       </c>
       <c r="D158" t="n">
-        <v>409.7495112929088</v>
+        <v>414.1217800179737</v>
       </c>
       <c r="E158" t="n">
-        <v>414.0719909667969</v>
+        <v>422.9061889648438</v>
       </c>
       <c r="F158" t="n">
-        <v>38308000</v>
+        <v>27457400</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B159" t="n">
-        <v>415.2870711617039</v>
+        <v>420.6752229306716</v>
       </c>
       <c r="C159" t="n">
-        <v>423.2348740747397</v>
+        <v>425.3861125683125</v>
       </c>
       <c r="D159" t="n">
-        <v>414.1217800179737</v>
+        <v>415.3866572294081</v>
       </c>
       <c r="E159" t="n">
-        <v>422.9061889648438</v>
+        <v>423.1053771972656</v>
       </c>
       <c r="F159" t="n">
-        <v>27457400</v>
+        <v>30867300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B160" t="n">
-        <v>420.6752229306716</v>
+        <v>422.8563830057505</v>
       </c>
       <c r="C160" t="n">
-        <v>425.3861125683125</v>
+        <v>428.1847957314844</v>
       </c>
       <c r="D160" t="n">
-        <v>415.3866572294081</v>
+        <v>420.197146128082</v>
       </c>
       <c r="E160" t="n">
-        <v>423.1053771972656</v>
+        <v>427.5174865722656</v>
       </c>
       <c r="F160" t="n">
-        <v>30867300</v>
+        <v>30438100</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B161" t="n">
-        <v>422.8563830057505</v>
+        <v>422.8663369761165</v>
       </c>
       <c r="C161" t="n">
-        <v>428.1847957314844</v>
+        <v>425.0973167681131</v>
       </c>
       <c r="D161" t="n">
-        <v>420.197146128082</v>
+        <v>418.593673752453</v>
       </c>
       <c r="E161" t="n">
-        <v>427.5174865722656</v>
+        <v>422.746826171875</v>
       </c>
       <c r="F161" t="n">
-        <v>30438100</v>
+        <v>38288300</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B162" t="n">
-        <v>422.8663369761165</v>
+        <v>409.1519246549498</v>
       </c>
       <c r="C162" t="n">
-        <v>425.0973167681131</v>
+        <v>412.7473701155562</v>
       </c>
       <c r="D162" t="n">
-        <v>418.593673752453</v>
+        <v>396.4035989759817</v>
       </c>
       <c r="E162" t="n">
-        <v>422.746826171875</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="F162" t="n">
-        <v>38288300</v>
+        <v>70909400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B163" t="n">
-        <v>409.1519246549498</v>
+        <v>411.1338775963461</v>
       </c>
       <c r="C163" t="n">
-        <v>412.7473701155562</v>
+        <v>415.4264794885345</v>
       </c>
       <c r="D163" t="n">
-        <v>396.4035989759817</v>
+        <v>408.7834174283456</v>
       </c>
       <c r="E163" t="n">
-        <v>406.1341552734375</v>
+        <v>412.7672729492188</v>
       </c>
       <c r="F163" t="n">
-        <v>70909400</v>
+        <v>31372400</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B164" t="n">
-        <v>411.1338775963461</v>
+        <v>409.8789700952638</v>
       </c>
       <c r="C164" t="n">
-        <v>415.4264794885345</v>
+        <v>419.0816663151199</v>
       </c>
       <c r="D164" t="n">
-        <v>408.7834174283456</v>
+        <v>409.1419361803058</v>
       </c>
       <c r="E164" t="n">
-        <v>412.7672729492188</v>
+        <v>411.9505615234375</v>
       </c>
       <c r="F164" t="n">
-        <v>31372400</v>
+        <v>28066500</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B165" t="n">
-        <v>409.8789700952638</v>
+        <v>413.6437044066962</v>
       </c>
       <c r="C165" t="n">
-        <v>419.0816663151199</v>
+        <v>415.0978030853789</v>
       </c>
       <c r="D165" t="n">
-        <v>409.1419361803058</v>
+        <v>407.1500007946646</v>
       </c>
       <c r="E165" t="n">
-        <v>411.9505615234375</v>
+        <v>409.7196044921875</v>
       </c>
       <c r="F165" t="n">
-        <v>28066500</v>
+        <v>25700900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B166" t="n">
-        <v>413.6437044066962</v>
+        <v>406.3532485673598</v>
       </c>
       <c r="C166" t="n">
-        <v>415.0978030853789</v>
+        <v>416.7312052008779</v>
       </c>
       <c r="D166" t="n">
-        <v>407.1500007946646</v>
+        <v>403.4748984673602</v>
       </c>
       <c r="E166" t="n">
-        <v>409.7196044921875</v>
+        <v>412.2891845703125</v>
       </c>
       <c r="F166" t="n">
-        <v>25700900</v>
+        <v>30285900</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B167" t="n">
-        <v>406.3532485673598</v>
+        <v>418.4143764918961</v>
       </c>
       <c r="C167" t="n">
-        <v>416.7312052008779</v>
+        <v>426.2526378609755</v>
       </c>
       <c r="D167" t="n">
-        <v>403.4748984673602</v>
+        <v>417.0698495518934</v>
       </c>
       <c r="E167" t="n">
-        <v>412.2891845703125</v>
+        <v>419.0717163085938</v>
       </c>
       <c r="F167" t="n">
-        <v>30285900</v>
+        <v>34942400</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B168" t="n">
-        <v>418.4143764918961</v>
+        <v>415.7053764922729</v>
       </c>
       <c r="C168" t="n">
-        <v>426.2526378609755</v>
+        <v>416.9403619714099</v>
       </c>
       <c r="D168" t="n">
-        <v>417.0698495518934</v>
+        <v>412.3290443657605</v>
       </c>
       <c r="E168" t="n">
-        <v>419.0717163085938</v>
+        <v>413.4445190429688</v>
       </c>
       <c r="F168" t="n">
-        <v>34942400</v>
+        <v>33383800</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B169" t="n">
-        <v>415.7053764922729</v>
+        <v>406.223770451025</v>
       </c>
       <c r="C169" t="n">
-        <v>416.9403619714099</v>
+        <v>411.0243235004914</v>
       </c>
       <c r="D169" t="n">
-        <v>412.3290443657605</v>
+        <v>403.8633409907068</v>
       </c>
       <c r="E169" t="n">
-        <v>413.4445190429688</v>
+        <v>410.9944458007812</v>
       </c>
       <c r="F169" t="n">
-        <v>33383800</v>
+        <v>35657900</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B170" t="n">
-        <v>406.223770451025</v>
+        <v>412.8071154720842</v>
       </c>
       <c r="C170" t="n">
-        <v>411.0243235004914</v>
+        <v>413.8229876767416</v>
       </c>
       <c r="D170" t="n">
-        <v>403.8633409907068</v>
+        <v>404.9987623844293</v>
       </c>
       <c r="E170" t="n">
-        <v>410.9944458007812</v>
+        <v>406.1241760253906</v>
       </c>
       <c r="F170" t="n">
-        <v>35657900</v>
+        <v>38594200</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B171" t="n">
-        <v>412.8071154720842</v>
+        <v>401.5726571524119</v>
       </c>
       <c r="C171" t="n">
-        <v>413.8229876767416</v>
+        <v>404.6700902960666</v>
       </c>
       <c r="D171" t="n">
-        <v>404.9987623844293</v>
+        <v>399.4114021131033</v>
       </c>
       <c r="E171" t="n">
-        <v>406.1241760253906</v>
+        <v>403.5745239257812</v>
       </c>
       <c r="F171" t="n">
-        <v>38594200</v>
+        <v>29667100</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B172" t="n">
-        <v>401.5726571524119</v>
+        <v>402.8474630718804</v>
       </c>
       <c r="C172" t="n">
-        <v>404.6700902960666</v>
+        <v>410.1777423108794</v>
       </c>
       <c r="D172" t="n">
-        <v>399.4114021131033</v>
+        <v>399.2619871856725</v>
       </c>
       <c r="E172" t="n">
-        <v>403.5745239257812</v>
+        <v>407.7774658203125</v>
       </c>
       <c r="F172" t="n">
-        <v>29667100</v>
+        <v>27077500</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B173" t="n">
-        <v>402.8474630718804</v>
+        <v>412.5979239362014</v>
       </c>
       <c r="C173" t="n">
-        <v>410.1777423108794</v>
+        <v>426.4418454559798</v>
       </c>
       <c r="D173" t="n">
-        <v>399.2619871856725</v>
+        <v>411.2434277199191</v>
       </c>
       <c r="E173" t="n">
-        <v>407.7774658203125</v>
+        <v>420.2170715332031</v>
       </c>
       <c r="F173" t="n">
-        <v>27077500</v>
+        <v>50771200</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B174" t="n">
-        <v>412.5979239362014</v>
+        <v>414.9384827190711</v>
       </c>
       <c r="C174" t="n">
-        <v>426.4418454559798</v>
+        <v>423.4041760233977</v>
       </c>
       <c r="D174" t="n">
-        <v>411.2434277199191</v>
+        <v>413.9325494355234</v>
       </c>
       <c r="E174" t="n">
-        <v>420.2170715332031</v>
+        <v>421.83056640625</v>
       </c>
       <c r="F174" t="n">
-        <v>50771200</v>
+        <v>32564100</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B175" t="n">
-        <v>414.9384827190711</v>
+        <v>428.1648698947521</v>
       </c>
       <c r="C175" t="n">
-        <v>423.4041760233977</v>
+        <v>430.9535870211983</v>
       </c>
       <c r="D175" t="n">
-        <v>413.9325494355234</v>
+        <v>414.808990493047</v>
       </c>
       <c r="E175" t="n">
-        <v>421.83056640625</v>
+        <v>415.7352600097656</v>
       </c>
       <c r="F175" t="n">
-        <v>32564100</v>
+        <v>33018700</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,22 +4993,22 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B176" t="n">
-        <v>428.1648698947521</v>
+        <v>412.4983595724376</v>
       </c>
       <c r="C176" t="n">
-        <v>430.9535870211983</v>
+        <v>420.3963455784958</v>
       </c>
       <c r="D176" t="n">
-        <v>414.808990493047</v>
+        <v>409.6399178024174</v>
       </c>
       <c r="E176" t="n">
-        <v>415.7352600097656</v>
+        <v>419.3605346679688</v>
       </c>
       <c r="F176" t="n">
-        <v>33018700</v>
+        <v>27864000</v>
       </c>
       <c r="G176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B177" t="n">
-        <v>412.4983595724376</v>
+        <v>423.9518891931334</v>
       </c>
       <c r="C177" t="n">
-        <v>420.3963455784958</v>
+        <v>425.5388979071037</v>
       </c>
       <c r="D177" t="n">
-        <v>409.6399178024174</v>
+        <v>414.928866942535</v>
       </c>
       <c r="E177" t="n">
-        <v>419.3605346679688</v>
+        <v>418.3025207519531</v>
       </c>
       <c r="F177" t="n">
-        <v>27864000</v>
+        <v>31393500</v>
       </c>
       <c r="G177" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,25 +5045,25 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B178" t="n">
-        <v>423.9518891931334</v>
+        <v>418.7517174636334</v>
       </c>
       <c r="C178" t="n">
-        <v>425.5388979071037</v>
+        <v>423.602571187628</v>
       </c>
       <c r="D178" t="n">
-        <v>414.928866942535</v>
+        <v>415.547726934082</v>
       </c>
       <c r="E178" t="n">
-        <v>418.3025207519531</v>
+        <v>417.7835388183594</v>
       </c>
       <c r="F178" t="n">
-        <v>31393500</v>
+        <v>22390300</v>
       </c>
       <c r="G178" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B179" t="n">
-        <v>418.7517174636334</v>
+        <v>415.6475333356961</v>
       </c>
       <c r="C179" t="n">
-        <v>423.602571187628</v>
+        <v>418.9812539216563</v>
       </c>
       <c r="D179" t="n">
-        <v>415.547726934082</v>
+        <v>412.2439369671584</v>
       </c>
       <c r="E179" t="n">
-        <v>417.7835388183594</v>
+        <v>415.248291015625</v>
       </c>
       <c r="F179" t="n">
-        <v>22390300</v>
+        <v>30398000</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B180" t="n">
-        <v>415.6475333356961</v>
+        <v>410.2377382218162</v>
       </c>
       <c r="C180" t="n">
-        <v>418.9812539216563</v>
+        <v>415.15846763645</v>
       </c>
       <c r="D180" t="n">
-        <v>412.2439369671584</v>
+        <v>408.8104019854481</v>
       </c>
       <c r="E180" t="n">
-        <v>415.248291015625</v>
+        <v>411.8946228027344</v>
       </c>
       <c r="F180" t="n">
-        <v>30398000</v>
+        <v>28901500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B181" t="n">
-        <v>410.2377382218162</v>
+        <v>412.2040283766931</v>
       </c>
       <c r="C181" t="n">
-        <v>415.15846763645</v>
+        <v>428.6829856468207</v>
       </c>
       <c r="D181" t="n">
-        <v>408.8104019854481</v>
+        <v>411.8946132983843</v>
       </c>
       <c r="E181" t="n">
-        <v>411.8946228027344</v>
+        <v>426.1876831054688</v>
       </c>
       <c r="F181" t="n">
-        <v>28901500</v>
+        <v>47250500</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B182" t="n">
-        <v>412.2040283766931</v>
+        <v>431.7372486144539</v>
       </c>
       <c r="C182" t="n">
-        <v>428.6829856468207</v>
+        <v>449.4838396905727</v>
       </c>
       <c r="D182" t="n">
-        <v>411.8946132983843</v>
+        <v>431.5476031778621</v>
       </c>
       <c r="E182" t="n">
-        <v>426.1876831054688</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="F182" t="n">
-        <v>47250500</v>
+        <v>79654400</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B183" t="n">
-        <v>431.7372486144539</v>
+        <v>463.9665838370572</v>
       </c>
       <c r="C183" t="n">
-        <v>449.4838396905727</v>
+        <v>465.4438139523178</v>
       </c>
       <c r="D183" t="n">
-        <v>431.5476031778621</v>
+        <v>457.4089212477423</v>
       </c>
       <c r="E183" t="n">
-        <v>449.3940124511719</v>
+        <v>459.6546936035156</v>
       </c>
       <c r="F183" t="n">
-        <v>79654400</v>
+        <v>53628900</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B184" t="n">
-        <v>463.9665838370572</v>
+        <v>446.0403151791343</v>
       </c>
       <c r="C184" t="n">
-        <v>465.4438139523178</v>
+        <v>452.647871293284</v>
       </c>
       <c r="D184" t="n">
-        <v>457.4089212477423</v>
+        <v>439.6024225764256</v>
       </c>
       <c r="E184" t="n">
-        <v>459.6546936035156</v>
+        <v>440.4807739257812</v>
       </c>
       <c r="F184" t="n">
-        <v>53628900</v>
+        <v>37036800</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B185" t="n">
-        <v>446.0403151791343</v>
+        <v>437.6261891093521</v>
       </c>
       <c r="C185" t="n">
-        <v>452.647871293284</v>
+        <v>439.5625463944663</v>
       </c>
       <c r="D185" t="n">
-        <v>439.6024225764256</v>
+        <v>423.4528579325815</v>
       </c>
       <c r="E185" t="n">
-        <v>440.4807739257812</v>
+        <v>426.5370483398438</v>
       </c>
       <c r="F185" t="n">
-        <v>37036800</v>
+        <v>39037000</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B186" t="n">
-        <v>437.6261891093521</v>
+        <v>434.9911260035114</v>
       </c>
       <c r="C186" t="n">
-        <v>439.5625463944663</v>
+        <v>435.3304835003211</v>
       </c>
       <c r="D186" t="n">
-        <v>423.4528579325815</v>
+        <v>425.6087943627414</v>
       </c>
       <c r="E186" t="n">
-        <v>426.5370483398438</v>
+        <v>427.2456970214844</v>
       </c>
       <c r="F186" t="n">
-        <v>39037000</v>
+        <v>26899500</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B187" t="n">
-        <v>434.9911260035114</v>
+        <v>427.5351398188391</v>
       </c>
       <c r="C187" t="n">
-        <v>435.3304835003211</v>
+        <v>428.6630214075295</v>
       </c>
       <c r="D187" t="n">
-        <v>425.6087943627414</v>
+        <v>413.6213308264138</v>
       </c>
       <c r="E187" t="n">
-        <v>427.2456970214844</v>
+        <v>415.8870849609375</v>
       </c>
       <c r="F187" t="n">
-        <v>26899500</v>
+        <v>34782200</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B188" t="n">
-        <v>427.5351398188391</v>
+        <v>413.3618539280056</v>
       </c>
       <c r="C188" t="n">
-        <v>428.6630214075295</v>
+        <v>416.3761684433352</v>
       </c>
       <c r="D188" t="n">
-        <v>413.6213308264138</v>
+        <v>407.7923215775376</v>
       </c>
       <c r="E188" t="n">
-        <v>415.8870849609375</v>
+        <v>410.9663391113281</v>
       </c>
       <c r="F188" t="n">
-        <v>34782200</v>
+        <v>32086700</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B189" t="n">
-        <v>413.3618539280056</v>
+        <v>408.2614433672717</v>
       </c>
       <c r="C189" t="n">
-        <v>416.3761684433352</v>
+        <v>411.2059125875929</v>
       </c>
       <c r="D189" t="n">
-        <v>407.7923215775376</v>
+        <v>397.7312786929967</v>
       </c>
       <c r="E189" t="n">
-        <v>410.9663391113281</v>
+        <v>402.6520080566406</v>
       </c>
       <c r="F189" t="n">
-        <v>32086700</v>
+        <v>35317300</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B190" t="n">
-        <v>408.2614433672717</v>
+        <v>397.8011087010324</v>
       </c>
       <c r="C190" t="n">
-        <v>411.2059125875929</v>
+        <v>404.2789346443135</v>
       </c>
       <c r="D190" t="n">
-        <v>397.7312786929967</v>
+        <v>396.4137363631365</v>
       </c>
       <c r="E190" t="n">
-        <v>402.6520080566406</v>
+        <v>396.6133422851562</v>
       </c>
       <c r="F190" t="n">
-        <v>35317300</v>
+        <v>32576000</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B191" t="n">
-        <v>397.8011087010324</v>
+        <v>394.4674120274286</v>
       </c>
       <c r="C191" t="n">
-        <v>404.2789346443135</v>
+        <v>396.1043451719433</v>
       </c>
       <c r="D191" t="n">
-        <v>396.4137363631365</v>
+        <v>383.278483574852</v>
       </c>
       <c r="E191" t="n">
-        <v>396.6133422851562</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F191" t="n">
-        <v>32576000</v>
+        <v>47224100</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B192" t="n">
-        <v>394.4674120274286</v>
+        <v>390.6945042817559</v>
       </c>
       <c r="C192" t="n">
-        <v>396.1043451719433</v>
+        <v>391.003919361718</v>
       </c>
       <c r="D192" t="n">
-        <v>383.278483574852</v>
+        <v>381.55171206616</v>
       </c>
       <c r="E192" t="n">
-        <v>389.6065673828125</v>
+        <v>390.0057983398438</v>
       </c>
       <c r="F192" t="n">
-        <v>47224100</v>
+        <v>34865800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B193" t="n">
-        <v>390.6945042817559</v>
+        <v>396.0544203764563</v>
       </c>
       <c r="C193" t="n">
-        <v>391.003919361718</v>
+        <v>400.9951317570601</v>
       </c>
       <c r="D193" t="n">
-        <v>381.55171206616</v>
+        <v>392.1118605058895</v>
       </c>
       <c r="E193" t="n">
-        <v>390.0057983398438</v>
+        <v>399.0088806152344</v>
       </c>
       <c r="F193" t="n">
-        <v>34865800</v>
+        <v>32266400</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B194" t="n">
-        <v>396.0544203764563</v>
+        <v>395.0463355104342</v>
       </c>
       <c r="C194" t="n">
-        <v>400.9951317570601</v>
+        <v>396.094350419825</v>
       </c>
       <c r="D194" t="n">
-        <v>392.1118605058895</v>
+        <v>389.9559121071713</v>
       </c>
       <c r="E194" t="n">
-        <v>399.0088806152344</v>
+        <v>393.0899963378906</v>
       </c>
       <c r="F194" t="n">
-        <v>32266400</v>
+        <v>31506800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B195" t="n">
-        <v>395.0463355104342</v>
+        <v>389.5167169534323</v>
       </c>
       <c r="C195" t="n">
-        <v>396.094350419825</v>
+        <v>389.6364865987809</v>
       </c>
       <c r="D195" t="n">
-        <v>389.9559121071713</v>
+        <v>376.6110198431126</v>
       </c>
       <c r="E195" t="n">
-        <v>393.0899963378906</v>
+        <v>378.1980285644531</v>
       </c>
       <c r="F195" t="n">
-        <v>31506800</v>
+        <v>41987800</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B196" t="n">
-        <v>389.5167169534323</v>
+        <v>377.1100854858111</v>
       </c>
       <c r="C196" t="n">
-        <v>389.6364865987809</v>
+        <v>380.6534028700893</v>
       </c>
       <c r="D196" t="n">
-        <v>376.6110198431126</v>
+        <v>372.5786075934489</v>
       </c>
       <c r="E196" t="n">
-        <v>378.1980285644531</v>
+        <v>378.6871032714844</v>
       </c>
       <c r="F196" t="n">
-        <v>41987800</v>
+        <v>59714200</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B197" t="n">
-        <v>377.1100854858111</v>
+        <v>375.0339909424311</v>
       </c>
       <c r="C197" t="n">
-        <v>380.6534028700893</v>
+        <v>380.9129385065033</v>
       </c>
       <c r="D197" t="n">
-        <v>372.5786075934489</v>
+        <v>366.3802985575179</v>
       </c>
       <c r="E197" t="n">
-        <v>378.6871032714844</v>
+        <v>366.6497802734375</v>
       </c>
       <c r="F197" t="n">
-        <v>59714200</v>
+        <v>45171100</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B198" t="n">
-        <v>375.0339909424311</v>
+        <v>371.6802994138851</v>
       </c>
       <c r="C198" t="n">
-        <v>380.9129385065033</v>
+        <v>376.5112013539488</v>
       </c>
       <c r="D198" t="n">
-        <v>366.3802985575179</v>
+        <v>369.9735210485466</v>
       </c>
       <c r="E198" t="n">
-        <v>366.6497802734375</v>
+        <v>373.2373657226562</v>
       </c>
       <c r="F198" t="n">
-        <v>45171100</v>
+        <v>40647600</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B199" t="n">
-        <v>371.6802994138851</v>
+        <v>370.8718509685315</v>
       </c>
       <c r="C199" t="n">
-        <v>376.5112013539488</v>
+        <v>378.1681135077346</v>
       </c>
       <c r="D199" t="n">
-        <v>369.9735210485466</v>
+        <v>364.0946004167936</v>
       </c>
       <c r="E199" t="n">
-        <v>373.2373657226562</v>
+        <v>364.7733154296875</v>
       </c>
       <c r="F199" t="n">
-        <v>40647600</v>
+        <v>44509900</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B200" t="n">
-        <v>370.8718509685315</v>
+        <v>362.0883479855026</v>
       </c>
       <c r="C200" t="n">
-        <v>378.1681135077346</v>
+        <v>363.5456265920902</v>
       </c>
       <c r="D200" t="n">
-        <v>364.0946004167936</v>
+        <v>348.5438690238404</v>
       </c>
       <c r="E200" t="n">
-        <v>364.7733154296875</v>
+        <v>352.1670227050781</v>
       </c>
       <c r="F200" t="n">
-        <v>44509900</v>
+        <v>66179000</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B201" t="n">
-        <v>362.0883479855026</v>
+        <v>356.4789138154501</v>
       </c>
       <c r="C201" t="n">
-        <v>363.5456265920902</v>
+        <v>375.9023402058053</v>
       </c>
       <c r="D201" t="n">
-        <v>348.5438690238404</v>
+        <v>354.762144454129</v>
       </c>
       <c r="E201" t="n">
-        <v>352.1670227050781</v>
+        <v>372.2691955566406</v>
       </c>
       <c r="F201" t="n">
-        <v>66179000</v>
+        <v>186201600</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B202" t="n">
-        <v>356.4789138154501</v>
+        <v>376.790685328561</v>
       </c>
       <c r="C202" t="n">
-        <v>375.9023402058053</v>
+        <v>379.7850483907747</v>
       </c>
       <c r="D202" t="n">
-        <v>354.762144454129</v>
+        <v>359.2237492715265</v>
       </c>
       <c r="E202" t="n">
-        <v>372.2691955566406</v>
+        <v>367.8774719238281</v>
       </c>
       <c r="F202" t="n">
-        <v>186201600</v>
+        <v>51229900</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B203" t="n">
-        <v>376.790685328561</v>
+        <v>370.3328407149792</v>
       </c>
       <c r="C203" t="n">
-        <v>379.7850483907747</v>
+        <v>373.4469734227558</v>
       </c>
       <c r="D203" t="n">
-        <v>359.2237492715265</v>
+        <v>366.7595808670141</v>
       </c>
       <c r="E203" t="n">
-        <v>367.8774719238281</v>
+        <v>372.319091796875</v>
       </c>
       <c r="F203" t="n">
-        <v>51229900</v>
+        <v>44945700</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B204" t="n">
-        <v>370.3328407149792</v>
+        <v>380.1144231011508</v>
       </c>
       <c r="C204" t="n">
-        <v>373.4469734227558</v>
+        <v>388.099391438806</v>
       </c>
       <c r="D204" t="n">
-        <v>366.7595808670141</v>
+        <v>374.1856121338598</v>
       </c>
       <c r="E204" t="n">
-        <v>372.319091796875</v>
+        <v>383.5579528808594</v>
       </c>
       <c r="F204" t="n">
-        <v>44945700</v>
+        <v>48065800</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B205" t="n">
-        <v>380.1144231011508</v>
+        <v>383.7575696594082</v>
       </c>
       <c r="C205" t="n">
-        <v>388.099391438806</v>
+        <v>391.4630649298244</v>
       </c>
       <c r="D205" t="n">
-        <v>374.1856121338598</v>
+        <v>382.9790365046874</v>
       </c>
       <c r="E205" t="n">
-        <v>383.5579528808594</v>
+        <v>389.7562561035156</v>
       </c>
       <c r="F205" t="n">
-        <v>48065800</v>
+        <v>42128900</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B206" t="n">
-        <v>383.7575696594082</v>
+        <v>386.3127602401041</v>
       </c>
       <c r="C206" t="n">
-        <v>391.4630649298244</v>
+        <v>388.418780928489</v>
       </c>
       <c r="D206" t="n">
-        <v>382.9790365046874</v>
+        <v>380.5036887115837</v>
       </c>
       <c r="E206" t="n">
-        <v>389.7562561035156</v>
+        <v>386.0133056640625</v>
       </c>
       <c r="F206" t="n">
-        <v>42128900</v>
+        <v>34224500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B207" t="n">
-        <v>386.3127602401041</v>
+        <v>391.7525106425778</v>
       </c>
       <c r="C207" t="n">
-        <v>388.418780928489</v>
+        <v>394.8267404517197</v>
       </c>
       <c r="D207" t="n">
-        <v>380.5036887115837</v>
+        <v>387.4905448392632</v>
       </c>
       <c r="E207" t="n">
-        <v>386.0133056640625</v>
+        <v>388.109375</v>
       </c>
       <c r="F207" t="n">
-        <v>34224500</v>
+        <v>29297500</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B208" t="n">
-        <v>391.7525106425778</v>
+        <v>383.3084264217563</v>
       </c>
       <c r="C208" t="n">
-        <v>394.8267404517197</v>
+        <v>384.5860201500421</v>
       </c>
       <c r="D208" t="n">
-        <v>387.4905448392632</v>
+        <v>380.6134873969759</v>
       </c>
       <c r="E208" t="n">
-        <v>388.109375</v>
+        <v>382.6197204589844</v>
       </c>
       <c r="F208" t="n">
-        <v>29297500</v>
+        <v>25908300</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B209" t="n">
-        <v>383.3084264217563</v>
+        <v>373.7464342011831</v>
       </c>
       <c r="C209" t="n">
-        <v>384.5860201500421</v>
+        <v>383.927250494608</v>
       </c>
       <c r="D209" t="n">
-        <v>380.6134873969759</v>
+        <v>372.6484949692805</v>
       </c>
       <c r="E209" t="n">
-        <v>382.6197204589844</v>
+        <v>383.6377868652344</v>
       </c>
       <c r="F209" t="n">
-        <v>25908300</v>
+        <v>31083200</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B210" t="n">
-        <v>373.7464342011831</v>
+        <v>387.071312236775</v>
       </c>
       <c r="C210" t="n">
-        <v>383.927250494608</v>
+        <v>391.1736053926777</v>
       </c>
       <c r="D210" t="n">
-        <v>372.6484949692805</v>
+        <v>380.783162110783</v>
       </c>
       <c r="E210" t="n">
-        <v>383.6377868652344</v>
+        <v>384.3764038085938</v>
       </c>
       <c r="F210" t="n">
-        <v>31083200</v>
+        <v>24644600</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B211" t="n">
-        <v>387.071312236775</v>
+        <v>387.0214381132942</v>
       </c>
       <c r="C211" t="n">
-        <v>391.1736053926777</v>
+        <v>392.9103462310944</v>
       </c>
       <c r="D211" t="n">
-        <v>380.783162110783</v>
+        <v>383.4281962321871</v>
       </c>
       <c r="E211" t="n">
-        <v>384.3764038085938</v>
+        <v>390.2553405761719</v>
       </c>
       <c r="F211" t="n">
-        <v>24644600</v>
+        <v>28914900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B212" t="n">
-        <v>387.0214381132942</v>
+        <v>382.1007052927433</v>
       </c>
       <c r="C212" t="n">
-        <v>392.9103462310944</v>
+        <v>387.460610424238</v>
       </c>
       <c r="D212" t="n">
-        <v>383.4281962321871</v>
+        <v>377.93852713765</v>
       </c>
       <c r="E212" t="n">
-        <v>390.2553405761719</v>
+        <v>384.2067260742188</v>
       </c>
       <c r="F212" t="n">
-        <v>28914900</v>
+        <v>27863900</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B213" t="n">
-        <v>382.1007052927433</v>
+        <v>387.0713224899768</v>
       </c>
       <c r="C213" t="n">
-        <v>387.460610424238</v>
+        <v>398.2103568181361</v>
       </c>
       <c r="D213" t="n">
-        <v>377.93852713765</v>
+        <v>385.6739591427675</v>
       </c>
       <c r="E213" t="n">
-        <v>384.2067260742188</v>
+        <v>394.8866271972656</v>
       </c>
       <c r="F213" t="n">
-        <v>27863900</v>
+        <v>36253700</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B214" t="n">
-        <v>387.0713224899768</v>
+        <v>397.5615778418718</v>
       </c>
       <c r="C214" t="n">
-        <v>398.2103568181361</v>
+        <v>405.2271399033625</v>
       </c>
       <c r="D214" t="n">
-        <v>385.6739591427675</v>
+        <v>391.3133305596497</v>
       </c>
       <c r="E214" t="n">
-        <v>394.8866271972656</v>
+        <v>400.3463439941406</v>
       </c>
       <c r="F214" t="n">
-        <v>36253700</v>
+        <v>37047400</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B215" t="n">
-        <v>397.5615778418718</v>
+        <v>394.1180409920291</v>
       </c>
       <c r="C215" t="n">
-        <v>405.2271399033625</v>
+        <v>397.6414373419786</v>
       </c>
       <c r="D215" t="n">
-        <v>391.3133305596497</v>
+        <v>388.6583483977542</v>
       </c>
       <c r="E215" t="n">
-        <v>400.3463439941406</v>
+        <v>393.0800170898438</v>
       </c>
       <c r="F215" t="n">
-        <v>37047400</v>
+        <v>33049800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B216" t="n">
-        <v>394.1180409920291</v>
+        <v>390.6745569462133</v>
       </c>
       <c r="C216" t="n">
-        <v>397.6414373419786</v>
+        <v>402.4224305318551</v>
       </c>
       <c r="D216" t="n">
-        <v>388.6583483977542</v>
+        <v>388.9178541819168</v>
       </c>
       <c r="E216" t="n">
-        <v>393.0800170898438</v>
+        <v>401.5341186523438</v>
       </c>
       <c r="F216" t="n">
-        <v>33049800</v>
+        <v>27915800</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B217" t="n">
-        <v>390.6745569462133</v>
+        <v>398.0606303262699</v>
       </c>
       <c r="C217" t="n">
-        <v>402.4224305318551</v>
+        <v>400.7156358198418</v>
       </c>
       <c r="D217" t="n">
-        <v>388.9178541819168</v>
+        <v>395.5753188038175</v>
       </c>
       <c r="E217" t="n">
-        <v>401.5341186523438</v>
+        <v>397.0026245117188</v>
       </c>
       <c r="F217" t="n">
-        <v>27915800</v>
+        <v>24126600</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B218" t="n">
-        <v>398.0606303262699</v>
+        <v>398.8291961465565</v>
       </c>
       <c r="C218" t="n">
-        <v>400.7156358198418</v>
+        <v>400.246541441447</v>
       </c>
       <c r="D218" t="n">
-        <v>395.5753188038175</v>
+        <v>386.2329133568751</v>
       </c>
       <c r="E218" t="n">
-        <v>397.0026245117188</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F218" t="n">
-        <v>24126600</v>
+        <v>28142500</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B219" t="n">
-        <v>398.8291961465565</v>
+        <v>389.237256596515</v>
       </c>
       <c r="C219" t="n">
-        <v>400.246541441447</v>
+        <v>391.0438532115061</v>
       </c>
       <c r="D219" t="n">
-        <v>386.2329133568751</v>
+        <v>376.6809075284274</v>
       </c>
       <c r="E219" t="n">
-        <v>389.6065673828125</v>
+        <v>380.8630065917969</v>
       </c>
       <c r="F219" t="n">
-        <v>28142500</v>
+        <v>30351800</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B220" t="n">
-        <v>389.237256596515</v>
+        <v>386.3227418757343</v>
       </c>
       <c r="C220" t="n">
-        <v>391.0438532115061</v>
+        <v>388.299032528898</v>
       </c>
       <c r="D220" t="n">
-        <v>376.6809075284274</v>
+        <v>379.9347732203772</v>
       </c>
       <c r="E220" t="n">
-        <v>380.8630065917969</v>
+        <v>380.9828186035156</v>
       </c>
       <c r="F220" t="n">
-        <v>30351800</v>
+        <v>27659400</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B221" t="n">
-        <v>386.3227418757343</v>
+        <v>389.3470355932277</v>
       </c>
       <c r="C221" t="n">
-        <v>388.299032528898</v>
+        <v>393.4593197982184</v>
       </c>
       <c r="D221" t="n">
-        <v>379.9347732203772</v>
+        <v>387.2609663085435</v>
       </c>
       <c r="E221" t="n">
-        <v>380.9828186035156</v>
+        <v>388.368896484375</v>
       </c>
       <c r="F221" t="n">
-        <v>27659400</v>
+        <v>27856200</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B222" t="n">
-        <v>389.3470355932277</v>
+        <v>392.4212554523594</v>
       </c>
       <c r="C222" t="n">
-        <v>393.4593197982184</v>
+        <v>399.567805457337</v>
       </c>
       <c r="D222" t="n">
-        <v>387.2609663085435</v>
+        <v>390.5647345556998</v>
       </c>
       <c r="E222" t="n">
-        <v>388.368896484375</v>
+        <v>392.6109008789062</v>
       </c>
       <c r="F222" t="n">
-        <v>27856200</v>
+        <v>32367500</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B223" t="n">
-        <v>392.4212554523594</v>
+        <v>392.6607942930367</v>
       </c>
       <c r="C223" t="n">
-        <v>399.567805457337</v>
+        <v>400.4960502148319</v>
       </c>
       <c r="D223" t="n">
-        <v>390.5647345556998</v>
+        <v>388.0095467898306</v>
       </c>
       <c r="E223" t="n">
-        <v>392.6109008789062</v>
+        <v>389.8061828613281</v>
       </c>
       <c r="F223" t="n">
-        <v>32367500</v>
+        <v>47209000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B224" t="n">
-        <v>392.6607942930367</v>
+        <v>437.0772008696947</v>
       </c>
       <c r="C224" t="n">
-        <v>400.4960502148319</v>
+        <v>457.8281459885008</v>
       </c>
       <c r="D224" t="n">
-        <v>388.0095467898306</v>
+        <v>431.6274684759506</v>
       </c>
       <c r="E224" t="n">
-        <v>389.8061828613281</v>
+        <v>450.2524108886719</v>
       </c>
       <c r="F224" t="n">
-        <v>47209000</v>
+        <v>110160700</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B225" t="n">
-        <v>437.0772008696947</v>
+        <v>449.1544591210436</v>
       </c>
       <c r="C225" t="n">
-        <v>457.8281459885008</v>
+        <v>465.962813447145</v>
       </c>
       <c r="D225" t="n">
-        <v>431.6274684759506</v>
+        <v>448.4857046349594</v>
       </c>
       <c r="E225" t="n">
-        <v>450.2524108886719</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="F225" t="n">
-        <v>110160700</v>
+        <v>60846000</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B226" t="n">
-        <v>449.1544591210436</v>
+        <v>475.2353605631651</v>
       </c>
       <c r="C226" t="n">
-        <v>465.962813447145</v>
+        <v>490.7261876465455</v>
       </c>
       <c r="D226" t="n">
-        <v>448.4857046349594</v>
+        <v>474.1074789501303</v>
       </c>
       <c r="E226" t="n">
-        <v>463.8468017578125</v>
+        <v>486.7337036132812</v>
       </c>
       <c r="F226" t="n">
-        <v>60846000</v>
+        <v>66762100</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B227" t="n">
-        <v>475.2353605631651</v>
+        <v>479.9964078184842</v>
       </c>
       <c r="C227" t="n">
-        <v>490.7261876465455</v>
+        <v>498.5015806515744</v>
       </c>
       <c r="D227" t="n">
-        <v>474.1074789501303</v>
+        <v>478.2696778930625</v>
       </c>
       <c r="E227" t="n">
-        <v>486.7337036132812</v>
+        <v>491.884033203125</v>
       </c>
       <c r="F227" t="n">
-        <v>66762100</v>
+        <v>50455500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B228" t="n">
-        <v>479.9964078184842</v>
+        <v>495.4273384327132</v>
       </c>
       <c r="C228" t="n">
-        <v>498.5015806515744</v>
+        <v>497.3038108374591</v>
       </c>
       <c r="D228" t="n">
-        <v>478.2696778930625</v>
+        <v>484.7674131728324</v>
       </c>
       <c r="E228" t="n">
-        <v>491.884033203125</v>
+        <v>486.5440673828125</v>
       </c>
       <c r="F228" t="n">
-        <v>50455500</v>
+        <v>33388900</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B229" t="n">
-        <v>495.4273384327132</v>
+        <v>487.6319998350186</v>
       </c>
       <c r="C229" t="n">
-        <v>497.3038108374591</v>
+        <v>500.6175637248969</v>
       </c>
       <c r="D229" t="n">
-        <v>484.7674131728324</v>
+        <v>487.6020574235835</v>
       </c>
       <c r="E229" t="n">
-        <v>486.5440673828125</v>
+        <v>498.9207458496094</v>
       </c>
       <c r="F229" t="n">
-        <v>33388900</v>
+        <v>36441500</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B230" t="n">
-        <v>487.6319998350186</v>
+        <v>498.2719734340298</v>
       </c>
       <c r="C230" t="n">
-        <v>500.6175637248969</v>
+        <v>504.2307569931746</v>
       </c>
       <c r="D230" t="n">
-        <v>487.6020574235835</v>
+        <v>497.7928948509335</v>
       </c>
       <c r="E230" t="n">
-        <v>498.9207458496094</v>
+        <v>499.0505065917969</v>
       </c>
       <c r="F230" t="n">
-        <v>36441500</v>
+        <v>28846200</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B231" t="n">
-        <v>498.2719734340298</v>
+        <v>502.4940586092805</v>
       </c>
       <c r="C231" t="n">
-        <v>504.2307569931746</v>
+        <v>512.7647021753171</v>
       </c>
       <c r="D231" t="n">
-        <v>497.7928948509335</v>
+        <v>501.326243590453</v>
       </c>
       <c r="E231" t="n">
-        <v>499.0505065917969</v>
+        <v>505.109130859375</v>
       </c>
       <c r="F231" t="n">
-        <v>28846200</v>
+        <v>31206100</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B232" t="n">
-        <v>502.4940586092805</v>
+        <v>503.3823542433026</v>
       </c>
       <c r="C232" t="n">
-        <v>512.7647021753171</v>
+        <v>504.3804752506704</v>
       </c>
       <c r="D232" t="n">
-        <v>501.326243590453</v>
+        <v>498.6113370464939</v>
       </c>
       <c r="E232" t="n">
-        <v>505.109130859375</v>
+        <v>502.8633422851562</v>
       </c>
       <c r="F232" t="n">
-        <v>31206100</v>
+        <v>23049800</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B233" t="n">
-        <v>503.3823542433026</v>
+        <v>499.0505227551261</v>
       </c>
       <c r="C233" t="n">
-        <v>504.3804752506704</v>
+        <v>500.557695253814</v>
       </c>
       <c r="D233" t="n">
-        <v>498.6113370464939</v>
+        <v>490.5964364344239</v>
       </c>
       <c r="E233" t="n">
-        <v>502.8633422851562</v>
+        <v>491.5047302246094</v>
       </c>
       <c r="F233" t="n">
-        <v>23049800</v>
+        <v>29001500</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B234" t="n">
-        <v>499.0505227551261</v>
+        <v>492.3431478695614</v>
       </c>
       <c r="C234" t="n">
-        <v>500.557695253814</v>
+        <v>500.3979918654044</v>
       </c>
       <c r="D234" t="n">
-        <v>490.5964364344239</v>
+        <v>492.0836571155829</v>
       </c>
       <c r="E234" t="n">
-        <v>491.5047302246094</v>
+        <v>495.9463806152344</v>
       </c>
       <c r="F234" t="n">
-        <v>29001500</v>
+        <v>23039000</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B235" t="n">
-        <v>492.3431478695614</v>
+        <v>495.427334377905</v>
       </c>
       <c r="C235" t="n">
-        <v>500.3979918654044</v>
+        <v>499.0705004655026</v>
       </c>
       <c r="D235" t="n">
-        <v>492.0836571155829</v>
+        <v>492.991947114923</v>
       </c>
       <c r="E235" t="n">
-        <v>495.9463806152344</v>
+        <v>494.4691467285156</v>
       </c>
       <c r="F235" t="n">
-        <v>23039000</v>
+        <v>16217600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B236" t="n">
-        <v>495.427334377905</v>
+        <v>489.2190622628328</v>
       </c>
       <c r="C236" t="n">
-        <v>499.0705004655026</v>
+        <v>491.7343163235842</v>
       </c>
       <c r="D236" t="n">
-        <v>492.991947114923</v>
+        <v>477.5110914717105</v>
       </c>
       <c r="E236" t="n">
-        <v>494.4691467285156</v>
+        <v>479.4474487304688</v>
       </c>
       <c r="F236" t="n">
-        <v>16217600</v>
+        <v>29635800</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B237" t="n">
-        <v>489.2190622628328</v>
+        <v>480.6352093836093</v>
       </c>
       <c r="C237" t="n">
-        <v>491.7343163235842</v>
+        <v>483.3600603013466</v>
       </c>
       <c r="D237" t="n">
-        <v>477.5110914717105</v>
+        <v>476.2534434403709</v>
       </c>
       <c r="E237" t="n">
-        <v>479.4474487304688</v>
+        <v>480.7250366210938</v>
       </c>
       <c r="F237" t="n">
-        <v>29635800</v>
+        <v>24087600</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,22 +6605,22 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B238" t="n">
-        <v>480.6352093836093</v>
+        <v>479.1679704739861</v>
       </c>
       <c r="C238" t="n">
-        <v>483.3600603013466</v>
+        <v>488.3806080919379</v>
       </c>
       <c r="D238" t="n">
-        <v>476.2534434403709</v>
+        <v>478.4592826108848</v>
       </c>
       <c r="E238" t="n">
-        <v>480.7250366210938</v>
+        <v>483.3999938964844</v>
       </c>
       <c r="F238" t="n">
-        <v>24087600</v>
+        <v>19961900</v>
       </c>
       <c r="G238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B239" t="n">
-        <v>479.1679704739861</v>
+        <v>483.2999877929688</v>
       </c>
       <c r="C239" t="n">
-        <v>488.3806080919379</v>
+        <v>484.1600036621094</v>
       </c>
       <c r="D239" t="n">
-        <v>478.4592826108848</v>
+        <v>479.5</v>
       </c>
       <c r="E239" t="n">
-        <v>483.3999938964844</v>
+        <v>481.1499938964844</v>
       </c>
       <c r="F239" t="n">
-        <v>19961900</v>
+        <v>20020800</v>
       </c>
       <c r="G239" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,25 +6657,25 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B240" t="n">
-        <v>483.2999877929688</v>
+        <v>479.8800048828125</v>
       </c>
       <c r="C240" t="n">
-        <v>484.1600036621094</v>
+        <v>486.3599853515625</v>
       </c>
       <c r="D240" t="n">
-        <v>479.5</v>
+        <v>478.5299987792969</v>
       </c>
       <c r="E240" t="n">
-        <v>481.1499938964844</v>
+        <v>483.239990234375</v>
       </c>
       <c r="F240" t="n">
-        <v>20020800</v>
+        <v>22510800</v>
       </c>
       <c r="G240" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B241" t="n">
-        <v>479.8800048828125</v>
+        <v>483.2099914550781</v>
       </c>
       <c r="C241" t="n">
-        <v>486.3599853515625</v>
+        <v>490.6099853515625</v>
       </c>
       <c r="D241" t="n">
-        <v>478.5299987792969</v>
+        <v>481.8599853515625</v>
       </c>
       <c r="E241" t="n">
-        <v>483.239990234375</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="F241" t="n">
-        <v>22510800</v>
+        <v>17230800</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B242" t="n">
-        <v>483.2099914550781</v>
+        <v>485.4400024414062</v>
       </c>
       <c r="C242" t="n">
-        <v>490.6099853515625</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="D242" t="n">
-        <v>481.8599853515625</v>
+        <v>484.2999877929688</v>
       </c>
       <c r="E242" t="n">
-        <v>487.3099975585938</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="F242" t="n">
-        <v>17230800</v>
+        <v>19519000</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B243" t="n">
-        <v>485.4400024414062</v>
+        <v>487.8500061035156</v>
       </c>
       <c r="C243" t="n">
-        <v>492.4400024414062</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="D243" t="n">
-        <v>484.2999877929688</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="E243" t="n">
-        <v>491.7099914550781</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="F243" t="n">
-        <v>19519000</v>
+        <v>20758900</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B244" t="n">
-        <v>487.8500061035156</v>
+        <v>494.8800048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>497.3999938964844</v>
+        <v>506.4800109863281</v>
       </c>
       <c r="D244" t="n">
-        <v>487.3099975585938</v>
+        <v>490.0799865722656</v>
       </c>
       <c r="E244" t="n">
-        <v>496.3699951171875</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="F244" t="n">
-        <v>20758900</v>
+        <v>28688800</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B245" t="n">
-        <v>494.8800048828125</v>
+        <v>505.3299865722656</v>
       </c>
       <c r="C245" t="n">
-        <v>506.4800109863281</v>
+        <v>517.780029296875</v>
       </c>
       <c r="D245" t="n">
-        <v>490.0799865722656</v>
+        <v>504.8699951171875</v>
       </c>
       <c r="E245" t="n">
-        <v>505.0599975585938</v>
+        <v>513.530029296875</v>
       </c>
       <c r="F245" t="n">
-        <v>28688800</v>
+        <v>29207300</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B246" t="n">
-        <v>505.3299865722656</v>
+        <v>510.3800048828125</v>
       </c>
       <c r="C246" t="n">
-        <v>517.780029296875</v>
+        <v>512.1900024414062</v>
       </c>
       <c r="D246" t="n">
-        <v>504.8699951171875</v>
+        <v>506.3900146484375</v>
       </c>
       <c r="E246" t="n">
-        <v>513.530029296875</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="F246" t="n">
-        <v>29207300</v>
+        <v>27208900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B247" t="n">
-        <v>510.3800048828125</v>
+        <v>497.5199890136719</v>
       </c>
       <c r="C247" t="n">
-        <v>512.1900024414062</v>
+        <v>505.9700012207031</v>
       </c>
       <c r="D247" t="n">
-        <v>506.3900146484375</v>
+        <v>496.7799987792969</v>
       </c>
       <c r="E247" t="n">
-        <v>507.2900085449219</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="F247" t="n">
-        <v>27208900</v>
+        <v>21046900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B248" t="n">
-        <v>497.5199890136719</v>
+        <v>499.8500061035156</v>
       </c>
       <c r="C248" t="n">
-        <v>505.9700012207031</v>
+        <v>500.2699890136719</v>
       </c>
       <c r="D248" t="n">
-        <v>496.7799987792969</v>
+        <v>493.8099975585938</v>
       </c>
       <c r="E248" t="n">
-        <v>501.0199890136719</v>
+        <v>496.8200073242188</v>
       </c>
       <c r="F248" t="n">
-        <v>21046900</v>
+        <v>15336100</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B249" t="n">
-        <v>499.8500061035156</v>
+        <v>501.6600036621094</v>
       </c>
       <c r="C249" t="n">
-        <v>500.2699890136719</v>
+        <v>515.6500244140625</v>
       </c>
       <c r="D249" t="n">
-        <v>493.8099975585938</v>
+        <v>500.7999877929688</v>
       </c>
       <c r="E249" t="n">
-        <v>496.8200073242188</v>
+        <v>510.1199951171875</v>
       </c>
       <c r="F249" t="n">
-        <v>15336100</v>
+        <v>24125900</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B250" t="n">
-        <v>501.6600036621094</v>
+        <v>510</v>
       </c>
       <c r="C250" t="n">
-        <v>515.6500244140625</v>
+        <v>511</v>
       </c>
       <c r="D250" t="n">
-        <v>500.7999877929688</v>
+        <v>499.3599853515625</v>
       </c>
       <c r="E250" t="n">
-        <v>510.1199951171875</v>
+        <v>499.7000122070312</v>
       </c>
       <c r="F250" t="n">
-        <v>24125900</v>
+        <v>18101800</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B251" t="n">
-        <v>510</v>
+        <v>493.010009765625</v>
       </c>
       <c r="C251" t="n">
-        <v>511</v>
+        <v>495.1900024414062</v>
       </c>
       <c r="D251" t="n">
-        <v>499.3599853515625</v>
+        <v>490.1499938964844</v>
       </c>
       <c r="E251" t="n">
-        <v>499.7000122070312</v>
+        <v>493.9500122070312</v>
       </c>
       <c r="F251" t="n">
-        <v>18074400</v>
+        <v>18882300</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,14 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46273</v>
-      </c>
-      <c r="B252" t="inlineStr"/>
-      <c r="C252" t="inlineStr"/>
-      <c r="D252" t="inlineStr"/>
-      <c r="E252" t="inlineStr"/>
+        <v>46274</v>
+      </c>
+      <c r="B252" t="n">
+        <v>493.0700073242188</v>
+      </c>
+      <c r="C252" t="n">
+        <v>494.3900146484375</v>
+      </c>
+      <c r="D252" t="n">
+        <v>489.7999877929688</v>
+      </c>
+      <c r="E252" t="n">
+        <v>491.6499938964844</v>
+      </c>
       <c r="F252" t="n">
-        <v>18684730</v>
+        <v>12875900</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10960,37 +10968,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>491.65</v>
+      </c>
+      <c r="D2" t="n">
         <v>493.95</v>
       </c>
-      <c r="D2" t="n">
-        <v>499.7</v>
-      </c>
       <c r="E2" t="n">
-        <v>493.01</v>
+        <v>493.07</v>
       </c>
       <c r="F2" t="n">
-        <v>495.19</v>
+        <v>494.39</v>
       </c>
       <c r="G2" t="n">
-        <v>490.15</v>
+        <v>489.8</v>
       </c>
       <c r="H2" t="n">
-        <v>18684730</v>
+        <v>12778304</v>
       </c>
       <c r="I2" t="n">
-        <v>36859408</v>
+        <v>36594769</v>
       </c>
       <c r="J2" t="n">
-        <v>3667848331264</v>
+        <v>3650769387520</v>
       </c>
       <c r="K2" t="n">
-        <v>27.533445</v>
+        <v>27.543417</v>
       </c>
       <c r="L2" t="n">
-        <v>20.95381</v>
+        <v>20.85624</v>
       </c>
       <c r="M2" t="n">
-        <v>17.94</v>
+        <v>17.85</v>
       </c>
       <c r="N2" t="n">
         <v>553.72</v>
@@ -11002,7 +11010,7 @@
         <v>1.108</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="R2" t="n">
         <v>0.40305</v>
@@ -11026,7 +11034,7 @@
         <v>59.565</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.292622</v>
+        <v>8.254008000000001</v>
       </c>
       <c r="Z2" t="n">
         <v>0.317</v>
@@ -11038,7 +11046,7 @@
         <v>331839012864</v>
       </c>
       <c r="AC2" t="n">
-        <v>3719818117120</v>
+        <v>3702739435520</v>
       </c>
       <c r="AD2" t="n">
         <v>194237005824</v>
@@ -11065,7 +11073,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-09 09:14:48</t>
+          <t>2026-09-10 18:59:04</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45910</v>
+        <v>45911</v>
       </c>
       <c r="B2" t="n">
-        <v>498.8754294126598</v>
+        <v>498.1513800613702</v>
       </c>
       <c r="C2" t="n">
-        <v>499.1233892811019</v>
+        <v>499.0638857033828</v>
       </c>
       <c r="D2" t="n">
-        <v>492.6665046209378</v>
+        <v>493.8170463660224</v>
       </c>
       <c r="E2" t="n">
-        <v>496.2867126464844</v>
+        <v>496.9215087890625</v>
       </c>
       <c r="F2" t="n">
-        <v>21611800</v>
+        <v>18881600</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B3" t="n">
-        <v>498.1513800613702</v>
+        <v>502.5154742767582</v>
       </c>
       <c r="C3" t="n">
-        <v>499.0638857033828</v>
+        <v>508.367321245748</v>
       </c>
       <c r="D3" t="n">
-        <v>493.8170463660224</v>
+        <v>499.738335797131</v>
       </c>
       <c r="E3" t="n">
-        <v>496.9215087890625</v>
+        <v>505.7389526367188</v>
       </c>
       <c r="F3" t="n">
-        <v>18881600</v>
+        <v>23624900</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B4" t="n">
-        <v>502.5154742767582</v>
+        <v>504.6380560678344</v>
       </c>
       <c r="C4" t="n">
-        <v>508.367321245748</v>
+        <v>511.2635067675502</v>
       </c>
       <c r="D4" t="n">
-        <v>499.738335797131</v>
+        <v>502.8626547877709</v>
       </c>
       <c r="E4" t="n">
-        <v>505.7389526367188</v>
+        <v>511.1544189453125</v>
       </c>
       <c r="F4" t="n">
-        <v>23624900</v>
+        <v>17143800</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B5" t="n">
-        <v>504.6380259393043</v>
+        <v>512.6620043570016</v>
       </c>
       <c r="C5" t="n">
-        <v>511.2634762434591</v>
+        <v>513.0091239663263</v>
       </c>
       <c r="D5" t="n">
-        <v>502.862624765238</v>
+        <v>504.4495745277025</v>
       </c>
       <c r="E5" t="n">
-        <v>511.1543884277344</v>
+        <v>504.885986328125</v>
       </c>
       <c r="F5" t="n">
-        <v>17143800</v>
+        <v>19711900</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B6" t="n">
-        <v>512.6620043570016</v>
+        <v>506.4530503919847</v>
       </c>
       <c r="C6" t="n">
-        <v>513.0091239663263</v>
+        <v>507.1175961354426</v>
       </c>
       <c r="D6" t="n">
-        <v>504.4495745277025</v>
+        <v>501.8013209933916</v>
       </c>
       <c r="E6" t="n">
-        <v>504.885986328125</v>
+        <v>505.8579406738281</v>
       </c>
       <c r="F6" t="n">
-        <v>19711900</v>
+        <v>15816600</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B7" t="n">
-        <v>506.4530503919847</v>
+        <v>507.3159513893766</v>
       </c>
       <c r="C7" t="n">
-        <v>507.1175961354426</v>
+        <v>508.883074673213</v>
       </c>
       <c r="D7" t="n">
-        <v>501.8013209933916</v>
+        <v>503.5172196080818</v>
       </c>
       <c r="E7" t="n">
-        <v>505.8579406738281</v>
+        <v>504.30078125</v>
       </c>
       <c r="F7" t="n">
-        <v>15816600</v>
+        <v>18913700</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B8" t="n">
-        <v>507.3159820894167</v>
+        <v>506.3935778296786</v>
       </c>
       <c r="C8" t="n">
-        <v>508.883105468087</v>
+        <v>515.0622454615835</v>
       </c>
       <c r="D8" t="n">
-        <v>503.517250078243</v>
+        <v>506.1456179521661</v>
       </c>
       <c r="E8" t="n">
-        <v>504.3008117675781</v>
+        <v>513.7034301757812</v>
       </c>
       <c r="F8" t="n">
-        <v>18913700</v>
+        <v>52474100</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B9" t="n">
-        <v>506.3935778296786</v>
+        <v>511.382573172581</v>
       </c>
       <c r="C9" t="n">
-        <v>515.0622454615835</v>
+        <v>513.5149918534414</v>
       </c>
       <c r="D9" t="n">
-        <v>506.1456179521661</v>
+        <v>508.3574141571104</v>
       </c>
       <c r="E9" t="n">
-        <v>513.7034301757812</v>
+        <v>510.2518615722656</v>
       </c>
       <c r="F9" t="n">
-        <v>52474100</v>
+        <v>20009300</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B10" t="n">
-        <v>511.3826037577857</v>
+        <v>509.6070850287104</v>
       </c>
       <c r="C10" t="n">
-        <v>513.5150225661836</v>
+        <v>510.3906769190661</v>
       </c>
       <c r="D10" t="n">
-        <v>508.3574445613838</v>
+        <v>503.1700568391782</v>
       </c>
       <c r="E10" t="n">
-        <v>510.2518920898438</v>
+        <v>505.0744018554688</v>
       </c>
       <c r="F10" t="n">
-        <v>20009300</v>
+        <v>19799600</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B11" t="n">
-        <v>509.6071158201621</v>
+        <v>506.215041937542</v>
       </c>
       <c r="C11" t="n">
-        <v>510.3907077578639</v>
+        <v>508.2978806442567</v>
       </c>
       <c r="D11" t="n">
-        <v>503.170087241692</v>
+        <v>502.7832857896144</v>
       </c>
       <c r="E11" t="n">
-        <v>505.0744323730469</v>
+        <v>505.9869079589844</v>
       </c>
       <c r="F11" t="n">
-        <v>19799600</v>
+        <v>13533700</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B12" t="n">
-        <v>506.2150114062044</v>
+        <v>504.1519897302721</v>
       </c>
       <c r="C12" t="n">
-        <v>508.297849987297</v>
+        <v>505.8480570147519</v>
       </c>
       <c r="D12" t="n">
-        <v>502.7832554652563</v>
+        <v>500.9186136455738</v>
       </c>
       <c r="E12" t="n">
-        <v>505.9868774414062</v>
+        <v>502.8923645019531</v>
       </c>
       <c r="F12" t="n">
-        <v>13533700</v>
+        <v>15786500</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B13" t="n">
-        <v>504.1519897302721</v>
+        <v>505.8975942449135</v>
       </c>
       <c r="C13" t="n">
-        <v>505.8480570147519</v>
+        <v>509.745935901324</v>
       </c>
       <c r="D13" t="n">
-        <v>500.9186136455738</v>
+        <v>502.4856643393456</v>
       </c>
       <c r="E13" t="n">
-        <v>502.8923645019531</v>
+        <v>507.2861633300781</v>
       </c>
       <c r="F13" t="n">
-        <v>15786500</v>
+        <v>16213100</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B14" t="n">
-        <v>505.8976246789574</v>
+        <v>507.3258348805616</v>
       </c>
       <c r="C14" t="n">
-        <v>509.7459665668783</v>
+        <v>512.6321512651683</v>
       </c>
       <c r="D14" t="n">
-        <v>502.4856945681329</v>
+        <v>504.7272205888506</v>
       </c>
       <c r="E14" t="n">
-        <v>507.2861938476562</v>
+        <v>510.4005126953125</v>
       </c>
       <c r="F14" t="n">
-        <v>16213100</v>
+        <v>17617800</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B15" t="n">
-        <v>507.3258652143003</v>
+        <v>509.0516808953516</v>
       </c>
       <c r="C15" t="n">
-        <v>512.6321819161793</v>
+        <v>513.9315141469417</v>
       </c>
       <c r="D15" t="n">
-        <v>504.7272507672145</v>
+        <v>505.5009089039439</v>
       </c>
       <c r="E15" t="n">
-        <v>510.4005432128906</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="F15" t="n">
-        <v>17617800</v>
+        <v>19728200</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B16" t="n">
-        <v>509.0516808953516</v>
+        <v>510.5989067561486</v>
       </c>
       <c r="C16" t="n">
-        <v>513.9315141469417</v>
+        <v>516.2623314762835</v>
       </c>
       <c r="D16" t="n">
-        <v>505.5009089039439</v>
+        <v>507.5143007767599</v>
       </c>
       <c r="E16" t="n">
-        <v>513.7232666015625</v>
+        <v>515.4688720703125</v>
       </c>
       <c r="F16" t="n">
-        <v>19728200</v>
+        <v>22632300</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B17" t="n">
-        <v>510.5989067561486</v>
+        <v>513.4157691025699</v>
       </c>
       <c r="C17" t="n">
-        <v>516.2623314762835</v>
+        <v>517.3434144406598</v>
       </c>
       <c r="D17" t="n">
-        <v>507.5143007767599</v>
+        <v>506.5125449836057</v>
       </c>
       <c r="E17" t="n">
-        <v>515.4688720703125</v>
+        <v>511.53125</v>
       </c>
       <c r="F17" t="n">
-        <v>22632300</v>
+        <v>21222900</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B18" t="n">
-        <v>513.4157691025699</v>
+        <v>512.8801529316524</v>
       </c>
       <c r="C18" t="n">
-        <v>517.3434144406598</v>
+        <v>516.2425031799986</v>
       </c>
       <c r="D18" t="n">
-        <v>506.5125449836057</v>
+        <v>510.7973143114264</v>
       </c>
       <c r="E18" t="n">
-        <v>511.53125</v>
+        <v>513.1281127929688</v>
       </c>
       <c r="F18" t="n">
-        <v>21222900</v>
+        <v>15112300</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B19" t="n">
-        <v>512.8801529316524</v>
+        <v>514.377848960065</v>
       </c>
       <c r="C19" t="n">
-        <v>516.2425031799986</v>
+        <v>526.6965386672223</v>
       </c>
       <c r="D19" t="n">
-        <v>510.7973143114264</v>
+        <v>513.9712214168786</v>
       </c>
       <c r="E19" t="n">
-        <v>513.1281127929688</v>
+        <v>524.256591796875</v>
       </c>
       <c r="F19" t="n">
-        <v>15112300</v>
+        <v>21388600</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B20" t="n">
-        <v>514.377848960065</v>
+        <v>523.9788048028778</v>
       </c>
       <c r="C20" t="n">
-        <v>526.6965386672223</v>
+        <v>525.4764919541412</v>
       </c>
       <c r="D20" t="n">
-        <v>513.9712214168786</v>
+        <v>517.1847292577561</v>
       </c>
       <c r="E20" t="n">
-        <v>524.256591796875</v>
+        <v>519.7039794921875</v>
       </c>
       <c r="F20" t="n">
-        <v>21388600</v>
+        <v>14615200</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B21" t="n">
-        <v>523.9788048028778</v>
+        <v>519.0097599169904</v>
       </c>
       <c r="C21" t="n">
-        <v>525.4764919541412</v>
+        <v>522.6497936321297</v>
       </c>
       <c r="D21" t="n">
-        <v>517.1847292577561</v>
+        <v>518.8213080060119</v>
       </c>
       <c r="E21" t="n">
-        <v>519.7039794921875</v>
+        <v>520.56689453125</v>
       </c>
       <c r="F21" t="n">
-        <v>14615200</v>
+        <v>13363400</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B22" t="n">
-        <v>519.0098207695767</v>
+        <v>518.07745494396</v>
       </c>
       <c r="C22" t="n">
-        <v>522.6498549115006</v>
+        <v>520.0512058016051</v>
       </c>
       <c r="D22" t="n">
-        <v>518.8213688365025</v>
+        <v>513.1777655449532</v>
       </c>
       <c r="E22" t="n">
-        <v>520.5669555664062</v>
+        <v>518.136962890625</v>
       </c>
       <c r="F22" t="n">
-        <v>13363400</v>
+        <v>18343600</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B23" t="n">
-        <v>518.0773939158137</v>
+        <v>515.3994727403434</v>
       </c>
       <c r="C23" t="n">
-        <v>520.0511445409561</v>
+        <v>519.3073226434543</v>
       </c>
       <c r="D23" t="n">
-        <v>513.1777050939771</v>
+        <v>505.4711500363669</v>
       </c>
       <c r="E23" t="n">
-        <v>518.1369018554688</v>
+        <v>506.790283203125</v>
       </c>
       <c r="F23" t="n">
-        <v>18343600</v>
+        <v>24133800</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B24" t="n">
-        <v>515.3995037763443</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="C24" t="n">
-        <v>519.3073539147757</v>
+        <v>512.1957986627914</v>
       </c>
       <c r="D24" t="n">
-        <v>505.4711804745103</v>
+        <v>507.504417299456</v>
       </c>
       <c r="E24" t="n">
-        <v>506.7903137207031</v>
+        <v>509.8550720214844</v>
       </c>
       <c r="F24" t="n">
-        <v>24133800</v>
+        <v>14284200</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B25" t="n">
-        <v>512.1958293204747</v>
+        <v>506.0662879637401</v>
       </c>
       <c r="C25" t="n">
-        <v>512.1958293204747</v>
+        <v>511.0750956887641</v>
       </c>
       <c r="D25" t="n">
-        <v>507.5044476763347</v>
+        <v>501.870795907601</v>
       </c>
       <c r="E25" t="n">
-        <v>509.8551025390625</v>
+        <v>509.3790283203125</v>
       </c>
       <c r="F25" t="n">
-        <v>14284200</v>
+        <v>14684300</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B26" t="n">
-        <v>506.0662273255252</v>
+        <v>510.7576556934355</v>
       </c>
       <c r="C26" t="n">
-        <v>511.0750344503804</v>
+        <v>512.9694382549203</v>
       </c>
       <c r="D26" t="n">
-        <v>501.8707357721012</v>
+        <v>505.838110317394</v>
       </c>
       <c r="E26" t="n">
-        <v>509.3789672851562</v>
+        <v>509.2401123046875</v>
       </c>
       <c r="F26" t="n">
-        <v>14684300</v>
+        <v>14694700</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B27" t="n">
-        <v>510.7577169104775</v>
+        <v>508.3970827878481</v>
       </c>
       <c r="C27" t="n">
-        <v>512.9694997370561</v>
+        <v>512.6321960787722</v>
       </c>
       <c r="D27" t="n">
-        <v>505.8381709448021</v>
+        <v>503.9833851231019</v>
       </c>
       <c r="E27" t="n">
-        <v>509.2401733398438</v>
+        <v>507.4349670410156</v>
       </c>
       <c r="F27" t="n">
-        <v>14694700</v>
+        <v>15559600</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B28" t="n">
-        <v>508.3970827878481</v>
+        <v>504.8859867353243</v>
       </c>
       <c r="C28" t="n">
-        <v>512.6321960787722</v>
+        <v>511.2734052578957</v>
       </c>
       <c r="D28" t="n">
-        <v>503.9833851231019</v>
+        <v>503.1700935064365</v>
       </c>
       <c r="E28" t="n">
-        <v>507.4349670410156</v>
+        <v>509.3889465332031</v>
       </c>
       <c r="F28" t="n">
-        <v>15559600</v>
+        <v>19867800</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B29" t="n">
-        <v>504.8859564875193</v>
+        <v>510.4104901121901</v>
       </c>
       <c r="C29" t="n">
-        <v>511.2733746274193</v>
+        <v>514.4671401409408</v>
       </c>
       <c r="D29" t="n">
-        <v>503.1700633614309</v>
+        <v>509.2401268135401</v>
       </c>
       <c r="E29" t="n">
-        <v>509.388916015625</v>
+        <v>512.5726928710938</v>
       </c>
       <c r="F29" t="n">
-        <v>19867800</v>
+        <v>14665600</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B30" t="n">
-        <v>510.4104901121901</v>
+        <v>513.2769402267872</v>
       </c>
       <c r="C30" t="n">
-        <v>514.4671401409408</v>
+        <v>514.4572316509175</v>
       </c>
       <c r="D30" t="n">
-        <v>509.2401268135401</v>
+        <v>508.8533142722573</v>
       </c>
       <c r="E30" t="n">
-        <v>512.5726928710938</v>
+        <v>513.4356079101562</v>
       </c>
       <c r="F30" t="n">
-        <v>14665600</v>
+        <v>15586200</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B31" t="n">
-        <v>513.2769402267872</v>
+        <v>516.8971823641815</v>
       </c>
       <c r="C31" t="n">
-        <v>514.4572316509175</v>
+        <v>520.943843958813</v>
       </c>
       <c r="D31" t="n">
-        <v>508.8533142722573</v>
+        <v>513.4852520447155</v>
       </c>
       <c r="E31" t="n">
-        <v>513.4356079101562</v>
+        <v>516.2921142578125</v>
       </c>
       <c r="F31" t="n">
-        <v>15586200</v>
+        <v>18962700</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B32" t="n">
-        <v>516.8971823641815</v>
+        <v>518.1964086283891</v>
       </c>
       <c r="C32" t="n">
-        <v>520.943843958813</v>
+        <v>519.6742395740552</v>
       </c>
       <c r="D32" t="n">
-        <v>513.4852520447155</v>
+        <v>514.3777908083965</v>
       </c>
       <c r="E32" t="n">
-        <v>516.2921142578125</v>
+        <v>516.3118896484375</v>
       </c>
       <c r="F32" t="n">
-        <v>18962700</v>
+        <v>14023500</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B33" t="n">
-        <v>518.1964698863214</v>
+        <v>518.5236595856693</v>
       </c>
       <c r="C33" t="n">
-        <v>519.6743010066873</v>
+        <v>521.0627658394295</v>
       </c>
       <c r="D33" t="n">
-        <v>514.3778516149157</v>
+        <v>516.4606773737235</v>
       </c>
       <c r="E33" t="n">
-        <v>516.3119506835938</v>
+        <v>519.3369750976562</v>
       </c>
       <c r="F33" t="n">
-        <v>14023500</v>
+        <v>15532400</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B34" t="n">
-        <v>518.5237205252405</v>
+        <v>527.440383046071</v>
       </c>
       <c r="C34" t="n">
-        <v>521.0628270774097</v>
+        <v>530.2175212473691</v>
       </c>
       <c r="D34" t="n">
-        <v>516.4607380708425</v>
+        <v>524.6929685473742</v>
       </c>
       <c r="E34" t="n">
-        <v>519.3370361328125</v>
+        <v>527.1824951171875</v>
       </c>
       <c r="F34" t="n">
-        <v>15532400</v>
+        <v>18734700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B35" t="n">
-        <v>527.440383046071</v>
+        <v>545.511702993095</v>
       </c>
       <c r="C35" t="n">
-        <v>530.2175212473691</v>
+        <v>549.2013167264516</v>
       </c>
       <c r="D35" t="n">
-        <v>524.6929685473742</v>
+        <v>536.3570441492753</v>
       </c>
       <c r="E35" t="n">
-        <v>527.1824951171875</v>
+        <v>537.6464233398438</v>
       </c>
       <c r="F35" t="n">
-        <v>18734700</v>
+        <v>29986700</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B36" t="n">
-        <v>545.5116410650497</v>
+        <v>540.4929653309738</v>
       </c>
       <c r="C36" t="n">
-        <v>549.2012543795508</v>
+        <v>541.8121286840217</v>
       </c>
       <c r="D36" t="n">
-        <v>536.3569832604931</v>
+        <v>532.3499420595073</v>
       </c>
       <c r="E36" t="n">
-        <v>537.6463623046875</v>
+        <v>537.130615234375</v>
       </c>
       <c r="F36" t="n">
-        <v>29986700</v>
+        <v>36023000</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B37" t="n">
-        <v>540.4929653309738</v>
+        <v>526.150935240438</v>
       </c>
       <c r="C37" t="n">
-        <v>541.8121286840217</v>
+        <v>530.6042843733296</v>
       </c>
       <c r="D37" t="n">
-        <v>532.3499420595073</v>
+        <v>517.8591725476514</v>
       </c>
       <c r="E37" t="n">
-        <v>537.130615234375</v>
+        <v>521.469482421875</v>
       </c>
       <c r="F37" t="n">
-        <v>36023000</v>
+        <v>41023100</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B38" t="n">
-        <v>526.1509968235328</v>
+        <v>524.5640822050067</v>
       </c>
       <c r="C38" t="n">
-        <v>530.6043464776645</v>
+        <v>525.0004940086545</v>
       </c>
       <c r="D38" t="n">
-        <v>517.8592331602406</v>
+        <v>510.8965047694123</v>
       </c>
       <c r="E38" t="n">
-        <v>521.4695434570312</v>
+        <v>513.5844116210938</v>
       </c>
       <c r="F38" t="n">
-        <v>41023100</v>
+        <v>34006400</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B39" t="n">
-        <v>524.5640198650095</v>
+        <v>515.5680732671589</v>
       </c>
       <c r="C39" t="n">
-        <v>525.0004316167937</v>
+        <v>520.6760707602963</v>
       </c>
       <c r="D39" t="n">
-        <v>510.896444053691</v>
+        <v>510.3907002836433</v>
       </c>
       <c r="E39" t="n">
-        <v>513.5843505859375</v>
+        <v>512.810791015625</v>
       </c>
       <c r="F39" t="n">
-        <v>34006400</v>
+        <v>22374700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B40" t="n">
-        <v>515.5680119038287</v>
+        <v>507.5837170627558</v>
       </c>
       <c r="C40" t="n">
-        <v>520.6760087890081</v>
+        <v>511.3427664179142</v>
       </c>
       <c r="D40" t="n">
-        <v>510.3906395365282</v>
+        <v>503.6956934801851</v>
       </c>
       <c r="E40" t="n">
-        <v>512.8107299804688</v>
+        <v>510.1327514648438</v>
       </c>
       <c r="F40" t="n">
-        <v>22374700</v>
+        <v>20958700</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B41" t="n">
-        <v>507.5837474278435</v>
+        <v>509.1111797792271</v>
       </c>
       <c r="C41" t="n">
-        <v>511.3427970078787</v>
+        <v>510.6287232020861</v>
       </c>
       <c r="D41" t="n">
-        <v>503.6957236126803</v>
+        <v>502.4460174356622</v>
       </c>
       <c r="E41" t="n">
-        <v>510.1327819824219</v>
+        <v>503.0213012695312</v>
       </c>
       <c r="F41" t="n">
-        <v>20958700</v>
+        <v>23024300</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B42" t="n">
-        <v>509.1111797792271</v>
+        <v>501.5335702984596</v>
       </c>
       <c r="C42" t="n">
-        <v>510.6287232020861</v>
+        <v>501.5732523540539</v>
       </c>
       <c r="D42" t="n">
-        <v>502.4460174356622</v>
+        <v>491.7639450704796</v>
       </c>
       <c r="E42" t="n">
-        <v>503.0213012695312</v>
+        <v>493.0434265136719</v>
       </c>
       <c r="F42" t="n">
-        <v>23024300</v>
+        <v>27406500</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B43" t="n">
-        <v>501.5335392553728</v>
+        <v>492.8946300074654</v>
       </c>
       <c r="C43" t="n">
-        <v>501.5732213085109</v>
+        <v>495.304792622274</v>
       </c>
       <c r="D43" t="n">
-        <v>491.7639146320967</v>
+        <v>489.2248119110569</v>
       </c>
       <c r="E43" t="n">
-        <v>493.0433959960938</v>
+        <v>492.7656860351562</v>
       </c>
       <c r="F43" t="n">
-        <v>27406500</v>
+        <v>24019800</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B44" t="n">
-        <v>492.8946300074654</v>
+        <v>495.9594034527451</v>
       </c>
       <c r="C44" t="n">
-        <v>495.304792622274</v>
+        <v>502.7138276367279</v>
       </c>
       <c r="D44" t="n">
-        <v>489.2248119110569</v>
+        <v>494.7295019610679</v>
       </c>
       <c r="E44" t="n">
-        <v>492.7656860351562</v>
+        <v>501.8707580566406</v>
       </c>
       <c r="F44" t="n">
-        <v>24019800</v>
+        <v>26101500</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B45" t="n">
-        <v>495.9594336108676</v>
+        <v>500.6805581155917</v>
       </c>
       <c r="C45" t="n">
-        <v>502.7138582055711</v>
+        <v>505.4414057875519</v>
       </c>
       <c r="D45" t="n">
-        <v>494.729532044403</v>
+        <v>498.2505695472254</v>
       </c>
       <c r="E45" t="n">
-        <v>501.8707885742188</v>
+        <v>504.5289001464844</v>
       </c>
       <c r="F45" t="n">
-        <v>26101500</v>
+        <v>17980000</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B46" t="n">
-        <v>500.6805884003941</v>
+        <v>505.203338237195</v>
       </c>
       <c r="C46" t="n">
-        <v>505.441436360325</v>
+        <v>507.494515261433</v>
       </c>
       <c r="D46" t="n">
-        <v>498.2505996850444</v>
+        <v>495.0469117437556</v>
       </c>
       <c r="E46" t="n">
-        <v>504.5289306640625</v>
+        <v>506.9688415527344</v>
       </c>
       <c r="F46" t="n">
-        <v>17980000</v>
+        <v>26574900</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B47" t="n">
-        <v>505.203338237195</v>
+        <v>506.1455939798088</v>
       </c>
       <c r="C47" t="n">
-        <v>507.494515261433</v>
+        <v>509.3095642884979</v>
       </c>
       <c r="D47" t="n">
-        <v>495.0469117437556</v>
+        <v>497.1992129195551</v>
       </c>
       <c r="E47" t="n">
-        <v>506.9688415527344</v>
+        <v>499.1828918457031</v>
       </c>
       <c r="F47" t="n">
-        <v>26574900</v>
+        <v>25273100</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B48" t="n">
-        <v>506.1455939798088</v>
+        <v>494.164169077362</v>
       </c>
       <c r="C48" t="n">
-        <v>509.3095642884979</v>
+        <v>507.425057385904</v>
       </c>
       <c r="D48" t="n">
-        <v>497.1992129195551</v>
+        <v>493.3806074541019</v>
       </c>
       <c r="E48" t="n">
-        <v>499.1828918457031</v>
+        <v>506.0166320800781</v>
       </c>
       <c r="F48" t="n">
-        <v>25273100</v>
+        <v>28505700</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B49" t="n">
-        <v>494.1641988801248</v>
+        <v>504.3007594029326</v>
       </c>
       <c r="C49" t="n">
-        <v>507.4250879884235</v>
+        <v>507.9407930820625</v>
       </c>
       <c r="D49" t="n">
-        <v>493.3806372096086</v>
+        <v>500.7896394213482</v>
       </c>
       <c r="E49" t="n">
-        <v>506.0166625976562</v>
+        <v>503.3485717773438</v>
       </c>
       <c r="F49" t="n">
-        <v>28505700</v>
+        <v>19092800</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B50" t="n">
-        <v>504.3008205535495</v>
+        <v>491.3275301094218</v>
       </c>
       <c r="C50" t="n">
-        <v>507.9408546740634</v>
+        <v>498.8754444722887</v>
       </c>
       <c r="D50" t="n">
-        <v>500.7897001462128</v>
+        <v>482.8076324047851</v>
       </c>
       <c r="E50" t="n">
-        <v>503.3486328125</v>
+        <v>489.7604370117188</v>
       </c>
       <c r="F50" t="n">
-        <v>19092800</v>
+        <v>33815100</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B51" t="n">
-        <v>491.3274994941962</v>
+        <v>486.1005289347495</v>
       </c>
       <c r="C51" t="n">
-        <v>498.8754133867433</v>
+        <v>491.1489881906385</v>
       </c>
       <c r="D51" t="n">
-        <v>482.8076023204449</v>
+        <v>478.8898366362471</v>
       </c>
       <c r="E51" t="n">
-        <v>489.7604064941406</v>
+        <v>483.1448364257812</v>
       </c>
       <c r="F51" t="n">
-        <v>33815100</v>
+        <v>23245300</v>
       </c>
       <c r="G51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B52" t="n">
-        <v>486.1005289347495</v>
+        <v>489.6038543571071</v>
       </c>
       <c r="C52" t="n">
-        <v>491.1489881906385</v>
+        <v>490.4584485233347</v>
       </c>
       <c r="D52" t="n">
-        <v>478.8898366362471</v>
+        <v>472.5023579474745</v>
       </c>
       <c r="E52" t="n">
-        <v>483.1448364257812</v>
+        <v>475.4138793945312</v>
       </c>
       <c r="F52" t="n">
-        <v>23245300</v>
+        <v>26802500</v>
       </c>
       <c r="G52" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,25 +1795,25 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B53" t="n">
-        <v>489.6038543571071</v>
+        <v>475.4834301610789</v>
       </c>
       <c r="C53" t="n">
-        <v>490.4584485233347</v>
+        <v>475.9007957312625</v>
       </c>
       <c r="D53" t="n">
-        <v>472.5023579474745</v>
+        <v>465.3179114267742</v>
       </c>
       <c r="E53" t="n">
-        <v>475.4138793945312</v>
+        <v>469.1436462402344</v>
       </c>
       <c r="F53" t="n">
-        <v>26802500</v>
+        <v>31769200</v>
       </c>
       <c r="G53" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B54" t="n">
-        <v>475.4834610910571</v>
+        <v>472.0055061050608</v>
       </c>
       <c r="C54" t="n">
-        <v>475.9008266883901</v>
+        <v>473.8935220644432</v>
       </c>
       <c r="D54" t="n">
-        <v>465.31794169549</v>
+        <v>465.0694984877541</v>
       </c>
       <c r="E54" t="n">
-        <v>469.1436767578125</v>
+        <v>471.0118103027344</v>
       </c>
       <c r="F54" t="n">
-        <v>31769200</v>
+        <v>34421000</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B55" t="n">
-        <v>472.0055061050608</v>
+        <v>471.0813659766461</v>
       </c>
       <c r="C55" t="n">
-        <v>473.8935220644432</v>
+        <v>476.1293271988991</v>
       </c>
       <c r="D55" t="n">
-        <v>465.0694984877541</v>
+        <v>461.9592459889855</v>
       </c>
       <c r="E55" t="n">
-        <v>471.0118103027344</v>
+        <v>473.9829406738281</v>
       </c>
       <c r="F55" t="n">
-        <v>34421000</v>
+        <v>28019800</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B56" t="n">
-        <v>471.0813659766461</v>
+        <v>483.244222260298</v>
       </c>
       <c r="C56" t="n">
-        <v>476.1293271988991</v>
+        <v>485.2316139433245</v>
       </c>
       <c r="D56" t="n">
-        <v>461.9592459889855</v>
+        <v>478.1664510662567</v>
       </c>
       <c r="E56" t="n">
-        <v>473.9829406738281</v>
+        <v>482.4393310546875</v>
       </c>
       <c r="F56" t="n">
-        <v>28019800</v>
+        <v>25709100</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B57" t="n">
-        <v>483.244191691805</v>
+        <v>484.5260924315005</v>
       </c>
       <c r="C57" t="n">
-        <v>485.2315832491155</v>
+        <v>489.5243812398697</v>
       </c>
       <c r="D57" t="n">
-        <v>478.1664208189674</v>
+        <v>483.5820692635899</v>
       </c>
       <c r="E57" t="n">
-        <v>482.4393005371094</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="F57" t="n">
-        <v>25709100</v>
+        <v>14386700</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B58" t="n">
-        <v>484.5260924315005</v>
+        <v>485.3608038657598</v>
       </c>
       <c r="C58" t="n">
-        <v>489.5243812398697</v>
+        <v>486.771834992007</v>
       </c>
       <c r="D58" t="n">
-        <v>483.5820692635899</v>
+        <v>481.5946880995925</v>
       </c>
       <c r="E58" t="n">
-        <v>488.9082946777344</v>
+        <v>483.6715087890625</v>
       </c>
       <c r="F58" t="n">
-        <v>14386700</v>
+        <v>23964000</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B59" t="n">
-        <v>485.3608038657598</v>
+        <v>483.6516286444489</v>
       </c>
       <c r="C59" t="n">
-        <v>486.771834992007</v>
+        <v>490.3888850620814</v>
       </c>
       <c r="D59" t="n">
-        <v>481.5946880995925</v>
+        <v>483.2541563831954</v>
       </c>
       <c r="E59" t="n">
-        <v>483.6715087890625</v>
+        <v>486.9109497070312</v>
       </c>
       <c r="F59" t="n">
-        <v>23964000</v>
+        <v>19562700</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B60" t="n">
-        <v>483.6516286444489</v>
+        <v>473.3172079858148</v>
       </c>
       <c r="C60" t="n">
-        <v>490.3888850620814</v>
+        <v>481.1872620265617</v>
       </c>
       <c r="D60" t="n">
-        <v>483.2541563831954</v>
+        <v>472.2042735012802</v>
       </c>
       <c r="E60" t="n">
-        <v>486.9109497070312</v>
+        <v>474.7183227539062</v>
       </c>
       <c r="F60" t="n">
-        <v>19562700</v>
+        <v>34615100</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B61" t="n">
-        <v>473.3171775583083</v>
+        <v>476.7355376297969</v>
       </c>
       <c r="C61" t="n">
-        <v>481.1872310931236</v>
+        <v>478.2857007523145</v>
       </c>
       <c r="D61" t="n">
-        <v>472.2042431453193</v>
+        <v>473.4861327449422</v>
       </c>
       <c r="E61" t="n">
-        <v>474.7182922363281</v>
+        <v>477.8087158203125</v>
       </c>
       <c r="F61" t="n">
-        <v>34615100</v>
+        <v>22318200</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B62" t="n">
-        <v>476.7355071807625</v>
+        <v>479.4780948278929</v>
       </c>
       <c r="C62" t="n">
-        <v>478.2856702042714</v>
+        <v>480.3525519991132</v>
       </c>
       <c r="D62" t="n">
-        <v>473.4861025034468</v>
+        <v>475.8610578221601</v>
       </c>
       <c r="E62" t="n">
-        <v>477.8086853027344</v>
+        <v>480.1140747070312</v>
       </c>
       <c r="F62" t="n">
-        <v>22318200</v>
+        <v>22608700</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B63" t="n">
-        <v>479.4780643507397</v>
+        <v>481.8331697469475</v>
       </c>
       <c r="C63" t="n">
-        <v>480.3525214663767</v>
+        <v>489.1964289193556</v>
       </c>
       <c r="D63" t="n">
-        <v>475.8610275749173</v>
+        <v>481.3263751862239</v>
       </c>
       <c r="E63" t="n">
-        <v>480.1140441894531</v>
+        <v>487.9244995117188</v>
       </c>
       <c r="F63" t="n">
-        <v>22608700</v>
+        <v>21965900</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B64" t="n">
-        <v>481.8331998835391</v>
+        <v>486.0166380400449</v>
       </c>
       <c r="C64" t="n">
-        <v>489.1964595164875</v>
+        <v>489.0175885389743</v>
       </c>
       <c r="D64" t="n">
-        <v>481.3264052911177</v>
+        <v>485.4204144751398</v>
       </c>
       <c r="E64" t="n">
-        <v>487.9245300292969</v>
+        <v>488.918212890625</v>
       </c>
       <c r="F64" t="n">
-        <v>21965900</v>
+        <v>14696100</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B65" t="n">
-        <v>486.0166380400449</v>
+        <v>480.978577549523</v>
       </c>
       <c r="C65" t="n">
-        <v>489.0175885389743</v>
+        <v>481.1971918388435</v>
       </c>
       <c r="D65" t="n">
-        <v>485.4204144751398</v>
+        <v>472.084987996716</v>
       </c>
       <c r="E65" t="n">
-        <v>488.918212890625</v>
+        <v>475.5430603027344</v>
       </c>
       <c r="F65" t="n">
-        <v>14696100</v>
+        <v>35756200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B66" t="n">
-        <v>480.978577549523</v>
+        <v>473.6252433732215</v>
       </c>
       <c r="C66" t="n">
-        <v>481.1971918388435</v>
+        <v>482.9659780129214</v>
       </c>
       <c r="D66" t="n">
-        <v>472.084987996716</v>
+        <v>472.8600781839672</v>
       </c>
       <c r="E66" t="n">
-        <v>475.5430603027344</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F66" t="n">
-        <v>35756200</v>
+        <v>24669200</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B67" t="n">
-        <v>473.6252433732215</v>
+        <v>476.7951206875852</v>
       </c>
       <c r="C67" t="n">
-        <v>482.9659780129214</v>
+        <v>479.4085454643102</v>
       </c>
       <c r="D67" t="n">
-        <v>472.8600781839672</v>
+        <v>473.3370484252935</v>
       </c>
       <c r="E67" t="n">
-        <v>480.422119140625</v>
+        <v>475.5132446289062</v>
       </c>
       <c r="F67" t="n">
-        <v>24669200</v>
+        <v>21248100</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B68" t="n">
-        <v>476.7951512874317</v>
+        <v>477.0733420562278</v>
       </c>
       <c r="C68" t="n">
-        <v>479.4085762318817</v>
+        <v>477.6894285774835</v>
       </c>
       <c r="D68" t="n">
-        <v>473.3370788032073</v>
+        <v>469.5411111878212</v>
       </c>
       <c r="E68" t="n">
-        <v>475.5132751464844</v>
+        <v>471.8266296386719</v>
       </c>
       <c r="F68" t="n">
-        <v>21248100</v>
+        <v>23727700</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B69" t="n">
-        <v>477.0733729131614</v>
+        <v>468.9350114671635</v>
       </c>
       <c r="C69" t="n">
-        <v>477.6894594742654</v>
+        <v>474.8773235577871</v>
       </c>
       <c r="D69" t="n">
-        <v>469.5411415575728</v>
+        <v>467.911505956298</v>
       </c>
       <c r="E69" t="n">
-        <v>471.82666015625</v>
+        <v>473.3867797851562</v>
       </c>
       <c r="F69" t="n">
-        <v>23727700</v>
+        <v>20705600</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B70" t="n">
-        <v>468.9349812365753</v>
+        <v>473.903466892556</v>
       </c>
       <c r="C70" t="n">
-        <v>474.8772929441188</v>
+        <v>476.9739832708393</v>
       </c>
       <c r="D70" t="n">
-        <v>467.9114757916915</v>
+        <v>472.0055042784347</v>
       </c>
       <c r="E70" t="n">
-        <v>473.3867492675781</v>
+        <v>473.1184387207031</v>
       </c>
       <c r="F70" t="n">
-        <v>20705600</v>
+        <v>24527200</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B71" t="n">
-        <v>473.903466892556</v>
+        <v>475.1754171439269</v>
       </c>
       <c r="C71" t="n">
-        <v>476.9739832708393</v>
+        <v>486.5134903409316</v>
       </c>
       <c r="D71" t="n">
-        <v>472.0055042784347</v>
+        <v>474.8773205213831</v>
       </c>
       <c r="E71" t="n">
-        <v>473.1184387207031</v>
+        <v>480.9289245605469</v>
       </c>
       <c r="F71" t="n">
-        <v>24527200</v>
+        <v>28573500</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B72" t="n">
-        <v>475.1754171439269</v>
+        <v>484.2875529363844</v>
       </c>
       <c r="C72" t="n">
-        <v>486.5134903409316</v>
+        <v>484.7744844818214</v>
       </c>
       <c r="D72" t="n">
-        <v>474.8773205213831</v>
+        <v>479.4482594182398</v>
       </c>
       <c r="E72" t="n">
-        <v>480.9289245605469</v>
+        <v>482.8566589355469</v>
       </c>
       <c r="F72" t="n">
-        <v>28573500</v>
+        <v>70836100</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B73" t="n">
-        <v>484.2875835443981</v>
+        <v>483.0554234208069</v>
       </c>
       <c r="C73" t="n">
-        <v>484.7745151206103</v>
+        <v>485.648985367377</v>
       </c>
       <c r="D73" t="n">
-        <v>479.4482897203998</v>
+        <v>479.6470539215635</v>
       </c>
       <c r="E73" t="n">
-        <v>482.856689453125</v>
+        <v>481.8630065917969</v>
       </c>
       <c r="F73" t="n">
-        <v>70836100</v>
+        <v>16963000</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B74" t="n">
-        <v>483.05539282771</v>
+        <v>481.922585996358</v>
       </c>
       <c r="C74" t="n">
-        <v>485.6489546100234</v>
+        <v>484.7545946839082</v>
       </c>
       <c r="D74" t="n">
-        <v>479.6470235443271</v>
+        <v>481.6840783901604</v>
       </c>
       <c r="E74" t="n">
-        <v>481.8629760742188</v>
+        <v>483.7807922363281</v>
       </c>
       <c r="F74" t="n">
-        <v>16963000</v>
+        <v>14683600</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B75" t="n">
-        <v>481.9226163967179</v>
+        <v>482.6181454723109</v>
       </c>
       <c r="C75" t="n">
-        <v>484.7546252629152</v>
+        <v>486.0762176057581</v>
       </c>
       <c r="D75" t="n">
-        <v>481.6841087754749</v>
+        <v>481.7734980182152</v>
       </c>
       <c r="E75" t="n">
-        <v>483.7808227539062</v>
+        <v>484.9433898925781</v>
       </c>
       <c r="F75" t="n">
-        <v>14683600</v>
+        <v>5855900</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B76" t="n">
-        <v>482.6181758435609</v>
+        <v>483.6416497095635</v>
       </c>
       <c r="C76" t="n">
-        <v>486.0762481946253</v>
+        <v>485.0427643552695</v>
       </c>
       <c r="D76" t="n">
-        <v>481.7735283363114</v>
+        <v>482.8963778974979</v>
       </c>
       <c r="E76" t="n">
-        <v>484.9434204101562</v>
+        <v>484.6353454589844</v>
       </c>
       <c r="F76" t="n">
-        <v>5855900</v>
+        <v>8842200</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B77" t="n">
-        <v>483.6417106195734</v>
+        <v>481.8033366009864</v>
       </c>
       <c r="C77" t="n">
-        <v>485.0428254417362</v>
+        <v>485.2713556042012</v>
       </c>
       <c r="D77" t="n">
-        <v>482.8964387136479</v>
+        <v>481.1276307272214</v>
       </c>
       <c r="E77" t="n">
-        <v>484.6354064941406</v>
+        <v>484.0292358398438</v>
       </c>
       <c r="F77" t="n">
-        <v>8842200</v>
+        <v>10893400</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B78" t="n">
-        <v>481.8033366009864</v>
+        <v>482.8666136001516</v>
       </c>
       <c r="C78" t="n">
-        <v>485.2713556042012</v>
+        <v>486.5929730105466</v>
       </c>
       <c r="D78" t="n">
-        <v>481.1276307272214</v>
+        <v>482.4393316658054</v>
       </c>
       <c r="E78" t="n">
-        <v>484.0292358398438</v>
+        <v>484.4068603515625</v>
       </c>
       <c r="F78" t="n">
-        <v>10893400</v>
+        <v>13944500</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B79" t="n">
-        <v>482.8666136001516</v>
+        <v>484.7645645601486</v>
       </c>
       <c r="C79" t="n">
-        <v>486.5929730105466</v>
+        <v>485.0626915008752</v>
       </c>
       <c r="D79" t="n">
-        <v>482.4393316658054</v>
+        <v>480.253177052155</v>
       </c>
       <c r="E79" t="n">
-        <v>484.4068603515625</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="F79" t="n">
-        <v>13944500</v>
+        <v>15601600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B80" t="n">
-        <v>484.7645645601486</v>
+        <v>481.3363251826272</v>
       </c>
       <c r="C80" t="n">
-        <v>485.0626915008752</v>
+        <v>481.6046121327098</v>
       </c>
       <c r="D80" t="n">
-        <v>480.253177052155</v>
+        <v>467.1960229709088</v>
       </c>
       <c r="E80" t="n">
-        <v>480.5711669921875</v>
+        <v>469.95849609375</v>
       </c>
       <c r="F80" t="n">
-        <v>15601600</v>
+        <v>25571600</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B81" t="n">
-        <v>481.3363251826272</v>
+        <v>471.071443053882</v>
       </c>
       <c r="C81" t="n">
-        <v>481.6046121327098</v>
+        <v>473.0687813775576</v>
       </c>
       <c r="D81" t="n">
-        <v>467.1960229709088</v>
+        <v>466.5401924921144</v>
       </c>
       <c r="E81" t="n">
-        <v>469.95849609375</v>
+        <v>469.8690795898438</v>
       </c>
       <c r="F81" t="n">
-        <v>25571600</v>
+        <v>25250300</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B82" t="n">
-        <v>471.071443053882</v>
+        <v>470.8130789419108</v>
       </c>
       <c r="C82" t="n">
-        <v>473.0687813775576</v>
+        <v>475.7219388392127</v>
       </c>
       <c r="D82" t="n">
-        <v>466.5401924921144</v>
+        <v>466.7886229022075</v>
       </c>
       <c r="E82" t="n">
-        <v>469.8690795898438</v>
+        <v>475.493408203125</v>
       </c>
       <c r="F82" t="n">
-        <v>25250300</v>
+        <v>23037700</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B83" t="n">
-        <v>470.8130487247203</v>
+        <v>476.7355161407656</v>
       </c>
       <c r="C83" t="n">
-        <v>475.7219083069673</v>
+        <v>486.6128550141313</v>
       </c>
       <c r="D83" t="n">
-        <v>466.7885929433101</v>
+        <v>474.936929133209</v>
       </c>
       <c r="E83" t="n">
-        <v>475.4933776855469</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F83" t="n">
-        <v>23037700</v>
+        <v>25564200</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B84" t="n">
-        <v>476.7355161407656</v>
+        <v>478.2061589486008</v>
       </c>
       <c r="C84" t="n">
-        <v>486.6128550141313</v>
+        <v>479.6172203331744</v>
       </c>
       <c r="D84" t="n">
-        <v>474.936929133209</v>
+        <v>472.8600706717694</v>
       </c>
       <c r="E84" t="n">
-        <v>480.422119140625</v>
+        <v>475.0958862304688</v>
       </c>
       <c r="F84" t="n">
-        <v>25564200</v>
+        <v>18162600</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B85" t="n">
-        <v>478.206189665966</v>
+        <v>471.0714211959582</v>
       </c>
       <c r="C85" t="n">
-        <v>479.6172511411785</v>
+        <v>476.7951186190047</v>
       </c>
       <c r="D85" t="n">
-        <v>472.8601010457309</v>
+        <v>469.2231615927928</v>
       </c>
       <c r="E85" t="n">
-        <v>475.0959167480469</v>
+        <v>476.2585144042969</v>
       </c>
       <c r="F85" t="n">
-        <v>18162600</v>
+        <v>18491000</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B86" t="n">
-        <v>471.071451381159</v>
+        <v>473.6649886945649</v>
       </c>
       <c r="C86" t="n">
-        <v>476.7951491709672</v>
+        <v>477.9577314886077</v>
       </c>
       <c r="D86" t="n">
-        <v>469.2231916595613</v>
+        <v>472.681209234831</v>
       </c>
       <c r="E86" t="n">
-        <v>476.258544921875</v>
+        <v>474.1717529296875</v>
       </c>
       <c r="F86" t="n">
-        <v>18491000</v>
+        <v>23519900</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B87" t="n">
-        <v>473.6649886945649</v>
+        <v>471.6875193976834</v>
       </c>
       <c r="C87" t="n">
-        <v>477.9577314886077</v>
+        <v>472.7805908527595</v>
       </c>
       <c r="D87" t="n">
-        <v>472.681209234831</v>
+        <v>463.0125743921384</v>
       </c>
       <c r="E87" t="n">
-        <v>474.1717529296875</v>
+        <v>467.7028198242188</v>
       </c>
       <c r="F87" t="n">
-        <v>23519900</v>
+        <v>28545800</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B88" t="n">
-        <v>471.6875193976834</v>
+        <v>463.5193311433208</v>
       </c>
       <c r="C88" t="n">
-        <v>472.7805908527595</v>
+        <v>465.2483824443871</v>
       </c>
       <c r="D88" t="n">
-        <v>463.0125743921384</v>
+        <v>454.2879190598576</v>
       </c>
       <c r="E88" t="n">
-        <v>467.7028198242188</v>
+        <v>456.4839782714844</v>
       </c>
       <c r="F88" t="n">
-        <v>28545800</v>
+        <v>28184300</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B89" t="n">
-        <v>463.5193621312372</v>
+        <v>461.1940901109254</v>
       </c>
       <c r="C89" t="n">
-        <v>465.2484135478969</v>
+        <v>461.3232754170305</v>
       </c>
       <c r="D89" t="n">
-        <v>454.2879494306214</v>
+        <v>453.0259094171898</v>
       </c>
       <c r="E89" t="n">
-        <v>456.4840087890625</v>
+        <v>453.7811279296875</v>
       </c>
       <c r="F89" t="n">
-        <v>28184300</v>
+        <v>23225800</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B90" t="n">
-        <v>461.1940901109254</v>
+        <v>454.943705849665</v>
       </c>
       <c r="C90" t="n">
-        <v>461.3232754170305</v>
+        <v>460.2699307681697</v>
       </c>
       <c r="D90" t="n">
-        <v>453.0259094171898</v>
+        <v>453.6022408650948</v>
       </c>
       <c r="E90" t="n">
-        <v>453.7811279296875</v>
+        <v>456.9609069824219</v>
       </c>
       <c r="F90" t="n">
-        <v>23225800</v>
+        <v>34246700</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B91" t="n">
-        <v>454.9437666153887</v>
+        <v>448.3754483517362</v>
       </c>
       <c r="C91" t="n">
-        <v>460.2699922453042</v>
+        <v>453.9202579221624</v>
       </c>
       <c r="D91" t="n">
-        <v>453.6023014516422</v>
+        <v>446.4476759522066</v>
       </c>
       <c r="E91" t="n">
-        <v>456.9609680175781</v>
+        <v>451.6546325683594</v>
       </c>
       <c r="F91" t="n">
-        <v>34246700</v>
+        <v>26130000</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B92" t="n">
-        <v>448.3754180557273</v>
+        <v>449.7467399398739</v>
       </c>
       <c r="C92" t="n">
-        <v>453.9202272514996</v>
+        <v>449.836168925793</v>
       </c>
       <c r="D92" t="n">
-        <v>446.4476457864541</v>
+        <v>435.9144806057656</v>
       </c>
       <c r="E92" t="n">
-        <v>451.6546020507812</v>
+        <v>441.3102416992188</v>
       </c>
       <c r="F92" t="n">
-        <v>26130000</v>
+        <v>37980500</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B93" t="n">
-        <v>449.7467088388933</v>
+        <v>444.7981003997206</v>
       </c>
       <c r="C93" t="n">
-        <v>449.8361378186282</v>
+        <v>449.9851935867555</v>
       </c>
       <c r="D93" t="n">
-        <v>435.9144504613163</v>
+        <v>441.8965257028684</v>
       </c>
       <c r="E93" t="n">
-        <v>441.3102111816406</v>
+        <v>448.2959289550781</v>
       </c>
       <c r="F93" t="n">
-        <v>37980500</v>
+        <v>25349400</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B94" t="n">
-        <v>444.7981003997206</v>
+        <v>449.0213193023424</v>
       </c>
       <c r="C94" t="n">
-        <v>449.9851935867555</v>
+        <v>468.1301005814363</v>
       </c>
       <c r="D94" t="n">
-        <v>441.8965257028684</v>
+        <v>447.6897705604439</v>
       </c>
       <c r="E94" t="n">
-        <v>448.2959289550781</v>
+        <v>463.0125732421875</v>
       </c>
       <c r="F94" t="n">
-        <v>25349400</v>
+        <v>38000200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B95" t="n">
-        <v>449.0213193023424</v>
+        <v>462.3766075757791</v>
       </c>
       <c r="C95" t="n">
-        <v>468.1301005814363</v>
+        <v>471.2602507862521</v>
       </c>
       <c r="D95" t="n">
-        <v>447.6897705604439</v>
+        <v>459.0874767807031</v>
       </c>
       <c r="E95" t="n">
-        <v>463.0125732421875</v>
+        <v>467.3152770996094</v>
       </c>
       <c r="F95" t="n">
-        <v>38000200</v>
+        <v>29291200</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B96" t="n">
-        <v>462.3766075757791</v>
+        <v>470.7136916421546</v>
       </c>
       <c r="C96" t="n">
-        <v>471.2602507862521</v>
+        <v>479.8258647405344</v>
       </c>
       <c r="D96" t="n">
-        <v>459.0874767807031</v>
+        <v>470.1770874429818</v>
       </c>
       <c r="E96" t="n">
-        <v>467.3152770996094</v>
+        <v>477.55029296875</v>
       </c>
       <c r="F96" t="n">
-        <v>29291200</v>
+        <v>29213900</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B97" t="n">
-        <v>470.7137217228436</v>
+        <v>480.1637455245844</v>
       </c>
       <c r="C97" t="n">
-        <v>479.8258954035317</v>
+        <v>480.6904030927037</v>
       </c>
       <c r="D97" t="n">
-        <v>470.1771174893794</v>
+        <v>474.9865988275796</v>
       </c>
       <c r="E97" t="n">
-        <v>477.5503234863281</v>
+        <v>478.5937194824219</v>
       </c>
       <c r="F97" t="n">
-        <v>29213900</v>
+        <v>36875400</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B98" t="n">
-        <v>480.1637149068934</v>
+        <v>437.2161962654454</v>
       </c>
       <c r="C98" t="n">
-        <v>480.6903724414303</v>
+        <v>439.7103823757502</v>
       </c>
       <c r="D98" t="n">
-        <v>474.9865685400099</v>
+        <v>418.365786117595</v>
       </c>
       <c r="E98" t="n">
-        <v>478.5936889648438</v>
+        <v>430.7671203613281</v>
       </c>
       <c r="F98" t="n">
-        <v>36875400</v>
+        <v>128855300</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B99" t="n">
-        <v>437.2162272399066</v>
+        <v>436.4014165119217</v>
       </c>
       <c r="C99" t="n">
-        <v>439.7104135269112</v>
+        <v>436.8286984461687</v>
       </c>
       <c r="D99" t="n">
-        <v>418.365815756604</v>
+        <v>423.7616041817895</v>
       </c>
       <c r="E99" t="n">
-        <v>430.7671508789062</v>
+        <v>427.577392578125</v>
       </c>
       <c r="F99" t="n">
-        <v>128855300</v>
+        <v>58566800</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B100" t="n">
-        <v>436.4013853645445</v>
+        <v>427.5276741085398</v>
       </c>
       <c r="C100" t="n">
-        <v>436.8286672682951</v>
+        <v>428.0245220118177</v>
       </c>
       <c r="D100" t="n">
-        <v>423.7615739365565</v>
+        <v>419.588054318219</v>
       </c>
       <c r="E100" t="n">
-        <v>427.5773620605469</v>
+        <v>420.7009887695312</v>
       </c>
       <c r="F100" t="n">
-        <v>58566800</v>
+        <v>42219900</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B101" t="n">
-        <v>427.5276741085398</v>
+        <v>419.3495781995532</v>
       </c>
       <c r="C101" t="n">
-        <v>428.0245220118177</v>
+        <v>419.3893041977899</v>
       </c>
       <c r="D101" t="n">
-        <v>419.588054318219</v>
+        <v>405.9843574339844</v>
       </c>
       <c r="E101" t="n">
-        <v>420.7009887695312</v>
+        <v>408.6176452636719</v>
       </c>
       <c r="F101" t="n">
-        <v>42219900</v>
+        <v>61424100</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B102" t="n">
-        <v>419.3495781995532</v>
+        <v>408.4089654586022</v>
       </c>
       <c r="C102" t="n">
-        <v>419.3893041977899</v>
+        <v>417.1534761899275</v>
       </c>
       <c r="D102" t="n">
-        <v>405.9843574339844</v>
+        <v>406.6600511822617</v>
       </c>
       <c r="E102" t="n">
-        <v>408.6176452636719</v>
+        <v>411.578857421875</v>
       </c>
       <c r="F102" t="n">
-        <v>61424100</v>
+        <v>45012400</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B103" t="n">
-        <v>408.4089957411405</v>
+        <v>404.8714124431945</v>
       </c>
       <c r="C103" t="n">
-        <v>417.1535071208501</v>
+        <v>405.7259762608884</v>
       </c>
       <c r="D103" t="n">
-        <v>406.6600813351222</v>
+        <v>389.8467370491522</v>
       </c>
       <c r="E103" t="n">
-        <v>411.5788879394531</v>
+        <v>391.188232421875</v>
       </c>
       <c r="F103" t="n">
-        <v>45012400</v>
+        <v>66289200</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B104" t="n">
-        <v>404.8714440282318</v>
+        <v>396.6535630940219</v>
       </c>
       <c r="C104" t="n">
-        <v>405.7260079125925</v>
+        <v>399.2570412200398</v>
       </c>
       <c r="D104" t="n">
-        <v>389.8467674620769</v>
+        <v>390.4429643868461</v>
       </c>
       <c r="E104" t="n">
-        <v>391.1882629394531</v>
+        <v>398.6111450195312</v>
       </c>
       <c r="F104" t="n">
-        <v>66289200</v>
+        <v>53515300</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B105" t="n">
-        <v>396.6535630940219</v>
+        <v>402.2977759502542</v>
       </c>
       <c r="C105" t="n">
-        <v>399.2570412200398</v>
+        <v>412.2744908996196</v>
       </c>
       <c r="D105" t="n">
-        <v>390.4429643868461</v>
+        <v>398.3428555009064</v>
       </c>
       <c r="E105" t="n">
-        <v>398.6111450195312</v>
+        <v>410.9926147460938</v>
       </c>
       <c r="F105" t="n">
-        <v>53515300</v>
+        <v>45480500</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B106" t="n">
-        <v>402.2977759502542</v>
+        <v>416.9746475616288</v>
       </c>
       <c r="C106" t="n">
-        <v>412.2744908996196</v>
+        <v>421.0090502850332</v>
       </c>
       <c r="D106" t="n">
-        <v>398.3428555009064</v>
+        <v>410.0982892644293</v>
       </c>
       <c r="E106" t="n">
-        <v>410.9926147460938</v>
+        <v>410.6646728515625</v>
       </c>
       <c r="F106" t="n">
-        <v>45480500</v>
+        <v>44857900</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B107" t="n">
-        <v>416.9746165751398</v>
+        <v>413.5563153661985</v>
       </c>
       <c r="C107" t="n">
-        <v>421.009018998737</v>
+        <v>413.8345489802859</v>
       </c>
       <c r="D107" t="n">
-        <v>410.0982587889407</v>
+        <v>398.4819668946231</v>
       </c>
       <c r="E107" t="n">
-        <v>410.6646423339844</v>
+        <v>401.8207702636719</v>
       </c>
       <c r="F107" t="n">
-        <v>44857900</v>
+        <v>42491000</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B108" t="n">
-        <v>413.5563153661985</v>
+        <v>402.4467839094351</v>
       </c>
       <c r="C108" t="n">
-        <v>413.8345489802859</v>
+        <v>403.6392309547976</v>
       </c>
       <c r="D108" t="n">
-        <v>398.4819668946231</v>
+        <v>395.5008602319473</v>
       </c>
       <c r="E108" t="n">
-        <v>401.8207702636719</v>
+        <v>399.3067016601562</v>
       </c>
       <c r="F108" t="n">
-        <v>42491000</v>
+        <v>40802400</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B109" t="n">
-        <v>402.4468146669985</v>
+        <v>401.900281272875</v>
       </c>
       <c r="C109" t="n">
-        <v>403.6392618034954</v>
+        <v>402.9834060634867</v>
       </c>
       <c r="D109" t="n">
-        <v>395.5008904586587</v>
+        <v>395.5406038478973</v>
       </c>
       <c r="E109" t="n">
-        <v>399.3067321777344</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="F109" t="n">
-        <v>40802400</v>
+        <v>34091600</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B110" t="n">
-        <v>401.900281272875</v>
+        <v>396.7032310749887</v>
       </c>
       <c r="C110" t="n">
-        <v>402.9834060634867</v>
+        <v>397.9950234607705</v>
       </c>
       <c r="D110" t="n">
-        <v>395.5406038478973</v>
+        <v>392.0427954340728</v>
       </c>
       <c r="E110" t="n">
-        <v>398.7900085449219</v>
+        <v>394.3580932617188</v>
       </c>
       <c r="F110" t="n">
-        <v>34091600</v>
+        <v>32078800</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,22 +3303,22 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B111" t="n">
-        <v>396.7032617740463</v>
+        <v>395.6201374553349</v>
       </c>
       <c r="C111" t="n">
-        <v>397.9950542597942</v>
+        <v>400.0222028355481</v>
       </c>
       <c r="D111" t="n">
-        <v>392.0428257724806</v>
+        <v>393.8215503753798</v>
       </c>
       <c r="E111" t="n">
-        <v>394.3581237792969</v>
+        <v>397.0808715820312</v>
       </c>
       <c r="F111" t="n">
-        <v>32078800</v>
+        <v>23223400</v>
       </c>
       <c r="G111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B112" t="n">
-        <v>395.6201070500213</v>
+        <v>399.0727866126232</v>
       </c>
       <c r="C112" t="n">
-        <v>400.0221720919145</v>
+        <v>402.7976819572589</v>
       </c>
       <c r="D112" t="n">
-        <v>393.8215201082963</v>
+        <v>395.0690225854118</v>
       </c>
       <c r="E112" t="n">
-        <v>397.0808410644531</v>
+        <v>396.8517761230469</v>
       </c>
       <c r="F112" t="n">
-        <v>23223400</v>
+        <v>28234000</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,25 +3355,25 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B113" t="n">
-        <v>399.0727866126232</v>
+        <v>394.5112344348997</v>
       </c>
       <c r="C113" t="n">
-        <v>402.7976819572589</v>
+        <v>398.5050592846536</v>
       </c>
       <c r="D113" t="n">
-        <v>395.0690225854118</v>
+        <v>393.5650869938952</v>
       </c>
       <c r="E113" t="n">
-        <v>396.8517761230469</v>
+        <v>395.6267395019531</v>
       </c>
       <c r="F113" t="n">
-        <v>28234000</v>
+        <v>34015200</v>
       </c>
       <c r="G113" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B114" t="n">
-        <v>394.5112344348997</v>
+        <v>393.4057107487328</v>
       </c>
       <c r="C114" t="n">
-        <v>398.5050592846536</v>
+        <v>393.7642431363039</v>
       </c>
       <c r="D114" t="n">
-        <v>393.5650869938952</v>
+        <v>381.5537473139175</v>
       </c>
       <c r="E114" t="n">
-        <v>395.6267395019531</v>
+        <v>382.918212890625</v>
       </c>
       <c r="F114" t="n">
-        <v>34015200</v>
+        <v>43238300</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B115" t="n">
-        <v>393.405742102137</v>
+        <v>382.5895921303232</v>
       </c>
       <c r="C115" t="n">
-        <v>393.7642745182822</v>
+        <v>387.7884945775691</v>
       </c>
       <c r="D115" t="n">
-        <v>381.5537777227514</v>
+        <v>380.1693767219767</v>
       </c>
       <c r="E115" t="n">
-        <v>382.9182434082031</v>
+        <v>387.4299621582031</v>
       </c>
       <c r="F115" t="n">
-        <v>43238300</v>
+        <v>33884700</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B116" t="n">
-        <v>382.5895619940176</v>
+        <v>388.9537605304631</v>
       </c>
       <c r="C116" t="n">
-        <v>387.7884640317496</v>
+        <v>399.8496074643683</v>
       </c>
       <c r="D116" t="n">
-        <v>380.1693467763097</v>
+        <v>388.5852587696308</v>
       </c>
       <c r="E116" t="n">
-        <v>387.429931640625</v>
+        <v>398.9831237792969</v>
       </c>
       <c r="F116" t="n">
-        <v>33884700</v>
+        <v>43625500</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B117" t="n">
-        <v>388.9537605304631</v>
+        <v>403.0765245044552</v>
       </c>
       <c r="C117" t="n">
-        <v>399.8496074643683</v>
+        <v>405.8453028142193</v>
       </c>
       <c r="D117" t="n">
-        <v>388.5852587696308</v>
+        <v>397.1306190557743</v>
       </c>
       <c r="E117" t="n">
-        <v>398.9831237792969</v>
+        <v>400.0986022949219</v>
       </c>
       <c r="F117" t="n">
-        <v>43625500</v>
+        <v>34405900</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B118" t="n">
-        <v>403.0765245044552</v>
+        <v>389.3023679559341</v>
       </c>
       <c r="C118" t="n">
-        <v>405.8453028142193</v>
+        <v>395.2183958601928</v>
       </c>
       <c r="D118" t="n">
-        <v>397.1306190557743</v>
+        <v>388.3064040716401</v>
       </c>
       <c r="E118" t="n">
-        <v>400.0986022949219</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="F118" t="n">
-        <v>34405900</v>
+        <v>51367200</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B119" t="n">
-        <v>389.3023679559341</v>
+        <v>391.2743390590049</v>
       </c>
       <c r="C119" t="n">
-        <v>395.2183958601928</v>
+        <v>399.5707348557469</v>
       </c>
       <c r="D119" t="n">
-        <v>388.3064040716401</v>
+        <v>389.0533591512552</v>
       </c>
       <c r="E119" t="n">
-        <v>391.1548461914062</v>
+        <v>396.9413757324219</v>
       </c>
       <c r="F119" t="n">
-        <v>51367200</v>
+        <v>35474900</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B120" t="n">
-        <v>391.2743390590049</v>
+        <v>391.5532542396072</v>
       </c>
       <c r="C120" t="n">
-        <v>399.5707348557469</v>
+        <v>405.0585220162706</v>
       </c>
       <c r="D120" t="n">
-        <v>389.0533591512552</v>
+        <v>391.0851500003899</v>
       </c>
       <c r="E120" t="n">
-        <v>396.9413757324219</v>
+        <v>402.2996826171875</v>
       </c>
       <c r="F120" t="n">
-        <v>35474900</v>
+        <v>38199200</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B121" t="n">
-        <v>391.5532542396072</v>
+        <v>399.6504140582061</v>
       </c>
       <c r="C121" t="n">
-        <v>405.0585220162706</v>
+        <v>409.3710312257941</v>
       </c>
       <c r="D121" t="n">
-        <v>391.0851500003899</v>
+        <v>398.6942972465368</v>
       </c>
       <c r="E121" t="n">
-        <v>402.2996826171875</v>
+        <v>403.5645751953125</v>
       </c>
       <c r="F121" t="n">
-        <v>38199200</v>
+        <v>35808000</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B122" t="n">
-        <v>399.6504140582061</v>
+        <v>402.7877173292459</v>
       </c>
       <c r="C122" t="n">
-        <v>409.3710312257941</v>
+        <v>409.9486695143622</v>
       </c>
       <c r="D122" t="n">
-        <v>398.6942972465368</v>
+        <v>402.7677785996419</v>
       </c>
       <c r="E122" t="n">
-        <v>403.5645751953125</v>
+        <v>409.0224304199219</v>
       </c>
       <c r="F122" t="n">
-        <v>35808000</v>
+        <v>39001300</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B123" t="n">
-        <v>402.7877173292459</v>
+        <v>407.5484392107423</v>
       </c>
       <c r="C123" t="n">
-        <v>409.9486695143622</v>
+        <v>411.3828759024364</v>
       </c>
       <c r="D123" t="n">
-        <v>402.7677785996419</v>
+        <v>406.8612216895844</v>
       </c>
       <c r="E123" t="n">
-        <v>409.0224304199219</v>
+        <v>407.3093872070312</v>
       </c>
       <c r="F123" t="n">
-        <v>39001300</v>
+        <v>31123900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B124" t="n">
-        <v>407.5484392107423</v>
+        <v>403.2857003455267</v>
       </c>
       <c r="C124" t="n">
-        <v>411.3828759024364</v>
+        <v>408.5543272911556</v>
       </c>
       <c r="D124" t="n">
-        <v>406.8612216895844</v>
+        <v>401.8714182880504</v>
       </c>
       <c r="E124" t="n">
-        <v>407.3093872070312</v>
+        <v>407.757568359375</v>
       </c>
       <c r="F124" t="n">
-        <v>31123900</v>
+        <v>30131900</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B125" t="n">
-        <v>403.2857003455267</v>
+        <v>408.3750692869274</v>
       </c>
       <c r="C125" t="n">
-        <v>408.5543272911556</v>
+        <v>408.5443965203919</v>
       </c>
       <c r="D125" t="n">
-        <v>401.8714182880504</v>
+        <v>401.3037196464309</v>
       </c>
       <c r="E125" t="n">
-        <v>407.757568359375</v>
+        <v>404.122314453125</v>
       </c>
       <c r="F125" t="n">
-        <v>30131900</v>
+        <v>31706400</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B126" t="n">
-        <v>408.3750692869274</v>
+        <v>403.9330670994013</v>
       </c>
       <c r="C126" t="n">
-        <v>408.5443965203919</v>
+        <v>407.3591851847947</v>
       </c>
       <c r="D126" t="n">
-        <v>401.3037196464309</v>
+        <v>399.9691200230297</v>
       </c>
       <c r="E126" t="n">
-        <v>404.122314453125</v>
+        <v>403.245849609375</v>
       </c>
       <c r="F126" t="n">
-        <v>31706400</v>
+        <v>25512100</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B127" t="n">
-        <v>403.9330670994013</v>
+        <v>402.9968765568314</v>
       </c>
       <c r="C127" t="n">
-        <v>407.3591851847947</v>
+        <v>404.4808530373378</v>
       </c>
       <c r="D127" t="n">
-        <v>399.9691200230297</v>
+        <v>400.0886486036874</v>
       </c>
       <c r="E127" t="n">
-        <v>403.245849609375</v>
+        <v>400.238037109375</v>
       </c>
       <c r="F127" t="n">
-        <v>25512100</v>
+        <v>27263900</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B128" t="n">
-        <v>402.9968458288957</v>
+        <v>399.3815063856616</v>
       </c>
       <c r="C128" t="n">
-        <v>404.4808221962511</v>
+        <v>403.1661568819284</v>
       </c>
       <c r="D128" t="n">
-        <v>400.0886180975</v>
+        <v>392.6587503554791</v>
       </c>
       <c r="E128" t="n">
-        <v>400.2380065917969</v>
+        <v>393.9534912109375</v>
       </c>
       <c r="F128" t="n">
-        <v>27263900</v>
+        <v>26848000</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B129" t="n">
-        <v>399.3815063856616</v>
+        <v>396.4633374914087</v>
       </c>
       <c r="C129" t="n">
-        <v>403.1661568819284</v>
+        <v>399.013002518604</v>
       </c>
       <c r="D129" t="n">
-        <v>392.6587503554791</v>
+        <v>393.1965772756644</v>
       </c>
       <c r="E129" t="n">
-        <v>393.9534912109375</v>
+        <v>398.3357543945312</v>
       </c>
       <c r="F129" t="n">
-        <v>26848000</v>
+        <v>27733700</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B130" t="n">
-        <v>396.4633374914087</v>
+        <v>398.6544268926901</v>
       </c>
       <c r="C130" t="n">
-        <v>399.013002518604</v>
+        <v>402.7677623283013</v>
       </c>
       <c r="D130" t="n">
-        <v>393.1965772756644</v>
+        <v>396.1446090107731</v>
       </c>
       <c r="E130" t="n">
-        <v>398.3357543945312</v>
+        <v>397.7979125976562</v>
       </c>
       <c r="F130" t="n">
-        <v>27733700</v>
+        <v>26228300</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B131" t="n">
-        <v>398.6544574759768</v>
+        <v>395.5271533612366</v>
       </c>
       <c r="C131" t="n">
-        <v>402.7677932271478</v>
+        <v>396.3936371018467</v>
       </c>
       <c r="D131" t="n">
-        <v>396.1446394015159</v>
+        <v>389.4218897156333</v>
       </c>
       <c r="E131" t="n">
-        <v>397.7979431152344</v>
+        <v>390.2087097167969</v>
       </c>
       <c r="F131" t="n">
-        <v>26228300</v>
+        <v>25908500</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B132" t="n">
-        <v>395.5271224277118</v>
+        <v>388.5255176358589</v>
       </c>
       <c r="C132" t="n">
-        <v>396.3936061005556</v>
+        <v>390.9058555160312</v>
       </c>
       <c r="D132" t="n">
-        <v>389.421859259591</v>
+        <v>385.4977789148814</v>
       </c>
       <c r="E132" t="n">
-        <v>390.2086791992188</v>
+        <v>387.4498596191406</v>
       </c>
       <c r="F132" t="n">
-        <v>25908500</v>
+        <v>25138800</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B133" t="n">
-        <v>388.5255176358589</v>
+        <v>385.2288911868192</v>
       </c>
       <c r="C133" t="n">
-        <v>390.9058555160312</v>
+        <v>385.4380350985318</v>
       </c>
       <c r="D133" t="n">
-        <v>385.4977789148814</v>
+        <v>378.5857985003418</v>
       </c>
       <c r="E133" t="n">
-        <v>387.4498596191406</v>
+        <v>380.3287353515625</v>
       </c>
       <c r="F133" t="n">
-        <v>25138800</v>
+        <v>50853200</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B134" t="n">
-        <v>385.2288602760525</v>
+        <v>382.3505545919761</v>
       </c>
       <c r="C134" t="n">
-        <v>385.4380041709834</v>
+        <v>385.6471928372158</v>
       </c>
       <c r="D134" t="n">
-        <v>378.5857681226169</v>
+        <v>380.1395134056624</v>
       </c>
       <c r="E134" t="n">
-        <v>380.3287048339844</v>
+        <v>381.4541931152344</v>
       </c>
       <c r="F134" t="n">
-        <v>50853200</v>
+        <v>29680100</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B135" t="n">
-        <v>382.3505545919761</v>
+        <v>380.8167328036651</v>
       </c>
       <c r="C135" t="n">
-        <v>385.6471928372158</v>
+        <v>380.9263046350485</v>
       </c>
       <c r="D135" t="n">
-        <v>380.1395134056624</v>
+        <v>370.3491731415432</v>
       </c>
       <c r="E135" t="n">
-        <v>381.4541931152344</v>
+        <v>371.2355651855469</v>
       </c>
       <c r="F135" t="n">
-        <v>29680100</v>
+        <v>42733600</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B136" t="n">
-        <v>380.8167328036651</v>
+        <v>375.3987224826456</v>
       </c>
       <c r="C136" t="n">
-        <v>380.9263046350485</v>
+        <v>375.5381416220395</v>
       </c>
       <c r="D136" t="n">
-        <v>370.3491731415432</v>
+        <v>368.1381372201017</v>
       </c>
       <c r="E136" t="n">
-        <v>371.2355651855469</v>
+        <v>369.5424499511719</v>
       </c>
       <c r="F136" t="n">
-        <v>42733600</v>
+        <v>31181200</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B137" t="n">
-        <v>375.3987224826456</v>
+        <v>369.3233510512375</v>
       </c>
       <c r="C137" t="n">
-        <v>375.5381416220395</v>
+        <v>373.2076042912997</v>
       </c>
       <c r="D137" t="n">
-        <v>368.1381372201017</v>
+        <v>363.7160692738626</v>
       </c>
       <c r="E137" t="n">
-        <v>369.5424499511719</v>
+        <v>364.492919921875</v>
       </c>
       <c r="F137" t="n">
-        <v>31181200</v>
+        <v>36836600</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B138" t="n">
-        <v>369.3233201292261</v>
+        <v>360.4393165791876</v>
       </c>
       <c r="C138" t="n">
-        <v>373.2075730440749</v>
+        <v>360.9871149414508</v>
       </c>
       <c r="D138" t="n">
-        <v>363.7160388213271</v>
+        <v>355.0710871532006</v>
       </c>
       <c r="E138" t="n">
-        <v>364.4928894042969</v>
+        <v>355.3300170898438</v>
       </c>
       <c r="F138" t="n">
-        <v>36836600</v>
+        <v>37883400</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B139" t="n">
-        <v>360.4393475355787</v>
+        <v>360.4393055378546</v>
       </c>
       <c r="C139" t="n">
-        <v>360.9871459448897</v>
+        <v>363.8853318939423</v>
       </c>
       <c r="D139" t="n">
-        <v>355.0711176485405</v>
+        <v>354.8419936524484</v>
       </c>
       <c r="E139" t="n">
-        <v>355.3300476074219</v>
+        <v>357.5111694335938</v>
       </c>
       <c r="F139" t="n">
-        <v>37883400</v>
+        <v>44797000</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B140" t="n">
-        <v>360.4393363053819</v>
+        <v>363.0786217954557</v>
       </c>
       <c r="C140" t="n">
-        <v>363.8853629556265</v>
+        <v>371.3949263066763</v>
       </c>
       <c r="D140" t="n">
-        <v>354.8420239421825</v>
+        <v>361.6046146993887</v>
       </c>
       <c r="E140" t="n">
-        <v>357.5111999511719</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="F140" t="n">
-        <v>44797000</v>
+        <v>45244400</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B141" t="n">
-        <v>363.0786217954557</v>
+        <v>371.9825473134139</v>
       </c>
       <c r="C141" t="n">
-        <v>371.3949263066763</v>
+        <v>372.4805292634522</v>
       </c>
       <c r="D141" t="n">
-        <v>361.6046146993887</v>
+        <v>366.7139201659809</v>
       </c>
       <c r="E141" t="n">
-        <v>368.6759643554688</v>
+        <v>367.8791809082031</v>
       </c>
       <c r="F141" t="n">
-        <v>45244400</v>
+        <v>29417200</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B142" t="n">
-        <v>371.9825473134139</v>
+        <v>365.7278929006101</v>
       </c>
       <c r="C142" t="n">
-        <v>372.4805292634522</v>
+        <v>372.1319638369453</v>
       </c>
       <c r="D142" t="n">
-        <v>366.7139201659809</v>
+        <v>362.680245817395</v>
       </c>
       <c r="E142" t="n">
-        <v>367.8791809082031</v>
+        <v>371.9526672363281</v>
       </c>
       <c r="F142" t="n">
-        <v>29417200</v>
+        <v>24099100</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B143" t="n">
-        <v>365.7278929006101</v>
+        <v>371.9825233505957</v>
       </c>
       <c r="C143" t="n">
-        <v>372.1319638369453</v>
+        <v>372.2215753394107</v>
       </c>
       <c r="D143" t="n">
-        <v>362.680245817395</v>
+        <v>368.0086373714944</v>
       </c>
       <c r="E143" t="n">
-        <v>371.9526672363281</v>
+        <v>371.375</v>
       </c>
       <c r="F143" t="n">
-        <v>24099100</v>
+        <v>16146600</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B144" t="n">
-        <v>371.9825539180967</v>
+        <v>368.8452727581139</v>
       </c>
       <c r="C144" t="n">
-        <v>372.2216059265558</v>
+        <v>370.9467724245638</v>
       </c>
       <c r="D144" t="n">
-        <v>368.0086676124431</v>
+        <v>365.080530373921</v>
       </c>
       <c r="E144" t="n">
-        <v>371.3750305175781</v>
+        <v>370.7874145507812</v>
       </c>
       <c r="F144" t="n">
-        <v>16146600</v>
+        <v>21443300</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B145" t="n">
-        <v>368.8452727581139</v>
+        <v>383.426192668859</v>
       </c>
       <c r="C145" t="n">
-        <v>370.9467724245638</v>
+        <v>383.4461010048471</v>
       </c>
       <c r="D145" t="n">
-        <v>365.080530373921</v>
+        <v>369.9109552686541</v>
       </c>
       <c r="E145" t="n">
-        <v>370.7874145507812</v>
+        <v>372.8191528320312</v>
       </c>
       <c r="F145" t="n">
-        <v>21443300</v>
+        <v>33064800</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B146" t="n">
-        <v>383.4261612830284</v>
+        <v>370.9965632857518</v>
       </c>
       <c r="C146" t="n">
-        <v>383.4460696173869</v>
+        <v>371.9925272140356</v>
       </c>
       <c r="D146" t="n">
-        <v>369.9109249891301</v>
+        <v>365.5685477188417</v>
       </c>
       <c r="E146" t="n">
-        <v>372.8191223144531</v>
+        <v>371.5642700195312</v>
       </c>
       <c r="F146" t="n">
-        <v>33064800</v>
+        <v>30435300</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B147" t="n">
-        <v>370.9965328148009</v>
+        <v>371.4746381283788</v>
       </c>
       <c r="C147" t="n">
-        <v>371.9924966612836</v>
+        <v>374.1239058336084</v>
       </c>
       <c r="D147" t="n">
-        <v>365.5685176937085</v>
+        <v>368.5365323725683</v>
       </c>
       <c r="E147" t="n">
-        <v>371.5642395019531</v>
+        <v>369.3731384277344</v>
       </c>
       <c r="F147" t="n">
-        <v>30435300</v>
+        <v>28111100</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B148" t="n">
-        <v>371.4746074371751</v>
+        <v>372.1020528926679</v>
       </c>
       <c r="C148" t="n">
-        <v>374.1238749235223</v>
+        <v>382.9879612673769</v>
       </c>
       <c r="D148" t="n">
-        <v>368.5365019241105</v>
+        <v>369.5225100750242</v>
       </c>
       <c r="E148" t="n">
-        <v>369.3731079101562</v>
+        <v>382.8186340332031</v>
       </c>
       <c r="F148" t="n">
-        <v>28111100</v>
+        <v>35745800</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B149" t="n">
-        <v>372.1020528926679</v>
+        <v>386.3543213772784</v>
       </c>
       <c r="C149" t="n">
-        <v>382.9879612673769</v>
+        <v>393.0969858972055</v>
       </c>
       <c r="D149" t="n">
-        <v>369.5225100750242</v>
+        <v>384.95994763093</v>
       </c>
       <c r="E149" t="n">
-        <v>382.8186340332031</v>
+        <v>391.5233459472656</v>
       </c>
       <c r="F149" t="n">
-        <v>35745800</v>
+        <v>37504500</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B150" t="n">
-        <v>386.3543213772784</v>
+        <v>396.3936283702306</v>
       </c>
       <c r="C150" t="n">
-        <v>393.0969858972055</v>
+        <v>412.6975523926047</v>
       </c>
       <c r="D150" t="n">
-        <v>384.95994763093</v>
+        <v>395.1287651714373</v>
       </c>
       <c r="E150" t="n">
-        <v>391.5233459472656</v>
+        <v>409.5602722167969</v>
       </c>
       <c r="F150" t="n">
-        <v>37504500</v>
+        <v>45063400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B151" t="n">
-        <v>396.3936283702306</v>
+        <v>418.1653718785589</v>
       </c>
       <c r="C151" t="n">
-        <v>412.6975523926047</v>
+        <v>419.1215190686066</v>
       </c>
       <c r="D151" t="n">
-        <v>395.1287651714373</v>
+        <v>410.4765600541581</v>
       </c>
       <c r="E151" t="n">
-        <v>409.5602722167969</v>
+        <v>418.5637817382812</v>
       </c>
       <c r="F151" t="n">
-        <v>45063400</v>
+        <v>41642400</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B152" t="n">
-        <v>418.1653718785589</v>
+        <v>423.105393156615</v>
       </c>
       <c r="C152" t="n">
-        <v>419.1215190686066</v>
+        <v>429.8380884820792</v>
       </c>
       <c r="D152" t="n">
-        <v>410.4765600541581</v>
+        <v>418.9920573683891</v>
       </c>
       <c r="E152" t="n">
-        <v>418.5637817382812</v>
+        <v>421.0835876464844</v>
       </c>
       <c r="F152" t="n">
-        <v>41642400</v>
+        <v>48568200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B153" t="n">
-        <v>423.105393156615</v>
+        <v>419.4501847919345</v>
       </c>
       <c r="C153" t="n">
-        <v>429.8380884820792</v>
+        <v>421.6213787702164</v>
       </c>
       <c r="D153" t="n">
-        <v>418.9920573683891</v>
+        <v>414.6197538627068</v>
       </c>
       <c r="E153" t="n">
-        <v>421.0835876464844</v>
+        <v>416.3826293945312</v>
       </c>
       <c r="F153" t="n">
-        <v>48568200</v>
+        <v>27582200</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B154" t="n">
-        <v>419.4501847919345</v>
+        <v>418.5438671501557</v>
       </c>
       <c r="C154" t="n">
-        <v>421.6213787702164</v>
+        <v>425.4558591722327</v>
       </c>
       <c r="D154" t="n">
-        <v>414.6197538627068</v>
+        <v>415.5161587235818</v>
       </c>
       <c r="E154" t="n">
-        <v>416.3826293945312</v>
+        <v>422.4480590820312</v>
       </c>
       <c r="F154" t="n">
-        <v>27582200</v>
+        <v>32048500</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B155" t="n">
-        <v>418.5438369146158</v>
+        <v>424.4698510786937</v>
       </c>
       <c r="C155" t="n">
-        <v>425.4558284373716</v>
+        <v>431.9495495900464</v>
       </c>
       <c r="D155" t="n">
-        <v>415.516128706763</v>
+        <v>421.9600330275293</v>
       </c>
       <c r="E155" t="n">
-        <v>422.4480285644531</v>
+        <v>431.1726989746094</v>
       </c>
       <c r="F155" t="n">
-        <v>32048500</v>
+        <v>29378200</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B156" t="n">
-        <v>424.4698510786937</v>
+        <v>418.1952652760787</v>
       </c>
       <c r="C156" t="n">
-        <v>431.9495495900464</v>
+        <v>421.9500379562064</v>
       </c>
       <c r="D156" t="n">
-        <v>421.9600330275293</v>
+        <v>409.7494810939023</v>
       </c>
       <c r="E156" t="n">
-        <v>431.1726989746094</v>
+        <v>414.0719604492188</v>
       </c>
       <c r="F156" t="n">
-        <v>29378200</v>
+        <v>38308000</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B157" t="n">
-        <v>418.195296097549</v>
+        <v>415.2870711617039</v>
       </c>
       <c r="C157" t="n">
-        <v>421.9500690544079</v>
+        <v>423.2348740747397</v>
       </c>
       <c r="D157" t="n">
-        <v>409.7495112929088</v>
+        <v>414.1217800179737</v>
       </c>
       <c r="E157" t="n">
-        <v>414.0719909667969</v>
+        <v>422.9061889648438</v>
       </c>
       <c r="F157" t="n">
-        <v>38308000</v>
+        <v>27457400</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B158" t="n">
-        <v>415.2870711617039</v>
+        <v>420.6752229306716</v>
       </c>
       <c r="C158" t="n">
-        <v>423.2348740747397</v>
+        <v>425.3861125683125</v>
       </c>
       <c r="D158" t="n">
-        <v>414.1217800179737</v>
+        <v>415.3866572294081</v>
       </c>
       <c r="E158" t="n">
-        <v>422.9061889648438</v>
+        <v>423.1053771972656</v>
       </c>
       <c r="F158" t="n">
-        <v>27457400</v>
+        <v>30867300</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B159" t="n">
-        <v>420.6752229306716</v>
+        <v>422.8563830057505</v>
       </c>
       <c r="C159" t="n">
-        <v>425.3861125683125</v>
+        <v>428.1847957314844</v>
       </c>
       <c r="D159" t="n">
-        <v>415.3866572294081</v>
+        <v>420.197146128082</v>
       </c>
       <c r="E159" t="n">
-        <v>423.1053771972656</v>
+        <v>427.5174865722656</v>
       </c>
       <c r="F159" t="n">
-        <v>30867300</v>
+        <v>30438100</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B160" t="n">
-        <v>422.8563830057505</v>
+        <v>422.866306449911</v>
       </c>
       <c r="C160" t="n">
-        <v>428.1847957314844</v>
+        <v>425.0972860808559</v>
       </c>
       <c r="D160" t="n">
-        <v>420.197146128082</v>
+        <v>418.5936435346858</v>
       </c>
       <c r="E160" t="n">
-        <v>427.5174865722656</v>
+        <v>422.7467956542969</v>
       </c>
       <c r="F160" t="n">
-        <v>30438100</v>
+        <v>38288300</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B161" t="n">
-        <v>422.8663369761165</v>
+        <v>409.1519246549498</v>
       </c>
       <c r="C161" t="n">
-        <v>425.0973167681131</v>
+        <v>412.7473701155562</v>
       </c>
       <c r="D161" t="n">
-        <v>418.593673752453</v>
+        <v>396.4035989759817</v>
       </c>
       <c r="E161" t="n">
-        <v>422.746826171875</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="F161" t="n">
-        <v>38288300</v>
+        <v>70909400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B162" t="n">
-        <v>409.1519246549498</v>
+        <v>411.1338775963461</v>
       </c>
       <c r="C162" t="n">
-        <v>412.7473701155562</v>
+        <v>415.4264794885345</v>
       </c>
       <c r="D162" t="n">
-        <v>396.4035989759817</v>
+        <v>408.7834174283456</v>
       </c>
       <c r="E162" t="n">
-        <v>406.1341552734375</v>
+        <v>412.7672729492188</v>
       </c>
       <c r="F162" t="n">
-        <v>70909400</v>
+        <v>31372400</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B163" t="n">
-        <v>411.1338775963461</v>
+        <v>409.8789700952638</v>
       </c>
       <c r="C163" t="n">
-        <v>415.4264794885345</v>
+        <v>419.0816663151199</v>
       </c>
       <c r="D163" t="n">
-        <v>408.7834174283456</v>
+        <v>409.1419361803058</v>
       </c>
       <c r="E163" t="n">
-        <v>412.7672729492188</v>
+        <v>411.9505615234375</v>
       </c>
       <c r="F163" t="n">
-        <v>31372400</v>
+        <v>28066500</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B164" t="n">
-        <v>409.8789700952638</v>
+        <v>413.6437352165572</v>
       </c>
       <c r="C164" t="n">
-        <v>419.0816663151199</v>
+        <v>415.0978340035471</v>
       </c>
       <c r="D164" t="n">
-        <v>409.1419361803058</v>
+        <v>407.1500311208482</v>
       </c>
       <c r="E164" t="n">
-        <v>411.9505615234375</v>
+        <v>409.7196350097656</v>
       </c>
       <c r="F164" t="n">
-        <v>28066500</v>
+        <v>25700900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B165" t="n">
-        <v>413.6437044066962</v>
+        <v>406.3532485673598</v>
       </c>
       <c r="C165" t="n">
-        <v>415.0978030853789</v>
+        <v>416.7312052008779</v>
       </c>
       <c r="D165" t="n">
-        <v>407.1500007946646</v>
+        <v>403.4748984673602</v>
       </c>
       <c r="E165" t="n">
-        <v>409.7196044921875</v>
+        <v>412.2891845703125</v>
       </c>
       <c r="F165" t="n">
-        <v>25700900</v>
+        <v>30285900</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B166" t="n">
-        <v>406.3532485673598</v>
+        <v>418.4143764918961</v>
       </c>
       <c r="C166" t="n">
-        <v>416.7312052008779</v>
+        <v>426.2526378609755</v>
       </c>
       <c r="D166" t="n">
-        <v>403.4748984673602</v>
+        <v>417.0698495518934</v>
       </c>
       <c r="E166" t="n">
-        <v>412.2891845703125</v>
+        <v>419.0717163085938</v>
       </c>
       <c r="F166" t="n">
-        <v>30285900</v>
+        <v>34942400</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B167" t="n">
-        <v>418.4143764918961</v>
+        <v>415.7053764922729</v>
       </c>
       <c r="C167" t="n">
-        <v>426.2526378609755</v>
+        <v>416.9403619714099</v>
       </c>
       <c r="D167" t="n">
-        <v>417.0698495518934</v>
+        <v>412.3290443657605</v>
       </c>
       <c r="E167" t="n">
-        <v>419.0717163085938</v>
+        <v>413.4445190429688</v>
       </c>
       <c r="F167" t="n">
-        <v>34942400</v>
+        <v>33383800</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B168" t="n">
-        <v>415.7053764922729</v>
+        <v>406.223770451025</v>
       </c>
       <c r="C168" t="n">
-        <v>416.9403619714099</v>
+        <v>411.0243235004914</v>
       </c>
       <c r="D168" t="n">
-        <v>412.3290443657605</v>
+        <v>403.8633409907068</v>
       </c>
       <c r="E168" t="n">
-        <v>413.4445190429688</v>
+        <v>410.9944458007812</v>
       </c>
       <c r="F168" t="n">
-        <v>33383800</v>
+        <v>35657900</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B169" t="n">
-        <v>406.223770451025</v>
+        <v>412.8071154720842</v>
       </c>
       <c r="C169" t="n">
-        <v>411.0243235004914</v>
+        <v>413.8229876767416</v>
       </c>
       <c r="D169" t="n">
-        <v>403.8633409907068</v>
+        <v>404.9987623844293</v>
       </c>
       <c r="E169" t="n">
-        <v>410.9944458007812</v>
+        <v>406.1241760253906</v>
       </c>
       <c r="F169" t="n">
-        <v>35657900</v>
+        <v>38594200</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B170" t="n">
-        <v>412.8071154720842</v>
+        <v>401.5726571524119</v>
       </c>
       <c r="C170" t="n">
-        <v>413.8229876767416</v>
+        <v>404.6700902960666</v>
       </c>
       <c r="D170" t="n">
-        <v>404.9987623844293</v>
+        <v>399.4114021131033</v>
       </c>
       <c r="E170" t="n">
-        <v>406.1241760253906</v>
+        <v>403.5745239257812</v>
       </c>
       <c r="F170" t="n">
-        <v>38594200</v>
+        <v>29667100</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B171" t="n">
-        <v>401.5726571524119</v>
+        <v>402.847493220503</v>
       </c>
       <c r="C171" t="n">
-        <v>404.6700902960666</v>
+        <v>410.1777730080913</v>
       </c>
       <c r="D171" t="n">
-        <v>399.4114021131033</v>
+        <v>399.2620170659624</v>
       </c>
       <c r="E171" t="n">
-        <v>403.5745239257812</v>
+        <v>407.7774963378906</v>
       </c>
       <c r="F171" t="n">
-        <v>29667100</v>
+        <v>27077500</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B172" t="n">
-        <v>402.8474630718804</v>
+        <v>412.5979239362014</v>
       </c>
       <c r="C172" t="n">
-        <v>410.1777423108794</v>
+        <v>426.4418454559798</v>
       </c>
       <c r="D172" t="n">
-        <v>399.2619871856725</v>
+        <v>411.2434277199191</v>
       </c>
       <c r="E172" t="n">
-        <v>407.7774658203125</v>
+        <v>420.2170715332031</v>
       </c>
       <c r="F172" t="n">
-        <v>27077500</v>
+        <v>50771200</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B173" t="n">
-        <v>412.5979239362014</v>
+        <v>414.9384827190711</v>
       </c>
       <c r="C173" t="n">
-        <v>426.4418454559798</v>
+        <v>423.4041760233977</v>
       </c>
       <c r="D173" t="n">
-        <v>411.2434277199191</v>
+        <v>413.9325494355234</v>
       </c>
       <c r="E173" t="n">
-        <v>420.2170715332031</v>
+        <v>421.83056640625</v>
       </c>
       <c r="F173" t="n">
-        <v>50771200</v>
+        <v>32564100</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B174" t="n">
-        <v>414.9384827190711</v>
+        <v>428.1648698947521</v>
       </c>
       <c r="C174" t="n">
-        <v>423.4041760233977</v>
+        <v>430.9535870211983</v>
       </c>
       <c r="D174" t="n">
-        <v>413.9325494355234</v>
+        <v>414.808990493047</v>
       </c>
       <c r="E174" t="n">
-        <v>421.83056640625</v>
+        <v>415.7352600097656</v>
       </c>
       <c r="F174" t="n">
-        <v>32564100</v>
+        <v>33018700</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,22 +4967,22 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B175" t="n">
-        <v>428.1648698947521</v>
+        <v>412.4983595724376</v>
       </c>
       <c r="C175" t="n">
-        <v>430.9535870211983</v>
+        <v>420.3963455784958</v>
       </c>
       <c r="D175" t="n">
-        <v>414.808990493047</v>
+        <v>409.6399178024174</v>
       </c>
       <c r="E175" t="n">
-        <v>415.7352600097656</v>
+        <v>419.3605346679688</v>
       </c>
       <c r="F175" t="n">
-        <v>33018700</v>
+        <v>27864000</v>
       </c>
       <c r="G175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B176" t="n">
-        <v>412.4983595724376</v>
+        <v>423.9518891931334</v>
       </c>
       <c r="C176" t="n">
-        <v>420.3963455784958</v>
+        <v>425.5388979071037</v>
       </c>
       <c r="D176" t="n">
-        <v>409.6399178024174</v>
+        <v>414.928866942535</v>
       </c>
       <c r="E176" t="n">
-        <v>419.3605346679688</v>
+        <v>418.3025207519531</v>
       </c>
       <c r="F176" t="n">
-        <v>27864000</v>
+        <v>31393500</v>
       </c>
       <c r="G176" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,25 +5019,25 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B177" t="n">
-        <v>423.9518891931334</v>
+        <v>418.7517174636334</v>
       </c>
       <c r="C177" t="n">
-        <v>425.5388979071037</v>
+        <v>423.602571187628</v>
       </c>
       <c r="D177" t="n">
-        <v>414.928866942535</v>
+        <v>415.547726934082</v>
       </c>
       <c r="E177" t="n">
-        <v>418.3025207519531</v>
+        <v>417.7835388183594</v>
       </c>
       <c r="F177" t="n">
-        <v>31393500</v>
+        <v>22390300</v>
       </c>
       <c r="G177" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B178" t="n">
-        <v>418.7517174636334</v>
+        <v>415.6475333356961</v>
       </c>
       <c r="C178" t="n">
-        <v>423.602571187628</v>
+        <v>418.9812539216563</v>
       </c>
       <c r="D178" t="n">
-        <v>415.547726934082</v>
+        <v>412.2439369671584</v>
       </c>
       <c r="E178" t="n">
-        <v>417.7835388183594</v>
+        <v>415.248291015625</v>
       </c>
       <c r="F178" t="n">
-        <v>22390300</v>
+        <v>30398000</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B179" t="n">
-        <v>415.6475333356961</v>
+        <v>410.2377382218162</v>
       </c>
       <c r="C179" t="n">
-        <v>418.9812539216563</v>
+        <v>415.15846763645</v>
       </c>
       <c r="D179" t="n">
-        <v>412.2439369671584</v>
+        <v>408.8104019854481</v>
       </c>
       <c r="E179" t="n">
-        <v>415.248291015625</v>
+        <v>411.8946228027344</v>
       </c>
       <c r="F179" t="n">
-        <v>30398000</v>
+        <v>28901500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B180" t="n">
-        <v>410.2377382218162</v>
+        <v>412.2040283766931</v>
       </c>
       <c r="C180" t="n">
-        <v>415.15846763645</v>
+        <v>428.6829856468207</v>
       </c>
       <c r="D180" t="n">
-        <v>408.8104019854481</v>
+        <v>411.8946132983843</v>
       </c>
       <c r="E180" t="n">
-        <v>411.8946228027344</v>
+        <v>426.1876831054688</v>
       </c>
       <c r="F180" t="n">
-        <v>28901500</v>
+        <v>47250500</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B181" t="n">
-        <v>412.2040283766931</v>
+        <v>431.7372486144539</v>
       </c>
       <c r="C181" t="n">
-        <v>428.6829856468207</v>
+        <v>449.4838396905727</v>
       </c>
       <c r="D181" t="n">
-        <v>411.8946132983843</v>
+        <v>431.5476031778621</v>
       </c>
       <c r="E181" t="n">
-        <v>426.1876831054688</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="F181" t="n">
-        <v>47250500</v>
+        <v>79654400</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B182" t="n">
-        <v>431.7372486144539</v>
+        <v>463.9665838370572</v>
       </c>
       <c r="C182" t="n">
-        <v>449.4838396905727</v>
+        <v>465.4438139523178</v>
       </c>
       <c r="D182" t="n">
-        <v>431.5476031778621</v>
+        <v>457.4089212477423</v>
       </c>
       <c r="E182" t="n">
-        <v>449.3940124511719</v>
+        <v>459.6546936035156</v>
       </c>
       <c r="F182" t="n">
-        <v>79654400</v>
+        <v>53628900</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B183" t="n">
-        <v>463.9665838370572</v>
+        <v>446.0403151791343</v>
       </c>
       <c r="C183" t="n">
-        <v>465.4438139523178</v>
+        <v>452.647871293284</v>
       </c>
       <c r="D183" t="n">
-        <v>457.4089212477423</v>
+        <v>439.6024225764256</v>
       </c>
       <c r="E183" t="n">
-        <v>459.6546936035156</v>
+        <v>440.4807739257812</v>
       </c>
       <c r="F183" t="n">
-        <v>53628900</v>
+        <v>37036800</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B184" t="n">
-        <v>446.0403151791343</v>
+        <v>437.6261891093521</v>
       </c>
       <c r="C184" t="n">
-        <v>452.647871293284</v>
+        <v>439.5625463944663</v>
       </c>
       <c r="D184" t="n">
-        <v>439.6024225764256</v>
+        <v>423.4528579325815</v>
       </c>
       <c r="E184" t="n">
-        <v>440.4807739257812</v>
+        <v>426.5370483398438</v>
       </c>
       <c r="F184" t="n">
-        <v>37036800</v>
+        <v>39037000</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B185" t="n">
-        <v>437.6261891093521</v>
+        <v>434.9911260035114</v>
       </c>
       <c r="C185" t="n">
-        <v>439.5625463944663</v>
+        <v>435.3304835003211</v>
       </c>
       <c r="D185" t="n">
-        <v>423.4528579325815</v>
+        <v>425.6087943627414</v>
       </c>
       <c r="E185" t="n">
-        <v>426.5370483398438</v>
+        <v>427.2456970214844</v>
       </c>
       <c r="F185" t="n">
-        <v>39037000</v>
+        <v>26899500</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B186" t="n">
-        <v>434.9911260035114</v>
+        <v>427.5351398188391</v>
       </c>
       <c r="C186" t="n">
-        <v>435.3304835003211</v>
+        <v>428.6630214075295</v>
       </c>
       <c r="D186" t="n">
-        <v>425.6087943627414</v>
+        <v>413.6213308264138</v>
       </c>
       <c r="E186" t="n">
-        <v>427.2456970214844</v>
+        <v>415.8870849609375</v>
       </c>
       <c r="F186" t="n">
-        <v>26899500</v>
+        <v>34782200</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B187" t="n">
-        <v>427.5351398188391</v>
+        <v>413.3618539280056</v>
       </c>
       <c r="C187" t="n">
-        <v>428.6630214075295</v>
+        <v>416.3761684433352</v>
       </c>
       <c r="D187" t="n">
-        <v>413.6213308264138</v>
+        <v>407.7923215775376</v>
       </c>
       <c r="E187" t="n">
-        <v>415.8870849609375</v>
+        <v>410.9663391113281</v>
       </c>
       <c r="F187" t="n">
-        <v>34782200</v>
+        <v>32086700</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B188" t="n">
-        <v>413.3618539280056</v>
+        <v>408.2614433672717</v>
       </c>
       <c r="C188" t="n">
-        <v>416.3761684433352</v>
+        <v>411.2059125875929</v>
       </c>
       <c r="D188" t="n">
-        <v>407.7923215775376</v>
+        <v>397.7312786929967</v>
       </c>
       <c r="E188" t="n">
-        <v>410.9663391113281</v>
+        <v>402.6520080566406</v>
       </c>
       <c r="F188" t="n">
-        <v>32086700</v>
+        <v>35317300</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B189" t="n">
-        <v>408.2614433672717</v>
+        <v>397.8011087010324</v>
       </c>
       <c r="C189" t="n">
-        <v>411.2059125875929</v>
+        <v>404.2789346443135</v>
       </c>
       <c r="D189" t="n">
-        <v>397.7312786929967</v>
+        <v>396.4137363631365</v>
       </c>
       <c r="E189" t="n">
-        <v>402.6520080566406</v>
+        <v>396.6133422851562</v>
       </c>
       <c r="F189" t="n">
-        <v>35317300</v>
+        <v>32576000</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B190" t="n">
-        <v>397.8011087010324</v>
+        <v>394.4674120274286</v>
       </c>
       <c r="C190" t="n">
-        <v>404.2789346443135</v>
+        <v>396.1043451719433</v>
       </c>
       <c r="D190" t="n">
-        <v>396.4137363631365</v>
+        <v>383.278483574852</v>
       </c>
       <c r="E190" t="n">
-        <v>396.6133422851562</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F190" t="n">
-        <v>32576000</v>
+        <v>47224100</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B191" t="n">
-        <v>394.4674120274286</v>
+        <v>390.6945042817559</v>
       </c>
       <c r="C191" t="n">
-        <v>396.1043451719433</v>
+        <v>391.003919361718</v>
       </c>
       <c r="D191" t="n">
-        <v>383.278483574852</v>
+        <v>381.55171206616</v>
       </c>
       <c r="E191" t="n">
-        <v>389.6065673828125</v>
+        <v>390.0057983398438</v>
       </c>
       <c r="F191" t="n">
-        <v>47224100</v>
+        <v>34865800</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B192" t="n">
-        <v>390.6945042817559</v>
+        <v>396.0544203764563</v>
       </c>
       <c r="C192" t="n">
-        <v>391.003919361718</v>
+        <v>400.9951317570601</v>
       </c>
       <c r="D192" t="n">
-        <v>381.55171206616</v>
+        <v>392.1118605058895</v>
       </c>
       <c r="E192" t="n">
-        <v>390.0057983398438</v>
+        <v>399.0088806152344</v>
       </c>
       <c r="F192" t="n">
-        <v>34865800</v>
+        <v>32266400</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B193" t="n">
-        <v>396.0544203764563</v>
+        <v>395.0463355104342</v>
       </c>
       <c r="C193" t="n">
-        <v>400.9951317570601</v>
+        <v>396.094350419825</v>
       </c>
       <c r="D193" t="n">
-        <v>392.1118605058895</v>
+        <v>389.9559121071713</v>
       </c>
       <c r="E193" t="n">
-        <v>399.0088806152344</v>
+        <v>393.0899963378906</v>
       </c>
       <c r="F193" t="n">
-        <v>32266400</v>
+        <v>31506800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B194" t="n">
-        <v>395.0463355104342</v>
+        <v>389.5167169534323</v>
       </c>
       <c r="C194" t="n">
-        <v>396.094350419825</v>
+        <v>389.6364865987809</v>
       </c>
       <c r="D194" t="n">
-        <v>389.9559121071713</v>
+        <v>376.6110198431126</v>
       </c>
       <c r="E194" t="n">
-        <v>393.0899963378906</v>
+        <v>378.1980285644531</v>
       </c>
       <c r="F194" t="n">
-        <v>31506800</v>
+        <v>41987800</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B195" t="n">
-        <v>389.5167169534323</v>
+        <v>377.1100854858111</v>
       </c>
       <c r="C195" t="n">
-        <v>389.6364865987809</v>
+        <v>380.6534028700893</v>
       </c>
       <c r="D195" t="n">
-        <v>376.6110198431126</v>
+        <v>372.5786075934489</v>
       </c>
       <c r="E195" t="n">
-        <v>378.1980285644531</v>
+        <v>378.6871032714844</v>
       </c>
       <c r="F195" t="n">
-        <v>41987800</v>
+        <v>59714200</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B196" t="n">
-        <v>377.1100854858111</v>
+        <v>375.0339909424311</v>
       </c>
       <c r="C196" t="n">
-        <v>380.6534028700893</v>
+        <v>380.9129385065033</v>
       </c>
       <c r="D196" t="n">
-        <v>372.5786075934489</v>
+        <v>366.3802985575179</v>
       </c>
       <c r="E196" t="n">
-        <v>378.6871032714844</v>
+        <v>366.6497802734375</v>
       </c>
       <c r="F196" t="n">
-        <v>59714200</v>
+        <v>45171100</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B197" t="n">
-        <v>375.0339909424311</v>
+        <v>371.6802994138851</v>
       </c>
       <c r="C197" t="n">
-        <v>380.9129385065033</v>
+        <v>376.5112013539488</v>
       </c>
       <c r="D197" t="n">
-        <v>366.3802985575179</v>
+        <v>369.9735210485466</v>
       </c>
       <c r="E197" t="n">
-        <v>366.6497802734375</v>
+        <v>373.2373657226562</v>
       </c>
       <c r="F197" t="n">
-        <v>45171100</v>
+        <v>40647600</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B198" t="n">
-        <v>371.6802994138851</v>
+        <v>370.8718509685315</v>
       </c>
       <c r="C198" t="n">
-        <v>376.5112013539488</v>
+        <v>378.1681135077346</v>
       </c>
       <c r="D198" t="n">
-        <v>369.9735210485466</v>
+        <v>364.0946004167936</v>
       </c>
       <c r="E198" t="n">
-        <v>373.2373657226562</v>
+        <v>364.7733154296875</v>
       </c>
       <c r="F198" t="n">
-        <v>40647600</v>
+        <v>44509900</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B199" t="n">
-        <v>370.8718509685315</v>
+        <v>362.0883479855026</v>
       </c>
       <c r="C199" t="n">
-        <v>378.1681135077346</v>
+        <v>363.5456265920902</v>
       </c>
       <c r="D199" t="n">
-        <v>364.0946004167936</v>
+        <v>348.5438690238404</v>
       </c>
       <c r="E199" t="n">
-        <v>364.7733154296875</v>
+        <v>352.1670227050781</v>
       </c>
       <c r="F199" t="n">
-        <v>44509900</v>
+        <v>66179000</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B200" t="n">
-        <v>362.0883479855026</v>
+        <v>356.4789138154501</v>
       </c>
       <c r="C200" t="n">
-        <v>363.5456265920902</v>
+        <v>375.9023402058053</v>
       </c>
       <c r="D200" t="n">
-        <v>348.5438690238404</v>
+        <v>354.762144454129</v>
       </c>
       <c r="E200" t="n">
-        <v>352.1670227050781</v>
+        <v>372.2691955566406</v>
       </c>
       <c r="F200" t="n">
-        <v>66179000</v>
+        <v>186201600</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B201" t="n">
-        <v>356.4789138154501</v>
+        <v>376.790685328561</v>
       </c>
       <c r="C201" t="n">
-        <v>375.9023402058053</v>
+        <v>379.7850483907747</v>
       </c>
       <c r="D201" t="n">
-        <v>354.762144454129</v>
+        <v>359.2237492715265</v>
       </c>
       <c r="E201" t="n">
-        <v>372.2691955566406</v>
+        <v>367.8774719238281</v>
       </c>
       <c r="F201" t="n">
-        <v>186201600</v>
+        <v>51229900</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B202" t="n">
-        <v>376.790685328561</v>
+        <v>370.3328407149792</v>
       </c>
       <c r="C202" t="n">
-        <v>379.7850483907747</v>
+        <v>373.4469734227558</v>
       </c>
       <c r="D202" t="n">
-        <v>359.2237492715265</v>
+        <v>366.7595808670141</v>
       </c>
       <c r="E202" t="n">
-        <v>367.8774719238281</v>
+        <v>372.319091796875</v>
       </c>
       <c r="F202" t="n">
-        <v>51229900</v>
+        <v>44945700</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B203" t="n">
-        <v>370.3328407149792</v>
+        <v>380.1144231011508</v>
       </c>
       <c r="C203" t="n">
-        <v>373.4469734227558</v>
+        <v>388.099391438806</v>
       </c>
       <c r="D203" t="n">
-        <v>366.7595808670141</v>
+        <v>374.1856121338598</v>
       </c>
       <c r="E203" t="n">
-        <v>372.319091796875</v>
+        <v>383.5579528808594</v>
       </c>
       <c r="F203" t="n">
-        <v>44945700</v>
+        <v>48065800</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B204" t="n">
-        <v>380.1144231011508</v>
+        <v>383.7575696594082</v>
       </c>
       <c r="C204" t="n">
-        <v>388.099391438806</v>
+        <v>391.4630649298244</v>
       </c>
       <c r="D204" t="n">
-        <v>374.1856121338598</v>
+        <v>382.9790365046874</v>
       </c>
       <c r="E204" t="n">
-        <v>383.5579528808594</v>
+        <v>389.7562561035156</v>
       </c>
       <c r="F204" t="n">
-        <v>48065800</v>
+        <v>42128900</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B205" t="n">
-        <v>383.7575696594082</v>
+        <v>386.3127602401041</v>
       </c>
       <c r="C205" t="n">
-        <v>391.4630649298244</v>
+        <v>388.418780928489</v>
       </c>
       <c r="D205" t="n">
-        <v>382.9790365046874</v>
+        <v>380.5036887115837</v>
       </c>
       <c r="E205" t="n">
-        <v>389.7562561035156</v>
+        <v>386.0133056640625</v>
       </c>
       <c r="F205" t="n">
-        <v>42128900</v>
+        <v>34224500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B206" t="n">
-        <v>386.3127602401041</v>
+        <v>391.7525106425778</v>
       </c>
       <c r="C206" t="n">
-        <v>388.418780928489</v>
+        <v>394.8267404517197</v>
       </c>
       <c r="D206" t="n">
-        <v>380.5036887115837</v>
+        <v>387.4905448392632</v>
       </c>
       <c r="E206" t="n">
-        <v>386.0133056640625</v>
+        <v>388.109375</v>
       </c>
       <c r="F206" t="n">
-        <v>34224500</v>
+        <v>29297500</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B207" t="n">
-        <v>391.7525106425778</v>
+        <v>383.3084264217563</v>
       </c>
       <c r="C207" t="n">
-        <v>394.8267404517197</v>
+        <v>384.5860201500421</v>
       </c>
       <c r="D207" t="n">
-        <v>387.4905448392632</v>
+        <v>380.6134873969759</v>
       </c>
       <c r="E207" t="n">
-        <v>388.109375</v>
+        <v>382.6197204589844</v>
       </c>
       <c r="F207" t="n">
-        <v>29297500</v>
+        <v>25908300</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B208" t="n">
-        <v>383.3084264217563</v>
+        <v>373.7464342011831</v>
       </c>
       <c r="C208" t="n">
-        <v>384.5860201500421</v>
+        <v>383.927250494608</v>
       </c>
       <c r="D208" t="n">
-        <v>380.6134873969759</v>
+        <v>372.6484949692805</v>
       </c>
       <c r="E208" t="n">
-        <v>382.6197204589844</v>
+        <v>383.6377868652344</v>
       </c>
       <c r="F208" t="n">
-        <v>25908300</v>
+        <v>31083200</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B209" t="n">
-        <v>373.7464342011831</v>
+        <v>387.071312236775</v>
       </c>
       <c r="C209" t="n">
-        <v>383.927250494608</v>
+        <v>391.1736053926777</v>
       </c>
       <c r="D209" t="n">
-        <v>372.6484949692805</v>
+        <v>380.783162110783</v>
       </c>
       <c r="E209" t="n">
-        <v>383.6377868652344</v>
+        <v>384.3764038085938</v>
       </c>
       <c r="F209" t="n">
-        <v>31083200</v>
+        <v>24644600</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B210" t="n">
-        <v>387.071312236775</v>
+        <v>387.0214381132942</v>
       </c>
       <c r="C210" t="n">
-        <v>391.1736053926777</v>
+        <v>392.9103462310944</v>
       </c>
       <c r="D210" t="n">
-        <v>380.783162110783</v>
+        <v>383.4281962321871</v>
       </c>
       <c r="E210" t="n">
-        <v>384.3764038085938</v>
+        <v>390.2553405761719</v>
       </c>
       <c r="F210" t="n">
-        <v>24644600</v>
+        <v>28914900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B211" t="n">
-        <v>387.0214381132942</v>
+        <v>382.1007052927433</v>
       </c>
       <c r="C211" t="n">
-        <v>392.9103462310944</v>
+        <v>387.460610424238</v>
       </c>
       <c r="D211" t="n">
-        <v>383.4281962321871</v>
+        <v>377.93852713765</v>
       </c>
       <c r="E211" t="n">
-        <v>390.2553405761719</v>
+        <v>384.2067260742188</v>
       </c>
       <c r="F211" t="n">
-        <v>28914900</v>
+        <v>27863900</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B212" t="n">
-        <v>382.1007052927433</v>
+        <v>387.0713224899768</v>
       </c>
       <c r="C212" t="n">
-        <v>387.460610424238</v>
+        <v>398.2103568181361</v>
       </c>
       <c r="D212" t="n">
-        <v>377.93852713765</v>
+        <v>385.6739591427675</v>
       </c>
       <c r="E212" t="n">
-        <v>384.2067260742188</v>
+        <v>394.8866271972656</v>
       </c>
       <c r="F212" t="n">
-        <v>27863900</v>
+        <v>36253700</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B213" t="n">
-        <v>387.0713224899768</v>
+        <v>397.5615778418718</v>
       </c>
       <c r="C213" t="n">
-        <v>398.2103568181361</v>
+        <v>405.2271399033625</v>
       </c>
       <c r="D213" t="n">
-        <v>385.6739591427675</v>
+        <v>391.3133305596497</v>
       </c>
       <c r="E213" t="n">
-        <v>394.8866271972656</v>
+        <v>400.3463439941406</v>
       </c>
       <c r="F213" t="n">
-        <v>36253700</v>
+        <v>37047400</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B214" t="n">
-        <v>397.5615778418718</v>
+        <v>394.1180409920291</v>
       </c>
       <c r="C214" t="n">
-        <v>405.2271399033625</v>
+        <v>397.6414373419786</v>
       </c>
       <c r="D214" t="n">
-        <v>391.3133305596497</v>
+        <v>388.6583483977542</v>
       </c>
       <c r="E214" t="n">
-        <v>400.3463439941406</v>
+        <v>393.0800170898438</v>
       </c>
       <c r="F214" t="n">
-        <v>37047400</v>
+        <v>33049800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B215" t="n">
-        <v>394.1180409920291</v>
+        <v>390.6745569462133</v>
       </c>
       <c r="C215" t="n">
-        <v>397.6414373419786</v>
+        <v>402.4224305318551</v>
       </c>
       <c r="D215" t="n">
-        <v>388.6583483977542</v>
+        <v>388.9178541819168</v>
       </c>
       <c r="E215" t="n">
-        <v>393.0800170898438</v>
+        <v>401.5341186523438</v>
       </c>
       <c r="F215" t="n">
-        <v>33049800</v>
+        <v>27915800</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B216" t="n">
-        <v>390.6745569462133</v>
+        <v>398.0606303262699</v>
       </c>
       <c r="C216" t="n">
-        <v>402.4224305318551</v>
+        <v>400.7156358198418</v>
       </c>
       <c r="D216" t="n">
-        <v>388.9178541819168</v>
+        <v>395.5753188038175</v>
       </c>
       <c r="E216" t="n">
-        <v>401.5341186523438</v>
+        <v>397.0026245117188</v>
       </c>
       <c r="F216" t="n">
-        <v>27915800</v>
+        <v>24126600</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B217" t="n">
-        <v>398.0606303262699</v>
+        <v>398.8291961465565</v>
       </c>
       <c r="C217" t="n">
-        <v>400.7156358198418</v>
+        <v>400.246541441447</v>
       </c>
       <c r="D217" t="n">
-        <v>395.5753188038175</v>
+        <v>386.2329133568751</v>
       </c>
       <c r="E217" t="n">
-        <v>397.0026245117188</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F217" t="n">
-        <v>24126600</v>
+        <v>28142500</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B218" t="n">
-        <v>398.8291961465565</v>
+        <v>389.237256596515</v>
       </c>
       <c r="C218" t="n">
-        <v>400.246541441447</v>
+        <v>391.0438532115061</v>
       </c>
       <c r="D218" t="n">
-        <v>386.2329133568751</v>
+        <v>376.6809075284274</v>
       </c>
       <c r="E218" t="n">
-        <v>389.6065673828125</v>
+        <v>380.8630065917969</v>
       </c>
       <c r="F218" t="n">
-        <v>28142500</v>
+        <v>30351800</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B219" t="n">
-        <v>389.237256596515</v>
+        <v>386.3227418757343</v>
       </c>
       <c r="C219" t="n">
-        <v>391.0438532115061</v>
+        <v>388.299032528898</v>
       </c>
       <c r="D219" t="n">
-        <v>376.6809075284274</v>
+        <v>379.9347732203772</v>
       </c>
       <c r="E219" t="n">
-        <v>380.8630065917969</v>
+        <v>380.9828186035156</v>
       </c>
       <c r="F219" t="n">
-        <v>30351800</v>
+        <v>27659400</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B220" t="n">
-        <v>386.3227418757343</v>
+        <v>389.3470355932277</v>
       </c>
       <c r="C220" t="n">
-        <v>388.299032528898</v>
+        <v>393.4593197982184</v>
       </c>
       <c r="D220" t="n">
-        <v>379.9347732203772</v>
+        <v>387.2609663085435</v>
       </c>
       <c r="E220" t="n">
-        <v>380.9828186035156</v>
+        <v>388.368896484375</v>
       </c>
       <c r="F220" t="n">
-        <v>27659400</v>
+        <v>27856200</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B221" t="n">
-        <v>389.3470355932277</v>
+        <v>392.4212554523594</v>
       </c>
       <c r="C221" t="n">
-        <v>393.4593197982184</v>
+        <v>399.567805457337</v>
       </c>
       <c r="D221" t="n">
-        <v>387.2609663085435</v>
+        <v>390.5647345556998</v>
       </c>
       <c r="E221" t="n">
-        <v>388.368896484375</v>
+        <v>392.6109008789062</v>
       </c>
       <c r="F221" t="n">
-        <v>27856200</v>
+        <v>32367500</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B222" t="n">
-        <v>392.4212554523594</v>
+        <v>392.6607942930367</v>
       </c>
       <c r="C222" t="n">
-        <v>399.567805457337</v>
+        <v>400.4960502148319</v>
       </c>
       <c r="D222" t="n">
-        <v>390.5647345556998</v>
+        <v>388.0095467898306</v>
       </c>
       <c r="E222" t="n">
-        <v>392.6109008789062</v>
+        <v>389.8061828613281</v>
       </c>
       <c r="F222" t="n">
-        <v>32367500</v>
+        <v>47209000</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B223" t="n">
-        <v>392.6607942930367</v>
+        <v>437.0772008696947</v>
       </c>
       <c r="C223" t="n">
-        <v>400.4960502148319</v>
+        <v>457.8281459885008</v>
       </c>
       <c r="D223" t="n">
-        <v>388.0095467898306</v>
+        <v>431.6274684759506</v>
       </c>
       <c r="E223" t="n">
-        <v>389.8061828613281</v>
+        <v>450.2524108886719</v>
       </c>
       <c r="F223" t="n">
-        <v>47209000</v>
+        <v>110160700</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B224" t="n">
-        <v>437.0772008696947</v>
+        <v>449.1544591210436</v>
       </c>
       <c r="C224" t="n">
-        <v>457.8281459885008</v>
+        <v>465.962813447145</v>
       </c>
       <c r="D224" t="n">
-        <v>431.6274684759506</v>
+        <v>448.4857046349594</v>
       </c>
       <c r="E224" t="n">
-        <v>450.2524108886719</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="F224" t="n">
-        <v>110160700</v>
+        <v>60846000</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B225" t="n">
-        <v>449.1544591210436</v>
+        <v>475.2353605631651</v>
       </c>
       <c r="C225" t="n">
-        <v>465.962813447145</v>
+        <v>490.7261876465455</v>
       </c>
       <c r="D225" t="n">
-        <v>448.4857046349594</v>
+        <v>474.1074789501303</v>
       </c>
       <c r="E225" t="n">
-        <v>463.8468017578125</v>
+        <v>486.7337036132812</v>
       </c>
       <c r="F225" t="n">
-        <v>60846000</v>
+        <v>66762100</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B226" t="n">
-        <v>475.2353605631651</v>
+        <v>479.9964078184842</v>
       </c>
       <c r="C226" t="n">
-        <v>490.7261876465455</v>
+        <v>498.5015806515744</v>
       </c>
       <c r="D226" t="n">
-        <v>474.1074789501303</v>
+        <v>478.2696778930625</v>
       </c>
       <c r="E226" t="n">
-        <v>486.7337036132812</v>
+        <v>491.884033203125</v>
       </c>
       <c r="F226" t="n">
-        <v>66762100</v>
+        <v>50455500</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B227" t="n">
-        <v>479.9964078184842</v>
+        <v>495.4273384327132</v>
       </c>
       <c r="C227" t="n">
-        <v>498.5015806515744</v>
+        <v>497.3038108374591</v>
       </c>
       <c r="D227" t="n">
-        <v>478.2696778930625</v>
+        <v>484.7674131728324</v>
       </c>
       <c r="E227" t="n">
-        <v>491.884033203125</v>
+        <v>486.5440673828125</v>
       </c>
       <c r="F227" t="n">
-        <v>50455500</v>
+        <v>33388900</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B228" t="n">
-        <v>495.4273384327132</v>
+        <v>487.6319998350186</v>
       </c>
       <c r="C228" t="n">
-        <v>497.3038108374591</v>
+        <v>500.6175637248969</v>
       </c>
       <c r="D228" t="n">
-        <v>484.7674131728324</v>
+        <v>487.6020574235835</v>
       </c>
       <c r="E228" t="n">
-        <v>486.5440673828125</v>
+        <v>498.9207458496094</v>
       </c>
       <c r="F228" t="n">
-        <v>33388900</v>
+        <v>36441500</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B229" t="n">
-        <v>487.6319998350186</v>
+        <v>498.2719734340298</v>
       </c>
       <c r="C229" t="n">
-        <v>500.6175637248969</v>
+        <v>504.2307569931746</v>
       </c>
       <c r="D229" t="n">
-        <v>487.6020574235835</v>
+        <v>497.7928948509335</v>
       </c>
       <c r="E229" t="n">
-        <v>498.9207458496094</v>
+        <v>499.0505065917969</v>
       </c>
       <c r="F229" t="n">
-        <v>36441500</v>
+        <v>28846200</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B230" t="n">
-        <v>498.2719734340298</v>
+        <v>502.4940586092805</v>
       </c>
       <c r="C230" t="n">
-        <v>504.2307569931746</v>
+        <v>512.7647021753171</v>
       </c>
       <c r="D230" t="n">
-        <v>497.7928948509335</v>
+        <v>501.326243590453</v>
       </c>
       <c r="E230" t="n">
-        <v>499.0505065917969</v>
+        <v>505.109130859375</v>
       </c>
       <c r="F230" t="n">
-        <v>28846200</v>
+        <v>31206100</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B231" t="n">
-        <v>502.4940586092805</v>
+        <v>503.3823542433026</v>
       </c>
       <c r="C231" t="n">
-        <v>512.7647021753171</v>
+        <v>504.3804752506704</v>
       </c>
       <c r="D231" t="n">
-        <v>501.326243590453</v>
+        <v>498.6113370464939</v>
       </c>
       <c r="E231" t="n">
-        <v>505.109130859375</v>
+        <v>502.8633422851562</v>
       </c>
       <c r="F231" t="n">
-        <v>31206100</v>
+        <v>23049800</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B232" t="n">
-        <v>503.3823542433026</v>
+        <v>499.0505227551261</v>
       </c>
       <c r="C232" t="n">
-        <v>504.3804752506704</v>
+        <v>500.557695253814</v>
       </c>
       <c r="D232" t="n">
-        <v>498.6113370464939</v>
+        <v>490.5964364344239</v>
       </c>
       <c r="E232" t="n">
-        <v>502.8633422851562</v>
+        <v>491.5047302246094</v>
       </c>
       <c r="F232" t="n">
-        <v>23049800</v>
+        <v>29001500</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B233" t="n">
-        <v>499.0505227551261</v>
+        <v>492.3431478695614</v>
       </c>
       <c r="C233" t="n">
-        <v>500.557695253814</v>
+        <v>500.3979918654044</v>
       </c>
       <c r="D233" t="n">
-        <v>490.5964364344239</v>
+        <v>492.0836571155829</v>
       </c>
       <c r="E233" t="n">
-        <v>491.5047302246094</v>
+        <v>495.9463806152344</v>
       </c>
       <c r="F233" t="n">
-        <v>29001500</v>
+        <v>23039000</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B234" t="n">
-        <v>492.3431478695614</v>
+        <v>495.427334377905</v>
       </c>
       <c r="C234" t="n">
-        <v>500.3979918654044</v>
+        <v>499.0705004655026</v>
       </c>
       <c r="D234" t="n">
-        <v>492.0836571155829</v>
+        <v>492.991947114923</v>
       </c>
       <c r="E234" t="n">
-        <v>495.9463806152344</v>
+        <v>494.4691467285156</v>
       </c>
       <c r="F234" t="n">
-        <v>23039000</v>
+        <v>16217600</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B235" t="n">
-        <v>495.427334377905</v>
+        <v>489.2190622628328</v>
       </c>
       <c r="C235" t="n">
-        <v>499.0705004655026</v>
+        <v>491.7343163235842</v>
       </c>
       <c r="D235" t="n">
-        <v>492.991947114923</v>
+        <v>477.5110914717105</v>
       </c>
       <c r="E235" t="n">
-        <v>494.4691467285156</v>
+        <v>479.4474487304688</v>
       </c>
       <c r="F235" t="n">
-        <v>16217600</v>
+        <v>29635800</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B236" t="n">
-        <v>489.2190622628328</v>
+        <v>480.6352093836093</v>
       </c>
       <c r="C236" t="n">
-        <v>491.7343163235842</v>
+        <v>483.3600603013466</v>
       </c>
       <c r="D236" t="n">
-        <v>477.5110914717105</v>
+        <v>476.2534434403709</v>
       </c>
       <c r="E236" t="n">
-        <v>479.4474487304688</v>
+        <v>480.7250366210938</v>
       </c>
       <c r="F236" t="n">
-        <v>29635800</v>
+        <v>24087600</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,22 +6579,22 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B237" t="n">
-        <v>480.6352093836093</v>
+        <v>479.1679704739861</v>
       </c>
       <c r="C237" t="n">
-        <v>483.3600603013466</v>
+        <v>488.3806080919379</v>
       </c>
       <c r="D237" t="n">
-        <v>476.2534434403709</v>
+        <v>478.4592826108848</v>
       </c>
       <c r="E237" t="n">
-        <v>480.7250366210938</v>
+        <v>483.3999938964844</v>
       </c>
       <c r="F237" t="n">
-        <v>24087600</v>
+        <v>19961900</v>
       </c>
       <c r="G237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B238" t="n">
-        <v>479.1679704739861</v>
+        <v>483.2999877929688</v>
       </c>
       <c r="C238" t="n">
-        <v>488.3806080919379</v>
+        <v>484.1600036621094</v>
       </c>
       <c r="D238" t="n">
-        <v>478.4592826108848</v>
+        <v>479.5</v>
       </c>
       <c r="E238" t="n">
-        <v>483.3999938964844</v>
+        <v>481.1499938964844</v>
       </c>
       <c r="F238" t="n">
-        <v>19961900</v>
+        <v>20020800</v>
       </c>
       <c r="G238" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,25 +6631,25 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B239" t="n">
-        <v>483.2999877929688</v>
+        <v>479.8800048828125</v>
       </c>
       <c r="C239" t="n">
-        <v>484.1600036621094</v>
+        <v>486.3599853515625</v>
       </c>
       <c r="D239" t="n">
-        <v>479.5</v>
+        <v>478.5299987792969</v>
       </c>
       <c r="E239" t="n">
-        <v>481.1499938964844</v>
+        <v>483.239990234375</v>
       </c>
       <c r="F239" t="n">
-        <v>20020800</v>
+        <v>22510800</v>
       </c>
       <c r="G239" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B240" t="n">
-        <v>479.8800048828125</v>
+        <v>483.2099914550781</v>
       </c>
       <c r="C240" t="n">
-        <v>486.3599853515625</v>
+        <v>490.6099853515625</v>
       </c>
       <c r="D240" t="n">
-        <v>478.5299987792969</v>
+        <v>481.8599853515625</v>
       </c>
       <c r="E240" t="n">
-        <v>483.239990234375</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="F240" t="n">
-        <v>22510800</v>
+        <v>17230800</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B241" t="n">
-        <v>483.2099914550781</v>
+        <v>485.4400024414062</v>
       </c>
       <c r="C241" t="n">
-        <v>490.6099853515625</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="D241" t="n">
-        <v>481.8599853515625</v>
+        <v>484.2999877929688</v>
       </c>
       <c r="E241" t="n">
-        <v>487.3099975585938</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="F241" t="n">
-        <v>17230800</v>
+        <v>19519000</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B242" t="n">
-        <v>485.4400024414062</v>
+        <v>487.8500061035156</v>
       </c>
       <c r="C242" t="n">
-        <v>492.4400024414062</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="D242" t="n">
-        <v>484.2999877929688</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="E242" t="n">
-        <v>491.7099914550781</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="F242" t="n">
-        <v>19519000</v>
+        <v>20758900</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B243" t="n">
-        <v>487.8500061035156</v>
+        <v>494.8800048828125</v>
       </c>
       <c r="C243" t="n">
-        <v>497.3999938964844</v>
+        <v>506.4800109863281</v>
       </c>
       <c r="D243" t="n">
-        <v>487.3099975585938</v>
+        <v>490.0799865722656</v>
       </c>
       <c r="E243" t="n">
-        <v>496.3699951171875</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="F243" t="n">
-        <v>20758900</v>
+        <v>28688800</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B244" t="n">
-        <v>494.8800048828125</v>
+        <v>505.3299865722656</v>
       </c>
       <c r="C244" t="n">
-        <v>506.4800109863281</v>
+        <v>517.780029296875</v>
       </c>
       <c r="D244" t="n">
-        <v>490.0799865722656</v>
+        <v>504.8699951171875</v>
       </c>
       <c r="E244" t="n">
-        <v>505.0599975585938</v>
+        <v>513.530029296875</v>
       </c>
       <c r="F244" t="n">
-        <v>28688800</v>
+        <v>29207300</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B245" t="n">
-        <v>505.3299865722656</v>
+        <v>510.3800048828125</v>
       </c>
       <c r="C245" t="n">
-        <v>517.780029296875</v>
+        <v>512.1900024414062</v>
       </c>
       <c r="D245" t="n">
-        <v>504.8699951171875</v>
+        <v>506.3900146484375</v>
       </c>
       <c r="E245" t="n">
-        <v>513.530029296875</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="F245" t="n">
-        <v>29207300</v>
+        <v>27208900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B246" t="n">
-        <v>510.3800048828125</v>
+        <v>497.5199890136719</v>
       </c>
       <c r="C246" t="n">
-        <v>512.1900024414062</v>
+        <v>505.9700012207031</v>
       </c>
       <c r="D246" t="n">
-        <v>506.3900146484375</v>
+        <v>496.7799987792969</v>
       </c>
       <c r="E246" t="n">
-        <v>507.2900085449219</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="F246" t="n">
-        <v>27208900</v>
+        <v>21046900</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B247" t="n">
-        <v>497.5199890136719</v>
+        <v>499.8500061035156</v>
       </c>
       <c r="C247" t="n">
-        <v>505.9700012207031</v>
+        <v>500.2699890136719</v>
       </c>
       <c r="D247" t="n">
-        <v>496.7799987792969</v>
+        <v>493.8099975585938</v>
       </c>
       <c r="E247" t="n">
-        <v>501.0199890136719</v>
+        <v>496.8200073242188</v>
       </c>
       <c r="F247" t="n">
-        <v>21046900</v>
+        <v>15336100</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B248" t="n">
-        <v>499.8500061035156</v>
+        <v>501.6600036621094</v>
       </c>
       <c r="C248" t="n">
-        <v>500.2699890136719</v>
+        <v>515.6500244140625</v>
       </c>
       <c r="D248" t="n">
-        <v>493.8099975585938</v>
+        <v>500.7999877929688</v>
       </c>
       <c r="E248" t="n">
-        <v>496.8200073242188</v>
+        <v>510.1199951171875</v>
       </c>
       <c r="F248" t="n">
-        <v>15336100</v>
+        <v>24125900</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B249" t="n">
-        <v>501.6600036621094</v>
+        <v>510</v>
       </c>
       <c r="C249" t="n">
-        <v>515.6500244140625</v>
+        <v>511</v>
       </c>
       <c r="D249" t="n">
-        <v>500.7999877929688</v>
+        <v>499.3599853515625</v>
       </c>
       <c r="E249" t="n">
-        <v>510.1199951171875</v>
+        <v>499.7000122070312</v>
       </c>
       <c r="F249" t="n">
-        <v>24125900</v>
+        <v>18101800</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B250" t="n">
-        <v>510</v>
+        <v>493.010009765625</v>
       </c>
       <c r="C250" t="n">
-        <v>511</v>
+        <v>495.1900024414062</v>
       </c>
       <c r="D250" t="n">
-        <v>499.3599853515625</v>
+        <v>490.1499938964844</v>
       </c>
       <c r="E250" t="n">
-        <v>499.7000122070312</v>
+        <v>493.9500122070312</v>
       </c>
       <c r="F250" t="n">
-        <v>18101800</v>
+        <v>18882300</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B251" t="n">
-        <v>493.010009765625</v>
+        <v>493.0700073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>495.1900024414062</v>
+        <v>494.3900146484375</v>
       </c>
       <c r="D251" t="n">
-        <v>490.1499938964844</v>
+        <v>489.7999877929688</v>
       </c>
       <c r="E251" t="n">
-        <v>493.9500122070312</v>
+        <v>491.6499938964844</v>
       </c>
       <c r="F251" t="n">
-        <v>18882300</v>
+        <v>12889600</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B252" t="n">
-        <v>493.0700073242188</v>
+        <v>488.3200073242188</v>
       </c>
       <c r="C252" t="n">
-        <v>494.3900146484375</v>
+        <v>494.5199890136719</v>
       </c>
       <c r="D252" t="n">
-        <v>489.7999877929688</v>
+        <v>486</v>
       </c>
       <c r="E252" t="n">
-        <v>491.6499938964844</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="F252" t="n">
-        <v>12875900</v>
+        <v>16018200</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10968,37 +10968,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>492.44</v>
+      </c>
+      <c r="D2" t="n">
         <v>491.65</v>
       </c>
-      <c r="D2" t="n">
-        <v>493.95</v>
-      </c>
       <c r="E2" t="n">
-        <v>493.07</v>
+        <v>488.32</v>
       </c>
       <c r="F2" t="n">
-        <v>494.39</v>
+        <v>494.52</v>
       </c>
       <c r="G2" t="n">
-        <v>489.8</v>
+        <v>486</v>
       </c>
       <c r="H2" t="n">
-        <v>12778304</v>
+        <v>15852734</v>
       </c>
       <c r="I2" t="n">
-        <v>36594769</v>
+        <v>36277246</v>
       </c>
       <c r="J2" t="n">
-        <v>3650769387520</v>
+        <v>3656635645952</v>
       </c>
       <c r="K2" t="n">
-        <v>27.543417</v>
+        <v>27.403452</v>
       </c>
       <c r="L2" t="n">
-        <v>20.85624</v>
+        <v>20.890018</v>
       </c>
       <c r="M2" t="n">
-        <v>17.85</v>
+        <v>17.97</v>
       </c>
       <c r="N2" t="n">
         <v>553.72</v>
@@ -11034,7 +11034,7 @@
         <v>59.565</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.254008000000001</v>
+        <v>8.267270999999999</v>
       </c>
       <c r="Z2" t="n">
         <v>0.317</v>
@@ -11046,7 +11046,7 @@
         <v>331839012864</v>
       </c>
       <c r="AC2" t="n">
-        <v>3702739435520</v>
+        <v>3708605693952</v>
       </c>
       <c r="AD2" t="n">
         <v>194237005824</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-10 18:59:04</t>
+          <t>2026-09-11 19:02:39</t>
         </is>
       </c>
     </row>

--- a/data/MSFT_data.xlsx
+++ b/data/MSFT_data.xlsx
@@ -469,22 +469,22 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45911</v>
+        <v>45912</v>
       </c>
       <c r="B2" t="n">
-        <v>498.1513800613702</v>
+        <v>502.5154742767582</v>
       </c>
       <c r="C2" t="n">
-        <v>499.0638857033828</v>
+        <v>508.367321245748</v>
       </c>
       <c r="D2" t="n">
-        <v>493.8170463660224</v>
+        <v>499.738335797131</v>
       </c>
       <c r="E2" t="n">
-        <v>496.9215087890625</v>
+        <v>505.7389526367188</v>
       </c>
       <c r="F2" t="n">
-        <v>18881600</v>
+        <v>23624900</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -495,22 +495,22 @@
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45912</v>
+        <v>45915</v>
       </c>
       <c r="B3" t="n">
-        <v>502.5154742767582</v>
+        <v>504.6380560678344</v>
       </c>
       <c r="C3" t="n">
-        <v>508.367321245748</v>
+        <v>511.2635067675502</v>
       </c>
       <c r="D3" t="n">
-        <v>499.738335797131</v>
+        <v>502.8626547877709</v>
       </c>
       <c r="E3" t="n">
-        <v>505.7389526367188</v>
+        <v>511.1544189453125</v>
       </c>
       <c r="F3" t="n">
-        <v>23624900</v>
+        <v>17143800</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -521,22 +521,22 @@
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45915</v>
+        <v>45916</v>
       </c>
       <c r="B4" t="n">
-        <v>504.6380560678344</v>
+        <v>512.6620043570016</v>
       </c>
       <c r="C4" t="n">
-        <v>511.2635067675502</v>
+        <v>513.0091239663263</v>
       </c>
       <c r="D4" t="n">
-        <v>502.8626547877709</v>
+        <v>504.4495745277025</v>
       </c>
       <c r="E4" t="n">
-        <v>511.1544189453125</v>
+        <v>504.885986328125</v>
       </c>
       <c r="F4" t="n">
-        <v>17143800</v>
+        <v>19711900</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -547,22 +547,22 @@
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45916</v>
+        <v>45917</v>
       </c>
       <c r="B5" t="n">
-        <v>512.6620043570016</v>
+        <v>506.4530503919847</v>
       </c>
       <c r="C5" t="n">
-        <v>513.0091239663263</v>
+        <v>507.1175961354426</v>
       </c>
       <c r="D5" t="n">
-        <v>504.4495745277025</v>
+        <v>501.8013209933916</v>
       </c>
       <c r="E5" t="n">
-        <v>504.885986328125</v>
+        <v>505.8579406738281</v>
       </c>
       <c r="F5" t="n">
-        <v>19711900</v>
+        <v>15816600</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -573,22 +573,22 @@
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45917</v>
+        <v>45918</v>
       </c>
       <c r="B6" t="n">
-        <v>506.4530503919847</v>
+        <v>507.3159820894167</v>
       </c>
       <c r="C6" t="n">
-        <v>507.1175961354426</v>
+        <v>508.883105468087</v>
       </c>
       <c r="D6" t="n">
-        <v>501.8013209933916</v>
+        <v>503.517250078243</v>
       </c>
       <c r="E6" t="n">
-        <v>505.8579406738281</v>
+        <v>504.3008117675781</v>
       </c>
       <c r="F6" t="n">
-        <v>15816600</v>
+        <v>18913700</v>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -599,22 +599,22 @@
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45918</v>
+        <v>45919</v>
       </c>
       <c r="B7" t="n">
-        <v>507.3159513893766</v>
+        <v>506.3935778296786</v>
       </c>
       <c r="C7" t="n">
-        <v>508.883074673213</v>
+        <v>515.0622454615835</v>
       </c>
       <c r="D7" t="n">
-        <v>503.5172196080818</v>
+        <v>506.1456179521661</v>
       </c>
       <c r="E7" t="n">
-        <v>504.30078125</v>
+        <v>513.7034301757812</v>
       </c>
       <c r="F7" t="n">
-        <v>18913700</v>
+        <v>52474100</v>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -625,22 +625,22 @@
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45919</v>
+        <v>45922</v>
       </c>
       <c r="B8" t="n">
-        <v>506.3935778296786</v>
+        <v>511.3826037577857</v>
       </c>
       <c r="C8" t="n">
-        <v>515.0622454615835</v>
+        <v>513.5150225661836</v>
       </c>
       <c r="D8" t="n">
-        <v>506.1456179521661</v>
+        <v>508.3574445613838</v>
       </c>
       <c r="E8" t="n">
-        <v>513.7034301757812</v>
+        <v>510.2518920898438</v>
       </c>
       <c r="F8" t="n">
-        <v>52474100</v>
+        <v>20009300</v>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -651,22 +651,22 @@
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45922</v>
+        <v>45923</v>
       </c>
       <c r="B9" t="n">
-        <v>511.382573172581</v>
+        <v>509.6071158201621</v>
       </c>
       <c r="C9" t="n">
-        <v>513.5149918534414</v>
+        <v>510.3907077578639</v>
       </c>
       <c r="D9" t="n">
-        <v>508.3574141571104</v>
+        <v>503.170087241692</v>
       </c>
       <c r="E9" t="n">
-        <v>510.2518615722656</v>
+        <v>505.0744323730469</v>
       </c>
       <c r="F9" t="n">
-        <v>20009300</v>
+        <v>19799600</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -677,22 +677,22 @@
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45923</v>
+        <v>45924</v>
       </c>
       <c r="B10" t="n">
-        <v>509.6070850287104</v>
+        <v>506.2150114062044</v>
       </c>
       <c r="C10" t="n">
-        <v>510.3906769190661</v>
+        <v>508.297849987297</v>
       </c>
       <c r="D10" t="n">
-        <v>503.1700568391782</v>
+        <v>502.7832554652563</v>
       </c>
       <c r="E10" t="n">
-        <v>505.0744018554688</v>
+        <v>505.9868774414062</v>
       </c>
       <c r="F10" t="n">
-        <v>19799600</v>
+        <v>13533700</v>
       </c>
       <c r="G10" t="n">
         <v>0</v>
@@ -703,22 +703,22 @@
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45924</v>
+        <v>45925</v>
       </c>
       <c r="B11" t="n">
-        <v>506.215041937542</v>
+        <v>504.1519897302721</v>
       </c>
       <c r="C11" t="n">
-        <v>508.2978806442567</v>
+        <v>505.8480570147519</v>
       </c>
       <c r="D11" t="n">
-        <v>502.7832857896144</v>
+        <v>500.9186136455738</v>
       </c>
       <c r="E11" t="n">
-        <v>505.9869079589844</v>
+        <v>502.8923645019531</v>
       </c>
       <c r="F11" t="n">
-        <v>13533700</v>
+        <v>15786500</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
@@ -729,22 +729,22 @@
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45925</v>
+        <v>45926</v>
       </c>
       <c r="B12" t="n">
-        <v>504.1519897302721</v>
+        <v>505.8976246789574</v>
       </c>
       <c r="C12" t="n">
-        <v>505.8480570147519</v>
+        <v>509.7459665668783</v>
       </c>
       <c r="D12" t="n">
-        <v>500.9186136455738</v>
+        <v>502.4856945681329</v>
       </c>
       <c r="E12" t="n">
-        <v>502.8923645019531</v>
+        <v>507.2861938476562</v>
       </c>
       <c r="F12" t="n">
-        <v>15786500</v>
+        <v>16213100</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
@@ -755,22 +755,22 @@
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45926</v>
+        <v>45929</v>
       </c>
       <c r="B13" t="n">
-        <v>505.8975942449135</v>
+        <v>507.325895548039</v>
       </c>
       <c r="C13" t="n">
-        <v>509.745935901324</v>
+        <v>512.6322125671903</v>
       </c>
       <c r="D13" t="n">
-        <v>502.4856643393456</v>
+        <v>504.7272809455783</v>
       </c>
       <c r="E13" t="n">
-        <v>507.2861633300781</v>
+        <v>510.4005737304688</v>
       </c>
       <c r="F13" t="n">
-        <v>16213100</v>
+        <v>17617800</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -781,22 +781,22 @@
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45929</v>
+        <v>45930</v>
       </c>
       <c r="B14" t="n">
-        <v>507.3258348805616</v>
+        <v>509.0516808953516</v>
       </c>
       <c r="C14" t="n">
-        <v>512.6321512651683</v>
+        <v>513.9315141469417</v>
       </c>
       <c r="D14" t="n">
-        <v>504.7272205888506</v>
+        <v>505.5009089039439</v>
       </c>
       <c r="E14" t="n">
-        <v>510.4005126953125</v>
+        <v>513.7232666015625</v>
       </c>
       <c r="F14" t="n">
-        <v>17617800</v>
+        <v>19728200</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
@@ -807,22 +807,22 @@
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45930</v>
+        <v>45931</v>
       </c>
       <c r="B15" t="n">
-        <v>509.0516808953516</v>
+        <v>510.5989067561486</v>
       </c>
       <c r="C15" t="n">
-        <v>513.9315141469417</v>
+        <v>516.2623314762835</v>
       </c>
       <c r="D15" t="n">
-        <v>505.5009089039439</v>
+        <v>507.5143007767599</v>
       </c>
       <c r="E15" t="n">
-        <v>513.7232666015625</v>
+        <v>515.4688720703125</v>
       </c>
       <c r="F15" t="n">
-        <v>19728200</v>
+        <v>22632300</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
@@ -833,22 +833,22 @@
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45931</v>
+        <v>45932</v>
       </c>
       <c r="B16" t="n">
-        <v>510.5989067561486</v>
+        <v>513.4157691025699</v>
       </c>
       <c r="C16" t="n">
-        <v>516.2623314762835</v>
+        <v>517.3434144406598</v>
       </c>
       <c r="D16" t="n">
-        <v>507.5143007767599</v>
+        <v>506.5125449836057</v>
       </c>
       <c r="E16" t="n">
-        <v>515.4688720703125</v>
+        <v>511.53125</v>
       </c>
       <c r="F16" t="n">
-        <v>22632300</v>
+        <v>21222900</v>
       </c>
       <c r="G16" t="n">
         <v>0</v>
@@ -859,22 +859,22 @@
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45932</v>
+        <v>45933</v>
       </c>
       <c r="B17" t="n">
-        <v>513.4157691025699</v>
+        <v>512.8801529316524</v>
       </c>
       <c r="C17" t="n">
-        <v>517.3434144406598</v>
+        <v>516.2425031799986</v>
       </c>
       <c r="D17" t="n">
-        <v>506.5125449836057</v>
+        <v>510.7973143114264</v>
       </c>
       <c r="E17" t="n">
-        <v>511.53125</v>
+        <v>513.1281127929688</v>
       </c>
       <c r="F17" t="n">
-        <v>21222900</v>
+        <v>15112300</v>
       </c>
       <c r="G17" t="n">
         <v>0</v>
@@ -885,22 +885,22 @@
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45933</v>
+        <v>45936</v>
       </c>
       <c r="B18" t="n">
-        <v>512.8801529316524</v>
+        <v>514.377848960065</v>
       </c>
       <c r="C18" t="n">
-        <v>516.2425031799986</v>
+        <v>526.6965386672223</v>
       </c>
       <c r="D18" t="n">
-        <v>510.7973143114264</v>
+        <v>513.9712214168786</v>
       </c>
       <c r="E18" t="n">
-        <v>513.1281127929688</v>
+        <v>524.256591796875</v>
       </c>
       <c r="F18" t="n">
-        <v>15112300</v>
+        <v>21388600</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
@@ -911,22 +911,22 @@
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45936</v>
+        <v>45937</v>
       </c>
       <c r="B19" t="n">
-        <v>514.377848960065</v>
+        <v>523.9788663400786</v>
       </c>
       <c r="C19" t="n">
-        <v>526.6965386672223</v>
+        <v>525.4765536672338</v>
       </c>
       <c r="D19" t="n">
-        <v>513.9712214168786</v>
+        <v>517.1847899970462</v>
       </c>
       <c r="E19" t="n">
-        <v>524.256591796875</v>
+        <v>519.7040405273438</v>
       </c>
       <c r="F19" t="n">
-        <v>21388600</v>
+        <v>14615200</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
@@ -937,22 +937,22 @@
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>45937</v>
+        <v>45938</v>
       </c>
       <c r="B20" t="n">
-        <v>523.9788048028778</v>
+        <v>519.0097599169904</v>
       </c>
       <c r="C20" t="n">
-        <v>525.4764919541412</v>
+        <v>522.6497936321297</v>
       </c>
       <c r="D20" t="n">
-        <v>517.1847292577561</v>
+        <v>518.8213080060119</v>
       </c>
       <c r="E20" t="n">
-        <v>519.7039794921875</v>
+        <v>520.56689453125</v>
       </c>
       <c r="F20" t="n">
-        <v>14615200</v>
+        <v>13363400</v>
       </c>
       <c r="G20" t="n">
         <v>0</v>
@@ -963,22 +963,22 @@
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>45938</v>
+        <v>45939</v>
       </c>
       <c r="B21" t="n">
-        <v>519.0097599169904</v>
+        <v>518.0773939158137</v>
       </c>
       <c r="C21" t="n">
-        <v>522.6497936321297</v>
+        <v>520.0511445409561</v>
       </c>
       <c r="D21" t="n">
-        <v>518.8213080060119</v>
+        <v>513.1777050939771</v>
       </c>
       <c r="E21" t="n">
-        <v>520.56689453125</v>
+        <v>518.1369018554688</v>
       </c>
       <c r="F21" t="n">
-        <v>13363400</v>
+        <v>18343600</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
@@ -989,22 +989,22 @@
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>45939</v>
+        <v>45940</v>
       </c>
       <c r="B22" t="n">
-        <v>518.07745494396</v>
+        <v>515.3995037763443</v>
       </c>
       <c r="C22" t="n">
-        <v>520.0512058016051</v>
+        <v>519.3073539147757</v>
       </c>
       <c r="D22" t="n">
-        <v>513.1777655449532</v>
+        <v>505.4711804745103</v>
       </c>
       <c r="E22" t="n">
-        <v>518.136962890625</v>
+        <v>506.7903137207031</v>
       </c>
       <c r="F22" t="n">
-        <v>18343600</v>
+        <v>24133800</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
@@ -1015,22 +1015,22 @@
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>45940</v>
+        <v>45943</v>
       </c>
       <c r="B23" t="n">
-        <v>515.3994727403434</v>
+        <v>512.1958293204747</v>
       </c>
       <c r="C23" t="n">
-        <v>519.3073226434543</v>
+        <v>512.1958293204747</v>
       </c>
       <c r="D23" t="n">
-        <v>505.4711500363669</v>
+        <v>507.5044476763347</v>
       </c>
       <c r="E23" t="n">
-        <v>506.790283203125</v>
+        <v>509.8551025390625</v>
       </c>
       <c r="F23" t="n">
-        <v>24133800</v>
+        <v>14284200</v>
       </c>
       <c r="G23" t="n">
         <v>0</v>
@@ -1041,22 +1041,22 @@
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>45943</v>
+        <v>45944</v>
       </c>
       <c r="B24" t="n">
-        <v>512.1957986627914</v>
+        <v>506.0661970064178</v>
       </c>
       <c r="C24" t="n">
-        <v>512.1957986627914</v>
+        <v>511.0750038311887</v>
       </c>
       <c r="D24" t="n">
-        <v>507.504417299456</v>
+        <v>501.8707057043513</v>
       </c>
       <c r="E24" t="n">
-        <v>509.8550720214844</v>
+        <v>509.3789367675781</v>
       </c>
       <c r="F24" t="n">
-        <v>14284200</v>
+        <v>14684300</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
@@ -1067,22 +1067,22 @@
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>45944</v>
+        <v>45945</v>
       </c>
       <c r="B25" t="n">
-        <v>506.0662879637401</v>
+        <v>510.7576863019565</v>
       </c>
       <c r="C25" t="n">
-        <v>511.0750956887641</v>
+        <v>512.9694689959882</v>
       </c>
       <c r="D25" t="n">
-        <v>501.870795907601</v>
+        <v>505.838140631098</v>
       </c>
       <c r="E25" t="n">
-        <v>509.3790283203125</v>
+        <v>509.2401428222656</v>
       </c>
       <c r="F25" t="n">
-        <v>14684300</v>
+        <v>14694700</v>
       </c>
       <c r="G25" t="n">
         <v>0</v>
@@ -1093,22 +1093,22 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>45945</v>
+        <v>45946</v>
       </c>
       <c r="B26" t="n">
-        <v>510.7576556934355</v>
+        <v>508.3970827878481</v>
       </c>
       <c r="C26" t="n">
-        <v>512.9694382549203</v>
+        <v>512.6321960787722</v>
       </c>
       <c r="D26" t="n">
-        <v>505.838110317394</v>
+        <v>503.9833851231019</v>
       </c>
       <c r="E26" t="n">
-        <v>509.2401123046875</v>
+        <v>507.4349670410156</v>
       </c>
       <c r="F26" t="n">
-        <v>14694700</v>
+        <v>15559600</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -1119,22 +1119,22 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>45946</v>
+        <v>45947</v>
       </c>
       <c r="B27" t="n">
-        <v>508.3970827878481</v>
+        <v>504.8859867353243</v>
       </c>
       <c r="C27" t="n">
-        <v>512.6321960787722</v>
+        <v>511.2734052578957</v>
       </c>
       <c r="D27" t="n">
-        <v>503.9833851231019</v>
+        <v>503.1700935064365</v>
       </c>
       <c r="E27" t="n">
-        <v>507.4349670410156</v>
+        <v>509.3889465332031</v>
       </c>
       <c r="F27" t="n">
-        <v>15559600</v>
+        <v>19867800</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
@@ -1145,22 +1145,22 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>45947</v>
+        <v>45950</v>
       </c>
       <c r="B28" t="n">
-        <v>504.8859867353243</v>
+        <v>510.4104901121901</v>
       </c>
       <c r="C28" t="n">
-        <v>511.2734052578957</v>
+        <v>514.4671401409408</v>
       </c>
       <c r="D28" t="n">
-        <v>503.1700935064365</v>
+        <v>509.2401268135401</v>
       </c>
       <c r="E28" t="n">
-        <v>509.3889465332031</v>
+        <v>512.5726928710938</v>
       </c>
       <c r="F28" t="n">
-        <v>19867800</v>
+        <v>14665600</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -1171,22 +1171,22 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="B29" t="n">
-        <v>510.4104901121901</v>
+        <v>513.2769402267872</v>
       </c>
       <c r="C29" t="n">
-        <v>514.4671401409408</v>
+        <v>514.4572316509175</v>
       </c>
       <c r="D29" t="n">
-        <v>509.2401268135401</v>
+        <v>508.8533142722573</v>
       </c>
       <c r="E29" t="n">
-        <v>512.5726928710938</v>
+        <v>513.4356079101562</v>
       </c>
       <c r="F29" t="n">
-        <v>14665600</v>
+        <v>15586200</v>
       </c>
       <c r="G29" t="n">
         <v>0</v>
@@ -1197,22 +1197,22 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>45951</v>
+        <v>45952</v>
       </c>
       <c r="B30" t="n">
-        <v>513.2769402267872</v>
+        <v>516.8971823641815</v>
       </c>
       <c r="C30" t="n">
-        <v>514.4572316509175</v>
+        <v>520.943843958813</v>
       </c>
       <c r="D30" t="n">
-        <v>508.8533142722573</v>
+        <v>513.4852520447155</v>
       </c>
       <c r="E30" t="n">
-        <v>513.4356079101562</v>
+        <v>516.2921142578125</v>
       </c>
       <c r="F30" t="n">
-        <v>15586200</v>
+        <v>18962700</v>
       </c>
       <c r="G30" t="n">
         <v>0</v>
@@ -1223,22 +1223,22 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>45952</v>
+        <v>45953</v>
       </c>
       <c r="B31" t="n">
-        <v>516.8971823641815</v>
+        <v>518.1964698863214</v>
       </c>
       <c r="C31" t="n">
-        <v>520.943843958813</v>
+        <v>519.6743010066873</v>
       </c>
       <c r="D31" t="n">
-        <v>513.4852520447155</v>
+        <v>514.3778516149157</v>
       </c>
       <c r="E31" t="n">
-        <v>516.2921142578125</v>
+        <v>516.3119506835938</v>
       </c>
       <c r="F31" t="n">
-        <v>18962700</v>
+        <v>14023500</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
@@ -1249,22 +1249,22 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>45953</v>
+        <v>45954</v>
       </c>
       <c r="B32" t="n">
-        <v>518.1964086283891</v>
+        <v>518.5237205252405</v>
       </c>
       <c r="C32" t="n">
-        <v>519.6742395740552</v>
+        <v>521.0628270774097</v>
       </c>
       <c r="D32" t="n">
-        <v>514.3777908083965</v>
+        <v>516.4607380708425</v>
       </c>
       <c r="E32" t="n">
-        <v>516.3118896484375</v>
+        <v>519.3370361328125</v>
       </c>
       <c r="F32" t="n">
-        <v>14023500</v>
+        <v>15532400</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
@@ -1275,22 +1275,22 @@
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>45954</v>
+        <v>45957</v>
       </c>
       <c r="B33" t="n">
-        <v>518.5236595856693</v>
+        <v>527.440383046071</v>
       </c>
       <c r="C33" t="n">
-        <v>521.0627658394295</v>
+        <v>530.2175212473691</v>
       </c>
       <c r="D33" t="n">
-        <v>516.4606773737235</v>
+        <v>524.6929685473742</v>
       </c>
       <c r="E33" t="n">
-        <v>519.3369750976562</v>
+        <v>527.1824951171875</v>
       </c>
       <c r="F33" t="n">
-        <v>15532400</v>
+        <v>18734700</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
@@ -1301,22 +1301,22 @@
     </row>
     <row r="34">
       <c r="A34" s="1" t="n">
-        <v>45957</v>
+        <v>45958</v>
       </c>
       <c r="B34" t="n">
-        <v>527.440383046071</v>
+        <v>545.511702993095</v>
       </c>
       <c r="C34" t="n">
-        <v>530.2175212473691</v>
+        <v>549.2013167264516</v>
       </c>
       <c r="D34" t="n">
-        <v>524.6929685473742</v>
+        <v>536.3570441492753</v>
       </c>
       <c r="E34" t="n">
-        <v>527.1824951171875</v>
+        <v>537.6464233398438</v>
       </c>
       <c r="F34" t="n">
-        <v>18734700</v>
+        <v>29986700</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
@@ -1327,22 +1327,22 @@
     </row>
     <row r="35">
       <c r="A35" s="1" t="n">
-        <v>45958</v>
+        <v>45959</v>
       </c>
       <c r="B35" t="n">
-        <v>545.511702993095</v>
+        <v>540.4929039137475</v>
       </c>
       <c r="C35" t="n">
-        <v>549.2013167264516</v>
+        <v>541.8120671168963</v>
       </c>
       <c r="D35" t="n">
-        <v>536.3570441492753</v>
+        <v>532.3498815675878</v>
       </c>
       <c r="E35" t="n">
-        <v>537.6464233398438</v>
+        <v>537.1305541992188</v>
       </c>
       <c r="F35" t="n">
-        <v>29986700</v>
+        <v>36023000</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
@@ -1353,22 +1353,22 @@
     </row>
     <row r="36">
       <c r="A36" s="1" t="n">
-        <v>45959</v>
+        <v>45960</v>
       </c>
       <c r="B36" t="n">
-        <v>540.4929653309738</v>
+        <v>526.1509968235328</v>
       </c>
       <c r="C36" t="n">
-        <v>541.8121286840217</v>
+        <v>530.6043464776645</v>
       </c>
       <c r="D36" t="n">
-        <v>532.3499420595073</v>
+        <v>517.8592331602406</v>
       </c>
       <c r="E36" t="n">
-        <v>537.130615234375</v>
+        <v>521.4695434570312</v>
       </c>
       <c r="F36" t="n">
-        <v>36023000</v>
+        <v>41023100</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
@@ -1379,22 +1379,22 @@
     </row>
     <row r="37">
       <c r="A37" s="1" t="n">
-        <v>45960</v>
+        <v>45961</v>
       </c>
       <c r="B37" t="n">
-        <v>526.150935240438</v>
+        <v>524.5640198650095</v>
       </c>
       <c r="C37" t="n">
-        <v>530.6042843733296</v>
+        <v>525.0004316167937</v>
       </c>
       <c r="D37" t="n">
-        <v>517.8591725476514</v>
+        <v>510.896444053691</v>
       </c>
       <c r="E37" t="n">
-        <v>521.469482421875</v>
+        <v>513.5843505859375</v>
       </c>
       <c r="F37" t="n">
-        <v>41023100</v>
+        <v>34006400</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
@@ -1405,22 +1405,22 @@
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>45961</v>
+        <v>45964</v>
       </c>
       <c r="B38" t="n">
-        <v>524.5640822050067</v>
+        <v>515.5680119038287</v>
       </c>
       <c r="C38" t="n">
-        <v>525.0004940086545</v>
+        <v>520.6760087890081</v>
       </c>
       <c r="D38" t="n">
-        <v>510.8965047694123</v>
+        <v>510.3906395365282</v>
       </c>
       <c r="E38" t="n">
-        <v>513.5844116210938</v>
+        <v>512.8107299804688</v>
       </c>
       <c r="F38" t="n">
-        <v>34006400</v>
+        <v>22374700</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
@@ -1431,22 +1431,22 @@
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>45964</v>
+        <v>45965</v>
       </c>
       <c r="B39" t="n">
-        <v>515.5680732671589</v>
+        <v>507.5837474278435</v>
       </c>
       <c r="C39" t="n">
-        <v>520.6760707602963</v>
+        <v>511.3427970078787</v>
       </c>
       <c r="D39" t="n">
-        <v>510.3907002836433</v>
+        <v>503.6957236126803</v>
       </c>
       <c r="E39" t="n">
-        <v>512.810791015625</v>
+        <v>510.1327819824219</v>
       </c>
       <c r="F39" t="n">
-        <v>22374700</v>
+        <v>20958700</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
@@ -1457,22 +1457,22 @@
     </row>
     <row r="40">
       <c r="A40" s="1" t="n">
-        <v>45965</v>
+        <v>45966</v>
       </c>
       <c r="B40" t="n">
-        <v>507.5837170627558</v>
+        <v>509.1111797792271</v>
       </c>
       <c r="C40" t="n">
-        <v>511.3427664179142</v>
+        <v>510.6287232020861</v>
       </c>
       <c r="D40" t="n">
-        <v>503.6956934801851</v>
+        <v>502.4460174356622</v>
       </c>
       <c r="E40" t="n">
-        <v>510.1327514648438</v>
+        <v>503.0213012695312</v>
       </c>
       <c r="F40" t="n">
-        <v>20958700</v>
+        <v>23024300</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
@@ -1483,22 +1483,22 @@
     </row>
     <row r="41">
       <c r="A41" s="1" t="n">
-        <v>45966</v>
+        <v>45967</v>
       </c>
       <c r="B41" t="n">
-        <v>509.1111797792271</v>
+        <v>501.5335392553728</v>
       </c>
       <c r="C41" t="n">
-        <v>510.6287232020861</v>
+        <v>501.5732213085109</v>
       </c>
       <c r="D41" t="n">
-        <v>502.4460174356622</v>
+        <v>491.7639146320967</v>
       </c>
       <c r="E41" t="n">
-        <v>503.0213012695312</v>
+        <v>493.0433959960938</v>
       </c>
       <c r="F41" t="n">
-        <v>23024300</v>
+        <v>27406500</v>
       </c>
       <c r="G41" t="n">
         <v>0</v>
@@ -1509,22 +1509,22 @@
     </row>
     <row r="42">
       <c r="A42" s="1" t="n">
-        <v>45967</v>
+        <v>45968</v>
       </c>
       <c r="B42" t="n">
-        <v>501.5335702984596</v>
+        <v>492.8946605330291</v>
       </c>
       <c r="C42" t="n">
-        <v>501.5732523540539</v>
+        <v>495.304823297102</v>
       </c>
       <c r="D42" t="n">
-        <v>491.7639450704796</v>
+        <v>489.2248422093443</v>
       </c>
       <c r="E42" t="n">
-        <v>493.0434265136719</v>
+        <v>492.7657165527344</v>
       </c>
       <c r="F42" t="n">
-        <v>27406500</v>
+        <v>24019800</v>
       </c>
       <c r="G42" t="n">
         <v>0</v>
@@ -1535,22 +1535,22 @@
     </row>
     <row r="43">
       <c r="A43" s="1" t="n">
-        <v>45968</v>
+        <v>45971</v>
       </c>
       <c r="B43" t="n">
-        <v>492.8946300074654</v>
+        <v>495.9594034527451</v>
       </c>
       <c r="C43" t="n">
-        <v>495.304792622274</v>
+        <v>502.7138276367279</v>
       </c>
       <c r="D43" t="n">
-        <v>489.2248119110569</v>
+        <v>494.7295019610679</v>
       </c>
       <c r="E43" t="n">
-        <v>492.7656860351562</v>
+        <v>501.8707580566406</v>
       </c>
       <c r="F43" t="n">
-        <v>24019800</v>
+        <v>26101500</v>
       </c>
       <c r="G43" t="n">
         <v>0</v>
@@ -1561,22 +1561,22 @@
     </row>
     <row r="44">
       <c r="A44" s="1" t="n">
-        <v>45971</v>
+        <v>45972</v>
       </c>
       <c r="B44" t="n">
-        <v>495.9594034527451</v>
+        <v>500.6805884003941</v>
       </c>
       <c r="C44" t="n">
-        <v>502.7138276367279</v>
+        <v>505.441436360325</v>
       </c>
       <c r="D44" t="n">
-        <v>494.7295019610679</v>
+        <v>498.2505996850444</v>
       </c>
       <c r="E44" t="n">
-        <v>501.8707580566406</v>
+        <v>504.5289306640625</v>
       </c>
       <c r="F44" t="n">
-        <v>26101500</v>
+        <v>17980000</v>
       </c>
       <c r="G44" t="n">
         <v>0</v>
@@ -1587,22 +1587,22 @@
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
-        <v>45972</v>
+        <v>45973</v>
       </c>
       <c r="B45" t="n">
-        <v>500.6805581155917</v>
+        <v>505.2033686484966</v>
       </c>
       <c r="C45" t="n">
-        <v>505.4414057875519</v>
+        <v>507.4945458106546</v>
       </c>
       <c r="D45" t="n">
-        <v>498.2505695472254</v>
+        <v>495.0469415436793</v>
       </c>
       <c r="E45" t="n">
-        <v>504.5289001464844</v>
+        <v>506.9688720703125</v>
       </c>
       <c r="F45" t="n">
-        <v>17980000</v>
+        <v>26574900</v>
       </c>
       <c r="G45" t="n">
         <v>0</v>
@@ -1613,22 +1613,22 @@
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
-        <v>45973</v>
+        <v>45974</v>
       </c>
       <c r="B46" t="n">
-        <v>505.203338237195</v>
+        <v>506.1455939798088</v>
       </c>
       <c r="C46" t="n">
-        <v>507.494515261433</v>
+        <v>509.3095642884979</v>
       </c>
       <c r="D46" t="n">
-        <v>495.0469117437556</v>
+        <v>497.1992129195551</v>
       </c>
       <c r="E46" t="n">
-        <v>506.9688415527344</v>
+        <v>499.1828918457031</v>
       </c>
       <c r="F46" t="n">
-        <v>26574900</v>
+        <v>25273100</v>
       </c>
       <c r="G46" t="n">
         <v>0</v>
@@ -1639,22 +1639,22 @@
     </row>
     <row r="47">
       <c r="A47" s="1" t="n">
-        <v>45974</v>
+        <v>45975</v>
       </c>
       <c r="B47" t="n">
-        <v>506.1455939798088</v>
+        <v>494.1641988801248</v>
       </c>
       <c r="C47" t="n">
-        <v>509.3095642884979</v>
+        <v>507.4250879884235</v>
       </c>
       <c r="D47" t="n">
-        <v>497.1992129195551</v>
+        <v>493.3806372096086</v>
       </c>
       <c r="E47" t="n">
-        <v>499.1828918457031</v>
+        <v>506.0166625976562</v>
       </c>
       <c r="F47" t="n">
-        <v>25273100</v>
+        <v>28505700</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
@@ -1665,22 +1665,22 @@
     </row>
     <row r="48">
       <c r="A48" s="1" t="n">
-        <v>45975</v>
+        <v>45978</v>
       </c>
       <c r="B48" t="n">
-        <v>494.164169077362</v>
+        <v>504.300789978241</v>
       </c>
       <c r="C48" t="n">
-        <v>507.425057385904</v>
+        <v>507.9408238780629</v>
       </c>
       <c r="D48" t="n">
-        <v>493.3806074541019</v>
+        <v>500.7896697837805</v>
       </c>
       <c r="E48" t="n">
-        <v>506.0166320800781</v>
+        <v>503.3486022949219</v>
       </c>
       <c r="F48" t="n">
-        <v>28505700</v>
+        <v>19092800</v>
       </c>
       <c r="G48" t="n">
         <v>0</v>
@@ -1691,22 +1691,22 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>45978</v>
+        <v>45979</v>
       </c>
       <c r="B49" t="n">
-        <v>504.3007594029326</v>
+        <v>491.3274994941962</v>
       </c>
       <c r="C49" t="n">
-        <v>507.9407930820625</v>
+        <v>498.8754133867433</v>
       </c>
       <c r="D49" t="n">
-        <v>500.7896394213482</v>
+        <v>482.8076023204449</v>
       </c>
       <c r="E49" t="n">
-        <v>503.3485717773438</v>
+        <v>489.7604064941406</v>
       </c>
       <c r="F49" t="n">
-        <v>19092800</v>
+        <v>33815100</v>
       </c>
       <c r="G49" t="n">
         <v>0</v>
@@ -1717,22 +1717,22 @@
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>45979</v>
+        <v>45980</v>
       </c>
       <c r="B50" t="n">
-        <v>491.3275301094218</v>
+        <v>486.1005289347495</v>
       </c>
       <c r="C50" t="n">
-        <v>498.8754444722887</v>
+        <v>491.1489881906385</v>
       </c>
       <c r="D50" t="n">
-        <v>482.8076324047851</v>
+        <v>478.8898366362471</v>
       </c>
       <c r="E50" t="n">
-        <v>489.7604370117188</v>
+        <v>483.1448364257812</v>
       </c>
       <c r="F50" t="n">
-        <v>33815100</v>
+        <v>23245300</v>
       </c>
       <c r="G50" t="n">
         <v>0</v>
@@ -1743,25 +1743,25 @@
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>45980</v>
+        <v>45981</v>
       </c>
       <c r="B51" t="n">
-        <v>486.1005289347495</v>
+        <v>489.6038543571071</v>
       </c>
       <c r="C51" t="n">
-        <v>491.1489881906385</v>
+        <v>490.4584485233347</v>
       </c>
       <c r="D51" t="n">
-        <v>478.8898366362471</v>
+        <v>472.5023579474745</v>
       </c>
       <c r="E51" t="n">
-        <v>483.1448364257812</v>
+        <v>475.4138793945312</v>
       </c>
       <c r="F51" t="n">
-        <v>23245300</v>
+        <v>26802500</v>
       </c>
       <c r="G51" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H51" t="n">
         <v>0</v>
@@ -1769,25 +1769,25 @@
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>45981</v>
+        <v>45982</v>
       </c>
       <c r="B52" t="n">
-        <v>489.6038543571071</v>
+        <v>475.4834610910571</v>
       </c>
       <c r="C52" t="n">
-        <v>490.4584485233347</v>
+        <v>475.9008266883901</v>
       </c>
       <c r="D52" t="n">
-        <v>472.5023579474745</v>
+        <v>465.31794169549</v>
       </c>
       <c r="E52" t="n">
-        <v>475.4138793945312</v>
+        <v>469.1436767578125</v>
       </c>
       <c r="F52" t="n">
-        <v>26802500</v>
+        <v>31769200</v>
       </c>
       <c r="G52" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H52" t="n">
         <v>0</v>
@@ -1795,22 +1795,22 @@
     </row>
     <row r="53">
       <c r="A53" s="1" t="n">
-        <v>45982</v>
+        <v>45985</v>
       </c>
       <c r="B53" t="n">
-        <v>475.4834301610789</v>
+        <v>472.0055061050608</v>
       </c>
       <c r="C53" t="n">
-        <v>475.9007957312625</v>
+        <v>473.8935220644432</v>
       </c>
       <c r="D53" t="n">
-        <v>465.3179114267742</v>
+        <v>465.0694984877541</v>
       </c>
       <c r="E53" t="n">
-        <v>469.1436462402344</v>
+        <v>471.0118103027344</v>
       </c>
       <c r="F53" t="n">
-        <v>31769200</v>
+        <v>34421000</v>
       </c>
       <c r="G53" t="n">
         <v>0</v>
@@ -1821,22 +1821,22 @@
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
-        <v>45985</v>
+        <v>45986</v>
       </c>
       <c r="B54" t="n">
-        <v>472.0055061050608</v>
+        <v>471.0813659766461</v>
       </c>
       <c r="C54" t="n">
-        <v>473.8935220644432</v>
+        <v>476.1293271988991</v>
       </c>
       <c r="D54" t="n">
-        <v>465.0694984877541</v>
+        <v>461.9592459889855</v>
       </c>
       <c r="E54" t="n">
-        <v>471.0118103027344</v>
+        <v>473.9829406738281</v>
       </c>
       <c r="F54" t="n">
-        <v>34421000</v>
+        <v>28019800</v>
       </c>
       <c r="G54" t="n">
         <v>0</v>
@@ -1847,22 +1847,22 @@
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
-        <v>45986</v>
+        <v>45987</v>
       </c>
       <c r="B55" t="n">
-        <v>471.0813659766461</v>
+        <v>483.244191691805</v>
       </c>
       <c r="C55" t="n">
-        <v>476.1293271988991</v>
+        <v>485.2315832491155</v>
       </c>
       <c r="D55" t="n">
-        <v>461.9592459889855</v>
+        <v>478.1664208189674</v>
       </c>
       <c r="E55" t="n">
-        <v>473.9829406738281</v>
+        <v>482.4393005371094</v>
       </c>
       <c r="F55" t="n">
-        <v>28019800</v>
+        <v>25709100</v>
       </c>
       <c r="G55" t="n">
         <v>0</v>
@@ -1873,22 +1873,22 @@
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
-        <v>45987</v>
+        <v>45989</v>
       </c>
       <c r="B56" t="n">
-        <v>483.244222260298</v>
+        <v>484.5260924315005</v>
       </c>
       <c r="C56" t="n">
-        <v>485.2316139433245</v>
+        <v>489.5243812398697</v>
       </c>
       <c r="D56" t="n">
-        <v>478.1664510662567</v>
+        <v>483.5820692635899</v>
       </c>
       <c r="E56" t="n">
-        <v>482.4393310546875</v>
+        <v>488.9082946777344</v>
       </c>
       <c r="F56" t="n">
-        <v>25709100</v>
+        <v>14386700</v>
       </c>
       <c r="G56" t="n">
         <v>0</v>
@@ -1899,22 +1899,22 @@
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
-        <v>45989</v>
+        <v>45992</v>
       </c>
       <c r="B57" t="n">
-        <v>484.5260924315005</v>
+        <v>485.3608038657598</v>
       </c>
       <c r="C57" t="n">
-        <v>489.5243812398697</v>
+        <v>486.771834992007</v>
       </c>
       <c r="D57" t="n">
-        <v>483.5820692635899</v>
+        <v>481.5946880995925</v>
       </c>
       <c r="E57" t="n">
-        <v>488.9082946777344</v>
+        <v>483.6715087890625</v>
       </c>
       <c r="F57" t="n">
-        <v>14386700</v>
+        <v>23964000</v>
       </c>
       <c r="G57" t="n">
         <v>0</v>
@@ -1925,22 +1925,22 @@
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
-        <v>45992</v>
+        <v>45993</v>
       </c>
       <c r="B58" t="n">
-        <v>485.3608038657598</v>
+        <v>483.6516286444489</v>
       </c>
       <c r="C58" t="n">
-        <v>486.771834992007</v>
+        <v>490.3888850620814</v>
       </c>
       <c r="D58" t="n">
-        <v>481.5946880995925</v>
+        <v>483.2541563831954</v>
       </c>
       <c r="E58" t="n">
-        <v>483.6715087890625</v>
+        <v>486.9109497070312</v>
       </c>
       <c r="F58" t="n">
-        <v>23964000</v>
+        <v>19562700</v>
       </c>
       <c r="G58" t="n">
         <v>0</v>
@@ -1951,22 +1951,22 @@
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
-        <v>45993</v>
+        <v>45994</v>
       </c>
       <c r="B59" t="n">
-        <v>483.6516286444489</v>
+        <v>473.3171775583083</v>
       </c>
       <c r="C59" t="n">
-        <v>490.3888850620814</v>
+        <v>481.1872310931236</v>
       </c>
       <c r="D59" t="n">
-        <v>483.2541563831954</v>
+        <v>472.2042431453193</v>
       </c>
       <c r="E59" t="n">
-        <v>486.9109497070312</v>
+        <v>474.7182922363281</v>
       </c>
       <c r="F59" t="n">
-        <v>19562700</v>
+        <v>34615100</v>
       </c>
       <c r="G59" t="n">
         <v>0</v>
@@ -1977,22 +1977,22 @@
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="B60" t="n">
-        <v>473.3172079858148</v>
+        <v>476.7355071807625</v>
       </c>
       <c r="C60" t="n">
-        <v>481.1872620265617</v>
+        <v>478.2856702042714</v>
       </c>
       <c r="D60" t="n">
-        <v>472.2042735012802</v>
+        <v>473.4861025034468</v>
       </c>
       <c r="E60" t="n">
-        <v>474.7183227539062</v>
+        <v>477.8086853027344</v>
       </c>
       <c r="F60" t="n">
-        <v>34615100</v>
+        <v>22318200</v>
       </c>
       <c r="G60" t="n">
         <v>0</v>
@@ -2003,22 +2003,22 @@
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
-        <v>45995</v>
+        <v>45996</v>
       </c>
       <c r="B61" t="n">
-        <v>476.7355376297969</v>
+        <v>479.4780643507397</v>
       </c>
       <c r="C61" t="n">
-        <v>478.2857007523145</v>
+        <v>480.3525214663767</v>
       </c>
       <c r="D61" t="n">
-        <v>473.4861327449422</v>
+        <v>475.8610275749173</v>
       </c>
       <c r="E61" t="n">
-        <v>477.8087158203125</v>
+        <v>480.1140441894531</v>
       </c>
       <c r="F61" t="n">
-        <v>22318200</v>
+        <v>22608700</v>
       </c>
       <c r="G61" t="n">
         <v>0</v>
@@ -2029,22 +2029,22 @@
     </row>
     <row r="62">
       <c r="A62" s="1" t="n">
-        <v>45996</v>
+        <v>45999</v>
       </c>
       <c r="B62" t="n">
-        <v>479.4780948278929</v>
+        <v>481.8331998835391</v>
       </c>
       <c r="C62" t="n">
-        <v>480.3525519991132</v>
+        <v>489.1964595164875</v>
       </c>
       <c r="D62" t="n">
-        <v>475.8610578221601</v>
+        <v>481.3264052911177</v>
       </c>
       <c r="E62" t="n">
-        <v>480.1140747070312</v>
+        <v>487.9245300292969</v>
       </c>
       <c r="F62" t="n">
-        <v>22608700</v>
+        <v>21965900</v>
       </c>
       <c r="G62" t="n">
         <v>0</v>
@@ -2055,22 +2055,22 @@
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>45999</v>
+        <v>46000</v>
       </c>
       <c r="B63" t="n">
-        <v>481.8331697469475</v>
+        <v>486.0166380400449</v>
       </c>
       <c r="C63" t="n">
-        <v>489.1964289193556</v>
+        <v>489.0175885389743</v>
       </c>
       <c r="D63" t="n">
-        <v>481.3263751862239</v>
+        <v>485.4204144751398</v>
       </c>
       <c r="E63" t="n">
-        <v>487.9244995117188</v>
+        <v>488.918212890625</v>
       </c>
       <c r="F63" t="n">
-        <v>21965900</v>
+        <v>14696100</v>
       </c>
       <c r="G63" t="n">
         <v>0</v>
@@ -2081,22 +2081,22 @@
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>46000</v>
+        <v>46001</v>
       </c>
       <c r="B64" t="n">
-        <v>486.0166380400449</v>
+        <v>480.978577549523</v>
       </c>
       <c r="C64" t="n">
-        <v>489.0175885389743</v>
+        <v>481.1971918388435</v>
       </c>
       <c r="D64" t="n">
-        <v>485.4204144751398</v>
+        <v>472.084987996716</v>
       </c>
       <c r="E64" t="n">
-        <v>488.918212890625</v>
+        <v>475.5430603027344</v>
       </c>
       <c r="F64" t="n">
-        <v>14696100</v>
+        <v>35756200</v>
       </c>
       <c r="G64" t="n">
         <v>0</v>
@@ -2107,22 +2107,22 @@
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
-        <v>46001</v>
+        <v>46002</v>
       </c>
       <c r="B65" t="n">
-        <v>480.978577549523</v>
+        <v>473.6252433732215</v>
       </c>
       <c r="C65" t="n">
-        <v>481.1971918388435</v>
+        <v>482.9659780129214</v>
       </c>
       <c r="D65" t="n">
-        <v>472.084987996716</v>
+        <v>472.8600781839672</v>
       </c>
       <c r="E65" t="n">
-        <v>475.5430603027344</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F65" t="n">
-        <v>35756200</v>
+        <v>24669200</v>
       </c>
       <c r="G65" t="n">
         <v>0</v>
@@ -2133,22 +2133,22 @@
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
-        <v>46002</v>
+        <v>46003</v>
       </c>
       <c r="B66" t="n">
-        <v>473.6252433732215</v>
+        <v>476.7951512874317</v>
       </c>
       <c r="C66" t="n">
-        <v>482.9659780129214</v>
+        <v>479.4085762318817</v>
       </c>
       <c r="D66" t="n">
-        <v>472.8600781839672</v>
+        <v>473.3370788032073</v>
       </c>
       <c r="E66" t="n">
-        <v>480.422119140625</v>
+        <v>475.5132751464844</v>
       </c>
       <c r="F66" t="n">
-        <v>24669200</v>
+        <v>21248100</v>
       </c>
       <c r="G66" t="n">
         <v>0</v>
@@ -2159,22 +2159,22 @@
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
-        <v>46003</v>
+        <v>46006</v>
       </c>
       <c r="B67" t="n">
-        <v>476.7951206875852</v>
+        <v>477.0733729131614</v>
       </c>
       <c r="C67" t="n">
-        <v>479.4085454643102</v>
+        <v>477.6894594742654</v>
       </c>
       <c r="D67" t="n">
-        <v>473.3370484252935</v>
+        <v>469.5411415575728</v>
       </c>
       <c r="E67" t="n">
-        <v>475.5132446289062</v>
+        <v>471.82666015625</v>
       </c>
       <c r="F67" t="n">
-        <v>21248100</v>
+        <v>23727700</v>
       </c>
       <c r="G67" t="n">
         <v>0</v>
@@ -2185,22 +2185,22 @@
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
-        <v>46006</v>
+        <v>46007</v>
       </c>
       <c r="B68" t="n">
-        <v>477.0733420562278</v>
+        <v>468.9349812365753</v>
       </c>
       <c r="C68" t="n">
-        <v>477.6894285774835</v>
+        <v>474.8772929441188</v>
       </c>
       <c r="D68" t="n">
-        <v>469.5411111878212</v>
+        <v>467.9114757916915</v>
       </c>
       <c r="E68" t="n">
-        <v>471.8266296386719</v>
+        <v>473.3867492675781</v>
       </c>
       <c r="F68" t="n">
-        <v>23727700</v>
+        <v>20705600</v>
       </c>
       <c r="G68" t="n">
         <v>0</v>
@@ -2211,22 +2211,22 @@
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
-        <v>46007</v>
+        <v>46008</v>
       </c>
       <c r="B69" t="n">
-        <v>468.9350114671635</v>
+        <v>473.903466892556</v>
       </c>
       <c r="C69" t="n">
-        <v>474.8773235577871</v>
+        <v>476.9739832708393</v>
       </c>
       <c r="D69" t="n">
-        <v>467.911505956298</v>
+        <v>472.0055042784347</v>
       </c>
       <c r="E69" t="n">
-        <v>473.3867797851562</v>
+        <v>473.1184387207031</v>
       </c>
       <c r="F69" t="n">
-        <v>20705600</v>
+        <v>24527200</v>
       </c>
       <c r="G69" t="n">
         <v>0</v>
@@ -2237,22 +2237,22 @@
     </row>
     <row r="70">
       <c r="A70" s="1" t="n">
-        <v>46008</v>
+        <v>46009</v>
       </c>
       <c r="B70" t="n">
-        <v>473.903466892556</v>
+        <v>475.1754171439269</v>
       </c>
       <c r="C70" t="n">
-        <v>476.9739832708393</v>
+        <v>486.5134903409316</v>
       </c>
       <c r="D70" t="n">
-        <v>472.0055042784347</v>
+        <v>474.8773205213831</v>
       </c>
       <c r="E70" t="n">
-        <v>473.1184387207031</v>
+        <v>480.9289245605469</v>
       </c>
       <c r="F70" t="n">
-        <v>24527200</v>
+        <v>28573500</v>
       </c>
       <c r="G70" t="n">
         <v>0</v>
@@ -2263,22 +2263,22 @@
     </row>
     <row r="71">
       <c r="A71" s="1" t="n">
-        <v>46009</v>
+        <v>46010</v>
       </c>
       <c r="B71" t="n">
-        <v>475.1754171439269</v>
+        <v>484.2875835443981</v>
       </c>
       <c r="C71" t="n">
-        <v>486.5134903409316</v>
+        <v>484.7745151206103</v>
       </c>
       <c r="D71" t="n">
-        <v>474.8773205213831</v>
+        <v>479.4482897203998</v>
       </c>
       <c r="E71" t="n">
-        <v>480.9289245605469</v>
+        <v>482.856689453125</v>
       </c>
       <c r="F71" t="n">
-        <v>28573500</v>
+        <v>70836100</v>
       </c>
       <c r="G71" t="n">
         <v>0</v>
@@ -2289,22 +2289,22 @@
     </row>
     <row r="72">
       <c r="A72" s="1" t="n">
-        <v>46010</v>
+        <v>46013</v>
       </c>
       <c r="B72" t="n">
-        <v>484.2875529363844</v>
+        <v>483.05539282771</v>
       </c>
       <c r="C72" t="n">
-        <v>484.7744844818214</v>
+        <v>485.6489546100234</v>
       </c>
       <c r="D72" t="n">
-        <v>479.4482594182398</v>
+        <v>479.6470235443271</v>
       </c>
       <c r="E72" t="n">
-        <v>482.8566589355469</v>
+        <v>481.8629760742188</v>
       </c>
       <c r="F72" t="n">
-        <v>70836100</v>
+        <v>16963000</v>
       </c>
       <c r="G72" t="n">
         <v>0</v>
@@ -2315,22 +2315,22 @@
     </row>
     <row r="73">
       <c r="A73" s="1" t="n">
-        <v>46013</v>
+        <v>46014</v>
       </c>
       <c r="B73" t="n">
-        <v>483.0554234208069</v>
+        <v>481.9226163967179</v>
       </c>
       <c r="C73" t="n">
-        <v>485.648985367377</v>
+        <v>484.7546252629152</v>
       </c>
       <c r="D73" t="n">
-        <v>479.6470539215635</v>
+        <v>481.6841087754749</v>
       </c>
       <c r="E73" t="n">
-        <v>481.8630065917969</v>
+        <v>483.7808227539062</v>
       </c>
       <c r="F73" t="n">
-        <v>16963000</v>
+        <v>14683600</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -2341,22 +2341,22 @@
     </row>
     <row r="74">
       <c r="A74" s="1" t="n">
-        <v>46014</v>
+        <v>46015</v>
       </c>
       <c r="B74" t="n">
-        <v>481.922585996358</v>
+        <v>482.6181758435609</v>
       </c>
       <c r="C74" t="n">
-        <v>484.7545946839082</v>
+        <v>486.0762481946253</v>
       </c>
       <c r="D74" t="n">
-        <v>481.6840783901604</v>
+        <v>481.7735283363114</v>
       </c>
       <c r="E74" t="n">
-        <v>483.7807922363281</v>
+        <v>484.9434204101562</v>
       </c>
       <c r="F74" t="n">
-        <v>14683600</v>
+        <v>5855900</v>
       </c>
       <c r="G74" t="n">
         <v>0</v>
@@ -2367,22 +2367,22 @@
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
-        <v>46015</v>
+        <v>46017</v>
       </c>
       <c r="B75" t="n">
-        <v>482.6181454723109</v>
+        <v>483.6417106195734</v>
       </c>
       <c r="C75" t="n">
-        <v>486.0762176057581</v>
+        <v>485.0428254417362</v>
       </c>
       <c r="D75" t="n">
-        <v>481.7734980182152</v>
+        <v>482.8964387136479</v>
       </c>
       <c r="E75" t="n">
-        <v>484.9433898925781</v>
+        <v>484.6354064941406</v>
       </c>
       <c r="F75" t="n">
-        <v>5855900</v>
+        <v>8842200</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
-        <v>46017</v>
+        <v>46020</v>
       </c>
       <c r="B76" t="n">
-        <v>483.6416497095635</v>
+        <v>481.8033366009864</v>
       </c>
       <c r="C76" t="n">
-        <v>485.0427643552695</v>
+        <v>485.2713556042012</v>
       </c>
       <c r="D76" t="n">
-        <v>482.8963778974979</v>
+        <v>481.1276307272214</v>
       </c>
       <c r="E76" t="n">
-        <v>484.6353454589844</v>
+        <v>484.0292358398438</v>
       </c>
       <c r="F76" t="n">
-        <v>8842200</v>
+        <v>10893400</v>
       </c>
       <c r="G76" t="n">
         <v>0</v>
@@ -2419,22 +2419,22 @@
     </row>
     <row r="77">
       <c r="A77" s="1" t="n">
-        <v>46020</v>
+        <v>46021</v>
       </c>
       <c r="B77" t="n">
-        <v>481.8033366009864</v>
+        <v>482.8666136001516</v>
       </c>
       <c r="C77" t="n">
-        <v>485.2713556042012</v>
+        <v>486.5929730105466</v>
       </c>
       <c r="D77" t="n">
-        <v>481.1276307272214</v>
+        <v>482.4393316658054</v>
       </c>
       <c r="E77" t="n">
-        <v>484.0292358398438</v>
+        <v>484.4068603515625</v>
       </c>
       <c r="F77" t="n">
-        <v>10893400</v>
+        <v>13944500</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -2445,22 +2445,22 @@
     </row>
     <row r="78">
       <c r="A78" s="1" t="n">
-        <v>46021</v>
+        <v>46022</v>
       </c>
       <c r="B78" t="n">
-        <v>482.8666136001516</v>
+        <v>484.7645645601486</v>
       </c>
       <c r="C78" t="n">
-        <v>486.5929730105466</v>
+        <v>485.0626915008752</v>
       </c>
       <c r="D78" t="n">
-        <v>482.4393316658054</v>
+        <v>480.253177052155</v>
       </c>
       <c r="E78" t="n">
-        <v>484.4068603515625</v>
+        <v>480.5711669921875</v>
       </c>
       <c r="F78" t="n">
-        <v>13944500</v>
+        <v>15601600</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -2471,22 +2471,22 @@
     </row>
     <row r="79">
       <c r="A79" s="1" t="n">
-        <v>46022</v>
+        <v>46024</v>
       </c>
       <c r="B79" t="n">
-        <v>484.7645645601486</v>
+        <v>481.3363251826272</v>
       </c>
       <c r="C79" t="n">
-        <v>485.0626915008752</v>
+        <v>481.6046121327098</v>
       </c>
       <c r="D79" t="n">
-        <v>480.253177052155</v>
+        <v>467.1960229709088</v>
       </c>
       <c r="E79" t="n">
-        <v>480.5711669921875</v>
+        <v>469.95849609375</v>
       </c>
       <c r="F79" t="n">
-        <v>15601600</v>
+        <v>25571600</v>
       </c>
       <c r="G79" t="n">
         <v>0</v>
@@ -2497,22 +2497,22 @@
     </row>
     <row r="80">
       <c r="A80" s="1" t="n">
-        <v>46024</v>
+        <v>46027</v>
       </c>
       <c r="B80" t="n">
-        <v>481.3363251826272</v>
+        <v>471.071443053882</v>
       </c>
       <c r="C80" t="n">
-        <v>481.6046121327098</v>
+        <v>473.0687813775576</v>
       </c>
       <c r="D80" t="n">
-        <v>467.1960229709088</v>
+        <v>466.5401924921144</v>
       </c>
       <c r="E80" t="n">
-        <v>469.95849609375</v>
+        <v>469.8690795898438</v>
       </c>
       <c r="F80" t="n">
-        <v>25571600</v>
+        <v>25250300</v>
       </c>
       <c r="G80" t="n">
         <v>0</v>
@@ -2523,22 +2523,22 @@
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
-        <v>46027</v>
+        <v>46028</v>
       </c>
       <c r="B81" t="n">
-        <v>471.071443053882</v>
+        <v>470.8130487247203</v>
       </c>
       <c r="C81" t="n">
-        <v>473.0687813775576</v>
+        <v>475.7219083069673</v>
       </c>
       <c r="D81" t="n">
-        <v>466.5401924921144</v>
+        <v>466.7885929433101</v>
       </c>
       <c r="E81" t="n">
-        <v>469.8690795898438</v>
+        <v>475.4933776855469</v>
       </c>
       <c r="F81" t="n">
-        <v>25250300</v>
+        <v>23037700</v>
       </c>
       <c r="G81" t="n">
         <v>0</v>
@@ -2549,22 +2549,22 @@
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
-        <v>46028</v>
+        <v>46029</v>
       </c>
       <c r="B82" t="n">
-        <v>470.8130789419108</v>
+        <v>476.7355161407656</v>
       </c>
       <c r="C82" t="n">
-        <v>475.7219388392127</v>
+        <v>486.6128550141313</v>
       </c>
       <c r="D82" t="n">
-        <v>466.7886229022075</v>
+        <v>474.936929133209</v>
       </c>
       <c r="E82" t="n">
-        <v>475.493408203125</v>
+        <v>480.422119140625</v>
       </c>
       <c r="F82" t="n">
-        <v>23037700</v>
+        <v>25564200</v>
       </c>
       <c r="G82" t="n">
         <v>0</v>
@@ -2575,22 +2575,22 @@
     </row>
     <row r="83">
       <c r="A83" s="1" t="n">
-        <v>46029</v>
+        <v>46030</v>
       </c>
       <c r="B83" t="n">
-        <v>476.7355161407656</v>
+        <v>478.206189665966</v>
       </c>
       <c r="C83" t="n">
-        <v>486.6128550141313</v>
+        <v>479.6172511411785</v>
       </c>
       <c r="D83" t="n">
-        <v>474.936929133209</v>
+        <v>472.8601010457309</v>
       </c>
       <c r="E83" t="n">
-        <v>480.422119140625</v>
+        <v>475.0959167480469</v>
       </c>
       <c r="F83" t="n">
-        <v>25564200</v>
+        <v>18162600</v>
       </c>
       <c r="G83" t="n">
         <v>0</v>
@@ -2601,22 +2601,22 @@
     </row>
     <row r="84">
       <c r="A84" s="1" t="n">
-        <v>46030</v>
+        <v>46031</v>
       </c>
       <c r="B84" t="n">
-        <v>478.2061589486008</v>
+        <v>471.071451381159</v>
       </c>
       <c r="C84" t="n">
-        <v>479.6172203331744</v>
+        <v>476.7951491709672</v>
       </c>
       <c r="D84" t="n">
-        <v>472.8600706717694</v>
+        <v>469.2231916595613</v>
       </c>
       <c r="E84" t="n">
-        <v>475.0958862304688</v>
+        <v>476.258544921875</v>
       </c>
       <c r="F84" t="n">
-        <v>18162600</v>
+        <v>18491000</v>
       </c>
       <c r="G84" t="n">
         <v>0</v>
@@ -2627,22 +2627,22 @@
     </row>
     <row r="85">
       <c r="A85" s="1" t="n">
-        <v>46031</v>
+        <v>46034</v>
       </c>
       <c r="B85" t="n">
-        <v>471.0714211959582</v>
+        <v>473.6649886945649</v>
       </c>
       <c r="C85" t="n">
-        <v>476.7951186190047</v>
+        <v>477.9577314886077</v>
       </c>
       <c r="D85" t="n">
-        <v>469.2231615927928</v>
+        <v>472.681209234831</v>
       </c>
       <c r="E85" t="n">
-        <v>476.2585144042969</v>
+        <v>474.1717529296875</v>
       </c>
       <c r="F85" t="n">
-        <v>18491000</v>
+        <v>23519900</v>
       </c>
       <c r="G85" t="n">
         <v>0</v>
@@ -2653,22 +2653,22 @@
     </row>
     <row r="86">
       <c r="A86" s="1" t="n">
-        <v>46034</v>
+        <v>46035</v>
       </c>
       <c r="B86" t="n">
-        <v>473.6649886945649</v>
+        <v>471.6875193976834</v>
       </c>
       <c r="C86" t="n">
-        <v>477.9577314886077</v>
+        <v>472.7805908527595</v>
       </c>
       <c r="D86" t="n">
-        <v>472.681209234831</v>
+        <v>463.0125743921384</v>
       </c>
       <c r="E86" t="n">
-        <v>474.1717529296875</v>
+        <v>467.7028198242188</v>
       </c>
       <c r="F86" t="n">
-        <v>23519900</v>
+        <v>28545800</v>
       </c>
       <c r="G86" t="n">
         <v>0</v>
@@ -2679,22 +2679,22 @@
     </row>
     <row r="87">
       <c r="A87" s="1" t="n">
-        <v>46035</v>
+        <v>46036</v>
       </c>
       <c r="B87" t="n">
-        <v>471.6875193976834</v>
+        <v>463.5193621312372</v>
       </c>
       <c r="C87" t="n">
-        <v>472.7805908527595</v>
+        <v>465.2484135478969</v>
       </c>
       <c r="D87" t="n">
-        <v>463.0125743921384</v>
+        <v>454.2879494306214</v>
       </c>
       <c r="E87" t="n">
-        <v>467.7028198242188</v>
+        <v>456.4840087890625</v>
       </c>
       <c r="F87" t="n">
-        <v>28545800</v>
+        <v>28184300</v>
       </c>
       <c r="G87" t="n">
         <v>0</v>
@@ -2705,22 +2705,22 @@
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
-        <v>46036</v>
+        <v>46037</v>
       </c>
       <c r="B88" t="n">
-        <v>463.5193311433208</v>
+        <v>461.1940901109254</v>
       </c>
       <c r="C88" t="n">
-        <v>465.2483824443871</v>
+        <v>461.3232754170305</v>
       </c>
       <c r="D88" t="n">
-        <v>454.2879190598576</v>
+        <v>453.0259094171898</v>
       </c>
       <c r="E88" t="n">
-        <v>456.4839782714844</v>
+        <v>453.7811279296875</v>
       </c>
       <c r="F88" t="n">
-        <v>28184300</v>
+        <v>23225800</v>
       </c>
       <c r="G88" t="n">
         <v>0</v>
@@ -2731,22 +2731,22 @@
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>46037</v>
+        <v>46038</v>
       </c>
       <c r="B89" t="n">
-        <v>461.1940901109254</v>
+        <v>454.9437666153887</v>
       </c>
       <c r="C89" t="n">
-        <v>461.3232754170305</v>
+        <v>460.2699922453042</v>
       </c>
       <c r="D89" t="n">
-        <v>453.0259094171898</v>
+        <v>453.6023014516422</v>
       </c>
       <c r="E89" t="n">
-        <v>453.7811279296875</v>
+        <v>456.9609680175781</v>
       </c>
       <c r="F89" t="n">
-        <v>23225800</v>
+        <v>34246700</v>
       </c>
       <c r="G89" t="n">
         <v>0</v>
@@ -2757,22 +2757,22 @@
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>46038</v>
+        <v>46042</v>
       </c>
       <c r="B90" t="n">
-        <v>454.943705849665</v>
+        <v>448.3754180557273</v>
       </c>
       <c r="C90" t="n">
-        <v>460.2699307681697</v>
+        <v>453.9202272514996</v>
       </c>
       <c r="D90" t="n">
-        <v>453.6022408650948</v>
+        <v>446.4476457864541</v>
       </c>
       <c r="E90" t="n">
-        <v>456.9609069824219</v>
+        <v>451.6546020507812</v>
       </c>
       <c r="F90" t="n">
-        <v>34246700</v>
+        <v>26130000</v>
       </c>
       <c r="G90" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
     </row>
     <row r="91">
       <c r="A91" s="1" t="n">
-        <v>46042</v>
+        <v>46043</v>
       </c>
       <c r="B91" t="n">
-        <v>448.3754483517362</v>
+        <v>449.7467088388933</v>
       </c>
       <c r="C91" t="n">
-        <v>453.9202579221624</v>
+        <v>449.8361378186282</v>
       </c>
       <c r="D91" t="n">
-        <v>446.4476759522066</v>
+        <v>435.9144504613163</v>
       </c>
       <c r="E91" t="n">
-        <v>451.6546325683594</v>
+        <v>441.3102111816406</v>
       </c>
       <c r="F91" t="n">
-        <v>26130000</v>
+        <v>37980500</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="92">
       <c r="A92" s="1" t="n">
-        <v>46043</v>
+        <v>46044</v>
       </c>
       <c r="B92" t="n">
-        <v>449.7467399398739</v>
+        <v>444.7981003997206</v>
       </c>
       <c r="C92" t="n">
-        <v>449.836168925793</v>
+        <v>449.9851935867555</v>
       </c>
       <c r="D92" t="n">
-        <v>435.9144806057656</v>
+        <v>441.8965257028684</v>
       </c>
       <c r="E92" t="n">
-        <v>441.3102416992188</v>
+        <v>448.2959289550781</v>
       </c>
       <c r="F92" t="n">
-        <v>37980500</v>
+        <v>25349400</v>
       </c>
       <c r="G92" t="n">
         <v>0</v>
@@ -2835,22 +2835,22 @@
     </row>
     <row r="93">
       <c r="A93" s="1" t="n">
-        <v>46044</v>
+        <v>46045</v>
       </c>
       <c r="B93" t="n">
-        <v>444.7981003997206</v>
+        <v>449.0213193023424</v>
       </c>
       <c r="C93" t="n">
-        <v>449.9851935867555</v>
+        <v>468.1301005814363</v>
       </c>
       <c r="D93" t="n">
-        <v>441.8965257028684</v>
+        <v>447.6897705604439</v>
       </c>
       <c r="E93" t="n">
-        <v>448.2959289550781</v>
+        <v>463.0125732421875</v>
       </c>
       <c r="F93" t="n">
-        <v>25349400</v>
+        <v>38000200</v>
       </c>
       <c r="G93" t="n">
         <v>0</v>
@@ -2861,22 +2861,22 @@
     </row>
     <row r="94">
       <c r="A94" s="1" t="n">
-        <v>46045</v>
+        <v>46048</v>
       </c>
       <c r="B94" t="n">
-        <v>449.0213193023424</v>
+        <v>462.3766075757791</v>
       </c>
       <c r="C94" t="n">
-        <v>468.1301005814363</v>
+        <v>471.2602507862521</v>
       </c>
       <c r="D94" t="n">
-        <v>447.6897705604439</v>
+        <v>459.0874767807031</v>
       </c>
       <c r="E94" t="n">
-        <v>463.0125732421875</v>
+        <v>467.3152770996094</v>
       </c>
       <c r="F94" t="n">
-        <v>38000200</v>
+        <v>29291200</v>
       </c>
       <c r="G94" t="n">
         <v>0</v>
@@ -2887,22 +2887,22 @@
     </row>
     <row r="95">
       <c r="A95" s="1" t="n">
-        <v>46048</v>
+        <v>46049</v>
       </c>
       <c r="B95" t="n">
-        <v>462.3766075757791</v>
+        <v>470.7137217228436</v>
       </c>
       <c r="C95" t="n">
-        <v>471.2602507862521</v>
+        <v>479.8258954035317</v>
       </c>
       <c r="D95" t="n">
-        <v>459.0874767807031</v>
+        <v>470.1771174893794</v>
       </c>
       <c r="E95" t="n">
-        <v>467.3152770996094</v>
+        <v>477.5503234863281</v>
       </c>
       <c r="F95" t="n">
-        <v>29291200</v>
+        <v>29213900</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
@@ -2913,22 +2913,22 @@
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
-        <v>46049</v>
+        <v>46050</v>
       </c>
       <c r="B96" t="n">
-        <v>470.7136916421546</v>
+        <v>480.1637149068934</v>
       </c>
       <c r="C96" t="n">
-        <v>479.8258647405344</v>
+        <v>480.6903724414303</v>
       </c>
       <c r="D96" t="n">
-        <v>470.1770874429818</v>
+        <v>474.9865685400099</v>
       </c>
       <c r="E96" t="n">
-        <v>477.55029296875</v>
+        <v>478.5936889648438</v>
       </c>
       <c r="F96" t="n">
-        <v>29213900</v>
+        <v>36875400</v>
       </c>
       <c r="G96" t="n">
         <v>0</v>
@@ -2939,22 +2939,22 @@
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
-        <v>46050</v>
+        <v>46051</v>
       </c>
       <c r="B97" t="n">
-        <v>480.1637455245844</v>
+        <v>437.2162272399066</v>
       </c>
       <c r="C97" t="n">
-        <v>480.6904030927037</v>
+        <v>439.7104135269112</v>
       </c>
       <c r="D97" t="n">
-        <v>474.9865988275796</v>
+        <v>418.365815756604</v>
       </c>
       <c r="E97" t="n">
-        <v>478.5937194824219</v>
+        <v>430.7671508789062</v>
       </c>
       <c r="F97" t="n">
-        <v>36875400</v>
+        <v>128855300</v>
       </c>
       <c r="G97" t="n">
         <v>0</v>
@@ -2965,22 +2965,22 @@
     </row>
     <row r="98">
       <c r="A98" s="1" t="n">
-        <v>46051</v>
+        <v>46052</v>
       </c>
       <c r="B98" t="n">
-        <v>437.2161962654454</v>
+        <v>436.4013853645445</v>
       </c>
       <c r="C98" t="n">
-        <v>439.7103823757502</v>
+        <v>436.8286672682951</v>
       </c>
       <c r="D98" t="n">
-        <v>418.365786117595</v>
+        <v>423.7615739365565</v>
       </c>
       <c r="E98" t="n">
-        <v>430.7671203613281</v>
+        <v>427.5773620605469</v>
       </c>
       <c r="F98" t="n">
-        <v>128855300</v>
+        <v>58566800</v>
       </c>
       <c r="G98" t="n">
         <v>0</v>
@@ -2991,22 +2991,22 @@
     </row>
     <row r="99">
       <c r="A99" s="1" t="n">
-        <v>46052</v>
+        <v>46055</v>
       </c>
       <c r="B99" t="n">
-        <v>436.4014165119217</v>
+        <v>427.5276741085398</v>
       </c>
       <c r="C99" t="n">
-        <v>436.8286984461687</v>
+        <v>428.0245220118177</v>
       </c>
       <c r="D99" t="n">
-        <v>423.7616041817895</v>
+        <v>419.588054318219</v>
       </c>
       <c r="E99" t="n">
-        <v>427.577392578125</v>
+        <v>420.7009887695312</v>
       </c>
       <c r="F99" t="n">
-        <v>58566800</v>
+        <v>42219900</v>
       </c>
       <c r="G99" t="n">
         <v>0</v>
@@ -3017,22 +3017,22 @@
     </row>
     <row r="100">
       <c r="A100" s="1" t="n">
-        <v>46055</v>
+        <v>46056</v>
       </c>
       <c r="B100" t="n">
-        <v>427.5276741085398</v>
+        <v>419.3495781995532</v>
       </c>
       <c r="C100" t="n">
-        <v>428.0245220118177</v>
+        <v>419.3893041977899</v>
       </c>
       <c r="D100" t="n">
-        <v>419.588054318219</v>
+        <v>405.9843574339844</v>
       </c>
       <c r="E100" t="n">
-        <v>420.7009887695312</v>
+        <v>408.6176452636719</v>
       </c>
       <c r="F100" t="n">
-        <v>42219900</v>
+        <v>61424100</v>
       </c>
       <c r="G100" t="n">
         <v>0</v>
@@ -3043,22 +3043,22 @@
     </row>
     <row r="101">
       <c r="A101" s="1" t="n">
-        <v>46056</v>
+        <v>46057</v>
       </c>
       <c r="B101" t="n">
-        <v>419.3495781995532</v>
+        <v>408.4089957411405</v>
       </c>
       <c r="C101" t="n">
-        <v>419.3893041977899</v>
+        <v>417.1535071208501</v>
       </c>
       <c r="D101" t="n">
-        <v>405.9843574339844</v>
+        <v>406.6600813351222</v>
       </c>
       <c r="E101" t="n">
-        <v>408.6176452636719</v>
+        <v>411.5788879394531</v>
       </c>
       <c r="F101" t="n">
-        <v>61424100</v>
+        <v>45012400</v>
       </c>
       <c r="G101" t="n">
         <v>0</v>
@@ -3069,22 +3069,22 @@
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>46057</v>
+        <v>46058</v>
       </c>
       <c r="B102" t="n">
-        <v>408.4089654586022</v>
+        <v>404.8714440282318</v>
       </c>
       <c r="C102" t="n">
-        <v>417.1534761899275</v>
+        <v>405.7260079125925</v>
       </c>
       <c r="D102" t="n">
-        <v>406.6600511822617</v>
+        <v>389.8467674620769</v>
       </c>
       <c r="E102" t="n">
-        <v>411.578857421875</v>
+        <v>391.1882629394531</v>
       </c>
       <c r="F102" t="n">
-        <v>45012400</v>
+        <v>66289200</v>
       </c>
       <c r="G102" t="n">
         <v>0</v>
@@ -3095,22 +3095,22 @@
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>46058</v>
+        <v>46059</v>
       </c>
       <c r="B103" t="n">
-        <v>404.8714124431945</v>
+        <v>396.6535630940219</v>
       </c>
       <c r="C103" t="n">
-        <v>405.7259762608884</v>
+        <v>399.2570412200398</v>
       </c>
       <c r="D103" t="n">
-        <v>389.8467370491522</v>
+        <v>390.4429643868461</v>
       </c>
       <c r="E103" t="n">
-        <v>391.188232421875</v>
+        <v>398.6111450195312</v>
       </c>
       <c r="F103" t="n">
-        <v>66289200</v>
+        <v>53515300</v>
       </c>
       <c r="G103" t="n">
         <v>0</v>
@@ -3121,22 +3121,22 @@
     </row>
     <row r="104">
       <c r="A104" s="1" t="n">
-        <v>46059</v>
+        <v>46062</v>
       </c>
       <c r="B104" t="n">
-        <v>396.6535630940219</v>
+        <v>402.2977759502542</v>
       </c>
       <c r="C104" t="n">
-        <v>399.2570412200398</v>
+        <v>412.2744908996196</v>
       </c>
       <c r="D104" t="n">
-        <v>390.4429643868461</v>
+        <v>398.3428555009064</v>
       </c>
       <c r="E104" t="n">
-        <v>398.6111450195312</v>
+        <v>410.9926147460938</v>
       </c>
       <c r="F104" t="n">
-        <v>53515300</v>
+        <v>45480500</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -3147,22 +3147,22 @@
     </row>
     <row r="105">
       <c r="A105" s="1" t="n">
-        <v>46062</v>
+        <v>46063</v>
       </c>
       <c r="B105" t="n">
-        <v>402.2977759502542</v>
+        <v>416.9746165751398</v>
       </c>
       <c r="C105" t="n">
-        <v>412.2744908996196</v>
+        <v>421.009018998737</v>
       </c>
       <c r="D105" t="n">
-        <v>398.3428555009064</v>
+        <v>410.0982587889407</v>
       </c>
       <c r="E105" t="n">
-        <v>410.9926147460938</v>
+        <v>410.6646423339844</v>
       </c>
       <c r="F105" t="n">
-        <v>45480500</v>
+        <v>44857900</v>
       </c>
       <c r="G105" t="n">
         <v>0</v>
@@ -3173,22 +3173,22 @@
     </row>
     <row r="106">
       <c r="A106" s="1" t="n">
-        <v>46063</v>
+        <v>46064</v>
       </c>
       <c r="B106" t="n">
-        <v>416.9746475616288</v>
+        <v>413.5563153661985</v>
       </c>
       <c r="C106" t="n">
-        <v>421.0090502850332</v>
+        <v>413.8345489802859</v>
       </c>
       <c r="D106" t="n">
-        <v>410.0982892644293</v>
+        <v>398.4819668946231</v>
       </c>
       <c r="E106" t="n">
-        <v>410.6646728515625</v>
+        <v>401.8207702636719</v>
       </c>
       <c r="F106" t="n">
-        <v>44857900</v>
+        <v>42491000</v>
       </c>
       <c r="G106" t="n">
         <v>0</v>
@@ -3199,22 +3199,22 @@
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
-        <v>46064</v>
+        <v>46065</v>
       </c>
       <c r="B107" t="n">
-        <v>413.5563153661985</v>
+        <v>402.4468146669985</v>
       </c>
       <c r="C107" t="n">
-        <v>413.8345489802859</v>
+        <v>403.6392618034954</v>
       </c>
       <c r="D107" t="n">
-        <v>398.4819668946231</v>
+        <v>395.5008904586587</v>
       </c>
       <c r="E107" t="n">
-        <v>401.8207702636719</v>
+        <v>399.3067321777344</v>
       </c>
       <c r="F107" t="n">
-        <v>42491000</v>
+        <v>40802400</v>
       </c>
       <c r="G107" t="n">
         <v>0</v>
@@ -3225,22 +3225,22 @@
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
-        <v>46065</v>
+        <v>46066</v>
       </c>
       <c r="B108" t="n">
-        <v>402.4467839094351</v>
+        <v>401.900281272875</v>
       </c>
       <c r="C108" t="n">
-        <v>403.6392309547976</v>
+        <v>402.9834060634867</v>
       </c>
       <c r="D108" t="n">
-        <v>395.5008602319473</v>
+        <v>395.5406038478973</v>
       </c>
       <c r="E108" t="n">
-        <v>399.3067016601562</v>
+        <v>398.7900085449219</v>
       </c>
       <c r="F108" t="n">
-        <v>40802400</v>
+        <v>34091600</v>
       </c>
       <c r="G108" t="n">
         <v>0</v>
@@ -3251,22 +3251,22 @@
     </row>
     <row r="109">
       <c r="A109" s="1" t="n">
-        <v>46066</v>
+        <v>46070</v>
       </c>
       <c r="B109" t="n">
-        <v>401.900281272875</v>
+        <v>396.7032617740463</v>
       </c>
       <c r="C109" t="n">
-        <v>402.9834060634867</v>
+        <v>397.9950542597942</v>
       </c>
       <c r="D109" t="n">
-        <v>395.5406038478973</v>
+        <v>392.0428257724806</v>
       </c>
       <c r="E109" t="n">
-        <v>398.7900085449219</v>
+        <v>394.3581237792969</v>
       </c>
       <c r="F109" t="n">
-        <v>34091600</v>
+        <v>32078800</v>
       </c>
       <c r="G109" t="n">
         <v>0</v>
@@ -3277,22 +3277,22 @@
     </row>
     <row r="110">
       <c r="A110" s="1" t="n">
-        <v>46070</v>
+        <v>46071</v>
       </c>
       <c r="B110" t="n">
-        <v>396.7032310749887</v>
+        <v>395.6201070500213</v>
       </c>
       <c r="C110" t="n">
-        <v>397.9950234607705</v>
+        <v>400.0221720919145</v>
       </c>
       <c r="D110" t="n">
-        <v>392.0427954340728</v>
+        <v>393.8215201082963</v>
       </c>
       <c r="E110" t="n">
-        <v>394.3580932617188</v>
+        <v>397.0808410644531</v>
       </c>
       <c r="F110" t="n">
-        <v>32078800</v>
+        <v>23223400</v>
       </c>
       <c r="G110" t="n">
         <v>0</v>
@@ -3303,25 +3303,25 @@
     </row>
     <row r="111">
       <c r="A111" s="1" t="n">
-        <v>46071</v>
+        <v>46072</v>
       </c>
       <c r="B111" t="n">
-        <v>395.6201374553349</v>
+        <v>399.0727866126232</v>
       </c>
       <c r="C111" t="n">
-        <v>400.0222028355481</v>
+        <v>402.7976819572589</v>
       </c>
       <c r="D111" t="n">
-        <v>393.8215503753798</v>
+        <v>395.0690225854118</v>
       </c>
       <c r="E111" t="n">
-        <v>397.0808715820312</v>
+        <v>396.8517761230469</v>
       </c>
       <c r="F111" t="n">
-        <v>23223400</v>
+        <v>28234000</v>
       </c>
       <c r="G111" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H111" t="n">
         <v>0</v>
@@ -3329,25 +3329,25 @@
     </row>
     <row r="112">
       <c r="A112" s="1" t="n">
-        <v>46072</v>
+        <v>46073</v>
       </c>
       <c r="B112" t="n">
-        <v>399.0727866126232</v>
+        <v>394.5112344348997</v>
       </c>
       <c r="C112" t="n">
-        <v>402.7976819572589</v>
+        <v>398.5050592846536</v>
       </c>
       <c r="D112" t="n">
-        <v>395.0690225854118</v>
+        <v>393.5650869938952</v>
       </c>
       <c r="E112" t="n">
-        <v>396.8517761230469</v>
+        <v>395.6267395019531</v>
       </c>
       <c r="F112" t="n">
-        <v>28234000</v>
+        <v>34015200</v>
       </c>
       <c r="G112" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
         <v>0</v>
@@ -3355,22 +3355,22 @@
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
-        <v>46073</v>
+        <v>46076</v>
       </c>
       <c r="B113" t="n">
-        <v>394.5112344348997</v>
+        <v>393.405742102137</v>
       </c>
       <c r="C113" t="n">
-        <v>398.5050592846536</v>
+        <v>393.7642745182822</v>
       </c>
       <c r="D113" t="n">
-        <v>393.5650869938952</v>
+        <v>381.5537777227514</v>
       </c>
       <c r="E113" t="n">
-        <v>395.6267395019531</v>
+        <v>382.9182434082031</v>
       </c>
       <c r="F113" t="n">
-        <v>34015200</v>
+        <v>43238300</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -3381,22 +3381,22 @@
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
-        <v>46076</v>
+        <v>46077</v>
       </c>
       <c r="B114" t="n">
-        <v>393.4057107487328</v>
+        <v>382.5895619940176</v>
       </c>
       <c r="C114" t="n">
-        <v>393.7642431363039</v>
+        <v>387.7884640317496</v>
       </c>
       <c r="D114" t="n">
-        <v>381.5537473139175</v>
+        <v>380.1693467763097</v>
       </c>
       <c r="E114" t="n">
-        <v>382.918212890625</v>
+        <v>387.429931640625</v>
       </c>
       <c r="F114" t="n">
-        <v>43238300</v>
+        <v>33884700</v>
       </c>
       <c r="G114" t="n">
         <v>0</v>
@@ -3407,22 +3407,22 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="B115" t="n">
-        <v>382.5895921303232</v>
+        <v>388.9537605304631</v>
       </c>
       <c r="C115" t="n">
-        <v>387.7884945775691</v>
+        <v>399.8496074643683</v>
       </c>
       <c r="D115" t="n">
-        <v>380.1693767219767</v>
+        <v>388.5852587696308</v>
       </c>
       <c r="E115" t="n">
-        <v>387.4299621582031</v>
+        <v>398.9831237792969</v>
       </c>
       <c r="F115" t="n">
-        <v>33884700</v>
+        <v>43625500</v>
       </c>
       <c r="G115" t="n">
         <v>0</v>
@@ -3433,22 +3433,22 @@
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>46078</v>
+        <v>46079</v>
       </c>
       <c r="B116" t="n">
-        <v>388.9537605304631</v>
+        <v>403.0765245044552</v>
       </c>
       <c r="C116" t="n">
-        <v>399.8496074643683</v>
+        <v>405.8453028142193</v>
       </c>
       <c r="D116" t="n">
-        <v>388.5852587696308</v>
+        <v>397.1306190557743</v>
       </c>
       <c r="E116" t="n">
-        <v>398.9831237792969</v>
+        <v>400.0986022949219</v>
       </c>
       <c r="F116" t="n">
-        <v>43625500</v>
+        <v>34405900</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
-        <v>46079</v>
+        <v>46080</v>
       </c>
       <c r="B117" t="n">
-        <v>403.0765245044552</v>
+        <v>389.3023679559341</v>
       </c>
       <c r="C117" t="n">
-        <v>405.8453028142193</v>
+        <v>395.2183958601928</v>
       </c>
       <c r="D117" t="n">
-        <v>397.1306190557743</v>
+        <v>388.3064040716401</v>
       </c>
       <c r="E117" t="n">
-        <v>400.0986022949219</v>
+        <v>391.1548461914062</v>
       </c>
       <c r="F117" t="n">
-        <v>34405900</v>
+        <v>51367200</v>
       </c>
       <c r="G117" t="n">
         <v>0</v>
@@ -3485,22 +3485,22 @@
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
-        <v>46080</v>
+        <v>46083</v>
       </c>
       <c r="B118" t="n">
-        <v>389.3023679559341</v>
+        <v>391.2743390590049</v>
       </c>
       <c r="C118" t="n">
-        <v>395.2183958601928</v>
+        <v>399.5707348557469</v>
       </c>
       <c r="D118" t="n">
-        <v>388.3064040716401</v>
+        <v>389.0533591512552</v>
       </c>
       <c r="E118" t="n">
-        <v>391.1548461914062</v>
+        <v>396.9413757324219</v>
       </c>
       <c r="F118" t="n">
-        <v>51367200</v>
+        <v>35474900</v>
       </c>
       <c r="G118" t="n">
         <v>0</v>
@@ -3511,22 +3511,22 @@
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
-        <v>46083</v>
+        <v>46084</v>
       </c>
       <c r="B119" t="n">
-        <v>391.2743390590049</v>
+        <v>391.5532542396072</v>
       </c>
       <c r="C119" t="n">
-        <v>399.5707348557469</v>
+        <v>405.0585220162706</v>
       </c>
       <c r="D119" t="n">
-        <v>389.0533591512552</v>
+        <v>391.0851500003899</v>
       </c>
       <c r="E119" t="n">
-        <v>396.9413757324219</v>
+        <v>402.2996826171875</v>
       </c>
       <c r="F119" t="n">
-        <v>35474900</v>
+        <v>38199200</v>
       </c>
       <c r="G119" t="n">
         <v>0</v>
@@ -3537,22 +3537,22 @@
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
-        <v>46084</v>
+        <v>46085</v>
       </c>
       <c r="B120" t="n">
-        <v>391.5532542396072</v>
+        <v>399.6504140582061</v>
       </c>
       <c r="C120" t="n">
-        <v>405.0585220162706</v>
+        <v>409.3710312257941</v>
       </c>
       <c r="D120" t="n">
-        <v>391.0851500003899</v>
+        <v>398.6942972465368</v>
       </c>
       <c r="E120" t="n">
-        <v>402.2996826171875</v>
+        <v>403.5645751953125</v>
       </c>
       <c r="F120" t="n">
-        <v>38199200</v>
+        <v>35808000</v>
       </c>
       <c r="G120" t="n">
         <v>0</v>
@@ -3563,22 +3563,22 @@
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
-        <v>46085</v>
+        <v>46086</v>
       </c>
       <c r="B121" t="n">
-        <v>399.6504140582061</v>
+        <v>402.7877173292459</v>
       </c>
       <c r="C121" t="n">
-        <v>409.3710312257941</v>
+        <v>409.9486695143622</v>
       </c>
       <c r="D121" t="n">
-        <v>398.6942972465368</v>
+        <v>402.7677785996419</v>
       </c>
       <c r="E121" t="n">
-        <v>403.5645751953125</v>
+        <v>409.0224304199219</v>
       </c>
       <c r="F121" t="n">
-        <v>35808000</v>
+        <v>39001300</v>
       </c>
       <c r="G121" t="n">
         <v>0</v>
@@ -3589,22 +3589,22 @@
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
-        <v>46086</v>
+        <v>46087</v>
       </c>
       <c r="B122" t="n">
-        <v>402.7877173292459</v>
+        <v>407.5484392107423</v>
       </c>
       <c r="C122" t="n">
-        <v>409.9486695143622</v>
+        <v>411.3828759024364</v>
       </c>
       <c r="D122" t="n">
-        <v>402.7677785996419</v>
+        <v>406.8612216895844</v>
       </c>
       <c r="E122" t="n">
-        <v>409.0224304199219</v>
+        <v>407.3093872070312</v>
       </c>
       <c r="F122" t="n">
-        <v>39001300</v>
+        <v>31123900</v>
       </c>
       <c r="G122" t="n">
         <v>0</v>
@@ -3615,22 +3615,22 @@
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
-        <v>46087</v>
+        <v>46090</v>
       </c>
       <c r="B123" t="n">
-        <v>407.5484392107423</v>
+        <v>403.2857003455267</v>
       </c>
       <c r="C123" t="n">
-        <v>411.3828759024364</v>
+        <v>408.5543272911556</v>
       </c>
       <c r="D123" t="n">
-        <v>406.8612216895844</v>
+        <v>401.8714182880504</v>
       </c>
       <c r="E123" t="n">
-        <v>407.3093872070312</v>
+        <v>407.757568359375</v>
       </c>
       <c r="F123" t="n">
-        <v>31123900</v>
+        <v>30131900</v>
       </c>
       <c r="G123" t="n">
         <v>0</v>
@@ -3641,22 +3641,22 @@
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
-        <v>46090</v>
+        <v>46091</v>
       </c>
       <c r="B124" t="n">
-        <v>403.2857003455267</v>
+        <v>408.3750692869274</v>
       </c>
       <c r="C124" t="n">
-        <v>408.5543272911556</v>
+        <v>408.5443965203919</v>
       </c>
       <c r="D124" t="n">
-        <v>401.8714182880504</v>
+        <v>401.3037196464309</v>
       </c>
       <c r="E124" t="n">
-        <v>407.757568359375</v>
+        <v>404.122314453125</v>
       </c>
       <c r="F124" t="n">
-        <v>30131900</v>
+        <v>31706400</v>
       </c>
       <c r="G124" t="n">
         <v>0</v>
@@ -3667,22 +3667,22 @@
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
-        <v>46091</v>
+        <v>46092</v>
       </c>
       <c r="B125" t="n">
-        <v>408.3750692869274</v>
+        <v>403.9330670994013</v>
       </c>
       <c r="C125" t="n">
-        <v>408.5443965203919</v>
+        <v>407.3591851847947</v>
       </c>
       <c r="D125" t="n">
-        <v>401.3037196464309</v>
+        <v>399.9691200230297</v>
       </c>
       <c r="E125" t="n">
-        <v>404.122314453125</v>
+        <v>403.245849609375</v>
       </c>
       <c r="F125" t="n">
-        <v>31706400</v>
+        <v>25512100</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -3693,22 +3693,22 @@
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
-        <v>46092</v>
+        <v>46093</v>
       </c>
       <c r="B126" t="n">
-        <v>403.9330670994013</v>
+        <v>402.9968458288957</v>
       </c>
       <c r="C126" t="n">
-        <v>407.3591851847947</v>
+        <v>404.4808221962511</v>
       </c>
       <c r="D126" t="n">
-        <v>399.9691200230297</v>
+        <v>400.0886180975</v>
       </c>
       <c r="E126" t="n">
-        <v>403.245849609375</v>
+        <v>400.2380065917969</v>
       </c>
       <c r="F126" t="n">
-        <v>25512100</v>
+        <v>27263900</v>
       </c>
       <c r="G126" t="n">
         <v>0</v>
@@ -3719,22 +3719,22 @@
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
-        <v>46093</v>
+        <v>46094</v>
       </c>
       <c r="B127" t="n">
-        <v>402.9968765568314</v>
+        <v>399.3815063856616</v>
       </c>
       <c r="C127" t="n">
-        <v>404.4808530373378</v>
+        <v>403.1661568819284</v>
       </c>
       <c r="D127" t="n">
-        <v>400.0886486036874</v>
+        <v>392.6587503554791</v>
       </c>
       <c r="E127" t="n">
-        <v>400.238037109375</v>
+        <v>393.9534912109375</v>
       </c>
       <c r="F127" t="n">
-        <v>27263900</v>
+        <v>26848000</v>
       </c>
       <c r="G127" t="n">
         <v>0</v>
@@ -3745,22 +3745,22 @@
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
-        <v>46094</v>
+        <v>46097</v>
       </c>
       <c r="B128" t="n">
-        <v>399.3815063856616</v>
+        <v>396.4633374914087</v>
       </c>
       <c r="C128" t="n">
-        <v>403.1661568819284</v>
+        <v>399.013002518604</v>
       </c>
       <c r="D128" t="n">
-        <v>392.6587503554791</v>
+        <v>393.1965772756644</v>
       </c>
       <c r="E128" t="n">
-        <v>393.9534912109375</v>
+        <v>398.3357543945312</v>
       </c>
       <c r="F128" t="n">
-        <v>26848000</v>
+        <v>27733700</v>
       </c>
       <c r="G128" t="n">
         <v>0</v>
@@ -3771,22 +3771,22 @@
     </row>
     <row r="129">
       <c r="A129" s="1" t="n">
-        <v>46097</v>
+        <v>46098</v>
       </c>
       <c r="B129" t="n">
-        <v>396.4633374914087</v>
+        <v>398.6544574759768</v>
       </c>
       <c r="C129" t="n">
-        <v>399.013002518604</v>
+        <v>402.7677932271478</v>
       </c>
       <c r="D129" t="n">
-        <v>393.1965772756644</v>
+        <v>396.1446394015159</v>
       </c>
       <c r="E129" t="n">
-        <v>398.3357543945312</v>
+        <v>397.7979431152344</v>
       </c>
       <c r="F129" t="n">
-        <v>27733700</v>
+        <v>26228300</v>
       </c>
       <c r="G129" t="n">
         <v>0</v>
@@ -3797,22 +3797,22 @@
     </row>
     <row r="130">
       <c r="A130" s="1" t="n">
-        <v>46098</v>
+        <v>46099</v>
       </c>
       <c r="B130" t="n">
-        <v>398.6544268926901</v>
+        <v>395.5271224277118</v>
       </c>
       <c r="C130" t="n">
-        <v>402.7677623283013</v>
+        <v>396.3936061005556</v>
       </c>
       <c r="D130" t="n">
-        <v>396.1446090107731</v>
+        <v>389.421859259591</v>
       </c>
       <c r="E130" t="n">
-        <v>397.7979125976562</v>
+        <v>390.2086791992188</v>
       </c>
       <c r="F130" t="n">
-        <v>26228300</v>
+        <v>25908500</v>
       </c>
       <c r="G130" t="n">
         <v>0</v>
@@ -3823,22 +3823,22 @@
     </row>
     <row r="131">
       <c r="A131" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="B131" t="n">
-        <v>395.5271533612366</v>
+        <v>388.5255176358589</v>
       </c>
       <c r="C131" t="n">
-        <v>396.3936371018467</v>
+        <v>390.9058555160312</v>
       </c>
       <c r="D131" t="n">
-        <v>389.4218897156333</v>
+        <v>385.4977789148814</v>
       </c>
       <c r="E131" t="n">
-        <v>390.2087097167969</v>
+        <v>387.4498596191406</v>
       </c>
       <c r="F131" t="n">
-        <v>25908500</v>
+        <v>25138800</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -3849,22 +3849,22 @@
     </row>
     <row r="132">
       <c r="A132" s="1" t="n">
-        <v>46100</v>
+        <v>46101</v>
       </c>
       <c r="B132" t="n">
-        <v>388.5255176358589</v>
+        <v>385.2288602760525</v>
       </c>
       <c r="C132" t="n">
-        <v>390.9058555160312</v>
+        <v>385.4380041709834</v>
       </c>
       <c r="D132" t="n">
-        <v>385.4977789148814</v>
+        <v>378.5857681226169</v>
       </c>
       <c r="E132" t="n">
-        <v>387.4498596191406</v>
+        <v>380.3287048339844</v>
       </c>
       <c r="F132" t="n">
-        <v>25138800</v>
+        <v>50853200</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="133">
       <c r="A133" s="1" t="n">
-        <v>46101</v>
+        <v>46104</v>
       </c>
       <c r="B133" t="n">
-        <v>385.2288911868192</v>
+        <v>382.3505545919761</v>
       </c>
       <c r="C133" t="n">
-        <v>385.4380350985318</v>
+        <v>385.6471928372158</v>
       </c>
       <c r="D133" t="n">
-        <v>378.5857985003418</v>
+        <v>380.1395134056624</v>
       </c>
       <c r="E133" t="n">
-        <v>380.3287353515625</v>
+        <v>381.4541931152344</v>
       </c>
       <c r="F133" t="n">
-        <v>50853200</v>
+        <v>29680100</v>
       </c>
       <c r="G133" t="n">
         <v>0</v>
@@ -3901,22 +3901,22 @@
     </row>
     <row r="134">
       <c r="A134" s="1" t="n">
-        <v>46104</v>
+        <v>46105</v>
       </c>
       <c r="B134" t="n">
-        <v>382.3505545919761</v>
+        <v>380.8167328036651</v>
       </c>
       <c r="C134" t="n">
-        <v>385.6471928372158</v>
+        <v>380.9263046350485</v>
       </c>
       <c r="D134" t="n">
-        <v>380.1395134056624</v>
+        <v>370.3491731415432</v>
       </c>
       <c r="E134" t="n">
-        <v>381.4541931152344</v>
+        <v>371.2355651855469</v>
       </c>
       <c r="F134" t="n">
-        <v>29680100</v>
+        <v>42733600</v>
       </c>
       <c r="G134" t="n">
         <v>0</v>
@@ -3927,22 +3927,22 @@
     </row>
     <row r="135">
       <c r="A135" s="1" t="n">
-        <v>46105</v>
+        <v>46106</v>
       </c>
       <c r="B135" t="n">
-        <v>380.8167328036651</v>
+        <v>375.3987224826456</v>
       </c>
       <c r="C135" t="n">
-        <v>380.9263046350485</v>
+        <v>375.5381416220395</v>
       </c>
       <c r="D135" t="n">
-        <v>370.3491731415432</v>
+        <v>368.1381372201017</v>
       </c>
       <c r="E135" t="n">
-        <v>371.2355651855469</v>
+        <v>369.5424499511719</v>
       </c>
       <c r="F135" t="n">
-        <v>42733600</v>
+        <v>31181200</v>
       </c>
       <c r="G135" t="n">
         <v>0</v>
@@ -3953,22 +3953,22 @@
     </row>
     <row r="136">
       <c r="A136" s="1" t="n">
-        <v>46106</v>
+        <v>46107</v>
       </c>
       <c r="B136" t="n">
-        <v>375.3987224826456</v>
+        <v>369.3233201292261</v>
       </c>
       <c r="C136" t="n">
-        <v>375.5381416220395</v>
+        <v>373.2075730440749</v>
       </c>
       <c r="D136" t="n">
-        <v>368.1381372201017</v>
+        <v>363.7160388213271</v>
       </c>
       <c r="E136" t="n">
-        <v>369.5424499511719</v>
+        <v>364.4928894042969</v>
       </c>
       <c r="F136" t="n">
-        <v>31181200</v>
+        <v>36836600</v>
       </c>
       <c r="G136" t="n">
         <v>0</v>
@@ -3979,22 +3979,22 @@
     </row>
     <row r="137">
       <c r="A137" s="1" t="n">
-        <v>46107</v>
+        <v>46108</v>
       </c>
       <c r="B137" t="n">
-        <v>369.3233510512375</v>
+        <v>360.4393475355787</v>
       </c>
       <c r="C137" t="n">
-        <v>373.2076042912997</v>
+        <v>360.9871459448897</v>
       </c>
       <c r="D137" t="n">
-        <v>363.7160692738626</v>
+        <v>355.0711176485405</v>
       </c>
       <c r="E137" t="n">
-        <v>364.492919921875</v>
+        <v>355.3300476074219</v>
       </c>
       <c r="F137" t="n">
-        <v>36836600</v>
+        <v>37883400</v>
       </c>
       <c r="G137" t="n">
         <v>0</v>
@@ -4005,22 +4005,22 @@
     </row>
     <row r="138">
       <c r="A138" s="1" t="n">
-        <v>46108</v>
+        <v>46111</v>
       </c>
       <c r="B138" t="n">
-        <v>360.4393165791876</v>
+        <v>360.4393363053819</v>
       </c>
       <c r="C138" t="n">
-        <v>360.9871149414508</v>
+        <v>363.8853629556265</v>
       </c>
       <c r="D138" t="n">
-        <v>355.0710871532006</v>
+        <v>354.8420239421825</v>
       </c>
       <c r="E138" t="n">
-        <v>355.3300170898438</v>
+        <v>357.5111999511719</v>
       </c>
       <c r="F138" t="n">
-        <v>37883400</v>
+        <v>44797000</v>
       </c>
       <c r="G138" t="n">
         <v>0</v>
@@ -4031,22 +4031,22 @@
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
-        <v>46111</v>
+        <v>46112</v>
       </c>
       <c r="B139" t="n">
-        <v>360.4393055378546</v>
+        <v>363.0786217954557</v>
       </c>
       <c r="C139" t="n">
-        <v>363.8853318939423</v>
+        <v>371.3949263066763</v>
       </c>
       <c r="D139" t="n">
-        <v>354.8419936524484</v>
+        <v>361.6046146993887</v>
       </c>
       <c r="E139" t="n">
-        <v>357.5111694335938</v>
+        <v>368.6759643554688</v>
       </c>
       <c r="F139" t="n">
-        <v>44797000</v>
+        <v>45244400</v>
       </c>
       <c r="G139" t="n">
         <v>0</v>
@@ -4057,22 +4057,22 @@
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
-        <v>46112</v>
+        <v>46113</v>
       </c>
       <c r="B140" t="n">
-        <v>363.0786217954557</v>
+        <v>371.9825473134139</v>
       </c>
       <c r="C140" t="n">
-        <v>371.3949263066763</v>
+        <v>372.4805292634522</v>
       </c>
       <c r="D140" t="n">
-        <v>361.6046146993887</v>
+        <v>366.7139201659809</v>
       </c>
       <c r="E140" t="n">
-        <v>368.6759643554688</v>
+        <v>367.8791809082031</v>
       </c>
       <c r="F140" t="n">
-        <v>45244400</v>
+        <v>29417200</v>
       </c>
       <c r="G140" t="n">
         <v>0</v>
@@ -4083,22 +4083,22 @@
     </row>
     <row r="141">
       <c r="A141" s="1" t="n">
-        <v>46113</v>
+        <v>46114</v>
       </c>
       <c r="B141" t="n">
-        <v>371.9825473134139</v>
+        <v>365.7278929006101</v>
       </c>
       <c r="C141" t="n">
-        <v>372.4805292634522</v>
+        <v>372.1319638369453</v>
       </c>
       <c r="D141" t="n">
-        <v>366.7139201659809</v>
+        <v>362.680245817395</v>
       </c>
       <c r="E141" t="n">
-        <v>367.8791809082031</v>
+        <v>371.9526672363281</v>
       </c>
       <c r="F141" t="n">
-        <v>29417200</v>
+        <v>24099100</v>
       </c>
       <c r="G141" t="n">
         <v>0</v>
@@ -4109,22 +4109,22 @@
     </row>
     <row r="142">
       <c r="A142" s="1" t="n">
-        <v>46114</v>
+        <v>46118</v>
       </c>
       <c r="B142" t="n">
-        <v>365.7278929006101</v>
+        <v>371.9825539180967</v>
       </c>
       <c r="C142" t="n">
-        <v>372.1319638369453</v>
+        <v>372.2216059265558</v>
       </c>
       <c r="D142" t="n">
-        <v>362.680245817395</v>
+        <v>368.0086676124431</v>
       </c>
       <c r="E142" t="n">
-        <v>371.9526672363281</v>
+        <v>371.3750305175781</v>
       </c>
       <c r="F142" t="n">
-        <v>24099100</v>
+        <v>16146600</v>
       </c>
       <c r="G142" t="n">
         <v>0</v>
@@ -4135,22 +4135,22 @@
     </row>
     <row r="143">
       <c r="A143" s="1" t="n">
-        <v>46118</v>
+        <v>46119</v>
       </c>
       <c r="B143" t="n">
-        <v>371.9825233505957</v>
+        <v>368.8452727581139</v>
       </c>
       <c r="C143" t="n">
-        <v>372.2215753394107</v>
+        <v>370.9467724245638</v>
       </c>
       <c r="D143" t="n">
-        <v>368.0086373714944</v>
+        <v>365.080530373921</v>
       </c>
       <c r="E143" t="n">
-        <v>371.375</v>
+        <v>370.7874145507812</v>
       </c>
       <c r="F143" t="n">
-        <v>16146600</v>
+        <v>21443300</v>
       </c>
       <c r="G143" t="n">
         <v>0</v>
@@ -4161,22 +4161,22 @@
     </row>
     <row r="144">
       <c r="A144" s="1" t="n">
-        <v>46119</v>
+        <v>46120</v>
       </c>
       <c r="B144" t="n">
-        <v>368.8452727581139</v>
+        <v>383.4261612830284</v>
       </c>
       <c r="C144" t="n">
-        <v>370.9467724245638</v>
+        <v>383.4460696173869</v>
       </c>
       <c r="D144" t="n">
-        <v>365.080530373921</v>
+        <v>369.9109249891301</v>
       </c>
       <c r="E144" t="n">
-        <v>370.7874145507812</v>
+        <v>372.8191223144531</v>
       </c>
       <c r="F144" t="n">
-        <v>21443300</v>
+        <v>33064800</v>
       </c>
       <c r="G144" t="n">
         <v>0</v>
@@ -4187,22 +4187,22 @@
     </row>
     <row r="145">
       <c r="A145" s="1" t="n">
-        <v>46120</v>
+        <v>46121</v>
       </c>
       <c r="B145" t="n">
-        <v>383.426192668859</v>
+        <v>370.9965328148009</v>
       </c>
       <c r="C145" t="n">
-        <v>383.4461010048471</v>
+        <v>371.9924966612836</v>
       </c>
       <c r="D145" t="n">
-        <v>369.9109552686541</v>
+        <v>365.5685176937085</v>
       </c>
       <c r="E145" t="n">
-        <v>372.8191528320312</v>
+        <v>371.5642395019531</v>
       </c>
       <c r="F145" t="n">
-        <v>33064800</v>
+        <v>30435300</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
@@ -4213,22 +4213,22 @@
     </row>
     <row r="146">
       <c r="A146" s="1" t="n">
-        <v>46121</v>
+        <v>46122</v>
       </c>
       <c r="B146" t="n">
-        <v>370.9965632857518</v>
+        <v>371.4746074371751</v>
       </c>
       <c r="C146" t="n">
-        <v>371.9925272140356</v>
+        <v>374.1238749235223</v>
       </c>
       <c r="D146" t="n">
-        <v>365.5685477188417</v>
+        <v>368.5365019241105</v>
       </c>
       <c r="E146" t="n">
-        <v>371.5642700195312</v>
+        <v>369.3731079101562</v>
       </c>
       <c r="F146" t="n">
-        <v>30435300</v>
+        <v>28111100</v>
       </c>
       <c r="G146" t="n">
         <v>0</v>
@@ -4239,22 +4239,22 @@
     </row>
     <row r="147">
       <c r="A147" s="1" t="n">
-        <v>46122</v>
+        <v>46125</v>
       </c>
       <c r="B147" t="n">
-        <v>371.4746381283788</v>
+        <v>372.1020528926679</v>
       </c>
       <c r="C147" t="n">
-        <v>374.1239058336084</v>
+        <v>382.9879612673769</v>
       </c>
       <c r="D147" t="n">
-        <v>368.5365323725683</v>
+        <v>369.5225100750242</v>
       </c>
       <c r="E147" t="n">
-        <v>369.3731384277344</v>
+        <v>382.8186340332031</v>
       </c>
       <c r="F147" t="n">
-        <v>28111100</v>
+        <v>35745800</v>
       </c>
       <c r="G147" t="n">
         <v>0</v>
@@ -4265,22 +4265,22 @@
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
-        <v>46125</v>
+        <v>46126</v>
       </c>
       <c r="B148" t="n">
-        <v>372.1020528926679</v>
+        <v>386.3543213772784</v>
       </c>
       <c r="C148" t="n">
-        <v>382.9879612673769</v>
+        <v>393.0969858972055</v>
       </c>
       <c r="D148" t="n">
-        <v>369.5225100750242</v>
+        <v>384.95994763093</v>
       </c>
       <c r="E148" t="n">
-        <v>382.8186340332031</v>
+        <v>391.5233459472656</v>
       </c>
       <c r="F148" t="n">
-        <v>35745800</v>
+        <v>37504500</v>
       </c>
       <c r="G148" t="n">
         <v>0</v>
@@ -4291,22 +4291,22 @@
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
-        <v>46126</v>
+        <v>46127</v>
       </c>
       <c r="B149" t="n">
-        <v>386.3543213772784</v>
+        <v>396.3936283702306</v>
       </c>
       <c r="C149" t="n">
-        <v>393.0969858972055</v>
+        <v>412.6975523926047</v>
       </c>
       <c r="D149" t="n">
-        <v>384.95994763093</v>
+        <v>395.1287651714373</v>
       </c>
       <c r="E149" t="n">
-        <v>391.5233459472656</v>
+        <v>409.5602722167969</v>
       </c>
       <c r="F149" t="n">
-        <v>37504500</v>
+        <v>45063400</v>
       </c>
       <c r="G149" t="n">
         <v>0</v>
@@ -4317,22 +4317,22 @@
     </row>
     <row r="150">
       <c r="A150" s="1" t="n">
-        <v>46127</v>
+        <v>46128</v>
       </c>
       <c r="B150" t="n">
-        <v>396.3936283702306</v>
+        <v>418.1653718785589</v>
       </c>
       <c r="C150" t="n">
-        <v>412.6975523926047</v>
+        <v>419.1215190686066</v>
       </c>
       <c r="D150" t="n">
-        <v>395.1287651714373</v>
+        <v>410.4765600541581</v>
       </c>
       <c r="E150" t="n">
-        <v>409.5602722167969</v>
+        <v>418.5637817382812</v>
       </c>
       <c r="F150" t="n">
-        <v>45063400</v>
+        <v>41642400</v>
       </c>
       <c r="G150" t="n">
         <v>0</v>
@@ -4343,22 +4343,22 @@
     </row>
     <row r="151">
       <c r="A151" s="1" t="n">
-        <v>46128</v>
+        <v>46129</v>
       </c>
       <c r="B151" t="n">
-        <v>418.1653718785589</v>
+        <v>423.105393156615</v>
       </c>
       <c r="C151" t="n">
-        <v>419.1215190686066</v>
+        <v>429.8380884820792</v>
       </c>
       <c r="D151" t="n">
-        <v>410.4765600541581</v>
+        <v>418.9920573683891</v>
       </c>
       <c r="E151" t="n">
-        <v>418.5637817382812</v>
+        <v>421.0835876464844</v>
       </c>
       <c r="F151" t="n">
-        <v>41642400</v>
+        <v>48568200</v>
       </c>
       <c r="G151" t="n">
         <v>0</v>
@@ -4369,22 +4369,22 @@
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
-        <v>46129</v>
+        <v>46132</v>
       </c>
       <c r="B152" t="n">
-        <v>423.105393156615</v>
+        <v>419.4501847919345</v>
       </c>
       <c r="C152" t="n">
-        <v>429.8380884820792</v>
+        <v>421.6213787702164</v>
       </c>
       <c r="D152" t="n">
-        <v>418.9920573683891</v>
+        <v>414.6197538627068</v>
       </c>
       <c r="E152" t="n">
-        <v>421.0835876464844</v>
+        <v>416.3826293945312</v>
       </c>
       <c r="F152" t="n">
-        <v>48568200</v>
+        <v>27582200</v>
       </c>
       <c r="G152" t="n">
         <v>0</v>
@@ -4395,22 +4395,22 @@
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
-        <v>46132</v>
+        <v>46133</v>
       </c>
       <c r="B153" t="n">
-        <v>419.4501847919345</v>
+        <v>418.5438369146158</v>
       </c>
       <c r="C153" t="n">
-        <v>421.6213787702164</v>
+        <v>425.4558284373716</v>
       </c>
       <c r="D153" t="n">
-        <v>414.6197538627068</v>
+        <v>415.516128706763</v>
       </c>
       <c r="E153" t="n">
-        <v>416.3826293945312</v>
+        <v>422.4480285644531</v>
       </c>
       <c r="F153" t="n">
-        <v>27582200</v>
+        <v>32048500</v>
       </c>
       <c r="G153" t="n">
         <v>0</v>
@@ -4421,22 +4421,22 @@
     </row>
     <row r="154">
       <c r="A154" s="1" t="n">
-        <v>46133</v>
+        <v>46134</v>
       </c>
       <c r="B154" t="n">
-        <v>418.5438671501557</v>
+        <v>424.4698510786937</v>
       </c>
       <c r="C154" t="n">
-        <v>425.4558591722327</v>
+        <v>431.9495495900464</v>
       </c>
       <c r="D154" t="n">
-        <v>415.5161587235818</v>
+        <v>421.9600330275293</v>
       </c>
       <c r="E154" t="n">
-        <v>422.4480590820312</v>
+        <v>431.1726989746094</v>
       </c>
       <c r="F154" t="n">
-        <v>32048500</v>
+        <v>29378200</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
@@ -4447,22 +4447,22 @@
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
-        <v>46134</v>
+        <v>46135</v>
       </c>
       <c r="B155" t="n">
-        <v>424.4698510786937</v>
+        <v>418.195296097549</v>
       </c>
       <c r="C155" t="n">
-        <v>431.9495495900464</v>
+        <v>421.9500690544079</v>
       </c>
       <c r="D155" t="n">
-        <v>421.9600330275293</v>
+        <v>409.7495112929088</v>
       </c>
       <c r="E155" t="n">
-        <v>431.1726989746094</v>
+        <v>414.0719909667969</v>
       </c>
       <c r="F155" t="n">
-        <v>29378200</v>
+        <v>38308000</v>
       </c>
       <c r="G155" t="n">
         <v>0</v>
@@ -4473,22 +4473,22 @@
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
-        <v>46135</v>
+        <v>46136</v>
       </c>
       <c r="B156" t="n">
-        <v>418.1952652760787</v>
+        <v>415.2870711617039</v>
       </c>
       <c r="C156" t="n">
-        <v>421.9500379562064</v>
+        <v>423.2348740747397</v>
       </c>
       <c r="D156" t="n">
-        <v>409.7494810939023</v>
+        <v>414.1217800179737</v>
       </c>
       <c r="E156" t="n">
-        <v>414.0719604492188</v>
+        <v>422.9061889648438</v>
       </c>
       <c r="F156" t="n">
-        <v>38308000</v>
+        <v>27457400</v>
       </c>
       <c r="G156" t="n">
         <v>0</v>
@@ -4499,22 +4499,22 @@
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
-        <v>46136</v>
+        <v>46139</v>
       </c>
       <c r="B157" t="n">
-        <v>415.2870711617039</v>
+        <v>420.6752229306716</v>
       </c>
       <c r="C157" t="n">
-        <v>423.2348740747397</v>
+        <v>425.3861125683125</v>
       </c>
       <c r="D157" t="n">
-        <v>414.1217800179737</v>
+        <v>415.3866572294081</v>
       </c>
       <c r="E157" t="n">
-        <v>422.9061889648438</v>
+        <v>423.1053771972656</v>
       </c>
       <c r="F157" t="n">
-        <v>27457400</v>
+        <v>30867300</v>
       </c>
       <c r="G157" t="n">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="158">
       <c r="A158" s="1" t="n">
-        <v>46139</v>
+        <v>46140</v>
       </c>
       <c r="B158" t="n">
-        <v>420.6752229306716</v>
+        <v>422.8563830057505</v>
       </c>
       <c r="C158" t="n">
-        <v>425.3861125683125</v>
+        <v>428.1847957314844</v>
       </c>
       <c r="D158" t="n">
-        <v>415.3866572294081</v>
+        <v>420.197146128082</v>
       </c>
       <c r="E158" t="n">
-        <v>423.1053771972656</v>
+        <v>427.5174865722656</v>
       </c>
       <c r="F158" t="n">
-        <v>30867300</v>
+        <v>30438100</v>
       </c>
       <c r="G158" t="n">
         <v>0</v>
@@ -4551,22 +4551,22 @@
     </row>
     <row r="159">
       <c r="A159" s="1" t="n">
-        <v>46140</v>
+        <v>46141</v>
       </c>
       <c r="B159" t="n">
-        <v>422.8563830057505</v>
+        <v>422.8663369761165</v>
       </c>
       <c r="C159" t="n">
-        <v>428.1847957314844</v>
+        <v>425.0973167681131</v>
       </c>
       <c r="D159" t="n">
-        <v>420.197146128082</v>
+        <v>418.593673752453</v>
       </c>
       <c r="E159" t="n">
-        <v>427.5174865722656</v>
+        <v>422.746826171875</v>
       </c>
       <c r="F159" t="n">
-        <v>30438100</v>
+        <v>38288300</v>
       </c>
       <c r="G159" t="n">
         <v>0</v>
@@ -4577,22 +4577,22 @@
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
-        <v>46141</v>
+        <v>46142</v>
       </c>
       <c r="B160" t="n">
-        <v>422.866306449911</v>
+        <v>409.1519246549498</v>
       </c>
       <c r="C160" t="n">
-        <v>425.0972860808559</v>
+        <v>412.7473701155562</v>
       </c>
       <c r="D160" t="n">
-        <v>418.5936435346858</v>
+        <v>396.4035989759817</v>
       </c>
       <c r="E160" t="n">
-        <v>422.7467956542969</v>
+        <v>406.1341552734375</v>
       </c>
       <c r="F160" t="n">
-        <v>38288300</v>
+        <v>70909400</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -4603,22 +4603,22 @@
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
-        <v>46142</v>
+        <v>46143</v>
       </c>
       <c r="B161" t="n">
-        <v>409.1519246549498</v>
+        <v>411.1338775963461</v>
       </c>
       <c r="C161" t="n">
-        <v>412.7473701155562</v>
+        <v>415.4264794885345</v>
       </c>
       <c r="D161" t="n">
-        <v>396.4035989759817</v>
+        <v>408.7834174283456</v>
       </c>
       <c r="E161" t="n">
-        <v>406.1341552734375</v>
+        <v>412.7672729492188</v>
       </c>
       <c r="F161" t="n">
-        <v>70909400</v>
+        <v>31372400</v>
       </c>
       <c r="G161" t="n">
         <v>0</v>
@@ -4629,22 +4629,22 @@
     </row>
     <row r="162">
       <c r="A162" s="1" t="n">
-        <v>46143</v>
+        <v>46146</v>
       </c>
       <c r="B162" t="n">
-        <v>411.1338775963461</v>
+        <v>409.8789700952638</v>
       </c>
       <c r="C162" t="n">
-        <v>415.4264794885345</v>
+        <v>419.0816663151199</v>
       </c>
       <c r="D162" t="n">
-        <v>408.7834174283456</v>
+        <v>409.1419361803058</v>
       </c>
       <c r="E162" t="n">
-        <v>412.7672729492188</v>
+        <v>411.9505615234375</v>
       </c>
       <c r="F162" t="n">
-        <v>31372400</v>
+        <v>28066500</v>
       </c>
       <c r="G162" t="n">
         <v>0</v>
@@ -4655,22 +4655,22 @@
     </row>
     <row r="163">
       <c r="A163" s="1" t="n">
-        <v>46146</v>
+        <v>46147</v>
       </c>
       <c r="B163" t="n">
-        <v>409.8789700952638</v>
+        <v>413.6437044066962</v>
       </c>
       <c r="C163" t="n">
-        <v>419.0816663151199</v>
+        <v>415.0978030853789</v>
       </c>
       <c r="D163" t="n">
-        <v>409.1419361803058</v>
+        <v>407.1500007946646</v>
       </c>
       <c r="E163" t="n">
-        <v>411.9505615234375</v>
+        <v>409.7196044921875</v>
       </c>
       <c r="F163" t="n">
-        <v>28066500</v>
+        <v>25700900</v>
       </c>
       <c r="G163" t="n">
         <v>0</v>
@@ -4681,22 +4681,22 @@
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="B164" t="n">
-        <v>413.6437352165572</v>
+        <v>406.3532485673598</v>
       </c>
       <c r="C164" t="n">
-        <v>415.0978340035471</v>
+        <v>416.7312052008779</v>
       </c>
       <c r="D164" t="n">
-        <v>407.1500311208482</v>
+        <v>403.4748984673602</v>
       </c>
       <c r="E164" t="n">
-        <v>409.7196350097656</v>
+        <v>412.2891845703125</v>
       </c>
       <c r="F164" t="n">
-        <v>25700900</v>
+        <v>30285900</v>
       </c>
       <c r="G164" t="n">
         <v>0</v>
@@ -4707,22 +4707,22 @@
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
-        <v>46148</v>
+        <v>46149</v>
       </c>
       <c r="B165" t="n">
-        <v>406.3532485673598</v>
+        <v>418.4143764918961</v>
       </c>
       <c r="C165" t="n">
-        <v>416.7312052008779</v>
+        <v>426.2526378609755</v>
       </c>
       <c r="D165" t="n">
-        <v>403.4748984673602</v>
+        <v>417.0698495518934</v>
       </c>
       <c r="E165" t="n">
-        <v>412.2891845703125</v>
+        <v>419.0717163085938</v>
       </c>
       <c r="F165" t="n">
-        <v>30285900</v>
+        <v>34942400</v>
       </c>
       <c r="G165" t="n">
         <v>0</v>
@@ -4733,22 +4733,22 @@
     </row>
     <row r="166">
       <c r="A166" s="1" t="n">
-        <v>46149</v>
+        <v>46150</v>
       </c>
       <c r="B166" t="n">
-        <v>418.4143764918961</v>
+        <v>415.7053764922729</v>
       </c>
       <c r="C166" t="n">
-        <v>426.2526378609755</v>
+        <v>416.9403619714099</v>
       </c>
       <c r="D166" t="n">
-        <v>417.0698495518934</v>
+        <v>412.3290443657605</v>
       </c>
       <c r="E166" t="n">
-        <v>419.0717163085938</v>
+        <v>413.4445190429688</v>
       </c>
       <c r="F166" t="n">
-        <v>34942400</v>
+        <v>33383800</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -4759,22 +4759,22 @@
     </row>
     <row r="167">
       <c r="A167" s="1" t="n">
-        <v>46150</v>
+        <v>46153</v>
       </c>
       <c r="B167" t="n">
-        <v>415.7053764922729</v>
+        <v>406.223770451025</v>
       </c>
       <c r="C167" t="n">
-        <v>416.9403619714099</v>
+        <v>411.0243235004914</v>
       </c>
       <c r="D167" t="n">
-        <v>412.3290443657605</v>
+        <v>403.8633409907068</v>
       </c>
       <c r="E167" t="n">
-        <v>413.4445190429688</v>
+        <v>410.9944458007812</v>
       </c>
       <c r="F167" t="n">
-        <v>33383800</v>
+        <v>35657900</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -4785,22 +4785,22 @@
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
-        <v>46153</v>
+        <v>46154</v>
       </c>
       <c r="B168" t="n">
-        <v>406.223770451025</v>
+        <v>412.8071154720842</v>
       </c>
       <c r="C168" t="n">
-        <v>411.0243235004914</v>
+        <v>413.8229876767416</v>
       </c>
       <c r="D168" t="n">
-        <v>403.8633409907068</v>
+        <v>404.9987623844293</v>
       </c>
       <c r="E168" t="n">
-        <v>410.9944458007812</v>
+        <v>406.1241760253906</v>
       </c>
       <c r="F168" t="n">
-        <v>35657900</v>
+        <v>38594200</v>
       </c>
       <c r="G168" t="n">
         <v>0</v>
@@ -4811,22 +4811,22 @@
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
-        <v>46154</v>
+        <v>46155</v>
       </c>
       <c r="B169" t="n">
-        <v>412.8071154720842</v>
+        <v>401.5726571524119</v>
       </c>
       <c r="C169" t="n">
-        <v>413.8229876767416</v>
+        <v>404.6700902960666</v>
       </c>
       <c r="D169" t="n">
-        <v>404.9987623844293</v>
+        <v>399.4114021131033</v>
       </c>
       <c r="E169" t="n">
-        <v>406.1241760253906</v>
+        <v>403.5745239257812</v>
       </c>
       <c r="F169" t="n">
-        <v>38594200</v>
+        <v>29667100</v>
       </c>
       <c r="G169" t="n">
         <v>0</v>
@@ -4837,22 +4837,22 @@
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
-        <v>46155</v>
+        <v>46156</v>
       </c>
       <c r="B170" t="n">
-        <v>401.5726571524119</v>
+        <v>402.8474630718804</v>
       </c>
       <c r="C170" t="n">
-        <v>404.6700902960666</v>
+        <v>410.1777423108794</v>
       </c>
       <c r="D170" t="n">
-        <v>399.4114021131033</v>
+        <v>399.2619871856725</v>
       </c>
       <c r="E170" t="n">
-        <v>403.5745239257812</v>
+        <v>407.7774658203125</v>
       </c>
       <c r="F170" t="n">
-        <v>29667100</v>
+        <v>27077500</v>
       </c>
       <c r="G170" t="n">
         <v>0</v>
@@ -4863,22 +4863,22 @@
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
-        <v>46156</v>
+        <v>46157</v>
       </c>
       <c r="B171" t="n">
-        <v>402.847493220503</v>
+        <v>412.5979239362014</v>
       </c>
       <c r="C171" t="n">
-        <v>410.1777730080913</v>
+        <v>426.4418454559798</v>
       </c>
       <c r="D171" t="n">
-        <v>399.2620170659624</v>
+        <v>411.2434277199191</v>
       </c>
       <c r="E171" t="n">
-        <v>407.7774963378906</v>
+        <v>420.2170715332031</v>
       </c>
       <c r="F171" t="n">
-        <v>27077500</v>
+        <v>50771200</v>
       </c>
       <c r="G171" t="n">
         <v>0</v>
@@ -4889,22 +4889,22 @@
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
-        <v>46157</v>
+        <v>46160</v>
       </c>
       <c r="B172" t="n">
-        <v>412.5979239362014</v>
+        <v>414.9384827190711</v>
       </c>
       <c r="C172" t="n">
-        <v>426.4418454559798</v>
+        <v>423.4041760233977</v>
       </c>
       <c r="D172" t="n">
-        <v>411.2434277199191</v>
+        <v>413.9325494355234</v>
       </c>
       <c r="E172" t="n">
-        <v>420.2170715332031</v>
+        <v>421.83056640625</v>
       </c>
       <c r="F172" t="n">
-        <v>50771200</v>
+        <v>32564100</v>
       </c>
       <c r="G172" t="n">
         <v>0</v>
@@ -4915,22 +4915,22 @@
     </row>
     <row r="173">
       <c r="A173" s="1" t="n">
-        <v>46160</v>
+        <v>46161</v>
       </c>
       <c r="B173" t="n">
-        <v>414.9384827190711</v>
+        <v>428.1648698947521</v>
       </c>
       <c r="C173" t="n">
-        <v>423.4041760233977</v>
+        <v>430.9535870211983</v>
       </c>
       <c r="D173" t="n">
-        <v>413.9325494355234</v>
+        <v>414.808990493047</v>
       </c>
       <c r="E173" t="n">
-        <v>421.83056640625</v>
+        <v>415.7352600097656</v>
       </c>
       <c r="F173" t="n">
-        <v>32564100</v>
+        <v>33018700</v>
       </c>
       <c r="G173" t="n">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="174">
       <c r="A174" s="1" t="n">
-        <v>46161</v>
+        <v>46162</v>
       </c>
       <c r="B174" t="n">
-        <v>428.1648698947521</v>
+        <v>412.4983595724376</v>
       </c>
       <c r="C174" t="n">
-        <v>430.9535870211983</v>
+        <v>420.3963455784958</v>
       </c>
       <c r="D174" t="n">
-        <v>414.808990493047</v>
+        <v>409.6399178024174</v>
       </c>
       <c r="E174" t="n">
-        <v>415.7352600097656</v>
+        <v>419.3605346679688</v>
       </c>
       <c r="F174" t="n">
-        <v>33018700</v>
+        <v>27864000</v>
       </c>
       <c r="G174" t="n">
         <v>0</v>
@@ -4967,25 +4967,25 @@
     </row>
     <row r="175">
       <c r="A175" s="1" t="n">
-        <v>46162</v>
+        <v>46163</v>
       </c>
       <c r="B175" t="n">
-        <v>412.4983595724376</v>
+        <v>423.9518891931334</v>
       </c>
       <c r="C175" t="n">
-        <v>420.3963455784958</v>
+        <v>425.5388979071037</v>
       </c>
       <c r="D175" t="n">
-        <v>409.6399178024174</v>
+        <v>414.928866942535</v>
       </c>
       <c r="E175" t="n">
-        <v>419.3605346679688</v>
+        <v>418.3025207519531</v>
       </c>
       <c r="F175" t="n">
-        <v>27864000</v>
+        <v>31393500</v>
       </c>
       <c r="G175" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H175" t="n">
         <v>0</v>
@@ -4993,25 +4993,25 @@
     </row>
     <row r="176">
       <c r="A176" s="1" t="n">
-        <v>46163</v>
+        <v>46164</v>
       </c>
       <c r="B176" t="n">
-        <v>423.9518891931334</v>
+        <v>418.7517174636334</v>
       </c>
       <c r="C176" t="n">
-        <v>425.5388979071037</v>
+        <v>423.602571187628</v>
       </c>
       <c r="D176" t="n">
-        <v>414.928866942535</v>
+        <v>415.547726934082</v>
       </c>
       <c r="E176" t="n">
-        <v>418.3025207519531</v>
+        <v>417.7835388183594</v>
       </c>
       <c r="F176" t="n">
-        <v>31393500</v>
+        <v>22390300</v>
       </c>
       <c r="G176" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H176" t="n">
         <v>0</v>
@@ -5019,22 +5019,22 @@
     </row>
     <row r="177">
       <c r="A177" s="1" t="n">
-        <v>46164</v>
+        <v>46168</v>
       </c>
       <c r="B177" t="n">
-        <v>418.7517174636334</v>
+        <v>415.6475333356961</v>
       </c>
       <c r="C177" t="n">
-        <v>423.602571187628</v>
+        <v>418.9812539216563</v>
       </c>
       <c r="D177" t="n">
-        <v>415.547726934082</v>
+        <v>412.2439369671584</v>
       </c>
       <c r="E177" t="n">
-        <v>417.7835388183594</v>
+        <v>415.248291015625</v>
       </c>
       <c r="F177" t="n">
-        <v>22390300</v>
+        <v>30398000</v>
       </c>
       <c r="G177" t="n">
         <v>0</v>
@@ -5045,22 +5045,22 @@
     </row>
     <row r="178">
       <c r="A178" s="1" t="n">
-        <v>46168</v>
+        <v>46169</v>
       </c>
       <c r="B178" t="n">
-        <v>415.6475333356961</v>
+        <v>410.2377382218162</v>
       </c>
       <c r="C178" t="n">
-        <v>418.9812539216563</v>
+        <v>415.15846763645</v>
       </c>
       <c r="D178" t="n">
-        <v>412.2439369671584</v>
+        <v>408.8104019854481</v>
       </c>
       <c r="E178" t="n">
-        <v>415.248291015625</v>
+        <v>411.8946228027344</v>
       </c>
       <c r="F178" t="n">
-        <v>30398000</v>
+        <v>28901500</v>
       </c>
       <c r="G178" t="n">
         <v>0</v>
@@ -5071,22 +5071,22 @@
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
-        <v>46169</v>
+        <v>46170</v>
       </c>
       <c r="B179" t="n">
-        <v>410.2377382218162</v>
+        <v>412.2040283766931</v>
       </c>
       <c r="C179" t="n">
-        <v>415.15846763645</v>
+        <v>428.6829856468207</v>
       </c>
       <c r="D179" t="n">
-        <v>408.8104019854481</v>
+        <v>411.8946132983843</v>
       </c>
       <c r="E179" t="n">
-        <v>411.8946228027344</v>
+        <v>426.1876831054688</v>
       </c>
       <c r="F179" t="n">
-        <v>28901500</v>
+        <v>47250500</v>
       </c>
       <c r="G179" t="n">
         <v>0</v>
@@ -5097,22 +5097,22 @@
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
-        <v>46170</v>
+        <v>46171</v>
       </c>
       <c r="B180" t="n">
-        <v>412.2040283766931</v>
+        <v>431.7372486144539</v>
       </c>
       <c r="C180" t="n">
-        <v>428.6829856468207</v>
+        <v>449.4838396905727</v>
       </c>
       <c r="D180" t="n">
-        <v>411.8946132983843</v>
+        <v>431.5476031778621</v>
       </c>
       <c r="E180" t="n">
-        <v>426.1876831054688</v>
+        <v>449.3940124511719</v>
       </c>
       <c r="F180" t="n">
-        <v>47250500</v>
+        <v>79654400</v>
       </c>
       <c r="G180" t="n">
         <v>0</v>
@@ -5123,22 +5123,22 @@
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
-        <v>46171</v>
+        <v>46174</v>
       </c>
       <c r="B181" t="n">
-        <v>431.7372486144539</v>
+        <v>463.9665838370572</v>
       </c>
       <c r="C181" t="n">
-        <v>449.4838396905727</v>
+        <v>465.4438139523178</v>
       </c>
       <c r="D181" t="n">
-        <v>431.5476031778621</v>
+        <v>457.4089212477423</v>
       </c>
       <c r="E181" t="n">
-        <v>449.3940124511719</v>
+        <v>459.6546936035156</v>
       </c>
       <c r="F181" t="n">
-        <v>79654400</v>
+        <v>53628900</v>
       </c>
       <c r="G181" t="n">
         <v>0</v>
@@ -5149,22 +5149,22 @@
     </row>
     <row r="182">
       <c r="A182" s="1" t="n">
-        <v>46174</v>
+        <v>46175</v>
       </c>
       <c r="B182" t="n">
-        <v>463.9665838370572</v>
+        <v>446.0403151791343</v>
       </c>
       <c r="C182" t="n">
-        <v>465.4438139523178</v>
+        <v>452.647871293284</v>
       </c>
       <c r="D182" t="n">
-        <v>457.4089212477423</v>
+        <v>439.6024225764256</v>
       </c>
       <c r="E182" t="n">
-        <v>459.6546936035156</v>
+        <v>440.4807739257812</v>
       </c>
       <c r="F182" t="n">
-        <v>53628900</v>
+        <v>37036800</v>
       </c>
       <c r="G182" t="n">
         <v>0</v>
@@ -5175,22 +5175,22 @@
     </row>
     <row r="183">
       <c r="A183" s="1" t="n">
-        <v>46175</v>
+        <v>46176</v>
       </c>
       <c r="B183" t="n">
-        <v>446.0403151791343</v>
+        <v>437.6261891093521</v>
       </c>
       <c r="C183" t="n">
-        <v>452.647871293284</v>
+        <v>439.5625463944663</v>
       </c>
       <c r="D183" t="n">
-        <v>439.6024225764256</v>
+        <v>423.4528579325815</v>
       </c>
       <c r="E183" t="n">
-        <v>440.4807739257812</v>
+        <v>426.5370483398438</v>
       </c>
       <c r="F183" t="n">
-        <v>37036800</v>
+        <v>39037000</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -5201,22 +5201,22 @@
     </row>
     <row r="184">
       <c r="A184" s="1" t="n">
-        <v>46176</v>
+        <v>46177</v>
       </c>
       <c r="B184" t="n">
-        <v>437.6261891093521</v>
+        <v>434.9911260035114</v>
       </c>
       <c r="C184" t="n">
-        <v>439.5625463944663</v>
+        <v>435.3304835003211</v>
       </c>
       <c r="D184" t="n">
-        <v>423.4528579325815</v>
+        <v>425.6087943627414</v>
       </c>
       <c r="E184" t="n">
-        <v>426.5370483398438</v>
+        <v>427.2456970214844</v>
       </c>
       <c r="F184" t="n">
-        <v>39037000</v>
+        <v>26899500</v>
       </c>
       <c r="G184" t="n">
         <v>0</v>
@@ -5227,22 +5227,22 @@
     </row>
     <row r="185">
       <c r="A185" s="1" t="n">
-        <v>46177</v>
+        <v>46178</v>
       </c>
       <c r="B185" t="n">
-        <v>434.9911260035114</v>
+        <v>427.5351398188391</v>
       </c>
       <c r="C185" t="n">
-        <v>435.3304835003211</v>
+        <v>428.6630214075295</v>
       </c>
       <c r="D185" t="n">
-        <v>425.6087943627414</v>
+        <v>413.6213308264138</v>
       </c>
       <c r="E185" t="n">
-        <v>427.2456970214844</v>
+        <v>415.8870849609375</v>
       </c>
       <c r="F185" t="n">
-        <v>26899500</v>
+        <v>34782200</v>
       </c>
       <c r="G185" t="n">
         <v>0</v>
@@ -5253,22 +5253,22 @@
     </row>
     <row r="186">
       <c r="A186" s="1" t="n">
-        <v>46178</v>
+        <v>46181</v>
       </c>
       <c r="B186" t="n">
-        <v>427.5351398188391</v>
+        <v>413.3618539280056</v>
       </c>
       <c r="C186" t="n">
-        <v>428.6630214075295</v>
+        <v>416.3761684433352</v>
       </c>
       <c r="D186" t="n">
-        <v>413.6213308264138</v>
+        <v>407.7923215775376</v>
       </c>
       <c r="E186" t="n">
-        <v>415.8870849609375</v>
+        <v>410.9663391113281</v>
       </c>
       <c r="F186" t="n">
-        <v>34782200</v>
+        <v>32086700</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -5279,22 +5279,22 @@
     </row>
     <row r="187">
       <c r="A187" s="1" t="n">
-        <v>46181</v>
+        <v>46182</v>
       </c>
       <c r="B187" t="n">
-        <v>413.3618539280056</v>
+        <v>408.2614433672717</v>
       </c>
       <c r="C187" t="n">
-        <v>416.3761684433352</v>
+        <v>411.2059125875929</v>
       </c>
       <c r="D187" t="n">
-        <v>407.7923215775376</v>
+        <v>397.7312786929967</v>
       </c>
       <c r="E187" t="n">
-        <v>410.9663391113281</v>
+        <v>402.6520080566406</v>
       </c>
       <c r="F187" t="n">
-        <v>32086700</v>
+        <v>35317300</v>
       </c>
       <c r="G187" t="n">
         <v>0</v>
@@ -5305,22 +5305,22 @@
     </row>
     <row r="188">
       <c r="A188" s="1" t="n">
-        <v>46182</v>
+        <v>46183</v>
       </c>
       <c r="B188" t="n">
-        <v>408.2614433672717</v>
+        <v>397.8011087010324</v>
       </c>
       <c r="C188" t="n">
-        <v>411.2059125875929</v>
+        <v>404.2789346443135</v>
       </c>
       <c r="D188" t="n">
-        <v>397.7312786929967</v>
+        <v>396.4137363631365</v>
       </c>
       <c r="E188" t="n">
-        <v>402.6520080566406</v>
+        <v>396.6133422851562</v>
       </c>
       <c r="F188" t="n">
-        <v>35317300</v>
+        <v>32576000</v>
       </c>
       <c r="G188" t="n">
         <v>0</v>
@@ -5331,22 +5331,22 @@
     </row>
     <row r="189">
       <c r="A189" s="1" t="n">
-        <v>46183</v>
+        <v>46184</v>
       </c>
       <c r="B189" t="n">
-        <v>397.8011087010324</v>
+        <v>394.4674120274286</v>
       </c>
       <c r="C189" t="n">
-        <v>404.2789346443135</v>
+        <v>396.1043451719433</v>
       </c>
       <c r="D189" t="n">
-        <v>396.4137363631365</v>
+        <v>383.278483574852</v>
       </c>
       <c r="E189" t="n">
-        <v>396.6133422851562</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F189" t="n">
-        <v>32576000</v>
+        <v>47224100</v>
       </c>
       <c r="G189" t="n">
         <v>0</v>
@@ -5357,22 +5357,22 @@
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
-        <v>46184</v>
+        <v>46185</v>
       </c>
       <c r="B190" t="n">
-        <v>394.4674120274286</v>
+        <v>390.6945042817559</v>
       </c>
       <c r="C190" t="n">
-        <v>396.1043451719433</v>
+        <v>391.003919361718</v>
       </c>
       <c r="D190" t="n">
-        <v>383.278483574852</v>
+        <v>381.55171206616</v>
       </c>
       <c r="E190" t="n">
-        <v>389.6065673828125</v>
+        <v>390.0057983398438</v>
       </c>
       <c r="F190" t="n">
-        <v>47224100</v>
+        <v>34865800</v>
       </c>
       <c r="G190" t="n">
         <v>0</v>
@@ -5383,22 +5383,22 @@
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
-        <v>46185</v>
+        <v>46188</v>
       </c>
       <c r="B191" t="n">
-        <v>390.6945042817559</v>
+        <v>396.0544203764563</v>
       </c>
       <c r="C191" t="n">
-        <v>391.003919361718</v>
+        <v>400.9951317570601</v>
       </c>
       <c r="D191" t="n">
-        <v>381.55171206616</v>
+        <v>392.1118605058895</v>
       </c>
       <c r="E191" t="n">
-        <v>390.0057983398438</v>
+        <v>399.0088806152344</v>
       </c>
       <c r="F191" t="n">
-        <v>34865800</v>
+        <v>32266400</v>
       </c>
       <c r="G191" t="n">
         <v>0</v>
@@ -5409,22 +5409,22 @@
     </row>
     <row r="192">
       <c r="A192" s="1" t="n">
-        <v>46188</v>
+        <v>46189</v>
       </c>
       <c r="B192" t="n">
-        <v>396.0544203764563</v>
+        <v>395.0463355104342</v>
       </c>
       <c r="C192" t="n">
-        <v>400.9951317570601</v>
+        <v>396.094350419825</v>
       </c>
       <c r="D192" t="n">
-        <v>392.1118605058895</v>
+        <v>389.9559121071713</v>
       </c>
       <c r="E192" t="n">
-        <v>399.0088806152344</v>
+        <v>393.0899963378906</v>
       </c>
       <c r="F192" t="n">
-        <v>32266400</v>
+        <v>31506800</v>
       </c>
       <c r="G192" t="n">
         <v>0</v>
@@ -5435,22 +5435,22 @@
     </row>
     <row r="193">
       <c r="A193" s="1" t="n">
-        <v>46189</v>
+        <v>46190</v>
       </c>
       <c r="B193" t="n">
-        <v>395.0463355104342</v>
+        <v>389.5167169534323</v>
       </c>
       <c r="C193" t="n">
-        <v>396.094350419825</v>
+        <v>389.6364865987809</v>
       </c>
       <c r="D193" t="n">
-        <v>389.9559121071713</v>
+        <v>376.6110198431126</v>
       </c>
       <c r="E193" t="n">
-        <v>393.0899963378906</v>
+        <v>378.1980285644531</v>
       </c>
       <c r="F193" t="n">
-        <v>31506800</v>
+        <v>41987800</v>
       </c>
       <c r="G193" t="n">
         <v>0</v>
@@ -5461,22 +5461,22 @@
     </row>
     <row r="194">
       <c r="A194" s="1" t="n">
-        <v>46190</v>
+        <v>46191</v>
       </c>
       <c r="B194" t="n">
-        <v>389.5167169534323</v>
+        <v>377.1100854858111</v>
       </c>
       <c r="C194" t="n">
-        <v>389.6364865987809</v>
+        <v>380.6534028700893</v>
       </c>
       <c r="D194" t="n">
-        <v>376.6110198431126</v>
+        <v>372.5786075934489</v>
       </c>
       <c r="E194" t="n">
-        <v>378.1980285644531</v>
+        <v>378.6871032714844</v>
       </c>
       <c r="F194" t="n">
-        <v>41987800</v>
+        <v>59714200</v>
       </c>
       <c r="G194" t="n">
         <v>0</v>
@@ -5487,22 +5487,22 @@
     </row>
     <row r="195">
       <c r="A195" s="1" t="n">
-        <v>46191</v>
+        <v>46195</v>
       </c>
       <c r="B195" t="n">
-        <v>377.1100854858111</v>
+        <v>375.0339909424311</v>
       </c>
       <c r="C195" t="n">
-        <v>380.6534028700893</v>
+        <v>380.9129385065033</v>
       </c>
       <c r="D195" t="n">
-        <v>372.5786075934489</v>
+        <v>366.3802985575179</v>
       </c>
       <c r="E195" t="n">
-        <v>378.6871032714844</v>
+        <v>366.6497802734375</v>
       </c>
       <c r="F195" t="n">
-        <v>59714200</v>
+        <v>45171100</v>
       </c>
       <c r="G195" t="n">
         <v>0</v>
@@ -5513,22 +5513,22 @@
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
-        <v>46195</v>
+        <v>46196</v>
       </c>
       <c r="B196" t="n">
-        <v>375.0339909424311</v>
+        <v>371.6802994138851</v>
       </c>
       <c r="C196" t="n">
-        <v>380.9129385065033</v>
+        <v>376.5112013539488</v>
       </c>
       <c r="D196" t="n">
-        <v>366.3802985575179</v>
+        <v>369.9735210485466</v>
       </c>
       <c r="E196" t="n">
-        <v>366.6497802734375</v>
+        <v>373.2373657226562</v>
       </c>
       <c r="F196" t="n">
-        <v>45171100</v>
+        <v>40647600</v>
       </c>
       <c r="G196" t="n">
         <v>0</v>
@@ -5539,22 +5539,22 @@
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
-        <v>46196</v>
+        <v>46197</v>
       </c>
       <c r="B197" t="n">
-        <v>371.6802994138851</v>
+        <v>370.8718509685315</v>
       </c>
       <c r="C197" t="n">
-        <v>376.5112013539488</v>
+        <v>378.1681135077346</v>
       </c>
       <c r="D197" t="n">
-        <v>369.9735210485466</v>
+        <v>364.0946004167936</v>
       </c>
       <c r="E197" t="n">
-        <v>373.2373657226562</v>
+        <v>364.7733154296875</v>
       </c>
       <c r="F197" t="n">
-        <v>40647600</v>
+        <v>44509900</v>
       </c>
       <c r="G197" t="n">
         <v>0</v>
@@ -5565,22 +5565,22 @@
     </row>
     <row r="198">
       <c r="A198" s="1" t="n">
-        <v>46197</v>
+        <v>46198</v>
       </c>
       <c r="B198" t="n">
-        <v>370.8718509685315</v>
+        <v>362.0883479855026</v>
       </c>
       <c r="C198" t="n">
-        <v>378.1681135077346</v>
+        <v>363.5456265920902</v>
       </c>
       <c r="D198" t="n">
-        <v>364.0946004167936</v>
+        <v>348.5438690238404</v>
       </c>
       <c r="E198" t="n">
-        <v>364.7733154296875</v>
+        <v>352.1670227050781</v>
       </c>
       <c r="F198" t="n">
-        <v>44509900</v>
+        <v>66179000</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="199">
       <c r="A199" s="1" t="n">
-        <v>46198</v>
+        <v>46199</v>
       </c>
       <c r="B199" t="n">
-        <v>362.0883479855026</v>
+        <v>356.4789138154501</v>
       </c>
       <c r="C199" t="n">
-        <v>363.5456265920902</v>
+        <v>375.9023402058053</v>
       </c>
       <c r="D199" t="n">
-        <v>348.5438690238404</v>
+        <v>354.762144454129</v>
       </c>
       <c r="E199" t="n">
-        <v>352.1670227050781</v>
+        <v>372.2691955566406</v>
       </c>
       <c r="F199" t="n">
-        <v>66179000</v>
+        <v>186201600</v>
       </c>
       <c r="G199" t="n">
         <v>0</v>
@@ -5617,22 +5617,22 @@
     </row>
     <row r="200">
       <c r="A200" s="1" t="n">
-        <v>46199</v>
+        <v>46202</v>
       </c>
       <c r="B200" t="n">
-        <v>356.4789138154501</v>
+        <v>376.790685328561</v>
       </c>
       <c r="C200" t="n">
-        <v>375.9023402058053</v>
+        <v>379.7850483907747</v>
       </c>
       <c r="D200" t="n">
-        <v>354.762144454129</v>
+        <v>359.2237492715265</v>
       </c>
       <c r="E200" t="n">
-        <v>372.2691955566406</v>
+        <v>367.8774719238281</v>
       </c>
       <c r="F200" t="n">
-        <v>186201600</v>
+        <v>51229900</v>
       </c>
       <c r="G200" t="n">
         <v>0</v>
@@ -5643,22 +5643,22 @@
     </row>
     <row r="201">
       <c r="A201" s="1" t="n">
-        <v>46202</v>
+        <v>46203</v>
       </c>
       <c r="B201" t="n">
-        <v>376.790685328561</v>
+        <v>370.3328407149792</v>
       </c>
       <c r="C201" t="n">
-        <v>379.7850483907747</v>
+        <v>373.4469734227558</v>
       </c>
       <c r="D201" t="n">
-        <v>359.2237492715265</v>
+        <v>366.7595808670141</v>
       </c>
       <c r="E201" t="n">
-        <v>367.8774719238281</v>
+        <v>372.319091796875</v>
       </c>
       <c r="F201" t="n">
-        <v>51229900</v>
+        <v>44945700</v>
       </c>
       <c r="G201" t="n">
         <v>0</v>
@@ -5669,22 +5669,22 @@
     </row>
     <row r="202">
       <c r="A202" s="1" t="n">
-        <v>46203</v>
+        <v>46204</v>
       </c>
       <c r="B202" t="n">
-        <v>370.3328407149792</v>
+        <v>380.1144231011508</v>
       </c>
       <c r="C202" t="n">
-        <v>373.4469734227558</v>
+        <v>388.099391438806</v>
       </c>
       <c r="D202" t="n">
-        <v>366.7595808670141</v>
+        <v>374.1856121338598</v>
       </c>
       <c r="E202" t="n">
-        <v>372.319091796875</v>
+        <v>383.5579528808594</v>
       </c>
       <c r="F202" t="n">
-        <v>44945700</v>
+        <v>48065800</v>
       </c>
       <c r="G202" t="n">
         <v>0</v>
@@ -5695,22 +5695,22 @@
     </row>
     <row r="203">
       <c r="A203" s="1" t="n">
-        <v>46204</v>
+        <v>46205</v>
       </c>
       <c r="B203" t="n">
-        <v>380.1144231011508</v>
+        <v>383.7575696594082</v>
       </c>
       <c r="C203" t="n">
-        <v>388.099391438806</v>
+        <v>391.4630649298244</v>
       </c>
       <c r="D203" t="n">
-        <v>374.1856121338598</v>
+        <v>382.9790365046874</v>
       </c>
       <c r="E203" t="n">
-        <v>383.5579528808594</v>
+        <v>389.7562561035156</v>
       </c>
       <c r="F203" t="n">
-        <v>48065800</v>
+        <v>42128900</v>
       </c>
       <c r="G203" t="n">
         <v>0</v>
@@ -5721,22 +5721,22 @@
     </row>
     <row r="204">
       <c r="A204" s="1" t="n">
-        <v>46205</v>
+        <v>46209</v>
       </c>
       <c r="B204" t="n">
-        <v>383.7575696594082</v>
+        <v>386.3127602401041</v>
       </c>
       <c r="C204" t="n">
-        <v>391.4630649298244</v>
+        <v>388.418780928489</v>
       </c>
       <c r="D204" t="n">
-        <v>382.9790365046874</v>
+        <v>380.5036887115837</v>
       </c>
       <c r="E204" t="n">
-        <v>389.7562561035156</v>
+        <v>386.0133056640625</v>
       </c>
       <c r="F204" t="n">
-        <v>42128900</v>
+        <v>34224500</v>
       </c>
       <c r="G204" t="n">
         <v>0</v>
@@ -5747,22 +5747,22 @@
     </row>
     <row r="205">
       <c r="A205" s="1" t="n">
-        <v>46209</v>
+        <v>46210</v>
       </c>
       <c r="B205" t="n">
-        <v>386.3127602401041</v>
+        <v>391.7525106425778</v>
       </c>
       <c r="C205" t="n">
-        <v>388.418780928489</v>
+        <v>394.8267404517197</v>
       </c>
       <c r="D205" t="n">
-        <v>380.5036887115837</v>
+        <v>387.4905448392632</v>
       </c>
       <c r="E205" t="n">
-        <v>386.0133056640625</v>
+        <v>388.109375</v>
       </c>
       <c r="F205" t="n">
-        <v>34224500</v>
+        <v>29297500</v>
       </c>
       <c r="G205" t="n">
         <v>0</v>
@@ -5773,22 +5773,22 @@
     </row>
     <row r="206">
       <c r="A206" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="B206" t="n">
-        <v>391.7525106425778</v>
+        <v>383.3084264217563</v>
       </c>
       <c r="C206" t="n">
-        <v>394.8267404517197</v>
+        <v>384.5860201500421</v>
       </c>
       <c r="D206" t="n">
-        <v>387.4905448392632</v>
+        <v>380.6134873969759</v>
       </c>
       <c r="E206" t="n">
-        <v>388.109375</v>
+        <v>382.6197204589844</v>
       </c>
       <c r="F206" t="n">
-        <v>29297500</v>
+        <v>25908300</v>
       </c>
       <c r="G206" t="n">
         <v>0</v>
@@ -5799,22 +5799,22 @@
     </row>
     <row r="207">
       <c r="A207" s="1" t="n">
-        <v>46211</v>
+        <v>46212</v>
       </c>
       <c r="B207" t="n">
-        <v>383.3084264217563</v>
+        <v>373.7464342011831</v>
       </c>
       <c r="C207" t="n">
-        <v>384.5860201500421</v>
+        <v>383.927250494608</v>
       </c>
       <c r="D207" t="n">
-        <v>380.6134873969759</v>
+        <v>372.6484949692805</v>
       </c>
       <c r="E207" t="n">
-        <v>382.6197204589844</v>
+        <v>383.6377868652344</v>
       </c>
       <c r="F207" t="n">
-        <v>25908300</v>
+        <v>31083200</v>
       </c>
       <c r="G207" t="n">
         <v>0</v>
@@ -5825,22 +5825,22 @@
     </row>
     <row r="208">
       <c r="A208" s="1" t="n">
-        <v>46212</v>
+        <v>46213</v>
       </c>
       <c r="B208" t="n">
-        <v>373.7464342011831</v>
+        <v>387.071312236775</v>
       </c>
       <c r="C208" t="n">
-        <v>383.927250494608</v>
+        <v>391.1736053926777</v>
       </c>
       <c r="D208" t="n">
-        <v>372.6484949692805</v>
+        <v>380.783162110783</v>
       </c>
       <c r="E208" t="n">
-        <v>383.6377868652344</v>
+        <v>384.3764038085938</v>
       </c>
       <c r="F208" t="n">
-        <v>31083200</v>
+        <v>24644600</v>
       </c>
       <c r="G208" t="n">
         <v>0</v>
@@ -5851,22 +5851,22 @@
     </row>
     <row r="209">
       <c r="A209" s="1" t="n">
-        <v>46213</v>
+        <v>46216</v>
       </c>
       <c r="B209" t="n">
-        <v>387.071312236775</v>
+        <v>387.0214381132942</v>
       </c>
       <c r="C209" t="n">
-        <v>391.1736053926777</v>
+        <v>392.9103462310944</v>
       </c>
       <c r="D209" t="n">
-        <v>380.783162110783</v>
+        <v>383.4281962321871</v>
       </c>
       <c r="E209" t="n">
-        <v>384.3764038085938</v>
+        <v>390.2553405761719</v>
       </c>
       <c r="F209" t="n">
-        <v>24644600</v>
+        <v>28914900</v>
       </c>
       <c r="G209" t="n">
         <v>0</v>
@@ -5877,22 +5877,22 @@
     </row>
     <row r="210">
       <c r="A210" s="1" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B210" t="n">
-        <v>387.0214381132942</v>
+        <v>382.1007052927433</v>
       </c>
       <c r="C210" t="n">
-        <v>392.9103462310944</v>
+        <v>387.460610424238</v>
       </c>
       <c r="D210" t="n">
-        <v>383.4281962321871</v>
+        <v>377.93852713765</v>
       </c>
       <c r="E210" t="n">
-        <v>390.2553405761719</v>
+        <v>384.2067260742188</v>
       </c>
       <c r="F210" t="n">
-        <v>28914900</v>
+        <v>27863900</v>
       </c>
       <c r="G210" t="n">
         <v>0</v>
@@ -5903,22 +5903,22 @@
     </row>
     <row r="211">
       <c r="A211" s="1" t="n">
-        <v>46217</v>
+        <v>46218</v>
       </c>
       <c r="B211" t="n">
-        <v>382.1007052927433</v>
+        <v>387.0713224899768</v>
       </c>
       <c r="C211" t="n">
-        <v>387.460610424238</v>
+        <v>398.2103568181361</v>
       </c>
       <c r="D211" t="n">
-        <v>377.93852713765</v>
+        <v>385.6739591427675</v>
       </c>
       <c r="E211" t="n">
-        <v>384.2067260742188</v>
+        <v>394.8866271972656</v>
       </c>
       <c r="F211" t="n">
-        <v>27863900</v>
+        <v>36253700</v>
       </c>
       <c r="G211" t="n">
         <v>0</v>
@@ -5929,22 +5929,22 @@
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="B212" t="n">
-        <v>387.0713224899768</v>
+        <v>397.5615778418718</v>
       </c>
       <c r="C212" t="n">
-        <v>398.2103568181361</v>
+        <v>405.2271399033625</v>
       </c>
       <c r="D212" t="n">
-        <v>385.6739591427675</v>
+        <v>391.3133305596497</v>
       </c>
       <c r="E212" t="n">
-        <v>394.8866271972656</v>
+        <v>400.3463439941406</v>
       </c>
       <c r="F212" t="n">
-        <v>36253700</v>
+        <v>37047400</v>
       </c>
       <c r="G212" t="n">
         <v>0</v>
@@ -5955,22 +5955,22 @@
     </row>
     <row r="213">
       <c r="A213" s="1" t="n">
-        <v>46219</v>
+        <v>46220</v>
       </c>
       <c r="B213" t="n">
-        <v>397.5615778418718</v>
+        <v>394.1180409920291</v>
       </c>
       <c r="C213" t="n">
-        <v>405.2271399033625</v>
+        <v>397.6414373419786</v>
       </c>
       <c r="D213" t="n">
-        <v>391.3133305596497</v>
+        <v>388.6583483977542</v>
       </c>
       <c r="E213" t="n">
-        <v>400.3463439941406</v>
+        <v>393.0800170898438</v>
       </c>
       <c r="F213" t="n">
-        <v>37047400</v>
+        <v>33049800</v>
       </c>
       <c r="G213" t="n">
         <v>0</v>
@@ -5981,22 +5981,22 @@
     </row>
     <row r="214">
       <c r="A214" s="1" t="n">
-        <v>46220</v>
+        <v>46223</v>
       </c>
       <c r="B214" t="n">
-        <v>394.1180409920291</v>
+        <v>390.6745569462133</v>
       </c>
       <c r="C214" t="n">
-        <v>397.6414373419786</v>
+        <v>402.4224305318551</v>
       </c>
       <c r="D214" t="n">
-        <v>388.6583483977542</v>
+        <v>388.9178541819168</v>
       </c>
       <c r="E214" t="n">
-        <v>393.0800170898438</v>
+        <v>401.5341186523438</v>
       </c>
       <c r="F214" t="n">
-        <v>33049800</v>
+        <v>27915800</v>
       </c>
       <c r="G214" t="n">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="215">
       <c r="A215" s="1" t="n">
-        <v>46223</v>
+        <v>46224</v>
       </c>
       <c r="B215" t="n">
-        <v>390.6745569462133</v>
+        <v>398.0606303262699</v>
       </c>
       <c r="C215" t="n">
-        <v>402.4224305318551</v>
+        <v>400.7156358198418</v>
       </c>
       <c r="D215" t="n">
-        <v>388.9178541819168</v>
+        <v>395.5753188038175</v>
       </c>
       <c r="E215" t="n">
-        <v>401.5341186523438</v>
+        <v>397.0026245117188</v>
       </c>
       <c r="F215" t="n">
-        <v>27915800</v>
+        <v>24126600</v>
       </c>
       <c r="G215" t="n">
         <v>0</v>
@@ -6033,22 +6033,22 @@
     </row>
     <row r="216">
       <c r="A216" s="1" t="n">
-        <v>46224</v>
+        <v>46225</v>
       </c>
       <c r="B216" t="n">
-        <v>398.0606303262699</v>
+        <v>398.8291961465565</v>
       </c>
       <c r="C216" t="n">
-        <v>400.7156358198418</v>
+        <v>400.246541441447</v>
       </c>
       <c r="D216" t="n">
-        <v>395.5753188038175</v>
+        <v>386.2329133568751</v>
       </c>
       <c r="E216" t="n">
-        <v>397.0026245117188</v>
+        <v>389.6065673828125</v>
       </c>
       <c r="F216" t="n">
-        <v>24126600</v>
+        <v>28142500</v>
       </c>
       <c r="G216" t="n">
         <v>0</v>
@@ -6059,22 +6059,22 @@
     </row>
     <row r="217">
       <c r="A217" s="1" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B217" t="n">
-        <v>398.8291961465565</v>
+        <v>389.237256596515</v>
       </c>
       <c r="C217" t="n">
-        <v>400.246541441447</v>
+        <v>391.0438532115061</v>
       </c>
       <c r="D217" t="n">
-        <v>386.2329133568751</v>
+        <v>376.6809075284274</v>
       </c>
       <c r="E217" t="n">
-        <v>389.6065673828125</v>
+        <v>380.8630065917969</v>
       </c>
       <c r="F217" t="n">
-        <v>28142500</v>
+        <v>30351800</v>
       </c>
       <c r="G217" t="n">
         <v>0</v>
@@ -6085,22 +6085,22 @@
     </row>
     <row r="218">
       <c r="A218" s="1" t="n">
-        <v>46226</v>
+        <v>46227</v>
       </c>
       <c r="B218" t="n">
-        <v>389.237256596515</v>
+        <v>386.3227418757343</v>
       </c>
       <c r="C218" t="n">
-        <v>391.0438532115061</v>
+        <v>388.299032528898</v>
       </c>
       <c r="D218" t="n">
-        <v>376.6809075284274</v>
+        <v>379.9347732203772</v>
       </c>
       <c r="E218" t="n">
-        <v>380.8630065917969</v>
+        <v>380.9828186035156</v>
       </c>
       <c r="F218" t="n">
-        <v>30351800</v>
+        <v>27659400</v>
       </c>
       <c r="G218" t="n">
         <v>0</v>
@@ -6111,22 +6111,22 @@
     </row>
     <row r="219">
       <c r="A219" s="1" t="n">
-        <v>46227</v>
+        <v>46230</v>
       </c>
       <c r="B219" t="n">
-        <v>386.3227418757343</v>
+        <v>389.3470355932277</v>
       </c>
       <c r="C219" t="n">
-        <v>388.299032528898</v>
+        <v>393.4593197982184</v>
       </c>
       <c r="D219" t="n">
-        <v>379.9347732203772</v>
+        <v>387.2609663085435</v>
       </c>
       <c r="E219" t="n">
-        <v>380.9828186035156</v>
+        <v>388.368896484375</v>
       </c>
       <c r="F219" t="n">
-        <v>27659400</v>
+        <v>27856200</v>
       </c>
       <c r="G219" t="n">
         <v>0</v>
@@ -6137,22 +6137,22 @@
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="B220" t="n">
-        <v>389.3470355932277</v>
+        <v>392.4212554523594</v>
       </c>
       <c r="C220" t="n">
-        <v>393.4593197982184</v>
+        <v>399.567805457337</v>
       </c>
       <c r="D220" t="n">
-        <v>387.2609663085435</v>
+        <v>390.5647345556998</v>
       </c>
       <c r="E220" t="n">
-        <v>388.368896484375</v>
+        <v>392.6109008789062</v>
       </c>
       <c r="F220" t="n">
-        <v>27856200</v>
+        <v>32367500</v>
       </c>
       <c r="G220" t="n">
         <v>0</v>
@@ -6163,22 +6163,22 @@
     </row>
     <row r="221">
       <c r="A221" s="1" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B221" t="n">
-        <v>392.4212554523594</v>
+        <v>392.6607942930367</v>
       </c>
       <c r="C221" t="n">
-        <v>399.567805457337</v>
+        <v>400.4960502148319</v>
       </c>
       <c r="D221" t="n">
-        <v>390.5647345556998</v>
+        <v>388.0095467898306</v>
       </c>
       <c r="E221" t="n">
-        <v>392.6109008789062</v>
+        <v>389.8061828613281</v>
       </c>
       <c r="F221" t="n">
-        <v>32367500</v>
+        <v>47209000</v>
       </c>
       <c r="G221" t="n">
         <v>0</v>
@@ -6189,22 +6189,22 @@
     </row>
     <row r="222">
       <c r="A222" s="1" t="n">
-        <v>46232</v>
+        <v>46233</v>
       </c>
       <c r="B222" t="n">
-        <v>392.6607942930367</v>
+        <v>437.0772008696947</v>
       </c>
       <c r="C222" t="n">
-        <v>400.4960502148319</v>
+        <v>457.8281459885008</v>
       </c>
       <c r="D222" t="n">
-        <v>388.0095467898306</v>
+        <v>431.6274684759506</v>
       </c>
       <c r="E222" t="n">
-        <v>389.8061828613281</v>
+        <v>450.2524108886719</v>
       </c>
       <c r="F222" t="n">
-        <v>47209000</v>
+        <v>110160700</v>
       </c>
       <c r="G222" t="n">
         <v>0</v>
@@ -6215,22 +6215,22 @@
     </row>
     <row r="223">
       <c r="A223" s="1" t="n">
-        <v>46233</v>
+        <v>46234</v>
       </c>
       <c r="B223" t="n">
-        <v>437.0772008696947</v>
+        <v>449.1544591210436</v>
       </c>
       <c r="C223" t="n">
-        <v>457.8281459885008</v>
+        <v>465.962813447145</v>
       </c>
       <c r="D223" t="n">
-        <v>431.6274684759506</v>
+        <v>448.4857046349594</v>
       </c>
       <c r="E223" t="n">
-        <v>450.2524108886719</v>
+        <v>463.8468017578125</v>
       </c>
       <c r="F223" t="n">
-        <v>110160700</v>
+        <v>60846000</v>
       </c>
       <c r="G223" t="n">
         <v>0</v>
@@ -6241,22 +6241,22 @@
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B224" t="n">
-        <v>449.1544591210436</v>
+        <v>475.2353605631651</v>
       </c>
       <c r="C224" t="n">
-        <v>465.962813447145</v>
+        <v>490.7261876465455</v>
       </c>
       <c r="D224" t="n">
-        <v>448.4857046349594</v>
+        <v>474.1074789501303</v>
       </c>
       <c r="E224" t="n">
-        <v>463.8468017578125</v>
+        <v>486.7337036132812</v>
       </c>
       <c r="F224" t="n">
-        <v>60846000</v>
+        <v>66762100</v>
       </c>
       <c r="G224" t="n">
         <v>0</v>
@@ -6267,22 +6267,22 @@
     </row>
     <row r="225">
       <c r="A225" s="1" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B225" t="n">
-        <v>475.2353605631651</v>
+        <v>479.9964078184842</v>
       </c>
       <c r="C225" t="n">
-        <v>490.7261876465455</v>
+        <v>498.5015806515744</v>
       </c>
       <c r="D225" t="n">
-        <v>474.1074789501303</v>
+        <v>478.2696778930625</v>
       </c>
       <c r="E225" t="n">
-        <v>486.7337036132812</v>
+        <v>491.884033203125</v>
       </c>
       <c r="F225" t="n">
-        <v>66762100</v>
+        <v>50455500</v>
       </c>
       <c r="G225" t="n">
         <v>0</v>
@@ -6293,22 +6293,22 @@
     </row>
     <row r="226">
       <c r="A226" s="1" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B226" t="n">
-        <v>479.9964078184842</v>
+        <v>495.4273384327132</v>
       </c>
       <c r="C226" t="n">
-        <v>498.5015806515744</v>
+        <v>497.3038108374591</v>
       </c>
       <c r="D226" t="n">
-        <v>478.2696778930625</v>
+        <v>484.7674131728324</v>
       </c>
       <c r="E226" t="n">
-        <v>491.884033203125</v>
+        <v>486.5440673828125</v>
       </c>
       <c r="F226" t="n">
-        <v>50455500</v>
+        <v>33388900</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
@@ -6319,22 +6319,22 @@
     </row>
     <row r="227">
       <c r="A227" s="1" t="n">
-        <v>46239</v>
+        <v>46240</v>
       </c>
       <c r="B227" t="n">
-        <v>495.4273384327132</v>
+        <v>487.6319998350186</v>
       </c>
       <c r="C227" t="n">
-        <v>497.3038108374591</v>
+        <v>500.6175637248969</v>
       </c>
       <c r="D227" t="n">
-        <v>484.7674131728324</v>
+        <v>487.6020574235835</v>
       </c>
       <c r="E227" t="n">
-        <v>486.5440673828125</v>
+        <v>498.9207458496094</v>
       </c>
       <c r="F227" t="n">
-        <v>33388900</v>
+        <v>36441500</v>
       </c>
       <c r="G227" t="n">
         <v>0</v>
@@ -6345,22 +6345,22 @@
     </row>
     <row r="228">
       <c r="A228" s="1" t="n">
-        <v>46240</v>
+        <v>46241</v>
       </c>
       <c r="B228" t="n">
-        <v>487.6319998350186</v>
+        <v>498.2719734340298</v>
       </c>
       <c r="C228" t="n">
-        <v>500.6175637248969</v>
+        <v>504.2307569931746</v>
       </c>
       <c r="D228" t="n">
-        <v>487.6020574235835</v>
+        <v>497.7928948509335</v>
       </c>
       <c r="E228" t="n">
-        <v>498.9207458496094</v>
+        <v>499.0505065917969</v>
       </c>
       <c r="F228" t="n">
-        <v>36441500</v>
+        <v>28846200</v>
       </c>
       <c r="G228" t="n">
         <v>0</v>
@@ -6371,22 +6371,22 @@
     </row>
     <row r="229">
       <c r="A229" s="1" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B229" t="n">
-        <v>498.2719734340298</v>
+        <v>502.4940586092805</v>
       </c>
       <c r="C229" t="n">
-        <v>504.2307569931746</v>
+        <v>512.7647021753171</v>
       </c>
       <c r="D229" t="n">
-        <v>497.7928948509335</v>
+        <v>501.326243590453</v>
       </c>
       <c r="E229" t="n">
-        <v>499.0505065917969</v>
+        <v>505.109130859375</v>
       </c>
       <c r="F229" t="n">
-        <v>28846200</v>
+        <v>31206100</v>
       </c>
       <c r="G229" t="n">
         <v>0</v>
@@ -6397,22 +6397,22 @@
     </row>
     <row r="230">
       <c r="A230" s="1" t="n">
-        <v>46244</v>
+        <v>46245</v>
       </c>
       <c r="B230" t="n">
-        <v>502.4940586092805</v>
+        <v>503.3823542433026</v>
       </c>
       <c r="C230" t="n">
-        <v>512.7647021753171</v>
+        <v>504.3804752506704</v>
       </c>
       <c r="D230" t="n">
-        <v>501.326243590453</v>
+        <v>498.6113370464939</v>
       </c>
       <c r="E230" t="n">
-        <v>505.109130859375</v>
+        <v>502.8633422851562</v>
       </c>
       <c r="F230" t="n">
-        <v>31206100</v>
+        <v>23049800</v>
       </c>
       <c r="G230" t="n">
         <v>0</v>
@@ -6423,22 +6423,22 @@
     </row>
     <row r="231">
       <c r="A231" s="1" t="n">
-        <v>46245</v>
+        <v>46246</v>
       </c>
       <c r="B231" t="n">
-        <v>503.3823542433026</v>
+        <v>499.0505227551261</v>
       </c>
       <c r="C231" t="n">
-        <v>504.3804752506704</v>
+        <v>500.557695253814</v>
       </c>
       <c r="D231" t="n">
-        <v>498.6113370464939</v>
+        <v>490.5964364344239</v>
       </c>
       <c r="E231" t="n">
-        <v>502.8633422851562</v>
+        <v>491.5047302246094</v>
       </c>
       <c r="F231" t="n">
-        <v>23049800</v>
+        <v>29001500</v>
       </c>
       <c r="G231" t="n">
         <v>0</v>
@@ -6449,22 +6449,22 @@
     </row>
     <row r="232">
       <c r="A232" s="1" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="B232" t="n">
-        <v>499.0505227551261</v>
+        <v>492.3431478695614</v>
       </c>
       <c r="C232" t="n">
-        <v>500.557695253814</v>
+        <v>500.3979918654044</v>
       </c>
       <c r="D232" t="n">
-        <v>490.5964364344239</v>
+        <v>492.0836571155829</v>
       </c>
       <c r="E232" t="n">
-        <v>491.5047302246094</v>
+        <v>495.9463806152344</v>
       </c>
       <c r="F232" t="n">
-        <v>29001500</v>
+        <v>23039000</v>
       </c>
       <c r="G232" t="n">
         <v>0</v>
@@ -6475,22 +6475,22 @@
     </row>
     <row r="233">
       <c r="A233" s="1" t="n">
-        <v>46247</v>
+        <v>46248</v>
       </c>
       <c r="B233" t="n">
-        <v>492.3431478695614</v>
+        <v>495.427334377905</v>
       </c>
       <c r="C233" t="n">
-        <v>500.3979918654044</v>
+        <v>499.0705004655026</v>
       </c>
       <c r="D233" t="n">
-        <v>492.0836571155829</v>
+        <v>492.991947114923</v>
       </c>
       <c r="E233" t="n">
-        <v>495.9463806152344</v>
+        <v>494.4691467285156</v>
       </c>
       <c r="F233" t="n">
-        <v>23039000</v>
+        <v>16217600</v>
       </c>
       <c r="G233" t="n">
         <v>0</v>
@@ -6501,22 +6501,22 @@
     </row>
     <row r="234">
       <c r="A234" s="1" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B234" t="n">
-        <v>495.427334377905</v>
+        <v>489.2190622628328</v>
       </c>
       <c r="C234" t="n">
-        <v>499.0705004655026</v>
+        <v>491.7343163235842</v>
       </c>
       <c r="D234" t="n">
-        <v>492.991947114923</v>
+        <v>477.5110914717105</v>
       </c>
       <c r="E234" t="n">
-        <v>494.4691467285156</v>
+        <v>479.4474487304688</v>
       </c>
       <c r="F234" t="n">
-        <v>16217600</v>
+        <v>29635800</v>
       </c>
       <c r="G234" t="n">
         <v>0</v>
@@ -6527,22 +6527,22 @@
     </row>
     <row r="235">
       <c r="A235" s="1" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B235" t="n">
-        <v>489.2190622628328</v>
+        <v>480.6352093836093</v>
       </c>
       <c r="C235" t="n">
-        <v>491.7343163235842</v>
+        <v>483.3600603013466</v>
       </c>
       <c r="D235" t="n">
-        <v>477.5110914717105</v>
+        <v>476.2534434403709</v>
       </c>
       <c r="E235" t="n">
-        <v>479.4474487304688</v>
+        <v>480.7250366210938</v>
       </c>
       <c r="F235" t="n">
-        <v>29635800</v>
+        <v>24087600</v>
       </c>
       <c r="G235" t="n">
         <v>0</v>
@@ -6553,22 +6553,22 @@
     </row>
     <row r="236">
       <c r="A236" s="1" t="n">
-        <v>46252</v>
+        <v>46253</v>
       </c>
       <c r="B236" t="n">
-        <v>480.6352093836093</v>
+        <v>479.1679704739861</v>
       </c>
       <c r="C236" t="n">
-        <v>483.3600603013466</v>
+        <v>488.3806080919379</v>
       </c>
       <c r="D236" t="n">
-        <v>476.2534434403709</v>
+        <v>478.4592826108848</v>
       </c>
       <c r="E236" t="n">
-        <v>480.7250366210938</v>
+        <v>483.3999938964844</v>
       </c>
       <c r="F236" t="n">
-        <v>24087600</v>
+        <v>19961900</v>
       </c>
       <c r="G236" t="n">
         <v>0</v>
@@ -6579,25 +6579,25 @@
     </row>
     <row r="237">
       <c r="A237" s="1" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B237" t="n">
-        <v>479.1679704739861</v>
+        <v>483.2999877929688</v>
       </c>
       <c r="C237" t="n">
-        <v>488.3806080919379</v>
+        <v>484.1600036621094</v>
       </c>
       <c r="D237" t="n">
-        <v>478.4592826108848</v>
+        <v>479.5</v>
       </c>
       <c r="E237" t="n">
-        <v>483.3999938964844</v>
+        <v>481.1499938964844</v>
       </c>
       <c r="F237" t="n">
-        <v>19961900</v>
+        <v>20020800</v>
       </c>
       <c r="G237" t="n">
-        <v>0</v>
+        <v>0.91</v>
       </c>
       <c r="H237" t="n">
         <v>0</v>
@@ -6605,25 +6605,25 @@
     </row>
     <row r="238">
       <c r="A238" s="1" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B238" t="n">
-        <v>483.2999877929688</v>
+        <v>479.8800048828125</v>
       </c>
       <c r="C238" t="n">
-        <v>484.1600036621094</v>
+        <v>486.3599853515625</v>
       </c>
       <c r="D238" t="n">
-        <v>479.5</v>
+        <v>478.5299987792969</v>
       </c>
       <c r="E238" t="n">
-        <v>481.1499938964844</v>
+        <v>483.239990234375</v>
       </c>
       <c r="F238" t="n">
-        <v>20020800</v>
+        <v>22510800</v>
       </c>
       <c r="G238" t="n">
-        <v>0.91</v>
+        <v>0</v>
       </c>
       <c r="H238" t="n">
         <v>0</v>
@@ -6631,22 +6631,22 @@
     </row>
     <row r="239">
       <c r="A239" s="1" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B239" t="n">
-        <v>479.8800048828125</v>
+        <v>483.2099914550781</v>
       </c>
       <c r="C239" t="n">
-        <v>486.3599853515625</v>
+        <v>490.6099853515625</v>
       </c>
       <c r="D239" t="n">
-        <v>478.5299987792969</v>
+        <v>481.8599853515625</v>
       </c>
       <c r="E239" t="n">
-        <v>483.239990234375</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="F239" t="n">
-        <v>22510800</v>
+        <v>17230800</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="240">
       <c r="A240" s="1" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B240" t="n">
-        <v>483.2099914550781</v>
+        <v>485.4400024414062</v>
       </c>
       <c r="C240" t="n">
-        <v>490.6099853515625</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="D240" t="n">
-        <v>481.8599853515625</v>
+        <v>484.2999877929688</v>
       </c>
       <c r="E240" t="n">
-        <v>487.3099975585938</v>
+        <v>491.7099914550781</v>
       </c>
       <c r="F240" t="n">
-        <v>17230800</v>
+        <v>19519000</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
@@ -6683,22 +6683,22 @@
     </row>
     <row r="241">
       <c r="A241" s="1" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B241" t="n">
-        <v>485.4400024414062</v>
+        <v>487.8500061035156</v>
       </c>
       <c r="C241" t="n">
-        <v>492.4400024414062</v>
+        <v>497.3999938964844</v>
       </c>
       <c r="D241" t="n">
-        <v>484.2999877929688</v>
+        <v>487.3099975585938</v>
       </c>
       <c r="E241" t="n">
-        <v>491.7099914550781</v>
+        <v>496.3699951171875</v>
       </c>
       <c r="F241" t="n">
-        <v>19519000</v>
+        <v>20758900</v>
       </c>
       <c r="G241" t="n">
         <v>0</v>
@@ -6709,22 +6709,22 @@
     </row>
     <row r="242">
       <c r="A242" s="1" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B242" t="n">
-        <v>487.8500061035156</v>
+        <v>494.8800048828125</v>
       </c>
       <c r="C242" t="n">
-        <v>497.3999938964844</v>
+        <v>506.4800109863281</v>
       </c>
       <c r="D242" t="n">
-        <v>487.3099975585938</v>
+        <v>490.0799865722656</v>
       </c>
       <c r="E242" t="n">
-        <v>496.3699951171875</v>
+        <v>505.0599975585938</v>
       </c>
       <c r="F242" t="n">
-        <v>20758900</v>
+        <v>28688800</v>
       </c>
       <c r="G242" t="n">
         <v>0</v>
@@ -6735,22 +6735,22 @@
     </row>
     <row r="243">
       <c r="A243" s="1" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B243" t="n">
-        <v>494.8800048828125</v>
+        <v>505.3299865722656</v>
       </c>
       <c r="C243" t="n">
-        <v>506.4800109863281</v>
+        <v>517.780029296875</v>
       </c>
       <c r="D243" t="n">
-        <v>490.0799865722656</v>
+        <v>504.8699951171875</v>
       </c>
       <c r="E243" t="n">
-        <v>505.0599975585938</v>
+        <v>513.530029296875</v>
       </c>
       <c r="F243" t="n">
-        <v>28688800</v>
+        <v>29207300</v>
       </c>
       <c r="G243" t="n">
         <v>0</v>
@@ -6761,22 +6761,22 @@
     </row>
     <row r="244">
       <c r="A244" s="1" t="n">
-        <v>46262</v>
+        <v>46265</v>
       </c>
       <c r="B244" t="n">
-        <v>505.3299865722656</v>
+        <v>510.3800048828125</v>
       </c>
       <c r="C244" t="n">
-        <v>517.780029296875</v>
+        <v>512.1900024414062</v>
       </c>
       <c r="D244" t="n">
-        <v>504.8699951171875</v>
+        <v>506.3900146484375</v>
       </c>
       <c r="E244" t="n">
-        <v>513.530029296875</v>
+        <v>507.2900085449219</v>
       </c>
       <c r="F244" t="n">
-        <v>29207300</v>
+        <v>27208900</v>
       </c>
       <c r="G244" t="n">
         <v>0</v>
@@ -6787,22 +6787,22 @@
     </row>
     <row r="245">
       <c r="A245" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="B245" t="n">
-        <v>510.3800048828125</v>
+        <v>497.5199890136719</v>
       </c>
       <c r="C245" t="n">
-        <v>512.1900024414062</v>
+        <v>505.9700012207031</v>
       </c>
       <c r="D245" t="n">
-        <v>506.3900146484375</v>
+        <v>496.7799987792969</v>
       </c>
       <c r="E245" t="n">
-        <v>507.2900085449219</v>
+        <v>501.0199890136719</v>
       </c>
       <c r="F245" t="n">
-        <v>27208900</v>
+        <v>21046900</v>
       </c>
       <c r="G245" t="n">
         <v>0</v>
@@ -6813,22 +6813,22 @@
     </row>
     <row r="246">
       <c r="A246" s="1" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="B246" t="n">
-        <v>497.5199890136719</v>
+        <v>499.8500061035156</v>
       </c>
       <c r="C246" t="n">
-        <v>505.9700012207031</v>
+        <v>500.2699890136719</v>
       </c>
       <c r="D246" t="n">
-        <v>496.7799987792969</v>
+        <v>493.8099975585938</v>
       </c>
       <c r="E246" t="n">
-        <v>501.0199890136719</v>
+        <v>496.8200073242188</v>
       </c>
       <c r="F246" t="n">
-        <v>21046900</v>
+        <v>15336100</v>
       </c>
       <c r="G246" t="n">
         <v>0</v>
@@ -6839,22 +6839,22 @@
     </row>
     <row r="247">
       <c r="A247" s="1" t="n">
-        <v>46267</v>
+        <v>46268</v>
       </c>
       <c r="B247" t="n">
-        <v>499.8500061035156</v>
+        <v>501.6600036621094</v>
       </c>
       <c r="C247" t="n">
-        <v>500.2699890136719</v>
+        <v>515.6500244140625</v>
       </c>
       <c r="D247" t="n">
-        <v>493.8099975585938</v>
+        <v>500.7999877929688</v>
       </c>
       <c r="E247" t="n">
-        <v>496.8200073242188</v>
+        <v>510.1199951171875</v>
       </c>
       <c r="F247" t="n">
-        <v>15336100</v>
+        <v>24125900</v>
       </c>
       <c r="G247" t="n">
         <v>0</v>
@@ -6865,22 +6865,22 @@
     </row>
     <row r="248">
       <c r="A248" s="1" t="n">
-        <v>46268</v>
+        <v>46269</v>
       </c>
       <c r="B248" t="n">
-        <v>501.6600036621094</v>
+        <v>510</v>
       </c>
       <c r="C248" t="n">
-        <v>515.6500244140625</v>
+        <v>511</v>
       </c>
       <c r="D248" t="n">
-        <v>500.7999877929688</v>
+        <v>499.3599853515625</v>
       </c>
       <c r="E248" t="n">
-        <v>510.1199951171875</v>
+        <v>499.7000122070312</v>
       </c>
       <c r="F248" t="n">
-        <v>24125900</v>
+        <v>18101800</v>
       </c>
       <c r="G248" t="n">
         <v>0</v>
@@ -6891,22 +6891,22 @@
     </row>
     <row r="249">
       <c r="A249" s="1" t="n">
-        <v>46269</v>
+        <v>46273</v>
       </c>
       <c r="B249" t="n">
-        <v>510</v>
+        <v>493.010009765625</v>
       </c>
       <c r="C249" t="n">
-        <v>511</v>
+        <v>495.1900024414062</v>
       </c>
       <c r="D249" t="n">
-        <v>499.3599853515625</v>
+        <v>490.1499938964844</v>
       </c>
       <c r="E249" t="n">
-        <v>499.7000122070312</v>
+        <v>493.9500122070312</v>
       </c>
       <c r="F249" t="n">
-        <v>18101800</v>
+        <v>18882300</v>
       </c>
       <c r="G249" t="n">
         <v>0</v>
@@ -6917,22 +6917,22 @@
     </row>
     <row r="250">
       <c r="A250" s="1" t="n">
-        <v>46273</v>
+        <v>46274</v>
       </c>
       <c r="B250" t="n">
-        <v>493.010009765625</v>
+        <v>493.0700073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>495.1900024414062</v>
+        <v>494.3900146484375</v>
       </c>
       <c r="D250" t="n">
-        <v>490.1499938964844</v>
+        <v>489.7999877929688</v>
       </c>
       <c r="E250" t="n">
-        <v>493.9500122070312</v>
+        <v>491.6499938964844</v>
       </c>
       <c r="F250" t="n">
-        <v>18882300</v>
+        <v>12889600</v>
       </c>
       <c r="G250" t="n">
         <v>0</v>
@@ -6943,22 +6943,22 @@
     </row>
     <row r="251">
       <c r="A251" s="1" t="n">
-        <v>46274</v>
+        <v>46275</v>
       </c>
       <c r="B251" t="n">
-        <v>493.0700073242188</v>
+        <v>488.3200073242188</v>
       </c>
       <c r="C251" t="n">
-        <v>494.3900146484375</v>
+        <v>494.5199890136719</v>
       </c>
       <c r="D251" t="n">
-        <v>489.7999877929688</v>
+        <v>486</v>
       </c>
       <c r="E251" t="n">
-        <v>491.6499938964844</v>
+        <v>492.4400024414062</v>
       </c>
       <c r="F251" t="n">
-        <v>12889600</v>
+        <v>16038800</v>
       </c>
       <c r="G251" t="n">
         <v>0</v>
@@ -6969,22 +6969,22 @@
     </row>
     <row r="252">
       <c r="A252" s="1" t="n">
-        <v>46275</v>
+        <v>46276</v>
       </c>
       <c r="B252" t="n">
-        <v>488.3200073242188</v>
+        <v>495.6499938964844</v>
       </c>
       <c r="C252" t="n">
-        <v>494.5199890136719</v>
+        <v>498.9700012207031</v>
       </c>
       <c r="D252" t="n">
-        <v>486</v>
+        <v>492.5799865722656</v>
       </c>
       <c r="E252" t="n">
-        <v>492.4400024414062</v>
+        <v>495.6300048828125</v>
       </c>
       <c r="F252" t="n">
-        <v>16018200</v>
+        <v>14510500</v>
       </c>
       <c r="G252" t="n">
         <v>0</v>
@@ -10968,37 +10968,37 @@
         </is>
       </c>
       <c r="C2" t="n">
+        <v>495.63</v>
+      </c>
+      <c r="D2" t="n">
         <v>492.44</v>
       </c>
-      <c r="D2" t="n">
-        <v>491.65</v>
-      </c>
       <c r="E2" t="n">
-        <v>488.32</v>
+        <v>495.625</v>
       </c>
       <c r="F2" t="n">
-        <v>494.52</v>
+        <v>498.97</v>
       </c>
       <c r="G2" t="n">
-        <v>486</v>
+        <v>492.58</v>
       </c>
       <c r="H2" t="n">
-        <v>15852734</v>
+        <v>14279577</v>
       </c>
       <c r="I2" t="n">
-        <v>36277246</v>
+        <v>35445946</v>
       </c>
       <c r="J2" t="n">
-        <v>3656635645952</v>
+        <v>3680323239936</v>
       </c>
       <c r="K2" t="n">
-        <v>27.403452</v>
+        <v>27.62709</v>
       </c>
       <c r="L2" t="n">
-        <v>20.890018</v>
+        <v>21.025343</v>
       </c>
       <c r="M2" t="n">
-        <v>17.97</v>
+        <v>18.09</v>
       </c>
       <c r="N2" t="n">
         <v>553.72</v>
@@ -11010,7 +11010,7 @@
         <v>1.108</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.74</v>
+        <v>0.73</v>
       </c>
       <c r="R2" t="n">
         <v>0.40305</v>
@@ -11034,7 +11034,7 @@
         <v>59.565</v>
       </c>
       <c r="Y2" t="n">
-        <v>8.267270999999999</v>
+        <v>8.320827</v>
       </c>
       <c r="Z2" t="n">
         <v>0.317</v>
@@ -11046,7 +11046,7 @@
         <v>331839012864</v>
       </c>
       <c r="AC2" t="n">
-        <v>3708605693952</v>
+        <v>3732293025792</v>
       </c>
       <c r="AD2" t="n">
         <v>194237005824</v>
@@ -11073,7 +11073,7 @@
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>2026-09-11 19:02:39</t>
+          <t>2026-09-12 21:46:46</t>
         </is>
       </c>
     </row>
